--- a/Result/checksun_type/濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料).xlsx
+++ b/Result/checksun_type/濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料).xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1393.968</t>
+          <t>1168.47</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -903,17 +903,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2.17</t>
-        </is>
-      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>61.27</t>
+          <t>53.47</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12.58</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1394</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>6.43</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>69.38</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>66.06</t>
+          <t>66.24</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>66.34</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>62.79</t>
+          <t>63.02</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>768.32</t>
+          <t>262.06</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-95.88</t>
+          <t>-88.05</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,45 +1099,45 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>75146786.40955137</t>
+          <t>75217998.52890173</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>100281347.0</t>
+          <t>82950382.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>131264222.4</t>
+          <t>132496129.6</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>81393410.0</t>
+          <t>86336133.4</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>119695734.58</t>
+          <t>120394266.18</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>49870812</t>
+          <t>46159996</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-5685337.758529304</t>
+          <t>-3742417.326026477</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>9733490.07</v>
+        <v>6943645.05</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>52.01</t>
+          <t>50.11</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,22 +1177,22 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>52.27878514847768</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>116.3549688302164</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>24.9400431068334</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
@@ -1207,47 +1207,47 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>14.92</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>101.27</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>12.28%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
-          <t>6.83%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>47.82</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>8531</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>動力電池材料42.58%、特用化學材料20.60%、氧化觸媒17.66%、化肥10.09%、其他9.07% (2024年)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1262,32 +1262,32 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>46.52</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 石化及塑橡膠 - 接著劑(合成樹脂)、PTA(對苯二甲酸)觸媒** 紡織 - 化學助劑** 電動車輛產業 - 鋰電池材料** 能源元件 - 原材料</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2657.246</t>
+          <t>1393.968</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>59.46</t>
+          <t>61.27</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>23.97</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1440,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1394</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>6.65</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>5.60</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>67.98</t>
+          <t>69.38</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>65.84</t>
+          <t>66.06</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>66.06</t>
+          <t>66.34</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>62.56</t>
+          <t>62.79</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>686.39</t>
+          <t>768.32</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-103.80</t>
+          <t>-95.88</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,45 +1530,45 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>75146786.40955137</t>
+          <t>75217998.52890173</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>190606270.0</t>
+          <t>100281347.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>118462794.8</t>
+          <t>131264222.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>74290109.7</t>
+          <t>81393410.0</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>120126016.38</t>
+          <t>119695734.58</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>44172685</t>
+          <t>49870812</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-8488760.999966215</t>
+          <t>-5685337.758529304</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>11514469.2</v>
+        <v>9733490.07</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>53.28</t>
+          <t>52.01</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,77 +1608,77 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>52.27878514847768</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>116.3549688302164</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>24.9400431068334</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>14.92</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>101.27</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>12.28%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
         <is>
-          <t>6.83%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>47.82</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>8531</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>動力電池材料42.58%、特用化學材料20.60%、氧化觸媒17.66%、化肥10.09%、其他9.07% (2024年)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1693,32 +1693,32 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
+          <t>71.2</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
           <t>70.6</t>
         </is>
       </c>
-      <c r="CD3" t="inlineStr">
-        <is>
-          <t>72.8</t>
-        </is>
-      </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>69.7</t>
-        </is>
-      </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>46.52</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 石化及塑橡膠 - 接著劑(合成樹脂)、PTA(對苯二甲酸)觸媒** 紡織 - 化學助劑** 電動車輛產業 - 鋰電池材料** 能源元件 - 原材料</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2598.844</t>
+          <t>2657.246</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,74 +1755,74 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>72.5</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>59.46</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-09-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>70.0</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>2.64</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2.17</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>46.05</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-11-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-11-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-09-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>70.0</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
       <c r="T4" t="inlineStr">
         <is>
           <t>67.8</t>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>23.45</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,12 +1871,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1394</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1891,57 +1891,57 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>5.80</t>
+          <t>6.65</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>5.60</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>66.16</t>
+          <t>67.98</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>65.64</t>
+          <t>65.84</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>65.73</t>
+          <t>66.06</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>62.31</t>
+          <t>62.56</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>122.79</t>
+          <t>686.39</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-110.31</t>
+          <t>-103.80</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,45 +1961,45 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>75146786.40955137</t>
+          <t>75217998.52890173</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>182793426.0</t>
+          <t>190606270.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>85235906.2</t>
+          <t>118462794.8</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>58360010.8</t>
+          <t>74290109.7</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>117218867.38</t>
+          <t>120126016.38</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>26875895</t>
+          <t>44172685</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-12125711.94501511</t>
+          <t>-8488760.999966215</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>3969823.73</v>
+        <v>11514469.2</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>47.99</t>
+          <t>53.28</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,22 +2039,22 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>52.27878514847768</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>116.3549688302164</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>24.9400431068334</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
@@ -2064,52 +2064,52 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>14.92</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>101.27</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>12.28%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>6.83%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>47.82</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>8531</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>動力電池材料42.58%、特用化學材料20.60%、氧化觸媒17.66%、化肥10.09%、其他9.07% (2024年)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>70.6</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>46.52</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 石化及塑橡膠 - 接著劑(合成樹脂)、PTA(對苯二甲酸)觸媒** 紡織 - 化學助劑** 電動車輛產業 - 鋰電池材料** 能源元件 - 原材料</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1558.105</t>
+          <t>2598.844</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>67.1</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,22 +2196,22 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6.68</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>24.49</t>
+          <t>46.05</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14.06</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,12 +2302,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1394</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2317,62 +2317,62 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>94.25</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>5.80</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>5.49</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>64.66</t>
+          <t>66.16</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>65.52</t>
+          <t>65.64</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>65.47</t>
+          <t>65.73</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>62.1</t>
+          <t>62.31</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>122.79</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-113.47</t>
+          <t>-110.31</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,45 +2392,45 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>75146786.40955137</t>
+          <t>75217998.52890173</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>105849223.0</t>
+          <t>182793426.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>54169279.2</t>
+          <t>85235906.2</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>43512116.9</t>
+          <t>58360010.8</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>113935358.54</t>
+          <t>117218867.38</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>10657162</t>
+          <t>26875895</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-15052172.97708171</t>
+          <t>-12125711.94501511</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-6112930.21</v>
+        <v>3969823.73</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>41.86</t>
+          <t>47.99</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,77 +2470,77 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>52.27878514847768</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>116.3549688302164</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>24.9400431068334</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>14.92</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>101.27</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>12.28%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>6.83%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>47.82</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>8531</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>動力電池材料42.58%、特用化學材料20.60%、氧化觸媒17.66%、化肥10.09%、其他9.07% (2024年)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2555,32 +2555,32 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>67.1</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>46.52</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 石化及塑橡膠 - 接著劑(合成樹脂)、PTA(對苯二甲酸)觸媒** 紡織 - 化學助劑** 電動車輛產業 - 鋰電池材料** 能源元件 - 原材料</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1161.669</t>
+          <t>1558.105</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>65.4</t>
+          <t>67.1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>11.47</t>
+          <t>24.49</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10.48</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.60</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,12 +2733,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1394</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2748,57 +2748,57 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>70.01</t>
+          <t>94.25</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>5.35</t>
+          <t>5.42</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>63.86000000000001</t>
+          <t>64.66</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>65.67</t>
+          <t>65.52</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>65.26</t>
+          <t>65.47</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>61.95</t>
+          <t>62.1</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-65.80</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>75146786.40955137</t>
+          <t>75217998.52890173</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>76790846.0</t>
+          <t>105849223.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>40176137.2</t>
+          <t>54169279.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>36041288.8</t>
+          <t>43512116.9</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>112225732.82</t>
+          <t>113935358.54</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>4134848</t>
+          <t>10657162</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-16677489.84361878</t>
+          <t>-15052172.97708171</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-12054523.73</v>
+        <v>-6112930.21</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>38.27</t>
+          <t>41.86</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,22 +2901,22 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>52.27878514847768</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>116.3549688302164</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>24.9400431068334</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
@@ -2926,52 +2926,52 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>14.92</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>101.27</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>12.28%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
         <is>
-          <t>6.83%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>47.82</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>8531</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>動力電池材料42.58%、特用化學材料20.60%、氧化觸媒17.66%、化肥10.09%、其他9.07% (2024年)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,32 +2986,32 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>65.1</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>67.4</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>65.1</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>65.4</t>
+          <t>67.1</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>46.52</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 石化及塑橡膠 - 接著劑(合成樹脂)、PTA(對苯二甲酸)觸媒** 紡織 - 化學助劑** 電動車輛產業 - 鋰電池材料** 能源元件 - 原材料</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>562.661</t>
+          <t>1161.669</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>64.9</t>
+          <t>65.4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>11.47</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>-2.60</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1394</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>82.76</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>36.68</t>
+          <t>70.01</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-3.82</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>5.35</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>63.5</t>
+          <t>63.86000000000001</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>66.03</t>
+          <t>65.67</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>65.08</t>
+          <t>65.26</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>61.76</t>
+          <t>61.95</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-137.89</t>
+          <t>-65.80</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-111.26</t>
+          <t>-113.47</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>75146786.40955137</t>
+          <t>75217998.52890173</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>36274209.0</t>
+          <t>76790846.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>31522597.6</t>
+          <t>40176137.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>31905787.9</t>
+          <t>36041288.8</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>111064675.6</t>
+          <t>112225732.82</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-383190</t>
+          <t>4134848</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-17518029.13726628</t>
+          <t>-16677489.84361878</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-16998598.23</v>
+        <v>-12054523.73</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>37.21</t>
+          <t>38.27</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,27 +3332,27 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>52.27878514847768</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>116.3549688302164</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>24.9400431068334</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3362,47 +3362,47 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>14.92</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>101.27</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>12.28%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
         <is>
-          <t>6.83%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>47.82</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>8531</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>動力電池材料42.58%、特用化學材料20.60%、氧化觸媒17.66%、化肥10.09%、其他9.07% (2024年)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3417,32 +3417,32 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>63.4</t>
+          <t>65.1</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
+          <t>67.4</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
+          <t>65.1</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
           <t>65.4</t>
         </is>
       </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>63.4</t>
-        </is>
-      </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>64.9</t>
-        </is>
-      </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>46.52</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 石化及塑橡膠 - 接著劑(合成樹脂)、PTA(對苯二甲酸)觸媒** 紡織 - 化學助劑** 電動車輛產業 - 鋰電池材料** 能源元件 - 原材料</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>386.127</t>
+          <t>562.661</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>63.4</t>
+          <t>64.9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>11.82</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3519,7 +3519,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1394</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>82.76</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>36.68</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-4.48</t>
+          <t>-3.82</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>63.34000000000001</t>
+          <t>63.5</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>66.31</t>
+          <t>66.03</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>64.92</t>
+          <t>65.08</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>61.58</t>
+          <t>61.76</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-308.50</t>
+          <t>-137.89</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-107.38</t>
+          <t>-111.26</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>75146786.40955137</t>
+          <t>75217998.52890173</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>24471827.0</t>
+          <t>36274209.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>30117424.6</t>
+          <t>31522597.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>31140083.6</t>
+          <t>31905787.9</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>110844509.38</t>
+          <t>111064675.6</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-1022659</t>
+          <t>-383190</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-17612471.12087157</t>
+          <t>-17518029.13726628</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-19113400.75</v>
+        <v>-16998598.23</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>34.04</t>
+          <t>37.21</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,27 +3763,27 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>52.27878514847768</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>116.3549688302164</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>24.9400431068334</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3793,47 +3793,47 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>14.92</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>101.27</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>12.28%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
         <is>
-          <t>6.83%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>47.82</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>8531</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>動力電池材料42.58%、特用化學材料20.60%、氧化觸媒17.66%、化肥10.09%、其他9.07% (2024年)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3848,32 +3848,32 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>63.4</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>63.9</t>
+          <t>65.4</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>63.4</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>63.4</t>
+          <t>64.9</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>46.52</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 石化及塑橡膠 - 接著劑(合成樹脂)、PTA(對苯二甲酸)觸媒** 紡織 - 化學助劑** 電動車輛產業 - 鋰電池材料** 能源元件 - 原材料</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>440.993</t>
+          <t>386.127</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>63.4</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>13.07</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-10.57</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,37 +4026,37 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1394</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.09</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-4.79</t>
+          <t>-4.48</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -4066,37 +4066,37 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>63.42</t>
+          <t>63.34000000000001</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>66.61</t>
+          <t>66.31</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>64.77</t>
+          <t>64.92</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>61.43</t>
+          <t>61.58</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-1571.66</t>
+          <t>-308.50</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-101.69</t>
+          <t>-107.38</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>75146786.40955137</t>
+          <t>75217998.52890173</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>27460291.0</t>
+          <t>24471827.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>31484115.4</t>
+          <t>30117424.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>35203368.5</t>
+          <t>31140083.6</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>110885096.24</t>
+          <t>110844509.38</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-3719253</t>
+          <t>-1022659</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-17339574.82404308</t>
+          <t>-17612471.12087157</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-20187384.84</v>
+        <v>-19113400.75</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>32.14</t>
+          <t>34.04</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,27 +4194,27 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>52.27878514847768</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>116.3549688302164</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>24.9400431068334</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4224,47 +4224,47 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>14.92</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>101.27</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>12.28%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
         <is>
-          <t>6.83%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>47.82</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>8531</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>動力電池材料42.58%、特用化學材料20.60%、氧化觸媒17.66%、化肥10.09%、其他9.07% (2024年)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4279,32 +4279,32 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>63.9</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>61.6</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>63.4</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>46.52</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 石化及塑橡膠 - 接著劑(合成樹脂)、PTA(對苯二甲酸)觸媒** 紡織 - 化學助劑** 電動車輛產業 - 鋰電池材料** 能源元件 - 原材料</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>559.37</t>
+          <t>440.993</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>63.1</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>12.24</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-20.46</t>
+          <t>-10.57</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,12 +4457,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1394</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4472,62 +4472,62 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-4.44</t>
+          <t>-4.79</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>5.42</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>64.00000000000001</t>
+          <t>63.42</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>66.97</t>
+          <t>66.61</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>64.65</t>
+          <t>64.77</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>61.29</t>
+          <t>61.43</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-542.60</t>
+          <t>-1571.66</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-95.06</t>
+          <t>-101.69</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>75146786.40955137</t>
+          <t>75217998.52890173</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>35883513.0</t>
+          <t>27460291.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>32854954.6</t>
+          <t>31484115.4</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>41305635.5</t>
+          <t>35203368.5</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>110944182.58</t>
+          <t>110885096.24</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-8450680</t>
+          <t>-3719253</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-16821791.18567295</t>
+          <t>-17339574.82404308</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-21320862.35</v>
+        <v>-20187384.84</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>33.40</t>
+          <t>32.14</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,77 +4625,77 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>52.27878514847768</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>116.3549688302164</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>24.9400431068334</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>14.92</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>101.27</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>12.28%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
         <is>
-          <t>6.83%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>47.82</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>8531</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>動力電池材料42.58%、特用化學材料20.60%、氧化觸媒17.66%、化肥10.09%、其他9.07% (2024年)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4710,32 +4710,32 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>63.7</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>65.3</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>63.1</t>
+          <t>61.6</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>63.1</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>46.52</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 石化及塑橡膠 - 接著劑(合成樹脂)、PTA(對苯二甲酸)觸媒** 紡織 - 化學助劑** 電動車輛產業 - 鋰電池材料** 能源元件 - 原材料</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>528.649</t>
+          <t>559.37</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>63.6</t>
+          <t>63.1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>11.54</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-24.06</t>
+          <t>-20.46</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-3.49</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,12 +4888,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1394</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4908,57 +4908,57 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>-4.44</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>5.53</t>
+          <t>5.48</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>64.42</t>
+          <t>64.00000000000001</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>67.26</t>
+          <t>66.97</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>64.51</t>
+          <t>64.65</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>61.13</t>
+          <t>61.29</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-235.52</t>
+          <t>-542.60</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-88.35</t>
+          <t>-95.06</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>75146786.40955137</t>
+          <t>75217998.52890173</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>33523148.0</t>
+          <t>35883513.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>31906440.4</t>
+          <t>32854954.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>42016145.3</t>
+          <t>41305635.5</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>111603019.84</t>
+          <t>110944182.58</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-10109704</t>
+          <t>-8450680</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-16003778.24661902</t>
+          <t>-16821791.18567295</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-23081144.65</v>
+        <v>-21320862.35</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>34.46</t>
+          <t>33.40</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,27 +5056,27 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>52.27878514847768</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>116.3549688302164</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>24.9400431068334</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,47 +5086,47 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>14.92</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>101.27</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>12.28%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
         <is>
-          <t>6.83%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>47.82</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>8531</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>動力電池材料42.58%、特用化學材料20.60%、氧化觸媒17.66%、化肥10.09%、其他9.07% (2024年)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5141,32 +5141,32 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>63.7</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>65.3</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>63.1</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>63.6</t>
+          <t>63.1</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>46.52</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 石化及塑橡膠 - 接著劑(合成樹脂)、PTA(對苯二甲酸)觸媒** 紡織 - 化學助劑** 電動車輛產業 - 鋰電池材料** 能源元件 - 原材料</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>454.207</t>
+          <t>528.649</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>64.1</t>
+          <t>63.6</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>10.85</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-29.12</t>
+          <t>-24.06</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1394</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>8.82</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>5.72</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.90</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>5.53</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>64.86000000000001</t>
+          <t>64.42</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>67.49</t>
+          <t>67.26</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>64.51</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>60.95</t>
+          <t>61.13</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-152.43</t>
+          <t>-235.52</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-81.50</t>
+          <t>-88.35</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>75146786.40955137</t>
+          <t>75217998.52890173</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>29248344.0</t>
+          <t>33523148.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>32288978.2</t>
+          <t>31906440.4</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>45554684.9</t>
+          <t>42016145.3</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>111738850.66</t>
+          <t>111603019.84</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-13265706</t>
+          <t>-10109704</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-14716984.35588541</t>
+          <t>-16003778.24661902</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-24518610.79</v>
+        <v>-23081144.65</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>35.52</t>
+          <t>34.46</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,27 +5487,27 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>52.27878514847768</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>116.3549688302164</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>24.9400431068334</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,47 +5517,47 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>14.92</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>101.27</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>12.28%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
         <is>
-          <t>6.83%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>47.82</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>8531</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>動力電池材料42.58%、特用化學材料20.60%、氧化觸媒17.66%、化肥10.09%、其他9.07% (2024年)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>64.7</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>65.2</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>63.7</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>64.1</t>
+          <t>63.6</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>46.52</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 石化及塑橡膠 - 接著劑(合成樹脂)、PTA(對苯二甲酸)觸媒** 紡織 - 化學助劑** 電動車輛產業 - 鋰電池材料** 能源元件 - 原材料</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CI12" t="inlineStr">
@@ -5619,127 +5619,127 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>-1.51</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>4870.0</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>0.18</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>22.85</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>2025-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>-1.53</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>-4.07</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>8.40</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
           <t>-1.35</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>4060.0</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>-1.83</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>36.21</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>2025-11-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>2025-10-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>59.6</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>61.5</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>-4.07</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>7.01</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>-1.86</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,77 +5750,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>3505</t>
+          <t>4870</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>55.93</t>
+          <t>40.68</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>67.23</t>
+          <t>55.37</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>60.12</t>
+          <t>59.73999999999999</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>59.74</t>
+          <t>59.51</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>60.09</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>57.46</t>
+          <t>57.55</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>14.66</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-107.17</t>
+          <t>-107.25</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,45 +5840,45 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>820098.9492017417</t>
+          <t>819526.3304347827</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>242218.0</t>
+          <t>283328.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>465573.8</t>
+          <t>437969.2</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>341803.5</t>
+          <t>356514.8</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>579417.88</t>
+          <t>570563.3</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>123770</t>
+          <t>81454</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-39492.00850249613</t>
+          <t>-36824.00107548192</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>-18693.88</v>
+        <v>-22149.96</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5918,42 +5918,42 @@
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>-3.841141774361624</t>
+          <t>-1.228328584465341</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>34.73629981257034</t>
+          <t>47.44460114587924</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>32.80397526962716</t>
+          <t>32.54445648609581</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>35642</t>
+          <t>34629</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>59.3</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>60.6</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>3505.0</t>
+          <t>4060.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,22 +6075,22 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>36.21</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -6105,7 +6105,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-17 00:00:00</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -6125,12 +6125,12 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,77 +6181,77 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>3505</t>
+          <t>4870</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>69.49</t>
+          <t>55.93</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>81.92</t>
+          <t>67.23</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>59.72000000000001</t>
+          <t>60.12</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>59.98</t>
+          <t>59.74</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>60.1</t>
+          <t>60.09</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>57.38</t>
+          <t>57.46</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>20.51</t>
+          <t>14.66</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-107.44</t>
+          <t>-107.17</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,45 +6271,45 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>820098.9492017417</t>
+          <t>819526.3304347827</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>209656.0</t>
+          <t>242218.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>452042.6</t>
+          <t>465573.8</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>332281.8</t>
+          <t>341803.5</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>596784.86</t>
+          <t>579417.88</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>119760</t>
+          <t>123770</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-43273.48695184787</t>
+          <t>-39492.00850249613</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>-8684.33</v>
+        <v>-18693.88</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6349,42 +6349,42 @@
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>-3.841141774361624</t>
+          <t>-1.228328584465341</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>34.73629981257034</t>
+          <t>47.44460114587924</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>32.80397526962716</t>
+          <t>32.54445648609581</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>35642</t>
+          <t>34629</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>60.1</t>
+          <t>59.3</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8540.0</t>
+          <t>3505.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>60.2</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>30.92</t>
+          <t>36.04</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6536,7 +6536,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-17 00:00:00</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -6556,7 +6556,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14.74</t>
+          <t>6.05</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,77 +6612,77 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>3505</t>
+          <t>4870</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>76.27</t>
+          <t>69.49</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>91.33</t>
+          <t>81.92</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>59.14</t>
+          <t>59.72000000000001</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>60.09</t>
+          <t>59.98</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>60.08</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>57.31</t>
+          <t>57.38</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>9.30</t>
+          <t>20.51</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-107.82</t>
+          <t>-107.44</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,41 +6702,41 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>820098.9492017417</t>
+          <t>819526.3304347827</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>517165.0</t>
+          <t>209656.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>445047.0</t>
+          <t>452042.6</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>339942.5</t>
+          <t>332281.8</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>643736.64</t>
+          <t>596784.86</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>105104</t>
+          <t>119760</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-49562.42385215155</t>
+          <t>-43273.48695184787</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>9413.950000000001</v>
+        <v>-8684.33</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6780,42 +6780,42 @@
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>-3.841141774361624</t>
+          <t>-1.228328584465341</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>34.73629981257034</t>
+          <t>47.44460114587924</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>32.80397526962716</t>
+          <t>32.54445648609581</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>35642</t>
+          <t>34629</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>61.7</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>61.8</t>
+          <t>60.4</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>59.6</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>60.2</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>15157.0</t>
+          <t>8540.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.6</t>
+          <t>60.2</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>29.74</t>
+          <t>30.92</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6967,7 +6967,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-17 00:00:00</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -6987,7 +6987,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>14.74</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,47 +7043,47 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>3505</t>
+          <t>4870</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>76.27</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>75.54</t>
+          <t>91.33</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>5.77</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>58.24000000000001</t>
+          <t>59.14</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -7098,22 +7098,22 @@
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>57.24</t>
+          <t>57.31</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-15.74</t>
+          <t>9.30</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-108.00</t>
+          <t>-107.82</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,41 +7133,41 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>820098.9492017417</t>
+          <t>819526.3304347827</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>937479.0</t>
+          <t>517165.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>393702.8</t>
+          <t>445047.0</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>303455.3</t>
+          <t>339942.5</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>659423.84</t>
+          <t>643736.64</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>90247</t>
+          <t>105104</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-60285.40158650742</t>
+          <t>-49562.42385215155</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>1985.04</v>
+        <v>9413.950000000001</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7211,27 +7211,27 @@
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>-3.841141774361624</t>
+          <t>-1.228328584465341</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>34.73629981257034</t>
+          <t>47.44460114587924</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>32.80397526962716</t>
+          <t>32.54445648609581</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>35642</t>
+          <t>34629</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>60.5</t>
+          <t>61.7</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>63.2</t>
+          <t>61.8</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>59.6</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>61.6</t>
+          <t>60.2</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>7091.0</t>
+          <t>15157.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>61.6</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-6.02</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>17.44</t>
+          <t>29.74</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7398,7 +7398,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-17 00:00:00</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -7418,7 +7418,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12.24</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,77 +7474,77 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>3505</t>
+          <t>4870</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>97.73</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>50.21</t>
+          <t>75.54</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>5.77</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-3.09</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>57.26000000000001</t>
+          <t>58.24000000000001</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>60.13</t>
+          <t>60.09</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>59.94</t>
+          <t>60.08</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>57.24</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-89.66</t>
+          <t>-15.74</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-107.68</t>
+          <t>-108.00</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>820098.9492017417</t>
+          <t>819526.3304347827</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>421351.0</t>
+          <t>937479.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>275060.4</t>
+          <t>393702.8</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>234213.9</t>
+          <t>303455.3</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>643815.04</t>
+          <t>659423.84</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>40846</t>
+          <t>90247</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-71607.30094654183</t>
+          <t>-60285.40158650742</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>-53732.22</v>
+        <v>1985.04</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7642,42 +7642,42 @@
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>-3.841141774361624</t>
+          <t>-1.228328584465341</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>34.73629981257034</t>
+          <t>47.44460114587924</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>32.80397526962716</t>
+          <t>32.54445648609581</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>35642</t>
+          <t>34629</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>60.5</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>60.2</t>
+          <t>63.2</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>61.6</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,42 +7774,42 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>7091.0</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>60.0</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-3.27</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
           <t>0.18</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>3057.0</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>57.0</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>4.68</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>-1.83</t>
-        </is>
-      </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>17.44</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7829,7 +7829,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-17 00:00:00</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -7849,7 +7849,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>12.24</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,77 +7905,77 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>3505</t>
+          <t>4870</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>97.73</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>17.63</t>
+          <t>50.21</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-5.40</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>57.04</t>
+          <t>57.26000000000001</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>60.3</t>
+          <t>60.13</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>59.83</t>
+          <t>59.94</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>57.06</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-203.28</t>
+          <t>-89.66</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-105.96</t>
+          <t>-107.68</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>820098.9492017417</t>
+          <t>819526.3304347827</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>174562.0</t>
+          <t>421351.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>218033.2</t>
+          <t>275060.4</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>218350.5</t>
+          <t>234213.9</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>642009.16</t>
+          <t>643815.04</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-317</t>
+          <t>40846</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-74857.31579659131</t>
+          <t>-71607.30094654183</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>-76109.87</v>
+        <v>-53732.22</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8073,42 +8073,42 @@
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>-3.841141774361624</t>
+          <t>-1.228328584465341</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>34.73629981257034</t>
+          <t>47.44460114587924</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>32.80397526962716</t>
+          <t>32.54445648609581</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>35642</t>
+          <t>34629</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>57.7</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
+          <t>60.2</t>
+        </is>
+      </c>
+      <c r="CE18" t="inlineStr">
+        <is>
           <t>57.7</t>
         </is>
       </c>
-      <c r="CE18" t="inlineStr">
-        <is>
-          <t>56.4</t>
-        </is>
-      </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>3065.0</t>
+          <t>3057.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>56.9</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-6.63</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8260,7 +8260,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-17 00:00:00</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -8280,7 +8280,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,275 +8336,275 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>3505</t>
+          <t>4870</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>17.63</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-5.09</t>
+          <t>-5.40</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>57.04</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>60.58</t>
+          <t>60.3</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>59.76</t>
+          <t>59.83</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
+          <t>57.06</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>-203.28</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>-0.96</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>-0.32</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>5.31</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr">
+        <is>
+          <t>-105.96</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>819526.3304347827</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>174562.0</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>218033.2</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>218350.5</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>642009.16</t>
+        </is>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>-317</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>-74857.31579659131</t>
+        </is>
+      </c>
+      <c r="BC19" t="n">
+        <v>-76109.87</v>
+      </c>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>58.9</t>
+        </is>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
+          <t>2025/08/29</t>
+        </is>
+      </c>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>-3.23</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>光洋科</t>
+        </is>
+      </c>
+      <c r="BI19" t="inlineStr">
+        <is>
+          <t>光洋科</t>
+        </is>
+      </c>
+      <c r="BJ19" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BK19" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL19" t="inlineStr">
+        <is>
+          <t>1.12</t>
+        </is>
+      </c>
+      <c r="BM19" t="inlineStr">
+        <is>
+          <t>-1.228328584465341</t>
+        </is>
+      </c>
+      <c r="BN19" t="inlineStr">
+        <is>
+          <t>47.44460114587924</t>
+        </is>
+      </c>
+      <c r="BO19" t="inlineStr">
+        <is>
+          <t>32.54445648609581</t>
+        </is>
+      </c>
+      <c r="BP19" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+        </is>
+      </c>
+      <c r="BQ19" t="inlineStr">
+        <is>
+          <t>價漲量-</t>
+        </is>
+      </c>
+      <c r="BR19" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="BS19" t="inlineStr">
+        <is>
+          <t>3.44</t>
+        </is>
+      </c>
+      <c r="BT19" t="inlineStr">
+        <is>
+          <t>17.51</t>
+        </is>
+      </c>
+      <c r="BU19" t="inlineStr">
+        <is>
+          <t>24.72</t>
+        </is>
+      </c>
+      <c r="BV19" t="inlineStr">
+        <is>
+          <t>14.09%</t>
+        </is>
+      </c>
+      <c r="BW19" t="inlineStr">
+        <is>
+          <t>9.19%</t>
+        </is>
+      </c>
+      <c r="BX19" t="inlineStr">
+        <is>
+          <t>43.93</t>
+        </is>
+      </c>
+      <c r="BY19" t="inlineStr">
+        <is>
+          <t>34629</t>
+        </is>
+      </c>
+      <c r="BZ19" t="inlineStr">
+        <is>
+          <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA19" t="inlineStr">
+        <is>
+          <t>光洋科-其他電子業-上櫃</t>
+        </is>
+      </c>
+      <c r="CB19" t="inlineStr">
+        <is>
+          <t>其他電子業右上上櫃</t>
+        </is>
+      </c>
+      <c r="CC19" t="inlineStr">
+        <is>
+          <t>56.6</t>
+        </is>
+      </c>
+      <c r="CD19" t="inlineStr">
+        <is>
+          <t>57.7</t>
+        </is>
+      </c>
+      <c r="CE19" t="inlineStr">
+        <is>
+          <t>56.4</t>
+        </is>
+      </c>
+      <c r="CF19" t="inlineStr">
+        <is>
           <t>57.0</t>
-        </is>
-      </c>
-      <c r="AP19" t="inlineStr">
-        <is>
-          <t>-464.25</t>
-        </is>
-      </c>
-      <c r="AQ19" t="inlineStr">
-        <is>
-          <t>-0.88</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>-0.16</t>
-        </is>
-      </c>
-      <c r="AS19" t="inlineStr">
-        <is>
-          <t>5.31</t>
-        </is>
-      </c>
-      <c r="AT19" t="inlineStr">
-        <is>
-          <t>-102.93</t>
-        </is>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV19" t="inlineStr">
-        <is>
-          <t>820098.9492017417</t>
-        </is>
-      </c>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>174678.0</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>212521.0</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>227616.4</t>
-        </is>
-      </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>643094.8</t>
-        </is>
-      </c>
-      <c r="BA19" t="inlineStr">
-        <is>
-          <t>-15095</t>
-        </is>
-      </c>
-      <c r="BB19" t="inlineStr">
-        <is>
-          <t>-74629.57784452781</t>
-        </is>
-      </c>
-      <c r="BC19" t="n">
-        <v>-78918.07000000001</v>
-      </c>
-      <c r="BD19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE19" t="inlineStr">
-        <is>
-          <t>58.9</t>
-        </is>
-      </c>
-      <c r="BF19" t="inlineStr">
-        <is>
-          <t>2025/08/29</t>
-        </is>
-      </c>
-      <c r="BG19" t="inlineStr">
-        <is>
-          <t>-3.40</t>
-        </is>
-      </c>
-      <c r="BH19" t="inlineStr">
-        <is>
-          <t>光洋科</t>
-        </is>
-      </c>
-      <c r="BI19" t="inlineStr">
-        <is>
-          <t>光洋科</t>
-        </is>
-      </c>
-      <c r="BJ19" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BK19" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL19" t="inlineStr">
-        <is>
-          <t>1.13</t>
-        </is>
-      </c>
-      <c r="BM19" t="inlineStr">
-        <is>
-          <t>-3.841141774361624</t>
-        </is>
-      </c>
-      <c r="BN19" t="inlineStr">
-        <is>
-          <t>34.73629981257034</t>
-        </is>
-      </c>
-      <c r="BO19" t="inlineStr">
-        <is>
-          <t>32.80397526962716</t>
-        </is>
-      </c>
-      <c r="BP19" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ19" t="inlineStr">
-        <is>
-          <t>價漲量-</t>
-        </is>
-      </c>
-      <c r="BR19" t="inlineStr">
-        <is>
-          <t>2.48</t>
-        </is>
-      </c>
-      <c r="BS19" t="inlineStr">
-        <is>
-          <t>3.39</t>
-        </is>
-      </c>
-      <c r="BT19" t="inlineStr">
-        <is>
-          <t>17.51</t>
-        </is>
-      </c>
-      <c r="BU19" t="inlineStr">
-        <is>
-          <t>25.45</t>
-        </is>
-      </c>
-      <c r="BV19" t="inlineStr">
-        <is>
-          <t>14.09%</t>
-        </is>
-      </c>
-      <c r="BW19" t="inlineStr">
-        <is>
-          <t>9.19%</t>
-        </is>
-      </c>
-      <c r="BX19" t="inlineStr">
-        <is>
-          <t>44.82</t>
-        </is>
-      </c>
-      <c r="BY19" t="inlineStr">
-        <is>
-          <t>35642</t>
-        </is>
-      </c>
-      <c r="BZ19" t="inlineStr">
-        <is>
-          <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA19" t="inlineStr">
-        <is>
-          <t>光洋科-其他電子業-上櫃</t>
-        </is>
-      </c>
-      <c r="CB19" t="inlineStr">
-        <is>
-          <t>其他電子業右上上櫃</t>
-        </is>
-      </c>
-      <c r="CC19" t="inlineStr">
-        <is>
-          <t>56.7</t>
-        </is>
-      </c>
-      <c r="CD19" t="inlineStr">
-        <is>
-          <t>57.8</t>
-        </is>
-      </c>
-      <c r="CE19" t="inlineStr">
-        <is>
-          <t>56.5</t>
-        </is>
-      </c>
-      <c r="CF19" t="inlineStr">
-        <is>
-          <t>56.9</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>4712.0</t>
+          <t>3065.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-6.63</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8691,7 +8691,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-17 00:00:00</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -8711,7 +8711,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>8.13</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,77 +8767,77 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>3505</t>
+          <t>4870</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-3.80</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-4.89</t>
+          <t>-5.09</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>57.9</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>60.88</t>
+          <t>60.58</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>59.67</t>
+          <t>59.76</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>56.96</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-3104.58</t>
+          <t>-464.25</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-99.53</t>
+          <t>-102.93</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>820098.9492017417</t>
+          <t>819526.3304347827</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>260444.0</t>
+          <t>174678.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>234838.0</t>
+          <t>212521.0</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>255984.1</t>
+          <t>227616.4</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>641889.36</t>
+          <t>643094.8</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-21146</t>
+          <t>-15095</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-73849.85288862225</t>
+          <t>-74629.57784452781</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>-80123.69</v>
+        <v>-78918.07000000001</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-5.43</t>
+          <t>-3.40</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8935,42 +8935,42 @@
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>-3.841141774361624</t>
+          <t>-1.228328584465341</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>34.73629981257034</t>
+          <t>47.44460114587924</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>32.80397526962716</t>
+          <t>32.54445648609581</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>35642</t>
+          <t>34629</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>56.7</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>5987.0</t>
+          <t>4712.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>56.7</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>5.18</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-19.62</t>
+          <t>-8.26</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9122,7 +9122,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-17 00:00:00</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -9142,7 +9142,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-4.13</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10.33</t>
+          <t>8.13</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-3.70</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,12 +9198,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>3505</t>
+          <t>4870</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9213,62 +9213,62 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>-3.80</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-4.89</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>58.77999999999999</t>
+          <t>57.9</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>61.17</t>
+          <t>60.88</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>59.62</t>
+          <t>59.67</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>56.92</t>
+          <t>56.96</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-308.20</t>
+          <t>-3104.58</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-95.87</t>
+          <t>-99.53</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>820098.9492017417</t>
+          <t>819526.3304347827</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>344267.0</t>
+          <t>260444.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>213207.8</t>
+          <t>234838.0</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>265240.8</t>
+          <t>255984.1</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>639604.54</t>
+          <t>641889.36</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-52033</t>
+          <t>-21146</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-72709.154839041</t>
+          <t>-73849.85288862225</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>-88173.67</v>
+        <v>-80123.69</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-3.74</t>
+          <t>-5.43</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9366,42 +9366,42 @@
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>-3.841141774361624</t>
+          <t>-1.228328584465341</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>34.73629981257034</t>
+          <t>47.44460114587924</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>32.80397526962716</t>
+          <t>32.54445648609581</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>35642</t>
+          <t>34629</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>59.1</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>56.7</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2301.0</t>
+          <t>5987.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>56.7</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-29.06</t>
+          <t>-19.62</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9553,7 +9553,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-17 00:00:00</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -9573,7 +9573,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>10.33</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-3.70</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,12 +9629,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>3505</t>
+          <t>4870</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9649,57 +9649,57 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>59.48</t>
+          <t>58.77999999999999</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>61.43</t>
+          <t>61.17</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>59.55</t>
+          <t>59.62</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>56.88</t>
+          <t>56.92</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-144.98</t>
+          <t>-308.20</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-92.69</t>
+          <t>-95.87</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>820098.9492017417</t>
+          <t>819526.3304347827</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>136215.0</t>
+          <t>344267.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>193367.4</t>
+          <t>213207.8</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>272587.5</t>
+          <t>265240.8</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>637064.6</t>
+          <t>639604.54</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-79220</t>
+          <t>-52033</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-69897.42474011309</t>
+          <t>-72709.154839041</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-105505.62</v>
+        <v>-88173.67</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-3.74</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9797,27 +9797,27 @@
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>-3.841141774361624</t>
+          <t>-1.228328584465341</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>34.73629981257034</t>
+          <t>47.44460114587924</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>32.80397526962716</t>
+          <t>32.54445648609581</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9827,12 +9827,12 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>35642</t>
+          <t>34629</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>59.7</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>59.9</t>
+          <t>59.1</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>58.7</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>56.7</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2470.0</t>
+          <t>2301.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>59.3</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-35.46</t>
+          <t>-29.06</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -9984,7 +9984,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-17 00:00:00</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -10004,7 +10004,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,17 +10060,17 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>3505</t>
+          <t>4870</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
@@ -10080,57 +10080,57 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>59.84</t>
+          <t>59.48</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>61.58</t>
+          <t>61.43</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>59.45</t>
+          <t>59.55</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>56.81</t>
+          <t>56.88</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-106.86</t>
+          <t>-144.98</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-90.04</t>
+          <t>-92.69</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>820098.9492017417</t>
+          <t>819526.3304347827</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>147001.0</t>
+          <t>136215.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>218667.8</t>
+          <t>193367.4</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>338806.2</t>
+          <t>272587.5</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>640131.16</t>
+          <t>637064.6</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-120138</t>
+          <t>-79220</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-63423.20826936791</t>
+          <t>-69897.42474011309</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-104206.19</v>
+        <v>-105505.62</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10228,27 +10228,27 @@
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>-3.841141774361624</t>
+          <t>-1.228328584465341</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>34.73629981257034</t>
+          <t>47.44460114587924</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>32.80397526962716</t>
+          <t>32.54445648609581</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>35642</t>
+          <t>34629</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,7 +10313,7 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>59.4</t>
+          <t>59.7</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>58.7</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>59.3</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料).xlsx
+++ b/Result/checksun_type/濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料).xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1168.47</t>
+          <t>1542.065</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>67.9</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -903,17 +903,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>53.47</t>
+          <t>41.98</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>-3.00</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>13.91</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1542</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>49.45</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>76.15</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>6.43</t>
+          <t>6.58</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>5.70</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>70.66</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>66.24</t>
+          <t>66.3</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>66.75</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>63.02</t>
+          <t>63.15</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>262.06</t>
+          <t>125.60</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-88.05</t>
+          <t>-82.57</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,45 +1099,45 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>75217998.52890173</t>
+          <t>75339280.78787878</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>82950382.0</t>
+          <t>106177736.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>132496129.6</t>
+          <t>132561832.2</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>86336133.4</t>
+          <t>93365555.7</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>120394266.18</t>
+          <t>120263879.18</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>46159996</t>
+          <t>39196276</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-3742417.326026477</t>
+          <t>-2157550.973595275</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>6943645.05</v>
+        <v>6559213.96</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>50.11</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,22 +1177,22 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-12.015112320512</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>97.95053699871907</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>39.23959558994965</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
@@ -1207,47 +1207,47 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14.92</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>95.63</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12.28%</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6.83%</t>
         </is>
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>46.38</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8056</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>動力電池材料42.58%、特用化學材料20.60%、氧化觸媒17.66%、化肥10.09%、其他9.07% (2024年)</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1262,32 +1262,32 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>67.9</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>46.52</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 石化及塑橡膠 - 接著劑(合成樹脂)、PTA(對苯二甲酸)觸媒** 紡織 - 化學助劑** 電動車輛產業 - 鋰電池材料** 能源元件 - 原材料</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1393.968</t>
+          <t>1168.47</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-4.57</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>61.27</t>
+          <t>53.47</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>10.54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1440,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1542</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>6.43</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>69.38</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>66.06</t>
+          <t>66.24</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>66.34</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>62.79</t>
+          <t>63.02</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>768.32</t>
+          <t>262.06</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-95.88</t>
+          <t>-88.05</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,45 +1530,45 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>75217998.52890173</t>
+          <t>75339280.78787878</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>100281347.0</t>
+          <t>82950382.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>131264222.4</t>
+          <t>132496129.6</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>81393410.0</t>
+          <t>86336133.4</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>119695734.58</t>
+          <t>120394266.18</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>49870812</t>
+          <t>46159996</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-5685337.758529304</t>
+          <t>-3742417.326026477</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>9733490.07</v>
+        <v>6943645.05</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>52.01</t>
+          <t>50.11</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,22 +1608,22 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-12.015112320512</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>97.95053699871907</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>39.23959558994965</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
@@ -1633,52 +1633,52 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14.92</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>95.63</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12.28%</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6.83%</t>
         </is>
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>46.38</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8056</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>動力電池材料42.58%、特用化學材料20.60%、氧化觸媒17.66%、化肥10.09%、其他9.07% (2024年)</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1693,32 +1693,32 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>46.52</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 石化及塑橡膠 - 接著劑(合成樹脂)、PTA(對苯二甲酸)觸媒** 紡織 - 化學助劑** 電動車輛產業 - 鋰電池材料** 能源元件 - 原材料</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2657.246</t>
+          <t>1393.968</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5.89</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>59.46</t>
+          <t>61.27</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>12.58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,77 +1871,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1542</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>6.65</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>5.60</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>67.98</t>
+          <t>69.38</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>65.84</t>
+          <t>66.06</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>66.06</t>
+          <t>66.34</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>62.56</t>
+          <t>62.79</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>686.39</t>
+          <t>768.32</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-103.80</t>
+          <t>-95.88</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,45 +1961,45 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>75217998.52890173</t>
+          <t>75339280.78787878</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>190606270.0</t>
+          <t>100281347.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>118462794.8</t>
+          <t>131264222.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>74290109.7</t>
+          <t>81393410.0</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>120126016.38</t>
+          <t>119695734.58</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>44172685</t>
+          <t>49870812</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-8488760.999966215</t>
+          <t>-5685337.758529304</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>11514469.2</v>
+        <v>9733490.07</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>53.28</t>
+          <t>52.01</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,77 +2039,77 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-12.015112320512</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>97.95053699871907</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>39.23959558994965</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14.92</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>95.63</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12.28%</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6.83%</t>
         </is>
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>46.38</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8056</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>動力電池材料42.58%、特用化學材料20.60%、氧化觸媒17.66%、化肥10.09%、其他9.07% (2024年)</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
+          <t>71.2</t>
+        </is>
+      </c>
+      <c r="CD4" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
           <t>70.6</t>
         </is>
       </c>
-      <c r="CD4" t="inlineStr">
-        <is>
-          <t>72.8</t>
-        </is>
-      </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>69.7</t>
-        </is>
-      </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>46.52</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 石化及塑橡膠 - 接著劑(合成樹脂)、PTA(對苯二甲酸)觸媒** 紡織 - 化學助劑** 電動車輛產業 - 鋰電池材料** 能源元件 - 原材料</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2598.844</t>
+          <t>2657.246</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,74 +2186,74 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>72.5</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-6.77</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>59.46</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-11-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-09-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>70.0</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>46.05</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2025-11-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-09-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>70.0</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
       <c r="T5" t="inlineStr">
         <is>
           <t>67.8</t>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>23.97</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,12 +2302,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1542</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2322,57 +2322,57 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>5.80</t>
+          <t>6.65</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>5.60</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>66.16</t>
+          <t>67.98</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>65.64</t>
+          <t>65.84</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>65.73</t>
+          <t>66.06</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>62.31</t>
+          <t>62.56</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>122.79</t>
+          <t>686.39</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-110.31</t>
+          <t>-103.80</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,45 +2392,45 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>75217998.52890173</t>
+          <t>75339280.78787878</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>182793426.0</t>
+          <t>190606270.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>85235906.2</t>
+          <t>118462794.8</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>58360010.8</t>
+          <t>74290109.7</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>117218867.38</t>
+          <t>120126016.38</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>26875895</t>
+          <t>44172685</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-12125711.94501511</t>
+          <t>-8488760.999966215</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>3969823.73</v>
+        <v>11514469.2</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>47.99</t>
+          <t>53.28</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,22 +2470,22 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-12.015112320512</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>97.95053699871907</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>39.23959558994965</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
@@ -2495,52 +2495,52 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14.92</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>95.63</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12.28%</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6.83%</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>46.38</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8056</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>動力電池材料42.58%、特用化學材料20.60%、氧化觸媒17.66%、化肥10.09%、其他9.07% (2024年)</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2555,32 +2555,32 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>70.6</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>46.52</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 石化及塑橡膠 - 接著劑(合成樹脂)、PTA(對苯二甲酸)觸媒** 紡織 - 化學助劑** 電動車輛產業 - 鋰電池材料** 能源元件 - 原材料</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1558.105</t>
+          <t>2598.844</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>67.1</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,27 +2627,27 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-3.09</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>24.49</t>
+          <t>46.05</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2682,7 +2682,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>23.45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,12 +2733,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1542</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2748,62 +2748,62 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>94.25</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>5.80</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>5.49</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>64.66</t>
+          <t>66.16</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>65.52</t>
+          <t>65.64</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>65.47</t>
+          <t>65.73</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>62.1</t>
+          <t>62.31</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>122.79</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-113.47</t>
+          <t>-110.31</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,45 +2823,45 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>75217998.52890173</t>
+          <t>75339280.78787878</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>105849223.0</t>
+          <t>182793426.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>54169279.2</t>
+          <t>85235906.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>43512116.9</t>
+          <t>58360010.8</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>113935358.54</t>
+          <t>117218867.38</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>10657162</t>
+          <t>26875895</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-15052172.97708171</t>
+          <t>-12125711.94501511</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-6112930.21</v>
+        <v>3969823.73</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>41.86</t>
+          <t>47.99</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,77 +2901,77 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-12.015112320512</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>97.95053699871907</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>39.23959558994965</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14.92</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>95.63</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12.28%</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6.83%</t>
         </is>
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>46.38</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8056</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>動力電池材料42.58%、特用化學材料20.60%、氧化觸媒17.66%、化肥10.09%、其他9.07% (2024年)</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,32 +2986,32 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>67.1</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>46.52</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 石化及塑橡膠 - 接著劑(合成樹脂)、PTA(對苯二甲酸)觸媒** 紡織 - 化學助劑** 電動車輛產業 - 鋰電池材料** 能源元件 - 原材料</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1161.669</t>
+          <t>1558.105</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>65.4</t>
+          <t>67.1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>11.47</t>
+          <t>24.49</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>14.06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.60</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3164,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1542</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3179,57 +3179,57 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>70.01</t>
+          <t>94.25</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>5.35</t>
+          <t>5.42</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>63.86000000000001</t>
+          <t>64.66</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>65.67</t>
+          <t>65.52</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>65.26</t>
+          <t>65.47</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>61.95</t>
+          <t>62.1</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-65.80</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>75217998.52890173</t>
+          <t>75339280.78787878</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>76790846.0</t>
+          <t>105849223.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>40176137.2</t>
+          <t>54169279.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>36041288.8</t>
+          <t>43512116.9</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>112225732.82</t>
+          <t>113935358.54</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>4134848</t>
+          <t>10657162</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-16677489.84361878</t>
+          <t>-15052172.97708171</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-12054523.73</v>
+        <v>-6112930.21</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>38.27</t>
+          <t>41.86</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,22 +3332,22 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-12.015112320512</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>97.95053699871907</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>39.23959558994965</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
@@ -3357,52 +3357,52 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14.92</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>95.63</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12.28%</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6.83%</t>
         </is>
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>46.38</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8056</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>動力電池材料42.58%、特用化學材料20.60%、氧化觸媒17.66%、化肥10.09%、其他9.07% (2024年)</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3417,32 +3417,32 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>65.1</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>67.4</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>65.1</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>65.4</t>
+          <t>67.1</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>46.52</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 石化及塑橡膠 - 接著劑(合成樹脂)、PTA(對苯二甲酸)觸媒** 紡織 - 化學助劑** 電動車輛產業 - 鋰電池材料** 能源元件 - 原材料</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>562.661</t>
+          <t>1161.669</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>64.9</t>
+          <t>65.4</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>11.47</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3519,7 +3519,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>10.48</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>-2.60</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1542</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>82.76</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>36.68</t>
+          <t>70.01</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-3.82</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>5.35</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>63.5</t>
+          <t>63.86000000000001</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>66.03</t>
+          <t>65.67</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>65.08</t>
+          <t>65.26</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>61.76</t>
+          <t>61.95</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-137.89</t>
+          <t>-65.80</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-111.26</t>
+          <t>-113.47</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>75217998.52890173</t>
+          <t>75339280.78787878</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>36274209.0</t>
+          <t>76790846.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>31522597.6</t>
+          <t>40176137.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>31905787.9</t>
+          <t>36041288.8</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>111064675.6</t>
+          <t>112225732.82</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-383190</t>
+          <t>4134848</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-17518029.13726628</t>
+          <t>-16677489.84361878</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-16998598.23</v>
+        <v>-12054523.73</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>37.21</t>
+          <t>38.27</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,77 +3763,77 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-12.015112320512</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>97.95053699871907</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>39.23959558994965</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14.92</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>95.63</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12.28%</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6.83%</t>
         </is>
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>46.38</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8056</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>動力電池材料42.58%、特用化學材料20.60%、氧化觸媒17.66%、化肥10.09%、其他9.07% (2024年)</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3848,32 +3848,32 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>63.4</t>
+          <t>65.1</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
+          <t>67.4</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
+          <t>65.1</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
           <t>65.4</t>
         </is>
       </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>63.4</t>
-        </is>
-      </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>64.9</t>
-        </is>
-      </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>46.52</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 石化及塑橡膠 - 接著劑(合成樹脂)、PTA(對苯二甲酸)觸媒** 紡織 - 化學助劑** 電動車輛產業 - 鋰電池材料** 能源元件 - 原材料</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>386.127</t>
+          <t>562.661</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>63.4</t>
+          <t>64.9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.42</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1542</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>82.76</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>36.68</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-4.48</t>
+          <t>-3.82</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>63.34000000000001</t>
+          <t>63.5</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>66.31</t>
+          <t>66.03</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>64.92</t>
+          <t>65.08</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>61.58</t>
+          <t>61.76</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-308.50</t>
+          <t>-137.89</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-107.38</t>
+          <t>-111.26</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>75217998.52890173</t>
+          <t>75339280.78787878</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>24471827.0</t>
+          <t>36274209.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>30117424.6</t>
+          <t>31522597.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>31140083.6</t>
+          <t>31905787.9</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>110844509.38</t>
+          <t>111064675.6</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-1022659</t>
+          <t>-383190</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-17612471.12087157</t>
+          <t>-17518029.13726628</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-19113400.75</v>
+        <v>-16998598.23</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>34.04</t>
+          <t>37.21</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,27 +4194,27 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-12.015112320512</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>97.95053699871907</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>39.23959558994965</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4224,47 +4224,47 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14.92</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>95.63</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12.28%</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6.83%</t>
         </is>
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>46.38</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8056</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>動力電池材料42.58%、特用化學材料20.60%、氧化觸媒17.66%、化肥10.09%、其他9.07% (2024年)</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4279,32 +4279,32 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>63.4</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>63.9</t>
+          <t>65.4</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>63.4</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>63.4</t>
+          <t>64.9</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>46.52</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 石化及塑橡膠 - 接著劑(合成樹脂)、PTA(對苯二甲酸)觸媒** 紡織 - 化學助劑** 電動車輛產業 - 鋰電池材料** 能源元件 - 原材料</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>440.993</t>
+          <t>386.127</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>63.4</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6.63</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-10.57</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,37 +4457,37 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1542</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.09</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-4.79</t>
+          <t>-4.48</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -4497,37 +4497,37 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>63.42</t>
+          <t>63.34000000000001</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>66.61</t>
+          <t>66.31</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>64.77</t>
+          <t>64.92</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>61.43</t>
+          <t>61.58</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-1571.66</t>
+          <t>-308.50</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-101.69</t>
+          <t>-107.38</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>75217998.52890173</t>
+          <t>75339280.78787878</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>27460291.0</t>
+          <t>24471827.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>31484115.4</t>
+          <t>30117424.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>35203368.5</t>
+          <t>31140083.6</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>110885096.24</t>
+          <t>110844509.38</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-3719253</t>
+          <t>-1022659</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-17339574.82404308</t>
+          <t>-17612471.12087157</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-20187384.84</v>
+        <v>-19113400.75</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>32.14</t>
+          <t>34.04</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,77 +4625,77 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-12.015112320512</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>97.95053699871907</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>39.23959558994965</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14.92</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>95.63</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12.28%</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6.83%</t>
         </is>
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>46.38</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8056</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>動力電池材料42.58%、特用化學材料20.60%、氧化觸媒17.66%、化肥10.09%、其他9.07% (2024年)</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4710,32 +4710,32 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>63.9</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>61.6</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>63.4</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>46.52</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 石化及塑橡膠 - 接著劑(合成樹脂)、PTA(對苯二甲酸)觸媒** 紡織 - 化學助劑** 電動車輛產業 - 鋰電池材料** 能源元件 - 原材料</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>559.37</t>
+          <t>440.993</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>63.1</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7.95</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-20.46</t>
+          <t>-10.57</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,12 +4888,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1542</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4903,62 +4903,62 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-4.44</t>
+          <t>-4.79</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>5.42</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>64.00000000000001</t>
+          <t>63.42</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>66.97</t>
+          <t>66.61</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>64.65</t>
+          <t>64.77</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>61.29</t>
+          <t>61.43</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-542.60</t>
+          <t>-1571.66</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-95.06</t>
+          <t>-101.69</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>75217998.52890173</t>
+          <t>75339280.78787878</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>35883513.0</t>
+          <t>27460291.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>32854954.6</t>
+          <t>31484115.4</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>41305635.5</t>
+          <t>35203368.5</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>110944182.58</t>
+          <t>110885096.24</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-8450680</t>
+          <t>-3719253</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-16821791.18567295</t>
+          <t>-17339574.82404308</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-21320862.35</v>
+        <v>-20187384.84</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>33.40</t>
+          <t>32.14</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,27 +5056,27 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-12.015112320512</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>97.95053699871907</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>39.23959558994965</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,47 +5086,47 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14.92</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>95.63</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12.28%</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6.83%</t>
         </is>
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>46.38</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8056</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>動力電池材料42.58%、特用化學材料20.60%、氧化觸媒17.66%、化肥10.09%、其他9.07% (2024年)</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5141,32 +5141,32 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>63.7</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>65.3</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>63.1</t>
+          <t>61.6</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>63.1</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>46.52</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 石化及塑橡膠 - 接著劑(合成樹脂)、PTA(對苯二甲酸)觸媒** 紡織 - 化學助劑** 電動車輛產業 - 鋰電池材料** 能源元件 - 原材料</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
@@ -5193,7 +5193,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>528.649</t>
+          <t>559.37</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>63.6</t>
+          <t>63.1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7.07</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-24.06</t>
+          <t>-20.46</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>5.05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-3.49</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,12 +5319,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1542</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5339,57 +5339,57 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>-4.44</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>5.53</t>
+          <t>5.48</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>64.42</t>
+          <t>64.00000000000001</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>67.26</t>
+          <t>66.97</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>64.51</t>
+          <t>64.65</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>61.13</t>
+          <t>61.29</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-235.52</t>
+          <t>-542.60</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-88.35</t>
+          <t>-95.06</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>75217998.52890173</t>
+          <t>75339280.78787878</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>33523148.0</t>
+          <t>35883513.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>31906440.4</t>
+          <t>32854954.6</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>42016145.3</t>
+          <t>41305635.5</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>111603019.84</t>
+          <t>110944182.58</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-10109704</t>
+          <t>-8450680</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-16003778.24661902</t>
+          <t>-16821791.18567295</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-23081144.65</v>
+        <v>-21320862.35</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>34.46</t>
+          <t>33.40</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,27 +5487,27 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-12.015112320512</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>97.95053699871907</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>39.23959558994965</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,47 +5517,47 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14.92</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>95.63</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12.28%</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6.83%</t>
         </is>
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>46.38</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8056</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>動力電池材料42.58%、特用化學材料20.60%、氧化觸媒17.66%、化肥10.09%、其他9.07% (2024年)</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>63.7</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>65.3</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>63.1</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>63.6</t>
+          <t>63.1</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>46.52</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 石化及塑橡膠 - 接著劑(合成樹脂)、PTA(對苯二甲酸)觸媒** 紡織 - 化學助劑** 電動車輛產業 - 鋰電池材料** 能源元件 - 原材料</t>
         </is>
       </c>
       <c r="CI12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>4870.0</t>
+          <t>3352.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,72 +5634,72 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>57.4</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>-1.6</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>-15.27</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>2025-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
           <t>58.1</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>0.18</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>22.85</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>2025-10-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>58.1</t>
-        </is>
-      </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
@@ -5714,12 +5714,12 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>8.40</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,77 +5750,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>42</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>4870</t>
+          <t>3352</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>40.68</t>
+          <t>10.64</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>55.37</t>
+          <t>35.75</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>59.73999999999999</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>59.51</t>
+          <t>59.24</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>60.1</t>
+          <t>60.11</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>57.55</t>
+          <t>57.62</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-24.96</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-107.25</t>
+          <t>-107.74</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,45 +5840,45 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>819526.3304347827</t>
+          <t>818763.0455861071</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>283328.0</t>
+          <t>194731.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>437969.2</t>
+          <t>289419.6</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>356514.8</t>
+          <t>341561.2</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>570563.3</t>
+          <t>568481.84</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>81454</t>
+          <t>-52141</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-36824.00107548192</t>
+          <t>-35875.73082668789</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>-22149.96</v>
+        <v>-30660.24</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BM13" t="inlineStr">
@@ -5938,7 +5938,7 @@
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
@@ -5948,12 +5948,12 @@
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>34629</t>
+          <t>34212</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>57.2</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,127 +6050,127 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>-1.51</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>4870.0</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-1.22</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>-1.6</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>22.85</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2025-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>-1.53</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>-4.07</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>8.40</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
           <t>-1.35</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>4060.0</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>-1.55</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>0.18</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>36.21</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>2025-10-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>58.1</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>59.6</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>61.5</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>-4.07</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>7.01</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>-1.86</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,77 +6181,77 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>42</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>4870</t>
+          <t>3352</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>55.93</t>
+          <t>40.68</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>67.23</t>
+          <t>55.37</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>60.12</t>
+          <t>59.73999999999999</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>59.74</t>
+          <t>59.51</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>60.09</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>57.46</t>
+          <t>57.55</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>14.66</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-107.17</t>
+          <t>-107.25</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,41 +6271,41 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>819526.3304347827</t>
+          <t>818763.0455861071</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>242218.0</t>
+          <t>283328.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>465573.8</t>
+          <t>437969.2</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>341803.5</t>
+          <t>356514.8</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>579417.88</t>
+          <t>570563.3</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>123770</t>
+          <t>81454</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-39492.00850249613</t>
+          <t>-36824.00107548192</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>-18693.88</v>
+        <v>-22149.96</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BM14" t="inlineStr">
@@ -6369,22 +6369,22 @@
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>34629</t>
+          <t>34212</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>59.3</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>60.6</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3505.0</t>
+          <t>4060.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,22 +6506,22 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>36.21</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -6561,7 +6561,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,77 +6612,77 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>42</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>4870</t>
+          <t>3352</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>69.49</t>
+          <t>55.93</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>81.92</t>
+          <t>67.23</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>59.72000000000001</t>
+          <t>60.12</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>59.98</t>
+          <t>59.74</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>60.1</t>
+          <t>60.09</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>57.38</t>
+          <t>57.46</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>20.51</t>
+          <t>14.66</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-107.44</t>
+          <t>-107.17</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,45 +6702,45 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>819526.3304347827</t>
+          <t>818763.0455861071</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>209656.0</t>
+          <t>242218.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>452042.6</t>
+          <t>465573.8</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>332281.8</t>
+          <t>341803.5</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>596784.86</t>
+          <t>579417.88</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>119760</t>
+          <t>123770</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-43273.48695184787</t>
+          <t>-39492.00850249613</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>-8684.33</v>
+        <v>-18693.88</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BM15" t="inlineStr">
@@ -6800,22 +6800,22 @@
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>34629</t>
+          <t>34212</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>60.1</t>
+          <t>59.3</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8540.0</t>
+          <t>3505.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>60.2</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>30.92</t>
+          <t>36.04</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14.74</t>
+          <t>6.05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,77 +7043,77 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>42</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>4870</t>
+          <t>3352</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>76.27</t>
+          <t>69.49</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>91.33</t>
+          <t>81.92</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>59.14</t>
+          <t>59.72000000000001</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>60.09</t>
+          <t>59.98</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>60.08</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>57.31</t>
+          <t>57.38</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>9.30</t>
+          <t>20.51</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-107.82</t>
+          <t>-107.44</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,41 +7133,41 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>819526.3304347827</t>
+          <t>818763.0455861071</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>517165.0</t>
+          <t>209656.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>445047.0</t>
+          <t>452042.6</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>339942.5</t>
+          <t>332281.8</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>643736.64</t>
+          <t>596784.86</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>105104</t>
+          <t>119760</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-49562.42385215155</t>
+          <t>-43273.48695184787</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>9413.950000000001</v>
+        <v>-8684.33</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BM16" t="inlineStr">
@@ -7231,22 +7231,22 @@
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>34629</t>
+          <t>34212</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>61.7</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>61.8</t>
+          <t>60.4</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>59.6</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>60.2</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>15157.0</t>
+          <t>8540.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.6</t>
+          <t>60.2</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-6.02</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>29.74</t>
+          <t>30.92</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>14.74</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,47 +7474,47 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>42</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>4870</t>
+          <t>3352</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>76.27</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>75.54</t>
+          <t>91.33</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>5.77</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>58.24000000000001</t>
+          <t>59.14</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -7529,22 +7529,22 @@
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>57.24</t>
+          <t>57.31</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-15.74</t>
+          <t>9.30</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-108.00</t>
+          <t>-107.82</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>819526.3304347827</t>
+          <t>818763.0455861071</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>937479.0</t>
+          <t>517165.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>393702.8</t>
+          <t>445047.0</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>303455.3</t>
+          <t>339942.5</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>659423.84</t>
+          <t>643736.64</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>90247</t>
+          <t>105104</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-60285.40158650742</t>
+          <t>-49562.42385215155</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>1985.04</v>
+        <v>9413.950000000001</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7642,7 +7642,7 @@
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BM17" t="inlineStr">
@@ -7662,7 +7662,7 @@
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
@@ -7672,12 +7672,12 @@
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>34629</t>
+          <t>34212</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>60.5</t>
+          <t>61.7</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>63.2</t>
+          <t>61.8</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>59.6</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>61.6</t>
+          <t>60.2</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>7091.0</t>
+          <t>15157.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>61.6</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-7.32</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>17.44</t>
+          <t>29.74</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12.24</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,77 +7905,77 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>42</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>4870</t>
+          <t>3352</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>97.73</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>50.21</t>
+          <t>75.54</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>5.77</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-3.09</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>57.26000000000001</t>
+          <t>58.24000000000001</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>60.13</t>
+          <t>60.09</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>59.94</t>
+          <t>60.08</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>57.24</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-89.66</t>
+          <t>-15.74</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-107.68</t>
+          <t>-108.00</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>819526.3304347827</t>
+          <t>818763.0455861071</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>421351.0</t>
+          <t>937479.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>275060.4</t>
+          <t>393702.8</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>234213.9</t>
+          <t>303455.3</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>643815.04</t>
+          <t>659423.84</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>40846</t>
+          <t>90247</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-71607.30094654183</t>
+          <t>-60285.40158650742</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>-53732.22</v>
+        <v>1985.04</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BM18" t="inlineStr">
@@ -8093,22 +8093,22 @@
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>34629</t>
+          <t>34212</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>60.5</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>60.2</t>
+          <t>63.2</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>61.6</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>3057.0</t>
+          <t>7091.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>17.44</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>12.24</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,77 +8336,77 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>42</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>4870</t>
+          <t>3352</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>97.73</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>17.63</t>
+          <t>50.21</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-5.40</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>57.04</t>
+          <t>57.26000000000001</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>60.3</t>
+          <t>60.13</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>59.83</t>
+          <t>59.94</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>57.06</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-203.28</t>
+          <t>-89.66</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-105.96</t>
+          <t>-107.68</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>819526.3304347827</t>
+          <t>818763.0455861071</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>174562.0</t>
+          <t>421351.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>218033.2</t>
+          <t>275060.4</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>218350.5</t>
+          <t>234213.9</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>642009.16</t>
+          <t>643815.04</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-317</t>
+          <t>40846</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-74857.31579659131</t>
+          <t>-71607.30094654183</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>-76109.87</v>
+        <v>-53732.22</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BM19" t="inlineStr">
@@ -8524,22 +8524,22 @@
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>34629</t>
+          <t>34212</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>57.7</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
+          <t>60.2</t>
+        </is>
+      </c>
+      <c r="CE19" t="inlineStr">
+        <is>
           <t>57.7</t>
         </is>
       </c>
-      <c r="CE19" t="inlineStr">
-        <is>
-          <t>56.4</t>
-        </is>
-      </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3065.0</t>
+          <t>3057.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>56.9</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-6.63</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,275 +8767,275 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>42</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>4870</t>
+          <t>3352</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>17.63</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-5.09</t>
+          <t>-5.40</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>57.04</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>60.58</t>
+          <t>60.3</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>59.76</t>
+          <t>59.83</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
+          <t>57.06</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>-203.28</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>-0.96</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>-0.32</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>5.31</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr">
+        <is>
+          <t>-105.96</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>818763.0455861071</t>
+        </is>
+      </c>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>174562.0</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>218033.2</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>218350.5</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>642009.16</t>
+        </is>
+      </c>
+      <c r="BA20" t="inlineStr">
+        <is>
+          <t>-317</t>
+        </is>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>-74857.31579659131</t>
+        </is>
+      </c>
+      <c r="BC20" t="n">
+        <v>-76109.87</v>
+      </c>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE20" t="inlineStr">
+        <is>
+          <t>58.9</t>
+        </is>
+      </c>
+      <c r="BF20" t="inlineStr">
+        <is>
+          <t>2025/08/29</t>
+        </is>
+      </c>
+      <c r="BG20" t="inlineStr">
+        <is>
+          <t>-3.23</t>
+        </is>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>光洋科</t>
+        </is>
+      </c>
+      <c r="BI20" t="inlineStr">
+        <is>
+          <t>光洋科</t>
+        </is>
+      </c>
+      <c r="BJ20" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BK20" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL20" t="inlineStr">
+        <is>
+          <t>1.11</t>
+        </is>
+      </c>
+      <c r="BM20" t="inlineStr">
+        <is>
+          <t>-1.228328584465341</t>
+        </is>
+      </c>
+      <c r="BN20" t="inlineStr">
+        <is>
+          <t>47.44460114587924</t>
+        </is>
+      </c>
+      <c r="BO20" t="inlineStr">
+        <is>
+          <t>32.54445648609581</t>
+        </is>
+      </c>
+      <c r="BP20" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+        </is>
+      </c>
+      <c r="BQ20" t="inlineStr">
+        <is>
+          <t>價漲量-</t>
+        </is>
+      </c>
+      <c r="BR20" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="BS20" t="inlineStr">
+        <is>
+          <t>3.48</t>
+        </is>
+      </c>
+      <c r="BT20" t="inlineStr">
+        <is>
+          <t>17.51</t>
+        </is>
+      </c>
+      <c r="BU20" t="inlineStr">
+        <is>
+          <t>24.43</t>
+        </is>
+      </c>
+      <c r="BV20" t="inlineStr">
+        <is>
+          <t>14.09%</t>
+        </is>
+      </c>
+      <c r="BW20" t="inlineStr">
+        <is>
+          <t>9.19%</t>
+        </is>
+      </c>
+      <c r="BX20" t="inlineStr">
+        <is>
+          <t>42.34</t>
+        </is>
+      </c>
+      <c r="BY20" t="inlineStr">
+        <is>
+          <t>34212</t>
+        </is>
+      </c>
+      <c r="BZ20" t="inlineStr">
+        <is>
+          <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA20" t="inlineStr">
+        <is>
+          <t>光洋科-其他電子業-上櫃</t>
+        </is>
+      </c>
+      <c r="CB20" t="inlineStr">
+        <is>
+          <t>其他電子業右上上櫃</t>
+        </is>
+      </c>
+      <c r="CC20" t="inlineStr">
+        <is>
+          <t>56.6</t>
+        </is>
+      </c>
+      <c r="CD20" t="inlineStr">
+        <is>
+          <t>57.7</t>
+        </is>
+      </c>
+      <c r="CE20" t="inlineStr">
+        <is>
+          <t>56.4</t>
+        </is>
+      </c>
+      <c r="CF20" t="inlineStr">
+        <is>
           <t>57.0</t>
-        </is>
-      </c>
-      <c r="AP20" t="inlineStr">
-        <is>
-          <t>-464.25</t>
-        </is>
-      </c>
-      <c r="AQ20" t="inlineStr">
-        <is>
-          <t>-0.88</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>-0.16</t>
-        </is>
-      </c>
-      <c r="AS20" t="inlineStr">
-        <is>
-          <t>5.31</t>
-        </is>
-      </c>
-      <c r="AT20" t="inlineStr">
-        <is>
-          <t>-102.93</t>
-        </is>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV20" t="inlineStr">
-        <is>
-          <t>819526.3304347827</t>
-        </is>
-      </c>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>174678.0</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>212521.0</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>227616.4</t>
-        </is>
-      </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>643094.8</t>
-        </is>
-      </c>
-      <c r="BA20" t="inlineStr">
-        <is>
-          <t>-15095</t>
-        </is>
-      </c>
-      <c r="BB20" t="inlineStr">
-        <is>
-          <t>-74629.57784452781</t>
-        </is>
-      </c>
-      <c r="BC20" t="n">
-        <v>-78918.07000000001</v>
-      </c>
-      <c r="BD20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE20" t="inlineStr">
-        <is>
-          <t>58.9</t>
-        </is>
-      </c>
-      <c r="BF20" t="inlineStr">
-        <is>
-          <t>2025/08/29</t>
-        </is>
-      </c>
-      <c r="BG20" t="inlineStr">
-        <is>
-          <t>-3.40</t>
-        </is>
-      </c>
-      <c r="BH20" t="inlineStr">
-        <is>
-          <t>光洋科</t>
-        </is>
-      </c>
-      <c r="BI20" t="inlineStr">
-        <is>
-          <t>光洋科</t>
-        </is>
-      </c>
-      <c r="BJ20" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BK20" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL20" t="inlineStr">
-        <is>
-          <t>1.12</t>
-        </is>
-      </c>
-      <c r="BM20" t="inlineStr">
-        <is>
-          <t>-1.228328584465341</t>
-        </is>
-      </c>
-      <c r="BN20" t="inlineStr">
-        <is>
-          <t>47.44460114587924</t>
-        </is>
-      </c>
-      <c r="BO20" t="inlineStr">
-        <is>
-          <t>32.54445648609581</t>
-        </is>
-      </c>
-      <c r="BP20" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ20" t="inlineStr">
-        <is>
-          <t>價漲量-</t>
-        </is>
-      </c>
-      <c r="BR20" t="inlineStr">
-        <is>
-          <t>2.48</t>
-        </is>
-      </c>
-      <c r="BS20" t="inlineStr">
-        <is>
-          <t>3.44</t>
-        </is>
-      </c>
-      <c r="BT20" t="inlineStr">
-        <is>
-          <t>17.51</t>
-        </is>
-      </c>
-      <c r="BU20" t="inlineStr">
-        <is>
-          <t>24.72</t>
-        </is>
-      </c>
-      <c r="BV20" t="inlineStr">
-        <is>
-          <t>14.09%</t>
-        </is>
-      </c>
-      <c r="BW20" t="inlineStr">
-        <is>
-          <t>9.19%</t>
-        </is>
-      </c>
-      <c r="BX20" t="inlineStr">
-        <is>
-          <t>43.93</t>
-        </is>
-      </c>
-      <c r="BY20" t="inlineStr">
-        <is>
-          <t>34629</t>
-        </is>
-      </c>
-      <c r="BZ20" t="inlineStr">
-        <is>
-          <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA20" t="inlineStr">
-        <is>
-          <t>光洋科-其他電子業-上櫃</t>
-        </is>
-      </c>
-      <c r="CB20" t="inlineStr">
-        <is>
-          <t>其他電子業右上上櫃</t>
-        </is>
-      </c>
-      <c r="CC20" t="inlineStr">
-        <is>
-          <t>56.7</t>
-        </is>
-      </c>
-      <c r="CD20" t="inlineStr">
-        <is>
-          <t>57.8</t>
-        </is>
-      </c>
-      <c r="CE20" t="inlineStr">
-        <is>
-          <t>56.5</t>
-        </is>
-      </c>
-      <c r="CF20" t="inlineStr">
-        <is>
-          <t>56.9</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>4712.0</t>
+          <t>3065.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-6.63</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-4.13</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>8.13</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,77 +9198,77 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>42</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>4870</t>
+          <t>3352</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-3.80</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-4.89</t>
+          <t>-5.09</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>57.9</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>60.88</t>
+          <t>60.58</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>59.67</t>
+          <t>59.76</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>56.96</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-3104.58</t>
+          <t>-464.25</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-99.53</t>
+          <t>-102.93</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>819526.3304347827</t>
+          <t>818763.0455861071</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>260444.0</t>
+          <t>174678.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>234838.0</t>
+          <t>212521.0</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>255984.1</t>
+          <t>227616.4</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>641889.36</t>
+          <t>643094.8</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-21146</t>
+          <t>-15095</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-73849.85288862225</t>
+          <t>-74629.57784452781</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>-80123.69</v>
+        <v>-78918.07000000001</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-5.43</t>
+          <t>-3.40</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BM21" t="inlineStr">
@@ -9386,22 +9386,22 @@
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>34629</t>
+          <t>34212</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>56.7</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>5987.0</t>
+          <t>4712.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>56.7</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-19.62</t>
+          <t>-8.26</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-4.13</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10.33</t>
+          <t>8.13</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-3.70</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,12 +9629,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>42</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>4870</t>
+          <t>3352</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9644,62 +9644,62 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>-3.80</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-4.89</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>58.77999999999999</t>
+          <t>57.9</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>61.17</t>
+          <t>60.88</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>59.62</t>
+          <t>59.67</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>56.92</t>
+          <t>56.96</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-308.20</t>
+          <t>-3104.58</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-95.87</t>
+          <t>-99.53</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>819526.3304347827</t>
+          <t>818763.0455861071</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>344267.0</t>
+          <t>260444.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>213207.8</t>
+          <t>234838.0</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>265240.8</t>
+          <t>255984.1</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>639604.54</t>
+          <t>641889.36</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-52033</t>
+          <t>-21146</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-72709.154839041</t>
+          <t>-73849.85288862225</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-88173.67</v>
+        <v>-80123.69</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-3.74</t>
+          <t>-5.43</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9797,7 +9797,7 @@
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BM22" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9827,12 +9827,12 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>34629</t>
+          <t>34212</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>59.1</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>56.7</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2301.0</t>
+          <t>5987.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>56.7</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-29.06</t>
+          <t>-19.62</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>10.33</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-3.70</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,12 +10060,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>42</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>4870</t>
+          <t>3352</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10080,57 +10080,57 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>59.48</t>
+          <t>58.77999999999999</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>61.43</t>
+          <t>61.17</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>59.55</t>
+          <t>59.62</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>56.88</t>
+          <t>56.92</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-144.98</t>
+          <t>-308.20</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-92.69</t>
+          <t>-95.87</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>819526.3304347827</t>
+          <t>818763.0455861071</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>136215.0</t>
+          <t>344267.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>193367.4</t>
+          <t>213207.8</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>272587.5</t>
+          <t>265240.8</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>637064.6</t>
+          <t>639604.54</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-79220</t>
+          <t>-52033</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-69897.42474011309</t>
+          <t>-72709.154839041</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-105505.62</v>
+        <v>-88173.67</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-3.74</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BM23" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>34629</t>
+          <t>34212</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>59.7</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>59.9</t>
+          <t>59.1</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>58.7</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>56.7</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料).xlsx
+++ b/Result/checksun_type/濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料).xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1542.065</t>
+          <t>735.417</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>67.9</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>41.98</t>
+          <t>10.77</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>-3.00</t>
+          <t>-5.71</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13.91</t>
+          <t>6.63</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1542</t>
+          <t>735</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>49.45</t>
+          <t>14.47</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>76.15</t>
+          <t>49.64</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-5.53</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>5.70</t>
+          <t>5.80</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>70.66</t>
+          <t>69.86000000000001</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>66.3</t>
+          <t>66.24</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>66.75</t>
+          <t>66.9</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>63.15</t>
+          <t>63.24</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>125.60</t>
+          <t>50.55</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-82.57</t>
+          <t>-80.05</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,45 +1099,45 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>75339280.78787878</t>
+          <t>75336741.62896253</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>106177736.0</t>
+          <t>49051403.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>132561832.2</t>
+          <t>105813427.6</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>93365555.7</t>
+          <t>95524666.9</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>120263879.18</t>
+          <t>120066640.9</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>39196276</t>
+          <t>10288760</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-2157550.973595275</t>
+          <t>-1542288.227029385</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>6559213.96</v>
+        <v>1841656.88</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>39.53</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1197,22 +1197,22 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>95.63</t>
+          <t>92.96</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>46.38</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>8056</t>
+          <t>7831</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>67.9</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1168.47</t>
+          <t>1542.065</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>67.9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-4.57</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>53.47</t>
+          <t>41.98</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>-3.00</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10.54</t>
+          <t>13.91</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1440,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1542</t>
+          <t>735</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>49.45</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>76.15</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>6.43</t>
+          <t>6.58</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>5.70</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>70.66</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>66.24</t>
+          <t>66.3</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>66.75</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>63.02</t>
+          <t>63.15</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>262.06</t>
+          <t>125.60</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-88.05</t>
+          <t>-82.57</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,45 +1530,45 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>75339280.78787878</t>
+          <t>75336741.62896253</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>82950382.0</t>
+          <t>106177736.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>132496129.6</t>
+          <t>132561832.2</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>86336133.4</t>
+          <t>93365555.7</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>120394266.18</t>
+          <t>120263879.18</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>46159996</t>
+          <t>39196276</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-3742417.326026477</t>
+          <t>-2157550.973595275</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>6943645.05</v>
+        <v>6559213.96</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>50.11</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1633,17 +1633,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>95.63</t>
+          <t>92.96</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>46.38</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>8056</t>
+          <t>7831</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>67.9</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1393.968</t>
+          <t>1168.47</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-5.89</t>
+          <t>-7.58</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>61.27</t>
+          <t>53.47</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12.58</t>
+          <t>10.54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,77 +1871,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1542</t>
+          <t>735</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>6.43</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>69.38</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>66.06</t>
+          <t>66.24</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>66.34</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>62.79</t>
+          <t>63.02</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>768.32</t>
+          <t>262.06</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-95.88</t>
+          <t>-88.05</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,45 +1961,45 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>75339280.78787878</t>
+          <t>75336741.62896253</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>100281347.0</t>
+          <t>82950382.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>131264222.4</t>
+          <t>132496129.6</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>81393410.0</t>
+          <t>86336133.4</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>119695734.58</t>
+          <t>120394266.18</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>49870812</t>
+          <t>46159996</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-5685337.758529304</t>
+          <t>-3742417.326026477</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>9733490.07</v>
+        <v>6943645.05</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>52.01</t>
+          <t>50.11</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2064,17 +2064,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>95.63</t>
+          <t>92.96</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>46.38</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>8056</t>
+          <t>7831</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2657.246</t>
+          <t>1393.968</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-6.77</t>
+          <t>-8.94</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>59.46</t>
+          <t>61.27</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>23.97</t>
+          <t>12.58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,77 +2302,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1542</t>
+          <t>735</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>6.65</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>5.60</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>67.98</t>
+          <t>69.38</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>65.84</t>
+          <t>66.06</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>66.06</t>
+          <t>66.34</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>62.56</t>
+          <t>62.79</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>686.39</t>
+          <t>768.32</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-103.80</t>
+          <t>-95.88</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,45 +2392,45 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>75339280.78787878</t>
+          <t>75336741.62896253</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>190606270.0</t>
+          <t>100281347.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>118462794.8</t>
+          <t>131264222.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>74290109.7</t>
+          <t>81393410.0</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>120126016.38</t>
+          <t>119695734.58</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>44172685</t>
+          <t>49870812</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-8488760.999966215</t>
+          <t>-5685337.758529304</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>11514469.2</v>
+        <v>9733490.07</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>53.28</t>
+          <t>52.01</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2490,22 +2490,22 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>95.63</t>
+          <t>92.96</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>46.38</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>8056</t>
+          <t>7831</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
+          <t>71.2</t>
+        </is>
+      </c>
+      <c r="CD5" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
           <t>70.6</t>
         </is>
       </c>
-      <c r="CD5" t="inlineStr">
-        <is>
-          <t>72.8</t>
-        </is>
-      </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>69.7</t>
-        </is>
-      </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2598.844</t>
+          <t>2657.246</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,74 +2617,74 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>72.5</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-9.85</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.96</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>59.46</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2025-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-11-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2025-09-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>70.0</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>-3.09</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1.87</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>46.05</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2025-11-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2025-11-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-09-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>70.0</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
       <c r="T6" t="inlineStr">
         <is>
           <t>67.8</t>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>23.45</t>
+          <t>23.97</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,12 +2733,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1542</t>
+          <t>735</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2753,57 +2753,57 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>5.80</t>
+          <t>6.65</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>5.60</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>66.16</t>
+          <t>67.98</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>65.64</t>
+          <t>65.84</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>65.73</t>
+          <t>66.06</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>62.31</t>
+          <t>62.56</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>122.79</t>
+          <t>686.39</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-110.31</t>
+          <t>-103.80</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,45 +2823,45 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>75339280.78787878</t>
+          <t>75336741.62896253</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>182793426.0</t>
+          <t>190606270.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>85235906.2</t>
+          <t>118462794.8</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>58360010.8</t>
+          <t>74290109.7</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>117218867.38</t>
+          <t>120126016.38</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>26875895</t>
+          <t>44172685</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-12125711.94501511</t>
+          <t>-8488760.999966215</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>3969823.73</v>
+        <v>11514469.2</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>47.99</t>
+          <t>53.28</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2926,17 +2926,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>95.63</t>
+          <t>92.96</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>46.38</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>8056</t>
+          <t>7831</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>70.6</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1558.105</t>
+          <t>2598.844</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>67.1</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,22 +3058,22 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>-6.06</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>24.49</t>
+          <t>46.05</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -3128,7 +3128,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14.06</t>
+          <t>23.45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3164,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1542</t>
+          <t>735</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3179,62 +3179,62 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>94.25</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>5.80</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>5.49</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>64.66</t>
+          <t>66.16</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>65.52</t>
+          <t>65.64</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>65.47</t>
+          <t>65.73</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>62.1</t>
+          <t>62.31</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>122.79</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-113.47</t>
+          <t>-110.31</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,45 +3254,45 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>75339280.78787878</t>
+          <t>75336741.62896253</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>105849223.0</t>
+          <t>182793426.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>54169279.2</t>
+          <t>85235906.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>43512116.9</t>
+          <t>58360010.8</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>113935358.54</t>
+          <t>117218867.38</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>10657162</t>
+          <t>26875895</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-15052172.97708171</t>
+          <t>-12125711.94501511</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-6112930.21</v>
+        <v>3969823.73</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>41.86</t>
+          <t>47.99</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3362,14 +3362,14 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
           <t>1.44</t>
         </is>
       </c>
-      <c r="BS7" t="inlineStr">
-        <is>
-          <t>1.4</t>
-        </is>
-      </c>
       <c r="BT7" t="inlineStr">
         <is>
           <t>14.92</t>
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>95.63</t>
+          <t>92.96</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>46.38</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>8056</t>
+          <t>7831</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>67.1</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1161.669</t>
+          <t>1558.105</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>65.4</t>
+          <t>67.1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>11.47</t>
+          <t>24.49</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3519,7 +3519,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10.48</t>
+          <t>14.06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.60</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,12 +3595,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1542</t>
+          <t>735</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3610,57 +3610,57 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>70.01</t>
+          <t>94.25</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>5.35</t>
+          <t>5.42</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>63.86000000000001</t>
+          <t>64.66</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>65.67</t>
+          <t>65.52</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>65.26</t>
+          <t>65.47</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>61.95</t>
+          <t>62.1</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-65.80</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>75339280.78787878</t>
+          <t>75336741.62896253</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>76790846.0</t>
+          <t>105849223.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>40176137.2</t>
+          <t>54169279.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>36041288.8</t>
+          <t>43512116.9</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>112225732.82</t>
+          <t>113935358.54</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>4134848</t>
+          <t>10657162</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-16677489.84361878</t>
+          <t>-15052172.97708171</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-12054523.73</v>
+        <v>-6112930.21</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>38.27</t>
+          <t>41.86</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>95.63</t>
+          <t>92.96</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>46.38</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>8056</t>
+          <t>7831</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>65.1</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>67.4</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>65.1</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>65.4</t>
+          <t>67.1</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>562.661</t>
+          <t>1161.669</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>64.9</t>
+          <t>65.4</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4.42</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>11.47</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>10.48</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>-2.60</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1542</t>
+          <t>735</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>82.76</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>36.68</t>
+          <t>70.01</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-3.82</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>5.35</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>63.5</t>
+          <t>63.86000000000001</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>66.03</t>
+          <t>65.67</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>65.08</t>
+          <t>65.26</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>61.76</t>
+          <t>61.95</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-137.89</t>
+          <t>-65.80</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-111.26</t>
+          <t>-113.47</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>75339280.78787878</t>
+          <t>75336741.62896253</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>36274209.0</t>
+          <t>76790846.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>31522597.6</t>
+          <t>40176137.2</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>31905787.9</t>
+          <t>36041288.8</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>111064675.6</t>
+          <t>112225732.82</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-383190</t>
+          <t>4134848</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-17518029.13726628</t>
+          <t>-16677489.84361878</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-16998598.23</v>
+        <v>-12054523.73</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>37.21</t>
+          <t>38.27</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4214,22 +4214,22 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>95.63</t>
+          <t>92.96</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>46.38</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>8056</t>
+          <t>7831</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>63.4</t>
+          <t>65.1</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
+          <t>67.4</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>65.1</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
           <t>65.4</t>
-        </is>
-      </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>63.4</t>
-        </is>
-      </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>64.9</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>386.127</t>
+          <t>562.661</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>63.4</t>
+          <t>64.9</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1542</t>
+          <t>735</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>82.76</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>36.68</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-4.48</t>
+          <t>-3.82</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>63.34000000000001</t>
+          <t>63.5</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>66.31</t>
+          <t>66.03</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>64.92</t>
+          <t>65.08</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>61.58</t>
+          <t>61.76</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-308.50</t>
+          <t>-137.89</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-107.38</t>
+          <t>-111.26</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>75339280.78787878</t>
+          <t>75336741.62896253</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>24471827.0</t>
+          <t>36274209.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>30117424.6</t>
+          <t>31522597.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>31140083.6</t>
+          <t>31905787.9</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>110844509.38</t>
+          <t>111064675.6</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-1022659</t>
+          <t>-383190</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-17612471.12087157</t>
+          <t>-17518029.13726628</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-19113400.75</v>
+        <v>-16998598.23</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>34.04</t>
+          <t>37.21</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>95.63</t>
+          <t>92.96</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>46.38</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>8056</t>
+          <t>7831</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>63.4</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>63.9</t>
+          <t>65.4</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>63.4</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>63.4</t>
+          <t>64.9</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>440.993</t>
+          <t>386.127</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>63.4</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>7.95</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-10.57</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,37 +4888,37 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1542</t>
+          <t>735</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.09</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-4.79</t>
+          <t>-4.48</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -4928,37 +4928,37 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>63.42</t>
+          <t>63.34000000000001</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>66.61</t>
+          <t>66.31</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>64.77</t>
+          <t>64.92</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>61.43</t>
+          <t>61.58</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-1571.66</t>
+          <t>-308.50</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-101.69</t>
+          <t>-107.38</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>75339280.78787878</t>
+          <t>75336741.62896253</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>27460291.0</t>
+          <t>24471827.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>31484115.4</t>
+          <t>30117424.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>35203368.5</t>
+          <t>31140083.6</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>110885096.24</t>
+          <t>110844509.38</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-3719253</t>
+          <t>-1022659</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-17339574.82404308</t>
+          <t>-17612471.12087157</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-20187384.84</v>
+        <v>-19113400.75</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>32.14</t>
+          <t>34.04</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>95.63</t>
+          <t>92.96</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>46.38</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>8056</t>
+          <t>7831</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>63.9</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>61.6</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>63.4</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>559.37</t>
+          <t>440.993</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>63.1</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-20.46</t>
+          <t>-10.57</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,12 +5319,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1542</t>
+          <t>735</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5334,62 +5334,62 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-4.44</t>
+          <t>-4.79</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>5.42</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>64.00000000000001</t>
+          <t>63.42</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>66.97</t>
+          <t>66.61</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>64.65</t>
+          <t>64.77</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>61.29</t>
+          <t>61.43</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-542.60</t>
+          <t>-1571.66</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-95.06</t>
+          <t>-101.69</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>75339280.78787878</t>
+          <t>75336741.62896253</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>35883513.0</t>
+          <t>27460291.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>32854954.6</t>
+          <t>31484115.4</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>41305635.5</t>
+          <t>35203368.5</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>110944182.58</t>
+          <t>110885096.24</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-8450680</t>
+          <t>-3719253</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-16821791.18567295</t>
+          <t>-17339574.82404308</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-21320862.35</v>
+        <v>-20187384.84</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>33.40</t>
+          <t>32.14</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>95.63</t>
+          <t>92.96</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>46.38</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>8056</t>
+          <t>7831</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>63.7</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>65.3</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>63.1</t>
+          <t>61.6</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>63.1</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3352.0</t>
+          <t>3082.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-15.27</t>
+          <t>-33.50</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,142 +5750,142 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>3352</t>
+          <t>3082</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>10.64</t>
+          <t>13.04</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
+          <t>58.38000000000001</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>59.01</t>
+        </is>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>60.14</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>57.69</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>-30.25</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>-0.58</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>-0.44</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>5.31</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>-108.37</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>817966.6647398844</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>178445.0</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>221675.6</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>333361.3</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>566147.36</t>
+        </is>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>-111685</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>-36059.8318239443</t>
+        </is>
+      </c>
+      <c r="BC13" t="n">
+        <v>-37072.39</v>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
           <t>58.9</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>59.24</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>60.11</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>57.62</t>
-        </is>
-      </c>
-      <c r="AP13" t="inlineStr">
-        <is>
-          <t>-24.96</t>
-        </is>
-      </c>
-      <c r="AQ13" t="inlineStr">
-        <is>
-          <t>-0.51</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>-0.41</t>
-        </is>
-      </c>
-      <c r="AS13" t="inlineStr">
-        <is>
-          <t>5.31</t>
-        </is>
-      </c>
-      <c r="AT13" t="inlineStr">
-        <is>
-          <t>-107.74</t>
-        </is>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV13" t="inlineStr">
-        <is>
-          <t>818763.0455861071</t>
-        </is>
-      </c>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>194731.0</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>289419.6</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>341561.2</t>
-        </is>
-      </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>568481.84</t>
-        </is>
-      </c>
-      <c r="BA13" t="inlineStr">
-        <is>
-          <t>-52141</t>
-        </is>
-      </c>
-      <c r="BB13" t="inlineStr">
-        <is>
-          <t>-35875.73082668789</t>
-        </is>
-      </c>
-      <c r="BC13" t="n">
-        <v>-30660.24</v>
-      </c>
-      <c r="BD13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE13" t="inlineStr">
-        <is>
-          <t>58.9</t>
-        </is>
-      </c>
       <c r="BF13" t="inlineStr">
         <is>
           <t>2025/08/29</t>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BM13" t="inlineStr">
@@ -5938,7 +5938,7 @@
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
@@ -5948,12 +5948,12 @@
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>24.51</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>34212</t>
+          <t>34331</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>4870.0</t>
+          <t>3352.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,72 +6065,72 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
+          <t>57.4</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>-0.07</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>-15.27</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2025-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
           <t>58.1</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>-1.22</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>-1.6</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>22.85</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>2025-10-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>58.1</t>
-        </is>
-      </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>8.40</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,77 +6181,77 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>3352</t>
+          <t>3082</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>40.68</t>
+          <t>10.64</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>55.37</t>
+          <t>35.75</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>59.73999999999999</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>59.51</t>
+          <t>59.24</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>60.1</t>
+          <t>60.11</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>57.55</t>
+          <t>57.62</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-24.96</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-107.25</t>
+          <t>-107.74</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,45 +6271,45 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>818763.0455861071</t>
+          <t>817966.6647398844</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>283328.0</t>
+          <t>194731.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>437969.2</t>
+          <t>289419.6</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>356514.8</t>
+          <t>341561.2</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>570563.3</t>
+          <t>568481.84</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>81454</t>
+          <t>-52141</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-36824.00107548192</t>
+          <t>-35875.73082668789</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>-22149.96</v>
+        <v>-30660.24</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BM14" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
@@ -6379,12 +6379,12 @@
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>24.51</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>34212</t>
+          <t>34331</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>57.2</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,127 +6481,127 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>-1.51</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>4870.0</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-0.87</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>-0.07</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>22.85</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2025-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>-1.53</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>-4.07</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>8.40</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
           <t>-1.35</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>4060.0</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>-2.79</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>-1.6</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>36.21</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>2025-10-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>58.1</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>59.6</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>61.5</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>-4.07</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>7.01</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>-1.86</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,77 +6612,77 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>3352</t>
+          <t>3082</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>55.93</t>
+          <t>40.68</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>67.23</t>
+          <t>55.37</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>60.12</t>
+          <t>59.73999999999999</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>59.74</t>
+          <t>59.51</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>60.09</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>57.46</t>
+          <t>57.55</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>14.66</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-107.17</t>
+          <t>-107.25</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,41 +6702,41 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>818763.0455861071</t>
+          <t>817966.6647398844</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>242218.0</t>
+          <t>283328.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>465573.8</t>
+          <t>437969.2</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>341803.5</t>
+          <t>356514.8</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>579417.88</t>
+          <t>570563.3</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>123770</t>
+          <t>81454</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-39492.00850249613</t>
+          <t>-36824.00107548192</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>-18693.88</v>
+        <v>-22149.96</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BM15" t="inlineStr">
@@ -6800,22 +6800,22 @@
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>24.51</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>34212</t>
+          <t>34331</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>59.3</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>60.6</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>3505.0</t>
+          <t>4060.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,22 +6937,22 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>36.21</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -6992,7 +6992,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
@@ -7007,12 +7007,12 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,77 +7043,77 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>3352</t>
+          <t>3082</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>69.49</t>
+          <t>55.93</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>81.92</t>
+          <t>67.23</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>59.72000000000001</t>
+          <t>60.12</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>59.98</t>
+          <t>59.74</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>60.1</t>
+          <t>60.09</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>57.38</t>
+          <t>57.46</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>20.51</t>
+          <t>14.66</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-107.44</t>
+          <t>-107.17</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,45 +7133,45 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>818763.0455861071</t>
+          <t>817966.6647398844</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>209656.0</t>
+          <t>242218.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>452042.6</t>
+          <t>465573.8</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>332281.8</t>
+          <t>341803.5</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>596784.86</t>
+          <t>579417.88</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>119760</t>
+          <t>123770</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-43273.48695184787</t>
+          <t>-39492.00850249613</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>-8684.33</v>
+        <v>-18693.88</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BM16" t="inlineStr">
@@ -7231,22 +7231,22 @@
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>24.51</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>34212</t>
+          <t>34331</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>60.1</t>
+          <t>59.3</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8540.0</t>
+          <t>3505.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>60.2</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-3.82</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>30.92</t>
+          <t>36.04</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14.74</t>
+          <t>6.05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,77 +7474,77 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>3352</t>
+          <t>3082</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>76.27</t>
+          <t>69.49</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>91.33</t>
+          <t>81.92</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>59.14</t>
+          <t>59.72000000000001</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>60.09</t>
+          <t>59.98</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>60.08</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>57.31</t>
+          <t>57.38</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>9.30</t>
+          <t>20.51</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-107.82</t>
+          <t>-107.44</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>818763.0455861071</t>
+          <t>817966.6647398844</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>517165.0</t>
+          <t>209656.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>445047.0</t>
+          <t>452042.6</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>339942.5</t>
+          <t>332281.8</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>643736.64</t>
+          <t>596784.86</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>105104</t>
+          <t>119760</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-49562.42385215155</t>
+          <t>-43273.48695184787</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>9413.950000000001</v>
+        <v>-8684.33</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7642,7 +7642,7 @@
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BM17" t="inlineStr">
@@ -7662,22 +7662,22 @@
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>24.51</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>34212</t>
+          <t>34331</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>61.7</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>61.8</t>
+          <t>60.4</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>59.6</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>60.2</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>15157.0</t>
+          <t>8540.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>61.6</t>
+          <t>60.2</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-7.32</t>
+          <t>-4.51</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>29.74</t>
+          <t>30.92</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>14.74</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,47 +7905,47 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>3352</t>
+          <t>3082</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>76.27</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>75.54</t>
+          <t>91.33</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>5.77</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>58.24000000000001</t>
+          <t>59.14</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -7960,22 +7960,22 @@
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>57.24</t>
+          <t>57.31</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-15.74</t>
+          <t>9.30</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-108.00</t>
+          <t>-107.82</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>818763.0455861071</t>
+          <t>817966.6647398844</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>937479.0</t>
+          <t>517165.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>393702.8</t>
+          <t>445047.0</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>303455.3</t>
+          <t>339942.5</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>659423.84</t>
+          <t>643736.64</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>90247</t>
+          <t>105104</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-60285.40158650742</t>
+          <t>-49562.42385215155</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>1985.04</v>
+        <v>9413.950000000001</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BM18" t="inlineStr">
@@ -8093,7 +8093,7 @@
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
@@ -8103,12 +8103,12 @@
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>24.51</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>34212</t>
+          <t>34331</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>60.5</t>
+          <t>61.7</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>63.2</t>
+          <t>61.8</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>59.6</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>61.6</t>
+          <t>60.2</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>7091.0</t>
+          <t>15157.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>61.6</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>-6.94</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>17.44</t>
+          <t>29.74</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12.24</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,77 +8336,77 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>3352</t>
+          <t>3082</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>97.73</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>50.21</t>
+          <t>75.54</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>5.77</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-3.09</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>57.26000000000001</t>
+          <t>58.24000000000001</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>60.13</t>
+          <t>60.09</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>59.94</t>
+          <t>60.08</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>57.24</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-89.66</t>
+          <t>-15.74</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-107.68</t>
+          <t>-108.00</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>818763.0455861071</t>
+          <t>817966.6647398844</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>421351.0</t>
+          <t>937479.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>275060.4</t>
+          <t>393702.8</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>234213.9</t>
+          <t>303455.3</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>643815.04</t>
+          <t>659423.84</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>40846</t>
+          <t>90247</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-71607.30094654183</t>
+          <t>-60285.40158650742</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>-53732.22</v>
+        <v>1985.04</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BM19" t="inlineStr">
@@ -8524,22 +8524,22 @@
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>24.51</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>34212</t>
+          <t>34331</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>60.5</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>60.2</t>
+          <t>63.2</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>61.6</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3057.0</t>
+          <t>7091.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>17.44</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>12.24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,77 +8767,77 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>3352</t>
+          <t>3082</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>97.73</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>17.63</t>
+          <t>50.21</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-5.40</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>57.04</t>
+          <t>57.26000000000001</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>60.3</t>
+          <t>60.13</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>59.83</t>
+          <t>59.94</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>57.06</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-203.28</t>
+          <t>-89.66</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-105.96</t>
+          <t>-107.68</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>818763.0455861071</t>
+          <t>817966.6647398844</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>174562.0</t>
+          <t>421351.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>218033.2</t>
+          <t>275060.4</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>218350.5</t>
+          <t>234213.9</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>642009.16</t>
+          <t>643815.04</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-317</t>
+          <t>40846</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-74857.31579659131</t>
+          <t>-71607.30094654183</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>-76109.87</v>
+        <v>-53732.22</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BM20" t="inlineStr">
@@ -8955,22 +8955,22 @@
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>24.51</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>34212</t>
+          <t>34331</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>57.7</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
+          <t>60.2</t>
+        </is>
+      </c>
+      <c r="CE20" t="inlineStr">
+        <is>
           <t>57.7</t>
         </is>
       </c>
-      <c r="CE20" t="inlineStr">
-        <is>
-          <t>56.4</t>
-        </is>
-      </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3065.0</t>
+          <t>3057.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>56.9</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-6.63</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,275 +9198,275 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>3352</t>
+          <t>3082</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>17.63</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-5.09</t>
+          <t>-5.40</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>57.04</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>60.58</t>
+          <t>60.3</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>59.76</t>
+          <t>59.83</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
+          <t>57.06</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>-203.28</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>-0.96</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>-0.32</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>5.31</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr">
+        <is>
+          <t>-105.96</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV21" t="inlineStr">
+        <is>
+          <t>817966.6647398844</t>
+        </is>
+      </c>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>174562.0</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>218033.2</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>218350.5</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>642009.16</t>
+        </is>
+      </c>
+      <c r="BA21" t="inlineStr">
+        <is>
+          <t>-317</t>
+        </is>
+      </c>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>-74857.31579659131</t>
+        </is>
+      </c>
+      <c r="BC21" t="n">
+        <v>-76109.87</v>
+      </c>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE21" t="inlineStr">
+        <is>
+          <t>58.9</t>
+        </is>
+      </c>
+      <c r="BF21" t="inlineStr">
+        <is>
+          <t>2025/08/29</t>
+        </is>
+      </c>
+      <c r="BG21" t="inlineStr">
+        <is>
+          <t>-3.23</t>
+        </is>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>光洋科</t>
+        </is>
+      </c>
+      <c r="BI21" t="inlineStr">
+        <is>
+          <t>光洋科</t>
+        </is>
+      </c>
+      <c r="BJ21" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BK21" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL21" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="BM21" t="inlineStr">
+        <is>
+          <t>-1.228328584465341</t>
+        </is>
+      </c>
+      <c r="BN21" t="inlineStr">
+        <is>
+          <t>47.44460114587924</t>
+        </is>
+      </c>
+      <c r="BO21" t="inlineStr">
+        <is>
+          <t>32.54445648609581</t>
+        </is>
+      </c>
+      <c r="BP21" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+        </is>
+      </c>
+      <c r="BQ21" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BR21" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="BS21" t="inlineStr">
+        <is>
+          <t>3.47</t>
+        </is>
+      </c>
+      <c r="BT21" t="inlineStr">
+        <is>
+          <t>17.51</t>
+        </is>
+      </c>
+      <c r="BU21" t="inlineStr">
+        <is>
+          <t>24.51</t>
+        </is>
+      </c>
+      <c r="BV21" t="inlineStr">
+        <is>
+          <t>14.09%</t>
+        </is>
+      </c>
+      <c r="BW21" t="inlineStr">
+        <is>
+          <t>9.19%</t>
+        </is>
+      </c>
+      <c r="BX21" t="inlineStr">
+        <is>
+          <t>41.96</t>
+        </is>
+      </c>
+      <c r="BY21" t="inlineStr">
+        <is>
+          <t>34331</t>
+        </is>
+      </c>
+      <c r="BZ21" t="inlineStr">
+        <is>
+          <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA21" t="inlineStr">
+        <is>
+          <t>光洋科-其他電子業-上櫃</t>
+        </is>
+      </c>
+      <c r="CB21" t="inlineStr">
+        <is>
+          <t>其他電子業右上上櫃</t>
+        </is>
+      </c>
+      <c r="CC21" t="inlineStr">
+        <is>
+          <t>56.6</t>
+        </is>
+      </c>
+      <c r="CD21" t="inlineStr">
+        <is>
+          <t>57.7</t>
+        </is>
+      </c>
+      <c r="CE21" t="inlineStr">
+        <is>
+          <t>56.4</t>
+        </is>
+      </c>
+      <c r="CF21" t="inlineStr">
+        <is>
           <t>57.0</t>
-        </is>
-      </c>
-      <c r="AP21" t="inlineStr">
-        <is>
-          <t>-464.25</t>
-        </is>
-      </c>
-      <c r="AQ21" t="inlineStr">
-        <is>
-          <t>-0.88</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>-0.16</t>
-        </is>
-      </c>
-      <c r="AS21" t="inlineStr">
-        <is>
-          <t>5.31</t>
-        </is>
-      </c>
-      <c r="AT21" t="inlineStr">
-        <is>
-          <t>-102.93</t>
-        </is>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV21" t="inlineStr">
-        <is>
-          <t>818763.0455861071</t>
-        </is>
-      </c>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>174678.0</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>212521.0</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>227616.4</t>
-        </is>
-      </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>643094.8</t>
-        </is>
-      </c>
-      <c r="BA21" t="inlineStr">
-        <is>
-          <t>-15095</t>
-        </is>
-      </c>
-      <c r="BB21" t="inlineStr">
-        <is>
-          <t>-74629.57784452781</t>
-        </is>
-      </c>
-      <c r="BC21" t="n">
-        <v>-78918.07000000001</v>
-      </c>
-      <c r="BD21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE21" t="inlineStr">
-        <is>
-          <t>58.9</t>
-        </is>
-      </c>
-      <c r="BF21" t="inlineStr">
-        <is>
-          <t>2025/08/29</t>
-        </is>
-      </c>
-      <c r="BG21" t="inlineStr">
-        <is>
-          <t>-3.40</t>
-        </is>
-      </c>
-      <c r="BH21" t="inlineStr">
-        <is>
-          <t>光洋科</t>
-        </is>
-      </c>
-      <c r="BI21" t="inlineStr">
-        <is>
-          <t>光洋科</t>
-        </is>
-      </c>
-      <c r="BJ21" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BK21" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL21" t="inlineStr">
-        <is>
-          <t>1.11</t>
-        </is>
-      </c>
-      <c r="BM21" t="inlineStr">
-        <is>
-          <t>-1.228328584465341</t>
-        </is>
-      </c>
-      <c r="BN21" t="inlineStr">
-        <is>
-          <t>47.44460114587924</t>
-        </is>
-      </c>
-      <c r="BO21" t="inlineStr">
-        <is>
-          <t>32.54445648609581</t>
-        </is>
-      </c>
-      <c r="BP21" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ21" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BR21" t="inlineStr">
-        <is>
-          <t>2.48</t>
-        </is>
-      </c>
-      <c r="BS21" t="inlineStr">
-        <is>
-          <t>3.48</t>
-        </is>
-      </c>
-      <c r="BT21" t="inlineStr">
-        <is>
-          <t>17.51</t>
-        </is>
-      </c>
-      <c r="BU21" t="inlineStr">
-        <is>
-          <t>24.43</t>
-        </is>
-      </c>
-      <c r="BV21" t="inlineStr">
-        <is>
-          <t>14.09%</t>
-        </is>
-      </c>
-      <c r="BW21" t="inlineStr">
-        <is>
-          <t>9.19%</t>
-        </is>
-      </c>
-      <c r="BX21" t="inlineStr">
-        <is>
-          <t>42.34</t>
-        </is>
-      </c>
-      <c r="BY21" t="inlineStr">
-        <is>
-          <t>34212</t>
-        </is>
-      </c>
-      <c r="BZ21" t="inlineStr">
-        <is>
-          <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA21" t="inlineStr">
-        <is>
-          <t>光洋科-其他電子業-上櫃</t>
-        </is>
-      </c>
-      <c r="CB21" t="inlineStr">
-        <is>
-          <t>其他電子業右上上櫃</t>
-        </is>
-      </c>
-      <c r="CC21" t="inlineStr">
-        <is>
-          <t>56.7</t>
-        </is>
-      </c>
-      <c r="CD21" t="inlineStr">
-        <is>
-          <t>57.8</t>
-        </is>
-      </c>
-      <c r="CE21" t="inlineStr">
-        <is>
-          <t>56.5</t>
-        </is>
-      </c>
-      <c r="CF21" t="inlineStr">
-        <is>
-          <t>56.9</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>4712.0</t>
+          <t>3065.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-6.63</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-4.13</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>8.13</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,77 +9629,77 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>3352</t>
+          <t>3082</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-3.80</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-4.89</t>
+          <t>-5.09</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>57.9</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>60.88</t>
+          <t>60.58</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>59.67</t>
+          <t>59.76</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>56.96</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-3104.58</t>
+          <t>-464.25</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-99.53</t>
+          <t>-102.93</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>818763.0455861071</t>
+          <t>817966.6647398844</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>260444.0</t>
+          <t>174678.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>234838.0</t>
+          <t>212521.0</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>255984.1</t>
+          <t>227616.4</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>641889.36</t>
+          <t>643094.8</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-21146</t>
+          <t>-15095</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-73849.85288862225</t>
+          <t>-74629.57784452781</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-80123.69</v>
+        <v>-78918.07000000001</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-5.43</t>
+          <t>-3.40</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9797,7 +9797,7 @@
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BM22" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9827,12 +9827,12 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>24.51</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>34212</t>
+          <t>34331</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>56.7</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>5987.0</t>
+          <t>4712.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>56.7</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-19.62</t>
+          <t>-8.26</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-4.13</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10.33</t>
+          <t>8.13</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-3.70</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,12 +10060,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>3352</t>
+          <t>3082</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10075,62 +10075,62 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>-3.80</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-4.89</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>58.77999999999999</t>
+          <t>57.9</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>61.17</t>
+          <t>60.88</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>59.62</t>
+          <t>59.67</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>56.92</t>
+          <t>56.96</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-308.20</t>
+          <t>-3104.58</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-95.87</t>
+          <t>-99.53</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>818763.0455861071</t>
+          <t>817966.6647398844</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>344267.0</t>
+          <t>260444.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>213207.8</t>
+          <t>234838.0</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>265240.8</t>
+          <t>255984.1</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>639604.54</t>
+          <t>641889.36</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-52033</t>
+          <t>-21146</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-72709.154839041</t>
+          <t>-73849.85288862225</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-88173.67</v>
+        <v>-80123.69</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-3.74</t>
+          <t>-5.43</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BM23" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>24.51</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>34212</t>
+          <t>34331</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>59.1</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>56.7</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料).xlsx
+++ b/Result/checksun_type/濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料).xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>735.417</t>
+          <t>412.165</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>10.77</t>
+          <t>-23.59</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>-5.71</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>412</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>14.47</t>
+          <t>23.94</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>49.64</t>
+          <t>29.29</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-5.53</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>5.80</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>69.86000000000001</t>
+          <t>68.78000000000002</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>66.24</t>
+          <t>66.31</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>66.9</t>
+          <t>66.98</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>63.24</t>
+          <t>63.36</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>50.55</t>
+          <t>21.92</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-80.05</t>
+          <t>-78.90</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,45 +1099,45 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>75336741.62896253</t>
+          <t>75288206.88129497</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>49051403.0</t>
+          <t>27736728.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>105813427.6</t>
+          <t>73239519.2</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>95524666.9</t>
+          <t>95851157.0</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>120066640.9</t>
+          <t>115231412.04</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>10288760</t>
+          <t>-22611637</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-1542288.227029385</t>
+          <t>-1782747.750237079</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>1841656.88</v>
+        <v>-3105275.13</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>39.53</t>
+          <t>41.86</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1197,24 +1197,24 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
           <t>1.42</t>
         </is>
       </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
       <c r="BT2" t="inlineStr">
         <is>
           <t>14.92</t>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>92.96</t>
+          <t>94.51</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>47.09</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>7831</t>
+          <t>7961</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>68.6</t>
+          <t>67.9</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>68.6</t>
+          <t>67.9</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>66.5</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.1</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1542.065</t>
+          <t>735.417</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>67.9</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>41.98</t>
+          <t>10.77</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>-3.00</t>
+          <t>-5.71</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13.91</t>
+          <t>6.63</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1440,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>412</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>49.45</t>
+          <t>14.47</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>76.15</t>
+          <t>49.64</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-5.53</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>5.70</t>
+          <t>5.80</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>70.66</t>
+          <t>69.86000000000001</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>66.3</t>
+          <t>66.24</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>66.75</t>
+          <t>66.9</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>63.15</t>
+          <t>63.24</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>125.60</t>
+          <t>50.55</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-82.57</t>
+          <t>-80.05</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,45 +1530,45 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>75336741.62896253</t>
+          <t>75288206.88129497</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>106177736.0</t>
+          <t>49051403.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>132561832.2</t>
+          <t>105813427.6</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>93365555.7</t>
+          <t>95524666.9</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>120263879.18</t>
+          <t>120066640.9</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>39196276</t>
+          <t>10288760</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-2157550.973595275</t>
+          <t>-1542288.227029385</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>6559213.96</v>
+        <v>1841656.88</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>39.53</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1628,22 +1628,22 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>92.96</t>
+          <t>94.51</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>47.09</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>7831</t>
+          <t>7961</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>67.9</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1168.47</t>
+          <t>1542.065</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>67.9</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-7.58</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>53.47</t>
+          <t>41.98</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>-3.00</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10.54</t>
+          <t>13.91</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,77 +1871,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>412</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>49.45</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>76.15</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>6.43</t>
+          <t>6.58</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>5.70</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>70.66</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>66.24</t>
+          <t>66.3</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>66.75</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>63.02</t>
+          <t>63.15</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>262.06</t>
+          <t>125.60</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-88.05</t>
+          <t>-82.57</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,45 +1961,45 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>75336741.62896253</t>
+          <t>75288206.88129497</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>82950382.0</t>
+          <t>106177736.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>132496129.6</t>
+          <t>132561832.2</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>86336133.4</t>
+          <t>93365555.7</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>120394266.18</t>
+          <t>120263879.18</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>46159996</t>
+          <t>39196276</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-3742417.326026477</t>
+          <t>-2157550.973595275</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>6943645.05</v>
+        <v>6559213.96</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>50.11</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2064,17 +2064,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>92.96</t>
+          <t>94.51</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>47.09</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>7831</t>
+          <t>7961</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>67.9</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1393.968</t>
+          <t>1168.47</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-8.94</t>
+          <t>-5.81</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>61.27</t>
+          <t>53.47</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12.58</t>
+          <t>10.54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,77 +2302,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>412</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>6.43</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>69.38</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>66.06</t>
+          <t>66.24</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>66.34</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>62.79</t>
+          <t>63.02</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>768.32</t>
+          <t>262.06</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-95.88</t>
+          <t>-88.05</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,45 +2392,45 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>75336741.62896253</t>
+          <t>75288206.88129497</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>100281347.0</t>
+          <t>82950382.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>131264222.4</t>
+          <t>132496129.6</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>81393410.0</t>
+          <t>86336133.4</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>119695734.58</t>
+          <t>120394266.18</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>49870812</t>
+          <t>46159996</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-5685337.758529304</t>
+          <t>-3742417.326026477</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>9733490.07</v>
+        <v>6943645.05</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>52.01</t>
+          <t>50.11</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2495,17 +2495,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>92.96</t>
+          <t>94.51</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>47.09</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>7831</t>
+          <t>7961</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2657.246</t>
+          <t>1393.968</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-9.85</t>
+          <t>-7.15</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>59.46</t>
+          <t>61.27</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>23.97</t>
+          <t>12.58</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,77 +2733,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>412</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>6.65</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>5.60</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>67.98</t>
+          <t>69.38</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>65.84</t>
+          <t>66.06</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>66.06</t>
+          <t>66.34</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>62.56</t>
+          <t>62.79</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>686.39</t>
+          <t>768.32</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-103.80</t>
+          <t>-95.88</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,45 +2823,45 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>75336741.62896253</t>
+          <t>75288206.88129497</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>190606270.0</t>
+          <t>100281347.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>118462794.8</t>
+          <t>131264222.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>74290109.7</t>
+          <t>81393410.0</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>120126016.38</t>
+          <t>119695734.58</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>44172685</t>
+          <t>49870812</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-8488760.999966215</t>
+          <t>-5685337.758529304</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>11514469.2</v>
+        <v>9733490.07</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>53.28</t>
+          <t>52.01</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>92.96</t>
+          <t>94.51</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>47.09</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>7831</t>
+          <t>7961</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
+          <t>71.2</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
           <t>70.6</t>
         </is>
       </c>
-      <c r="CD6" t="inlineStr">
-        <is>
-          <t>72.8</t>
-        </is>
-      </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>69.7</t>
-        </is>
-      </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2598.844</t>
+          <t>2657.246</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,74 +3048,74 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>72.5</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-8.05</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>-1.04</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>59.46</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2025-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2025-09-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>70.0</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>-6.06</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.96</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>46.05</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2025-11-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2025-11-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2025-09-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>70.0</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
       <c r="T7" t="inlineStr">
         <is>
           <t>67.8</t>
@@ -3128,7 +3128,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>23.45</t>
+          <t>23.97</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3164,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>412</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3184,57 +3184,57 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>5.80</t>
+          <t>6.65</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>5.60</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>66.16</t>
+          <t>67.98</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>65.64</t>
+          <t>65.84</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>65.73</t>
+          <t>66.06</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>62.31</t>
+          <t>62.56</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>122.79</t>
+          <t>686.39</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-110.31</t>
+          <t>-103.80</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,45 +3254,45 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>75336741.62896253</t>
+          <t>75288206.88129497</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>182793426.0</t>
+          <t>190606270.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>85235906.2</t>
+          <t>118462794.8</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>58360010.8</t>
+          <t>74290109.7</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>117218867.38</t>
+          <t>120126016.38</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>26875895</t>
+          <t>44172685</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-12125711.94501511</t>
+          <t>-8488760.999966215</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>3969823.73</v>
+        <v>11514469.2</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>47.99</t>
+          <t>53.28</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3357,17 +3357,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>92.96</t>
+          <t>94.51</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>47.09</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>7831</t>
+          <t>7961</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>70.6</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1558.105</t>
+          <t>2598.844</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>67.1</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,22 +3489,22 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>24.49</t>
+          <t>46.05</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -3519,7 +3519,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14.06</t>
+          <t>23.45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,12 +3595,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>412</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3610,62 +3610,62 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>94.25</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>5.80</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>5.49</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>64.66</t>
+          <t>66.16</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>65.52</t>
+          <t>65.64</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>65.47</t>
+          <t>65.73</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>62.1</t>
+          <t>62.31</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>122.79</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-113.47</t>
+          <t>-110.31</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,45 +3685,45 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>75336741.62896253</t>
+          <t>75288206.88129497</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>105849223.0</t>
+          <t>182793426.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>54169279.2</t>
+          <t>85235906.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>43512116.9</t>
+          <t>58360010.8</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>113935358.54</t>
+          <t>117218867.38</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>10657162</t>
+          <t>26875895</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-15052172.97708171</t>
+          <t>-12125711.94501511</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-6112930.21</v>
+        <v>3969823.73</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>41.86</t>
+          <t>47.99</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>92.96</t>
+          <t>94.51</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>47.09</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>7831</t>
+          <t>7961</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>67.1</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1161.669</t>
+          <t>1558.105</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>65.4</t>
+          <t>67.1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>11.47</t>
+          <t>24.49</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10.48</t>
+          <t>14.06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.60</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,12 +4026,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>412</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4041,57 +4041,57 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>70.01</t>
+          <t>94.25</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>5.35</t>
+          <t>5.42</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>63.86000000000001</t>
+          <t>64.66</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>65.67</t>
+          <t>65.52</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>65.26</t>
+          <t>65.47</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>61.95</t>
+          <t>62.1</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-65.80</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>75336741.62896253</t>
+          <t>75288206.88129497</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>76790846.0</t>
+          <t>105849223.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>40176137.2</t>
+          <t>54169279.2</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>36041288.8</t>
+          <t>43512116.9</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>112225732.82</t>
+          <t>113935358.54</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>4134848</t>
+          <t>10657162</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-16677489.84361878</t>
+          <t>-15052172.97708171</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-12054523.73</v>
+        <v>-6112930.21</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>38.27</t>
+          <t>41.86</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4224,12 +4224,12 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>92.96</t>
+          <t>94.51</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>47.09</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>7831</t>
+          <t>7961</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>65.1</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>67.4</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>65.1</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>65.4</t>
+          <t>67.1</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>562.661</t>
+          <t>1161.669</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>64.9</t>
+          <t>65.4</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>11.47</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>10.48</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>-2.60</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>412</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>82.76</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>36.68</t>
+          <t>70.01</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.82</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>5.35</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>63.5</t>
+          <t>63.86000000000001</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>66.03</t>
+          <t>65.67</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>65.08</t>
+          <t>65.26</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>61.76</t>
+          <t>61.95</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-137.89</t>
+          <t>-65.80</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-111.26</t>
+          <t>-113.47</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>75336741.62896253</t>
+          <t>75288206.88129497</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>36274209.0</t>
+          <t>76790846.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>31522597.6</t>
+          <t>40176137.2</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>31905787.9</t>
+          <t>36041288.8</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>111064675.6</t>
+          <t>112225732.82</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-383190</t>
+          <t>4134848</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-17518029.13726628</t>
+          <t>-16677489.84361878</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-16998598.23</v>
+        <v>-12054523.73</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>37.21</t>
+          <t>38.27</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4645,22 +4645,22 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>92.96</t>
+          <t>94.51</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>47.09</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>7831</t>
+          <t>7961</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>63.4</t>
+          <t>65.1</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
+          <t>67.4</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
+          <t>65.1</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
           <t>65.4</t>
-        </is>
-      </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>63.4</t>
-        </is>
-      </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>64.9</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>386.127</t>
+          <t>562.661</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>63.4</t>
+          <t>64.9</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4888,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>412</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>82.76</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>36.68</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-4.48</t>
+          <t>-3.82</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>63.34000000000001</t>
+          <t>63.5</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>66.31</t>
+          <t>66.03</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>64.92</t>
+          <t>65.08</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>61.58</t>
+          <t>61.76</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-308.50</t>
+          <t>-137.89</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-107.38</t>
+          <t>-111.26</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>75336741.62896253</t>
+          <t>75288206.88129497</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>24471827.0</t>
+          <t>36274209.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>30117424.6</t>
+          <t>31522597.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>31140083.6</t>
+          <t>31905787.9</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>110844509.38</t>
+          <t>111064675.6</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-1022659</t>
+          <t>-383190</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-17612471.12087157</t>
+          <t>-17518029.13726628</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-19113400.75</v>
+        <v>-16998598.23</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>34.04</t>
+          <t>37.21</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>92.96</t>
+          <t>94.51</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>47.09</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>7831</t>
+          <t>7961</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>63.4</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>63.9</t>
+          <t>65.4</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>63.4</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>63.4</t>
+          <t>64.9</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>440.993</t>
+          <t>386.127</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>63.4</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>5.51</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-10.57</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,37 +5319,37 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>412</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.09</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-4.79</t>
+          <t>-4.48</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -5359,37 +5359,37 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>63.42</t>
+          <t>63.34000000000001</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>66.61</t>
+          <t>66.31</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>64.77</t>
+          <t>64.92</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>61.43</t>
+          <t>61.58</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-1571.66</t>
+          <t>-308.50</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-101.69</t>
+          <t>-107.38</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>75336741.62896253</t>
+          <t>75288206.88129497</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>27460291.0</t>
+          <t>24471827.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>31484115.4</t>
+          <t>30117424.6</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>35203368.5</t>
+          <t>31140083.6</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>110885096.24</t>
+          <t>110844509.38</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-3719253</t>
+          <t>-1022659</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-17339574.82404308</t>
+          <t>-17612471.12087157</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-20187384.84</v>
+        <v>-19113400.75</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>32.14</t>
+          <t>34.04</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>92.96</t>
+          <t>94.51</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>47.09</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>7831</t>
+          <t>7961</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>63.9</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>61.6</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>63.4</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3082.0</t>
+          <t>4747.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-33.50</t>
+          <t>-31.52</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>8.19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,77 +5750,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>3082</t>
+          <t>4747</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>13.04</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>19.01</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-2.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>58.38000000000001</t>
+          <t>58.17999999999999</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>59.01</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>60.14</t>
+          <t>60.16</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>57.69</t>
+          <t>57.77</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-30.25</t>
+          <t>-14.48</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-108.37</t>
+          <t>-108.68</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,41 +5840,41 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>817966.6647398844</t>
+          <t>817388.4242424243</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>178445.0</t>
+          <t>278164.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>221675.6</t>
+          <t>235377.2</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>333361.3</t>
+          <t>343709.9</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>566147.36</t>
+          <t>560862.08</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-111685</t>
+          <t>-108332</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-36059.8318239443</t>
+          <t>-35612.95810049239</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>-37072.39</v>
+        <v>-33155.15</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5938,22 +5938,22 @@
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>24.51</t>
+          <t>25.02</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.77</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>34331</t>
+          <t>35046</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.9</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>3352.0</t>
+          <t>3082.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-15.27</t>
+          <t>-33.50</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,142 +6181,142 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>3082</t>
+          <t>4747</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>10.64</t>
+          <t>13.04</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
+          <t>58.38000000000001</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>59.01</t>
+        </is>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>60.14</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>57.69</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>-30.25</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>-0.58</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>-0.44</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>5.31</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>-108.37</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>817388.4242424243</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>178445.0</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>221675.6</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>333361.3</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>566147.36</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>-111685</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>-36059.8318239443</t>
+        </is>
+      </c>
+      <c r="BC14" t="n">
+        <v>-37072.39</v>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
           <t>58.9</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>59.24</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>60.11</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>57.62</t>
-        </is>
-      </c>
-      <c r="AP14" t="inlineStr">
-        <is>
-          <t>-24.96</t>
-        </is>
-      </c>
-      <c r="AQ14" t="inlineStr">
-        <is>
-          <t>-0.51</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>-0.41</t>
-        </is>
-      </c>
-      <c r="AS14" t="inlineStr">
-        <is>
-          <t>5.31</t>
-        </is>
-      </c>
-      <c r="AT14" t="inlineStr">
-        <is>
-          <t>-107.74</t>
-        </is>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV14" t="inlineStr">
-        <is>
-          <t>817966.6647398844</t>
-        </is>
-      </c>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>194731.0</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>289419.6</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>341561.2</t>
-        </is>
-      </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>568481.84</t>
-        </is>
-      </c>
-      <c r="BA14" t="inlineStr">
-        <is>
-          <t>-52141</t>
-        </is>
-      </c>
-      <c r="BB14" t="inlineStr">
-        <is>
-          <t>-35875.73082668789</t>
-        </is>
-      </c>
-      <c r="BC14" t="n">
-        <v>-30660.24</v>
-      </c>
-      <c r="BD14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE14" t="inlineStr">
-        <is>
-          <t>58.9</t>
-        </is>
-      </c>
       <c r="BF14" t="inlineStr">
         <is>
           <t>2025/08/29</t>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
@@ -6379,12 +6379,12 @@
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>24.51</t>
+          <t>25.02</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.77</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>34331</t>
+          <t>35046</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>4870.0</t>
+          <t>3352.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,72 +6496,72 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
+          <t>57.4</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>-15.27</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2025-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
           <t>58.1</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>-0.87</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>-0.07</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>22.85</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>2025-10-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>58.1</t>
-        </is>
-      </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>8.40</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,77 +6612,77 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>3082</t>
+          <t>4747</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>40.68</t>
+          <t>10.64</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>55.37</t>
+          <t>35.75</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>59.73999999999999</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>59.51</t>
+          <t>59.24</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>60.1</t>
+          <t>60.11</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>57.55</t>
+          <t>57.62</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-24.96</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-107.25</t>
+          <t>-107.74</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,45 +6702,45 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>817966.6647398844</t>
+          <t>817388.4242424243</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>283328.0</t>
+          <t>194731.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>437969.2</t>
+          <t>289419.6</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>356514.8</t>
+          <t>341561.2</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>570563.3</t>
+          <t>568481.84</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>81454</t>
+          <t>-52141</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-36824.00107548192</t>
+          <t>-35875.73082668789</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>-22149.96</v>
+        <v>-30660.24</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6800,7 +6800,7 @@
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>24.51</t>
+          <t>25.02</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.77</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>34331</t>
+          <t>35046</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>57.2</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,127 +6912,127 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>-1.51</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>4870.0</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>22.85</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2025-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>-1.53</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>-4.07</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>8.40</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
           <t>-1.35</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>4060.0</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>-2.43</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>-0.07</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>36.21</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>2025-10-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>58.1</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>59.6</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>61.5</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>-4.07</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>7.01</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>-1.86</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,77 +7043,77 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>3082</t>
+          <t>4747</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>55.93</t>
+          <t>40.68</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>67.23</t>
+          <t>55.37</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>60.12</t>
+          <t>59.73999999999999</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>59.74</t>
+          <t>59.51</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>60.09</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>57.46</t>
+          <t>57.55</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>14.66</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-107.17</t>
+          <t>-107.25</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,41 +7133,41 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>817966.6647398844</t>
+          <t>817388.4242424243</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>242218.0</t>
+          <t>283328.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>465573.8</t>
+          <t>437969.2</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>341803.5</t>
+          <t>356514.8</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>579417.88</t>
+          <t>570563.3</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>123770</t>
+          <t>81454</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-39492.00850249613</t>
+          <t>-36824.00107548192</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>-18693.88</v>
+        <v>-22149.96</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7231,22 +7231,22 @@
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>24.51</t>
+          <t>25.02</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.77</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>34331</t>
+          <t>35046</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>59.3</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>60.6</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>3505.0</t>
+          <t>4060.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,22 +7368,22 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-3.82</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>36.21</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
@@ -7438,12 +7438,12 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,77 +7474,77 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>3082</t>
+          <t>4747</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>69.49</t>
+          <t>55.93</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>81.92</t>
+          <t>67.23</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>59.72000000000001</t>
+          <t>60.12</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>59.98</t>
+          <t>59.74</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>60.1</t>
+          <t>60.09</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>57.38</t>
+          <t>57.46</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>20.51</t>
+          <t>14.66</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-107.44</t>
+          <t>-107.17</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,45 +7564,45 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>817966.6647398844</t>
+          <t>817388.4242424243</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>209656.0</t>
+          <t>242218.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>452042.6</t>
+          <t>465573.8</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>332281.8</t>
+          <t>341803.5</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>596784.86</t>
+          <t>579417.88</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>119760</t>
+          <t>123770</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-43273.48695184787</t>
+          <t>-39492.00850249613</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>-8684.33</v>
+        <v>-18693.88</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7662,22 +7662,22 @@
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>24.51</t>
+          <t>25.02</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.77</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>34331</t>
+          <t>35046</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>60.1</t>
+          <t>59.3</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8540.0</t>
+          <t>3505.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>60.2</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-4.51</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>30.92</t>
+          <t>36.04</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14.74</t>
+          <t>6.05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,77 +7905,77 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>3082</t>
+          <t>4747</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>76.27</t>
+          <t>69.49</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>91.33</t>
+          <t>81.92</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>59.14</t>
+          <t>59.72000000000001</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>60.09</t>
+          <t>59.98</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>60.08</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>57.31</t>
+          <t>57.38</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>9.30</t>
+          <t>20.51</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-107.82</t>
+          <t>-107.44</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>817966.6647398844</t>
+          <t>817388.4242424243</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>517165.0</t>
+          <t>209656.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>445047.0</t>
+          <t>452042.6</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>339942.5</t>
+          <t>332281.8</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>643736.64</t>
+          <t>596784.86</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>105104</t>
+          <t>119760</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-49562.42385215155</t>
+          <t>-43273.48695184787</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>9413.950000000001</v>
+        <v>-8684.33</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8093,22 +8093,22 @@
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>24.51</t>
+          <t>25.02</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.77</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>34331</t>
+          <t>35046</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>61.7</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>61.8</t>
+          <t>60.4</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>59.6</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>60.2</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>15157.0</t>
+          <t>8540.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.6</t>
+          <t>60.2</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-6.94</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>29.74</t>
+          <t>30.92</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>14.74</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,47 +8336,47 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>3082</t>
+          <t>4747</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>76.27</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>75.54</t>
+          <t>91.33</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>5.77</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>58.24000000000001</t>
+          <t>59.14</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -8391,22 +8391,22 @@
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>57.24</t>
+          <t>57.31</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-15.74</t>
+          <t>9.30</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-108.00</t>
+          <t>-107.82</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>817966.6647398844</t>
+          <t>817388.4242424243</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>937479.0</t>
+          <t>517165.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>393702.8</t>
+          <t>445047.0</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>303455.3</t>
+          <t>339942.5</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>659423.84</t>
+          <t>643736.64</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>90247</t>
+          <t>105104</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-60285.40158650742</t>
+          <t>-49562.42385215155</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>1985.04</v>
+        <v>9413.950000000001</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>24.51</t>
+          <t>25.02</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.77</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>34331</t>
+          <t>35046</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>60.5</t>
+          <t>61.7</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>63.2</t>
+          <t>61.8</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>59.6</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>61.6</t>
+          <t>60.2</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>7091.0</t>
+          <t>15157.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>61.6</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>-4.76</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>17.44</t>
+          <t>29.74</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12.24</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,77 +8767,77 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>3082</t>
+          <t>4747</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>97.73</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>50.21</t>
+          <t>75.54</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>5.77</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-3.09</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>57.26000000000001</t>
+          <t>58.24000000000001</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>60.13</t>
+          <t>60.09</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>59.94</t>
+          <t>60.08</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>57.24</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-89.66</t>
+          <t>-15.74</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-107.68</t>
+          <t>-108.00</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>817966.6647398844</t>
+          <t>817388.4242424243</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>421351.0</t>
+          <t>937479.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>275060.4</t>
+          <t>393702.8</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>234213.9</t>
+          <t>303455.3</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>643815.04</t>
+          <t>659423.84</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>40846</t>
+          <t>90247</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-71607.30094654183</t>
+          <t>-60285.40158650742</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>-53732.22</v>
+        <v>1985.04</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8955,22 +8955,22 @@
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>24.51</t>
+          <t>25.02</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.77</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>34331</t>
+          <t>35046</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>60.5</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>60.2</t>
+          <t>63.2</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>61.6</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3057.0</t>
+          <t>7091.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>17.44</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>12.24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,77 +9198,77 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>3082</t>
+          <t>4747</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>97.73</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>17.63</t>
+          <t>50.21</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-5.40</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>57.04</t>
+          <t>57.26000000000001</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>60.3</t>
+          <t>60.13</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>59.83</t>
+          <t>59.94</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>57.06</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-203.28</t>
+          <t>-89.66</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-105.96</t>
+          <t>-107.68</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>817966.6647398844</t>
+          <t>817388.4242424243</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>174562.0</t>
+          <t>421351.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>218033.2</t>
+          <t>275060.4</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>218350.5</t>
+          <t>234213.9</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>642009.16</t>
+          <t>643815.04</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-317</t>
+          <t>40846</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-74857.31579659131</t>
+          <t>-71607.30094654183</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>-76109.87</v>
+        <v>-53732.22</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9386,22 +9386,22 @@
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>24.51</t>
+          <t>25.02</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.77</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>34331</t>
+          <t>35046</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>57.7</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
+          <t>60.2</t>
+        </is>
+      </c>
+      <c r="CE21" t="inlineStr">
+        <is>
           <t>57.7</t>
         </is>
       </c>
-      <c r="CE21" t="inlineStr">
-        <is>
-          <t>56.4</t>
-        </is>
-      </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3065.0</t>
+          <t>3057.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>56.9</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-6.63</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,275 +9629,275 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>3082</t>
+          <t>4747</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>17.63</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-5.09</t>
+          <t>-5.40</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>57.04</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>60.58</t>
+          <t>60.3</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>59.76</t>
+          <t>59.83</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
+          <t>57.06</t>
+        </is>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t>-203.28</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>-0.96</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>-0.32</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>5.31</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr">
+        <is>
+          <t>-105.96</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV22" t="inlineStr">
+        <is>
+          <t>817388.4242424243</t>
+        </is>
+      </c>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>174562.0</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>218033.2</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>218350.5</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>642009.16</t>
+        </is>
+      </c>
+      <c r="BA22" t="inlineStr">
+        <is>
+          <t>-317</t>
+        </is>
+      </c>
+      <c r="BB22" t="inlineStr">
+        <is>
+          <t>-74857.31579659131</t>
+        </is>
+      </c>
+      <c r="BC22" t="n">
+        <v>-76109.87</v>
+      </c>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE22" t="inlineStr">
+        <is>
+          <t>58.9</t>
+        </is>
+      </c>
+      <c r="BF22" t="inlineStr">
+        <is>
+          <t>2025/08/29</t>
+        </is>
+      </c>
+      <c r="BG22" t="inlineStr">
+        <is>
+          <t>-3.23</t>
+        </is>
+      </c>
+      <c r="BH22" t="inlineStr">
+        <is>
+          <t>光洋科</t>
+        </is>
+      </c>
+      <c r="BI22" t="inlineStr">
+        <is>
+          <t>光洋科</t>
+        </is>
+      </c>
+      <c r="BJ22" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BK22" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL22" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="BM22" t="inlineStr">
+        <is>
+          <t>-1.228328584465341</t>
+        </is>
+      </c>
+      <c r="BN22" t="inlineStr">
+        <is>
+          <t>47.44460114587924</t>
+        </is>
+      </c>
+      <c r="BO22" t="inlineStr">
+        <is>
+          <t>32.54445648609581</t>
+        </is>
+      </c>
+      <c r="BP22" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+        </is>
+      </c>
+      <c r="BQ22" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR22" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="BS22" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
+      </c>
+      <c r="BT22" t="inlineStr">
+        <is>
+          <t>17.51</t>
+        </is>
+      </c>
+      <c r="BU22" t="inlineStr">
+        <is>
+          <t>25.02</t>
+        </is>
+      </c>
+      <c r="BV22" t="inlineStr">
+        <is>
+          <t>14.09%</t>
+        </is>
+      </c>
+      <c r="BW22" t="inlineStr">
+        <is>
+          <t>9.19%</t>
+        </is>
+      </c>
+      <c r="BX22" t="inlineStr">
+        <is>
+          <t>42.77</t>
+        </is>
+      </c>
+      <c r="BY22" t="inlineStr">
+        <is>
+          <t>35046</t>
+        </is>
+      </c>
+      <c r="BZ22" t="inlineStr">
+        <is>
+          <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA22" t="inlineStr">
+        <is>
+          <t>光洋科-其他電子業-上櫃</t>
+        </is>
+      </c>
+      <c r="CB22" t="inlineStr">
+        <is>
+          <t>其他電子業右上上櫃</t>
+        </is>
+      </c>
+      <c r="CC22" t="inlineStr">
+        <is>
+          <t>56.6</t>
+        </is>
+      </c>
+      <c r="CD22" t="inlineStr">
+        <is>
+          <t>57.7</t>
+        </is>
+      </c>
+      <c r="CE22" t="inlineStr">
+        <is>
+          <t>56.4</t>
+        </is>
+      </c>
+      <c r="CF22" t="inlineStr">
+        <is>
           <t>57.0</t>
-        </is>
-      </c>
-      <c r="AP22" t="inlineStr">
-        <is>
-          <t>-464.25</t>
-        </is>
-      </c>
-      <c r="AQ22" t="inlineStr">
-        <is>
-          <t>-0.88</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>-0.16</t>
-        </is>
-      </c>
-      <c r="AS22" t="inlineStr">
-        <is>
-          <t>5.31</t>
-        </is>
-      </c>
-      <c r="AT22" t="inlineStr">
-        <is>
-          <t>-102.93</t>
-        </is>
-      </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV22" t="inlineStr">
-        <is>
-          <t>817966.6647398844</t>
-        </is>
-      </c>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>174678.0</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>212521.0</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>227616.4</t>
-        </is>
-      </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>643094.8</t>
-        </is>
-      </c>
-      <c r="BA22" t="inlineStr">
-        <is>
-          <t>-15095</t>
-        </is>
-      </c>
-      <c r="BB22" t="inlineStr">
-        <is>
-          <t>-74629.57784452781</t>
-        </is>
-      </c>
-      <c r="BC22" t="n">
-        <v>-78918.07000000001</v>
-      </c>
-      <c r="BD22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE22" t="inlineStr">
-        <is>
-          <t>58.9</t>
-        </is>
-      </c>
-      <c r="BF22" t="inlineStr">
-        <is>
-          <t>2025/08/29</t>
-        </is>
-      </c>
-      <c r="BG22" t="inlineStr">
-        <is>
-          <t>-3.40</t>
-        </is>
-      </c>
-      <c r="BH22" t="inlineStr">
-        <is>
-          <t>光洋科</t>
-        </is>
-      </c>
-      <c r="BI22" t="inlineStr">
-        <is>
-          <t>光洋科</t>
-        </is>
-      </c>
-      <c r="BJ22" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BK22" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL22" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="BM22" t="inlineStr">
-        <is>
-          <t>-1.228328584465341</t>
-        </is>
-      </c>
-      <c r="BN22" t="inlineStr">
-        <is>
-          <t>47.44460114587924</t>
-        </is>
-      </c>
-      <c r="BO22" t="inlineStr">
-        <is>
-          <t>32.54445648609581</t>
-        </is>
-      </c>
-      <c r="BP22" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ22" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BR22" t="inlineStr">
-        <is>
-          <t>2.48</t>
-        </is>
-      </c>
-      <c r="BS22" t="inlineStr">
-        <is>
-          <t>3.47</t>
-        </is>
-      </c>
-      <c r="BT22" t="inlineStr">
-        <is>
-          <t>17.51</t>
-        </is>
-      </c>
-      <c r="BU22" t="inlineStr">
-        <is>
-          <t>24.51</t>
-        </is>
-      </c>
-      <c r="BV22" t="inlineStr">
-        <is>
-          <t>14.09%</t>
-        </is>
-      </c>
-      <c r="BW22" t="inlineStr">
-        <is>
-          <t>9.19%</t>
-        </is>
-      </c>
-      <c r="BX22" t="inlineStr">
-        <is>
-          <t>41.96</t>
-        </is>
-      </c>
-      <c r="BY22" t="inlineStr">
-        <is>
-          <t>34331</t>
-        </is>
-      </c>
-      <c r="BZ22" t="inlineStr">
-        <is>
-          <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA22" t="inlineStr">
-        <is>
-          <t>光洋科-其他電子業-上櫃</t>
-        </is>
-      </c>
-      <c r="CB22" t="inlineStr">
-        <is>
-          <t>其他電子業右上上櫃</t>
-        </is>
-      </c>
-      <c r="CC22" t="inlineStr">
-        <is>
-          <t>56.7</t>
-        </is>
-      </c>
-      <c r="CD22" t="inlineStr">
-        <is>
-          <t>57.8</t>
-        </is>
-      </c>
-      <c r="CE22" t="inlineStr">
-        <is>
-          <t>56.5</t>
-        </is>
-      </c>
-      <c r="CF22" t="inlineStr">
-        <is>
-          <t>56.9</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>4712.0</t>
+          <t>3065.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-6.63</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-4.13</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>8.13</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,77 +10060,77 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>3082</t>
+          <t>4747</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-3.80</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-4.89</t>
+          <t>-5.09</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>57.9</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>60.88</t>
+          <t>60.58</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>59.67</t>
+          <t>59.76</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>56.96</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-3104.58</t>
+          <t>-464.25</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-99.53</t>
+          <t>-102.93</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>817966.6647398844</t>
+          <t>817388.4242424243</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>260444.0</t>
+          <t>174678.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>234838.0</t>
+          <t>212521.0</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>255984.1</t>
+          <t>227616.4</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>641889.36</t>
+          <t>643094.8</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-21146</t>
+          <t>-15095</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-73849.85288862225</t>
+          <t>-74629.57784452781</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-80123.69</v>
+        <v>-78918.07000000001</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-5.43</t>
+          <t>-3.40</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>24.51</t>
+          <t>25.02</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.77</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>34331</t>
+          <t>35046</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>56.7</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料).xlsx
+++ b/Result/checksun_type/濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料).xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-3.15</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>677.83</t>
+          <t>427.384</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,72 +898,72 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>64.0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>-1.85</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>-44.43</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2025-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2025-09-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
           <t>65.0</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>-2.09</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>-35.82</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2025-11-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-09-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>-7.14</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>427</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,62 +1029,62 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>12.81</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>5.55</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>67.4</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>66.28</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>66.98</t>
+          <t>66.9</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>63.46</t>
+          <t>63.56</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-21.43</t>
+          <t>-72.20</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-79.97</t>
+          <t>-83.03</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,50 +1104,50 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>75275336.41163793</t>
+          <t>75226946.41032998</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>44220240.0</t>
+          <t>27698337.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>62027297.8</t>
+          <t>50976888.8</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>96645760.1</t>
+          <t>91736509.2</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>113463276.16</t>
+          <t>107077260.2</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-34618462</t>
+          <t>-40759620</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-2316822.289363078</t>
+          <t>-3170586.423594275</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-5254232.254556075</t>
+          <t>-7866289.16186586</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>44220240</v>
+        <v>27698337</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>37.42</t>
+          <t>35.31</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>91.55</t>
+          <t>90.14</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>46.75</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>7712</t>
+          <t>7594</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>64.3</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>-3.15</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>412.165</t>
+          <t>677.83</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>67.1</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-23.59</t>
+          <t>-35.82</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1414,12 +1414,12 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-7.14</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,52 +1450,52 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>427</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>23.94</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>29.29</t>
+          <t>12.81</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>5.55</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>68.78000000000002</t>
+          <t>67.4</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>66.31</t>
+          <t>66.28</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1505,22 +1505,22 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>63.36</t>
+          <t>63.46</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>21.92</t>
+          <t>-21.43</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-78.90</t>
+          <t>-79.97</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>75275336.41163793</t>
+          <t>75226946.41032998</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>27736728.0</t>
+          <t>44220240.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>73239519.2</t>
+          <t>62027297.8</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>95851157.0</t>
+          <t>96645760.1</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>115231412.04</t>
+          <t>113463276.16</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-22611637</t>
+          <t>-34618462</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-1782747.750237079</t>
+          <t>-2316822.289363078</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-3105275.127879396</t>
+          <t>-5254232.254556075</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>27736728</v>
+        <v>44220240</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>41.86</t>
+          <t>37.42</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1643,22 +1643,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>91.55</t>
+          <t>90.14</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>46.75</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>7712</t>
+          <t>7594</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>67.9</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>67.9</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>66.5</t>
+          <t>64.3</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>67.1</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>735.417</t>
+          <t>412.165</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-4.84</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>10.77</t>
+          <t>-23.59</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>-5.71</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>427</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>14.47</t>
+          <t>23.94</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>49.64</t>
+          <t>29.29</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-5.53</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>5.80</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>69.86000000000001</t>
+          <t>68.78000000000002</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>66.24</t>
+          <t>66.31</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>66.9</t>
+          <t>66.98</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>63.24</t>
+          <t>63.36</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>50.55</t>
+          <t>21.92</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-80.05</t>
+          <t>-78.90</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>75275336.41163793</t>
+          <t>75226946.41032998</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>49051403.0</t>
+          <t>27736728.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>105813427.6</t>
+          <t>73239519.2</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>95524666.9</t>
+          <t>95851157.0</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>120066640.9</t>
+          <t>115231412.04</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>10288760</t>
+          <t>-22611637</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-1542288.227029385</t>
+          <t>-1782747.750237079</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>1841656.879083008</t>
+          <t>-3105275.127879396</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>49051403</v>
+        <v>27736728</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>39.53</t>
+          <t>41.86</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,22 +2079,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>91.55</t>
+          <t>90.14</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>46.75</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>7712</t>
+          <t>7594</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>68.6</t>
+          <t>67.9</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>68.6</t>
+          <t>67.9</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>66.5</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.1</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1542.065</t>
+          <t>735.417</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>67.9</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-4.46</t>
+          <t>-3.12</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>41.98</t>
+          <t>10.77</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>-3.00</t>
+          <t>-5.71</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13.91</t>
+          <t>6.63</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,77 +2322,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>427</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>49.45</t>
+          <t>14.47</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>76.15</t>
+          <t>49.64</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-5.53</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>5.70</t>
+          <t>5.80</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>70.66</t>
+          <t>69.86000000000001</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>66.3</t>
+          <t>66.24</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>66.75</t>
+          <t>66.9</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>63.15</t>
+          <t>63.24</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>125.60</t>
+          <t>50.55</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-82.57</t>
+          <t>-80.05</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>75275336.41163793</t>
+          <t>75226946.41032998</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>106177736.0</t>
+          <t>49051403.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>132561832.2</t>
+          <t>105813427.6</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>93365555.7</t>
+          <t>95524666.9</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>120263879.18</t>
+          <t>120066640.9</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>39196276</t>
+          <t>10288760</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-2157550.973595275</t>
+          <t>-1542288.227029385</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>6559213.964776337</t>
+          <t>1841656.879083008</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>106177736</v>
+        <v>49051403</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>39.53</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,22 +2515,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>91.55</t>
+          <t>90.14</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>46.75</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>7712</t>
+          <t>7594</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>67.9</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1168.47</t>
+          <t>1542.065</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>67.9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-9.23</t>
+          <t>-6.09</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>53.47</t>
+          <t>41.98</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>-3.00</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>9.23</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10.54</t>
+          <t>13.91</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,77 +2758,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>427</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>49.45</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>76.15</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>6.43</t>
+          <t>6.58</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>5.70</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>70.66</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>66.24</t>
+          <t>66.3</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>66.75</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>63.02</t>
+          <t>63.15</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>262.06</t>
+          <t>125.60</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-88.05</t>
+          <t>-82.57</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>75275336.41163793</t>
+          <t>75226946.41032998</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>82950382.0</t>
+          <t>106177736.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>132496129.6</t>
+          <t>132561832.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>86336133.4</t>
+          <t>93365555.7</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>120394266.18</t>
+          <t>120263879.18</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>46159996</t>
+          <t>39196276</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-3742417.326026477</t>
+          <t>-2157550.973595275</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>6943645.052739069</t>
+          <t>6559213.964776337</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>82950382</v>
+        <v>106177736</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>50.11</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2956,17 +2956,17 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>91.55</t>
+          <t>90.14</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>46.75</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>7712</t>
+          <t>7594</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>67.9</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1393.968</t>
+          <t>1168.47</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-10.62</t>
+          <t>-10.94</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>61.27</t>
+          <t>53.47</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>10.62</t>
+          <t>9.23</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12.58</t>
+          <t>10.54</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,77 +3194,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>427</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>6.43</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>69.38</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>66.06</t>
+          <t>66.24</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>66.34</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>62.79</t>
+          <t>63.02</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>768.32</t>
+          <t>262.06</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-95.88</t>
+          <t>-88.05</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>75275336.41163793</t>
+          <t>75226946.41032998</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>100281347.0</t>
+          <t>82950382.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>131264222.4</t>
+          <t>132496129.6</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>81393410.0</t>
+          <t>86336133.4</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>119695734.58</t>
+          <t>120394266.18</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>49870812</t>
+          <t>46159996</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-5685337.758529304</t>
+          <t>-3742417.326026477</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>9733490.069373712</t>
+          <t>6943645.052739069</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>100281347</v>
+        <v>82950382</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>52.01</t>
+          <t>50.11</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3392,17 +3392,17 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>91.55</t>
+          <t>90.14</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>46.75</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>7712</t>
+          <t>7594</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2657.246</t>
+          <t>1393.968</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-11.54</t>
+          <t>-12.34</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>59.46</t>
+          <t>61.27</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>11.54</t>
+          <t>10.62</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>23.97</t>
+          <t>12.58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,77 +3630,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>427</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>6.65</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>5.60</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>67.98</t>
+          <t>69.38</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>65.84</t>
+          <t>66.06</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>66.06</t>
+          <t>66.34</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>62.56</t>
+          <t>62.79</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>686.39</t>
+          <t>768.32</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-103.80</t>
+          <t>-95.88</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>75275336.41163793</t>
+          <t>75226946.41032998</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>190606270.0</t>
+          <t>100281347.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>118462794.8</t>
+          <t>131264222.4</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>74290109.7</t>
+          <t>81393410.0</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>120126016.38</t>
+          <t>119695734.58</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>44172685</t>
+          <t>49870812</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-8488760.999966215</t>
+          <t>-5685337.758529304</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>11514469.19780271</t>
+          <t>9733490.069373712</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>190606270</v>
+        <v>100281347</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>53.28</t>
+          <t>52.01</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>91.55</t>
+          <t>90.14</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>46.75</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>7712</t>
+          <t>7594</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
+          <t>71.2</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
           <t>70.6</t>
         </is>
       </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>72.8</t>
-        </is>
-      </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>69.7</t>
-        </is>
-      </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2598.844</t>
+          <t>2657.246</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,74 +3950,74 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>72.5</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-13.28</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>-1.85</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>59.46</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2025-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2025-09-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>70.0</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>-7.69</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>-2.09</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>46.05</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2025-11-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2025-09-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>70.0</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
       <c r="T9" t="inlineStr">
         <is>
           <t>67.8</t>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>11.54</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>23.45</t>
+          <t>23.97</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,12 +4066,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>427</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4086,57 +4086,57 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>5.80</t>
+          <t>6.65</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>5.60</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>66.16</t>
+          <t>67.98</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>65.64</t>
+          <t>65.84</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>65.73</t>
+          <t>66.06</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>62.31</t>
+          <t>62.56</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>122.79</t>
+          <t>686.39</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-110.31</t>
+          <t>-103.80</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>75275336.41163793</t>
+          <t>75226946.41032998</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>182793426.0</t>
+          <t>190606270.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>85235906.2</t>
+          <t>118462794.8</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>58360010.8</t>
+          <t>74290109.7</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>117218867.38</t>
+          <t>120126016.38</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>26875895</t>
+          <t>44172685</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-12125711.94501511</t>
+          <t>-8488760.999966215</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>3969823.731351182</t>
+          <t>11514469.19780271</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>182793426</v>
+        <v>190606270</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>47.99</t>
+          <t>53.28</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4264,17 +4264,17 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>91.55</t>
+          <t>90.14</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>46.75</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>7712</t>
+          <t>7594</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>70.6</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1558.105</t>
+          <t>2598.844</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>67.1</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,22 +4396,22 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>-9.38</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>24.49</t>
+          <t>46.05</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14.06</t>
+          <t>23.45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,12 +4502,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>427</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4517,62 +4517,62 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>94.25</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>5.80</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>5.49</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>64.66</t>
+          <t>66.16</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>65.52</t>
+          <t>65.64</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>65.47</t>
+          <t>65.73</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>62.1</t>
+          <t>62.31</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>122.79</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-113.47</t>
+          <t>-110.31</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,50 +4592,50 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>75275336.41163793</t>
+          <t>75226946.41032998</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>105849223.0</t>
+          <t>182793426.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>54169279.2</t>
+          <t>85235906.2</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>43512116.9</t>
+          <t>58360010.8</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>113935358.54</t>
+          <t>117218867.38</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>10657162</t>
+          <t>26875895</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-15052172.97708171</t>
+          <t>-12125711.94501511</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-6112930.21112781</t>
+          <t>3969823.731351182</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>105849223</v>
+        <v>182793426</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>41.86</t>
+          <t>47.99</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4705,12 +4705,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>91.55</t>
+          <t>90.14</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>46.75</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>7712</t>
+          <t>7594</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>67.1</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1161.669</t>
+          <t>1558.105</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>65.4</t>
+          <t>67.1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-4.84</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>11.47</t>
+          <t>24.49</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10.48</t>
+          <t>14.06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.60</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,12 +4938,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>427</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4953,57 +4953,57 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>70.01</t>
+          <t>94.25</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>5.35</t>
+          <t>5.42</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>63.86000000000001</t>
+          <t>64.66</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>65.67</t>
+          <t>65.52</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>65.26</t>
+          <t>65.47</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>61.95</t>
+          <t>62.1</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-65.80</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>75275336.41163793</t>
+          <t>75226946.41032998</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>76790846.0</t>
+          <t>105849223.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>40176137.2</t>
+          <t>54169279.2</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>36041288.8</t>
+          <t>43512116.9</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>112225732.82</t>
+          <t>113935358.54</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>4134848</t>
+          <t>10657162</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-16677489.84361878</t>
+          <t>-15052172.97708171</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-12054523.72855752</t>
+          <t>-6112930.21112781</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>76790846</v>
+        <v>105849223</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>38.27</t>
+          <t>41.86</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>91.55</t>
+          <t>90.14</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>46.75</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>7712</t>
+          <t>7594</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>65.1</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>67.4</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>65.1</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>65.4</t>
+          <t>67.1</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>562.661</t>
+          <t>1161.669</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>64.9</t>
+          <t>65.4</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>11.47</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>10.48</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>-2.60</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,77 +5374,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>427</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>82.76</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>36.68</t>
+          <t>70.01</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.82</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>5.35</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>63.5</t>
+          <t>63.86000000000001</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>66.03</t>
+          <t>65.67</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>65.08</t>
+          <t>65.26</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>61.76</t>
+          <t>61.95</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-137.89</t>
+          <t>-65.80</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-111.26</t>
+          <t>-113.47</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>75275336.41163793</t>
+          <t>75226946.41032998</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>36274209.0</t>
+          <t>76790846.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>31522597.6</t>
+          <t>40176137.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>31905787.9</t>
+          <t>36041288.8</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>111064675.6</t>
+          <t>112225732.82</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-383190</t>
+          <t>4134848</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-17518029.13726628</t>
+          <t>-16677489.84361878</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-16998598.2274372</t>
+          <t>-12054523.72855752</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>36274209</v>
+        <v>76790846</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>37.21</t>
+          <t>38.27</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>91.55</t>
+          <t>90.14</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>46.75</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>7712</t>
+          <t>7594</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>63.4</t>
+          <t>65.1</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
+          <t>67.4</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
+          <t>65.1</t>
+        </is>
+      </c>
+      <c r="CG12" t="inlineStr">
+        <is>
           <t>65.4</t>
-        </is>
-      </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>63.4</t>
-        </is>
-      </c>
-      <c r="CG12" t="inlineStr">
-        <is>
-          <t>64.9</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-4.5</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>4791.0</t>
+          <t>2408.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-31.67</t>
+          <t>-34.72</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>8.27</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5810,77 +5810,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>4791</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>15.46</t>
+          <t>16.11</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-2.71</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>57.62</t>
+          <t>57.36</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>58.66</t>
+          <t>58.46</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>60.11</t>
+          <t>60.09</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>57.83</t>
+          <t>57.91</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-36.02</t>
+          <t>-36.35</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-109.54</t>
+          <t>-110.50</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5900,46 +5900,46 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>816801.7154178674</t>
+          <t>815920.4784172662</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>273475.0</t>
+          <t>136228.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>241628.6</t>
+          <t>212208.6</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>353601.2</t>
+          <t>325088.9</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>558552.82</t>
+          <t>556448.64</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-111972</t>
+          <t>-112880</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-34739.56216577447</t>
+          <t>-35122.32563935201</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-29935.8845248259</t>
+          <t>-37227.52474402849</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>273475</v>
+        <v>136228</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-3.57</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>24.17</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>33496</t>
+          <t>33854</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6068,22 +6068,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>58.7</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>-4.5</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>4747.0</t>
+          <t>4791.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6140,17 +6140,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-31.52</t>
+          <t>-31.67</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>8.19</t>
+          <t>8.27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6246,147 +6246,147 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>4791</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>19.01</t>
+          <t>15.46</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-2.1</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>58.17999999999999</t>
+          <t>57.62</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
+          <t>58.66</t>
+        </is>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>60.11</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>57.83</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>-36.02</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>-0.69</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>-0.51</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>5.31</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>-109.54</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>815920.4784172662</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>273475.0</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>241628.6</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>353601.2</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>558552.82</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>-111972</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>-34739.56216577447</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>-29935.8845248259</t>
+        </is>
+      </c>
+      <c r="BD14" t="n">
+        <v>273475</v>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
           <t>58.9</t>
         </is>
       </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>60.16</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>57.77</t>
-        </is>
-      </c>
-      <c r="AP14" t="inlineStr">
-        <is>
-          <t>-14.48</t>
-        </is>
-      </c>
-      <c r="AQ14" t="inlineStr">
-        <is>
-          <t>-0.53</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>-0.46</t>
-        </is>
-      </c>
-      <c r="AS14" t="inlineStr">
-        <is>
-          <t>5.31</t>
-        </is>
-      </c>
-      <c r="AT14" t="inlineStr">
-        <is>
-          <t>-108.68</t>
-        </is>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV14" t="inlineStr">
-        <is>
-          <t>816801.7154178674</t>
-        </is>
-      </c>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>278164.0</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>235377.2</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>343709.9</t>
-        </is>
-      </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>560862.08</t>
-        </is>
-      </c>
-      <c r="BA14" t="inlineStr">
-        <is>
-          <t>-108332</t>
-        </is>
-      </c>
-      <c r="BB14" t="inlineStr">
-        <is>
-          <t>-35612.95810049239</t>
-        </is>
-      </c>
-      <c r="BC14" t="inlineStr">
-        <is>
-          <t>-33155.15262150689</t>
-        </is>
-      </c>
-      <c r="BD14" t="n">
-        <v>278164</v>
-      </c>
-      <c r="BE14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF14" t="inlineStr">
-        <is>
-          <t>58.9</t>
-        </is>
-      </c>
       <c r="BG14" t="inlineStr">
         <is>
           <t>2025/08/29</t>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6439,22 +6439,22 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>24.17</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>33496</t>
+          <t>33854</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6504,22 +6504,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>58.7</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>57.9</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3082.0</t>
+          <t>4747.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6576,17 +6576,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-33.50</t>
+          <t>-31.52</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>8.19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6682,77 +6682,77 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>4791</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>13.04</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>19.01</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-2.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>58.38000000000001</t>
+          <t>58.17999999999999</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>59.01</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>60.14</t>
+          <t>60.16</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>57.69</t>
+          <t>57.77</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-30.25</t>
+          <t>-14.48</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-108.37</t>
+          <t>-108.68</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6772,46 +6772,46 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>816801.7154178674</t>
+          <t>815920.4784172662</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>178445.0</t>
+          <t>278164.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>221675.6</t>
+          <t>235377.2</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>333361.3</t>
+          <t>343709.9</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>566147.36</t>
+          <t>560862.08</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-111685</t>
+          <t>-108332</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-36059.8318239443</t>
+          <t>-35612.95810049239</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-37072.38730885455</t>
+          <t>-33155.15262150689</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>178445</v>
+        <v>278164</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6875,22 +6875,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>24.17</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>33496</t>
+          <t>33854</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6940,22 +6940,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.9</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>3352.0</t>
+          <t>3082.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7012,17 +7012,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-15.27</t>
+          <t>-33.50</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7118,147 +7118,147 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>4791</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>10.64</t>
+          <t>13.04</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
+          <t>58.38000000000001</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>59.01</t>
+        </is>
+      </c>
+      <c r="AN16" t="inlineStr">
+        <is>
+          <t>60.14</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>57.69</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>-30.25</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>-0.58</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>-0.44</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>5.31</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr">
+        <is>
+          <t>-108.37</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>815920.4784172662</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>178445.0</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>221675.6</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>333361.3</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>566147.36</t>
+        </is>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>-111685</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>-36059.8318239443</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>-37072.38730885455</t>
+        </is>
+      </c>
+      <c r="BD16" t="n">
+        <v>178445</v>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
           <t>58.9</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>59.24</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>60.11</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>57.62</t>
-        </is>
-      </c>
-      <c r="AP16" t="inlineStr">
-        <is>
-          <t>-24.96</t>
-        </is>
-      </c>
-      <c r="AQ16" t="inlineStr">
-        <is>
-          <t>-0.51</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>-0.41</t>
-        </is>
-      </c>
-      <c r="AS16" t="inlineStr">
-        <is>
-          <t>5.31</t>
-        </is>
-      </c>
-      <c r="AT16" t="inlineStr">
-        <is>
-          <t>-107.74</t>
-        </is>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV16" t="inlineStr">
-        <is>
-          <t>816801.7154178674</t>
-        </is>
-      </c>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>194731.0</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>289419.6</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>341561.2</t>
-        </is>
-      </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>568481.84</t>
-        </is>
-      </c>
-      <c r="BA16" t="inlineStr">
-        <is>
-          <t>-52141</t>
-        </is>
-      </c>
-      <c r="BB16" t="inlineStr">
-        <is>
-          <t>-35875.73082668789</t>
-        </is>
-      </c>
-      <c r="BC16" t="inlineStr">
-        <is>
-          <t>-30660.24445832073</t>
-        </is>
-      </c>
-      <c r="BD16" t="n">
-        <v>194731</v>
-      </c>
-      <c r="BE16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF16" t="inlineStr">
-        <is>
-          <t>58.9</t>
-        </is>
-      </c>
       <c r="BG16" t="inlineStr">
         <is>
           <t>2025/08/29</t>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7311,7 +7311,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7321,12 +7321,12 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>24.17</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>33496</t>
+          <t>33854</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7376,22 +7376,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>4870.0</t>
+          <t>3352.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,72 +7438,72 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
+          <t>57.4</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-1.06</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>-2.03</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>-15.27</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2025-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
           <t>58.1</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>-3.38</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>-0.55</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>22.85</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>2025-10-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>58.1</t>
-        </is>
-      </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
@@ -7518,12 +7518,12 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>8.40</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7554,77 +7554,77 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>4791</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>40.68</t>
+          <t>10.64</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>55.37</t>
+          <t>35.75</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>59.73999999999999</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>59.51</t>
+          <t>59.24</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>60.1</t>
+          <t>60.11</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>57.55</t>
+          <t>57.62</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-24.96</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-107.25</t>
+          <t>-107.74</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7644,50 +7644,50 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>816801.7154178674</t>
+          <t>815920.4784172662</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>283328.0</t>
+          <t>194731.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>437969.2</t>
+          <t>289419.6</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>356514.8</t>
+          <t>341561.2</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>570563.3</t>
+          <t>568481.84</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>81454</t>
+          <t>-52141</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-36824.00107548192</t>
+          <t>-35875.73082668789</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-22149.96022690379</t>
+          <t>-30660.24445832073</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>283328</v>
+        <v>194731</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>24.17</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>33496</t>
+          <t>33854</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7812,22 +7812,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>57.2</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7859,127 +7859,127 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>-1.51</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>4870.0</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-2.29</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-2.03</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>22.85</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2025-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>-1.53</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>-4.07</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>8.40</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
           <t>-1.35</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>4060.0</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>-4.98</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>-0.55</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>36.21</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>2025-10-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>58.1</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>59.6</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>61.5</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>-4.07</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>7.01</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>-1.86</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7990,77 +7990,77 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>4791</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>55.93</t>
+          <t>40.68</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>67.23</t>
+          <t>55.37</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>60.12</t>
+          <t>59.73999999999999</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>59.74</t>
+          <t>59.51</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>60.09</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>57.46</t>
+          <t>57.55</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>14.66</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-107.17</t>
+          <t>-107.25</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -8080,46 +8080,46 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>816801.7154178674</t>
+          <t>815920.4784172662</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>242218.0</t>
+          <t>283328.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>465573.8</t>
+          <t>437969.2</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>341803.5</t>
+          <t>356514.8</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>579417.88</t>
+          <t>570563.3</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>123770</t>
+          <t>81454</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-39492.00850249613</t>
+          <t>-36824.00107548192</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-18693.87703106157</t>
+          <t>-22149.96022690379</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>242218</v>
+        <v>283328</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8183,22 +8183,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>24.17</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>33496</t>
+          <t>33854</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8248,22 +8248,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>59.3</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>60.6</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>3505.0</t>
+          <t>4060.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8320,22 +8320,22 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-6.41</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>36.21</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -8375,7 +8375,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8426,77 +8426,77 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>4791</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>69.49</t>
+          <t>55.93</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>81.92</t>
+          <t>67.23</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>59.72000000000001</t>
+          <t>60.12</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>59.98</t>
+          <t>59.74</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>60.1</t>
+          <t>60.09</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>57.38</t>
+          <t>57.46</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>20.51</t>
+          <t>14.66</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-107.44</t>
+          <t>-107.17</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8516,50 +8516,50 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>816801.7154178674</t>
+          <t>815920.4784172662</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>209656.0</t>
+          <t>242218.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>452042.6</t>
+          <t>465573.8</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>332281.8</t>
+          <t>341803.5</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>596784.86</t>
+          <t>579417.88</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>119760</t>
+          <t>123770</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-43273.48695184787</t>
+          <t>-39492.00850249613</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-8684.334000177623</t>
+          <t>-18693.87703106157</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>209656</v>
+        <v>242218</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr">
@@ -8574,7 +8574,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8619,22 +8619,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>24.17</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>33496</t>
+          <t>33854</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8684,22 +8684,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>60.1</t>
+          <t>59.3</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8540.0</t>
+          <t>3505.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>60.2</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8756,17 +8756,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-7.12</t>
+          <t>-5.28</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>30.92</t>
+          <t>36.04</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14.74</t>
+          <t>6.05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8862,77 +8862,77 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>4791</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>76.27</t>
+          <t>69.49</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>91.33</t>
+          <t>81.92</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>59.14</t>
+          <t>59.72000000000001</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>60.09</t>
+          <t>59.98</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>60.08</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>57.31</t>
+          <t>57.38</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>9.30</t>
+          <t>20.51</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-107.82</t>
+          <t>-107.44</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8952,46 +8952,46 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>816801.7154178674</t>
+          <t>815920.4784172662</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>517165.0</t>
+          <t>209656.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>445047.0</t>
+          <t>452042.6</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>339942.5</t>
+          <t>332281.8</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>643736.64</t>
+          <t>596784.86</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>105104</t>
+          <t>119760</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-49562.42385215155</t>
+          <t>-43273.48695184787</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>9413.953686805733</t>
+          <t>-8684.334000177623</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>517165</v>
+        <v>209656</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -9055,22 +9055,22 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>24.17</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>33496</t>
+          <t>33854</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9120,22 +9120,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>61.7</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>61.8</t>
+          <t>60.4</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>59.6</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>60.2</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>15157.0</t>
+          <t>8540.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.6</t>
+          <t>60.2</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9192,17 +9192,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-9.61</t>
+          <t>-5.99</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>29.74</t>
+          <t>30.92</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>14.74</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9298,47 +9298,47 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>4791</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>76.27</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>75.54</t>
+          <t>91.33</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>5.77</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>58.24000000000001</t>
+          <t>59.14</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
@@ -9353,22 +9353,22 @@
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>57.24</t>
+          <t>57.31</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-15.74</t>
+          <t>9.30</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-108.00</t>
+          <t>-107.82</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,46 +9388,46 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>816801.7154178674</t>
+          <t>815920.4784172662</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>937479.0</t>
+          <t>517165.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>393702.8</t>
+          <t>445047.0</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>303455.3</t>
+          <t>339942.5</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>659423.84</t>
+          <t>643736.64</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>90247</t>
+          <t>105104</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-60285.40158650742</t>
+          <t>-49562.42385215155</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>1985.044893681828</t>
+          <t>9413.953686805733</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>937479</v>
+        <v>517165</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9501,12 +9501,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>24.17</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>33496</t>
+          <t>33854</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9556,22 +9556,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>60.5</t>
+          <t>61.7</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>63.2</t>
+          <t>61.8</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>59.6</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>61.6</t>
+          <t>60.2</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>7091.0</t>
+          <t>15157.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>61.6</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9628,17 +9628,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-6.76</t>
+          <t>-8.45</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>17.44</t>
+          <t>29.74</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12.24</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9734,77 +9734,77 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>4791</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>97.73</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>50.21</t>
+          <t>75.54</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>5.77</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-3.09</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>57.26000000000001</t>
+          <t>58.24000000000001</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>60.13</t>
+          <t>60.09</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>59.94</t>
+          <t>60.08</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>57.24</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-89.66</t>
+          <t>-15.74</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-107.68</t>
+          <t>-108.00</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,46 +9824,46 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>816801.7154178674</t>
+          <t>815920.4784172662</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>421351.0</t>
+          <t>937479.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>275060.4</t>
+          <t>393702.8</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>234213.9</t>
+          <t>303455.3</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>643815.04</t>
+          <t>659423.84</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>40846</t>
+          <t>90247</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-71607.30094654183</t>
+          <t>-60285.40158650742</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-53732.21927126963</t>
+          <t>1985.044893681828</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>421351</v>
+        <v>937479</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>24.17</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>33496</t>
+          <t>33854</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9992,22 +9992,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>60.5</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>60.2</t>
+          <t>63.2</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>61.6</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3057.0</t>
+          <t>7091.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10064,17 +10064,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-5.63</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>17.44</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>12.24</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10170,77 +10170,77 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>4791</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>97.73</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>17.63</t>
+          <t>50.21</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-5.40</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>57.04</t>
+          <t>57.26000000000001</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>60.3</t>
+          <t>60.13</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>59.83</t>
+          <t>59.94</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>57.06</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-203.28</t>
+          <t>-89.66</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-105.96</t>
+          <t>-107.68</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10260,46 +10260,46 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>816801.7154178674</t>
+          <t>815920.4784172662</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>174562.0</t>
+          <t>421351.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>218033.2</t>
+          <t>275060.4</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>218350.5</t>
+          <t>234213.9</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>642009.16</t>
+          <t>643815.04</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-317</t>
+          <t>40846</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-74857.31579659131</t>
+          <t>-71607.30094654183</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-76109.8745329406</t>
+          <t>-53732.21927126963</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>174562</v>
+        <v>421351</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>24.17</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>33496</t>
+          <t>33854</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10428,22 +10428,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>57.7</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
+          <t>60.2</t>
+        </is>
+      </c>
+      <c r="CF23" t="inlineStr">
+        <is>
           <t>57.7</t>
         </is>
       </c>
-      <c r="CF23" t="inlineStr">
-        <is>
-          <t>56.4</t>
-        </is>
-      </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料).xlsx
+++ b/Result/checksun_type/濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料).xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CJ23"/>
+  <dimension ref="A1:CJ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>427.384</t>
+          <t>436.423</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>64.1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-44.43</t>
+          <t>-57.89</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,77 +1014,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>427</t>
+          <t>436</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>65.24000000000001</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>66.14</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>66.9</t>
+          <t>66.84</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>63.56</t>
+          <t>63.67</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-72.20</t>
+          <t>-128.59</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-83.03</t>
+          <t>-87.16</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>75226946.41032998</t>
+          <t>75179432.90759313</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>27698337.0</t>
+          <t>28041681.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>50976888.8</t>
+          <t>35349677.8</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>91736509.2</t>
+          <t>83955755.0</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>107077260.2</t>
+          <t>105161801.84</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-40759620</t>
+          <t>-48606077</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-3170586.423594275</t>
+          <t>-4140084.045800703</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-7866289.16186586</t>
+          <t>-9472320.967936054</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>27698337</v>
+        <v>28041681</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>35.31</t>
+          <t>35.52</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>90.14</t>
+          <t>90.28</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>46.75</t>
+          <t>48.67</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>7594</t>
+          <t>7605</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>64.7</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>63.5</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>64.1</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-3.15</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>677.83</t>
+          <t>427.384</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,72 +1334,72 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>64.0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.16</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-1.01</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-44.43</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-09-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
           <t>65.0</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>-1.56</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>-1.85</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>-35.82</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-11-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-09-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1414,12 +1414,12 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>-7.14</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,12 +1450,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>427</t>
+          <t>436</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1465,62 +1465,62 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>12.81</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>5.55</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>67.4</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>66.28</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>66.98</t>
+          <t>66.9</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>63.46</t>
+          <t>63.56</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-21.43</t>
+          <t>-72.20</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-79.97</t>
+          <t>-83.03</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,50 +1540,50 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>75226946.41032998</t>
+          <t>75179432.90759313</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>44220240.0</t>
+          <t>27698337.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>62027297.8</t>
+          <t>50976888.8</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>96645760.1</t>
+          <t>91736509.2</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>113463276.16</t>
+          <t>107077260.2</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-34618462</t>
+          <t>-40759620</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-2316822.289363078</t>
+          <t>-3170586.423594275</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-5254232.254556075</t>
+          <t>-7866289.16186586</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>44220240</v>
+        <v>27698337</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>37.42</t>
+          <t>35.31</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>90.14</t>
+          <t>90.28</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>46.75</t>
+          <t>48.67</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>7594</t>
+          <t>7605</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>64.3</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>-3.15</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>412.165</t>
+          <t>677.83</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>67.1</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-23.59</t>
+          <t>-35.82</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-7.14</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,52 +1886,52 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>427</t>
+          <t>436</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>23.94</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>29.29</t>
+          <t>12.81</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>5.55</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>68.78000000000002</t>
+          <t>67.4</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>66.31</t>
+          <t>66.28</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -1941,22 +1941,22 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>63.36</t>
+          <t>63.46</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>21.92</t>
+          <t>-21.43</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-78.90</t>
+          <t>-79.97</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>75226946.41032998</t>
+          <t>75179432.90759313</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>27736728.0</t>
+          <t>44220240.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>73239519.2</t>
+          <t>62027297.8</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>95851157.0</t>
+          <t>96645760.1</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>115231412.04</t>
+          <t>113463276.16</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-22611637</t>
+          <t>-34618462</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-1782747.750237079</t>
+          <t>-2316822.289363078</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-3105275.127879396</t>
+          <t>-5254232.254556075</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>27736728</v>
+        <v>44220240</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>41.86</t>
+          <t>37.42</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,17 +2079,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>90.14</t>
+          <t>90.28</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>46.75</t>
+          <t>48.67</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>7594</t>
+          <t>7605</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>67.9</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>67.9</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>66.5</t>
+          <t>64.3</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>67.1</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>735.417</t>
+          <t>412.165</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-3.12</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>10.77</t>
+          <t>-23.59</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>-5.71</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,77 +2322,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>427</t>
+          <t>436</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>14.47</t>
+          <t>23.94</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>49.64</t>
+          <t>29.29</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-5.53</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>5.80</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>69.86000000000001</t>
+          <t>68.78000000000002</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>66.24</t>
+          <t>66.31</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>66.9</t>
+          <t>66.98</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>63.24</t>
+          <t>63.36</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>50.55</t>
+          <t>21.92</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-80.05</t>
+          <t>-78.90</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>75226946.41032998</t>
+          <t>75179432.90759313</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>49051403.0</t>
+          <t>27736728.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>105813427.6</t>
+          <t>73239519.2</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>95524666.9</t>
+          <t>95851157.0</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>120066640.9</t>
+          <t>115231412.04</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>10288760</t>
+          <t>-22611637</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-1542288.227029385</t>
+          <t>-1782747.750237079</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>1841656.879083008</t>
+          <t>-3105275.127879396</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>49051403</v>
+        <v>27736728</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>39.53</t>
+          <t>41.86</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,17 +2515,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>90.14</t>
+          <t>90.28</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>46.75</t>
+          <t>48.67</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>7594</t>
+          <t>7605</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>68.6</t>
+          <t>67.9</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>68.6</t>
+          <t>67.9</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>66.5</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.1</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1542.065</t>
+          <t>735.417</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>67.9</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-6.09</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>41.98</t>
+          <t>10.77</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>-3.00</t>
+          <t>-5.71</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13.91</t>
+          <t>6.63</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,77 +2758,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>427</t>
+          <t>436</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>49.45</t>
+          <t>14.47</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>76.15</t>
+          <t>49.64</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-5.53</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>5.70</t>
+          <t>5.80</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>70.66</t>
+          <t>69.86000000000001</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>66.3</t>
+          <t>66.24</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>66.75</t>
+          <t>66.9</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>63.15</t>
+          <t>63.24</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>125.60</t>
+          <t>50.55</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-82.57</t>
+          <t>-80.05</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>75226946.41032998</t>
+          <t>75179432.90759313</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>106177736.0</t>
+          <t>49051403.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>132561832.2</t>
+          <t>105813427.6</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>93365555.7</t>
+          <t>95524666.9</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>120263879.18</t>
+          <t>120066640.9</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>39196276</t>
+          <t>10288760</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-2157550.973595275</t>
+          <t>-1542288.227029385</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>6559213.964776337</t>
+          <t>1841656.879083008</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>106177736</v>
+        <v>49051403</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>39.53</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2951,17 +2951,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>90.14</t>
+          <t>90.28</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>46.75</t>
+          <t>48.67</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>7594</t>
+          <t>7605</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>67.9</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1168.47</t>
+          <t>1542.065</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>67.9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-10.94</t>
+          <t>-5.93</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>53.47</t>
+          <t>41.98</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>-3.00</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>9.23</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10.54</t>
+          <t>13.91</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,77 +3194,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>427</t>
+          <t>436</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>49.45</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>76.15</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>6.43</t>
+          <t>6.58</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>5.70</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>70.66</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>66.24</t>
+          <t>66.3</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>66.75</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>63.02</t>
+          <t>63.15</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>262.06</t>
+          <t>125.60</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-88.05</t>
+          <t>-82.57</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>75226946.41032998</t>
+          <t>75179432.90759313</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>82950382.0</t>
+          <t>106177736.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>132496129.6</t>
+          <t>132561832.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>86336133.4</t>
+          <t>93365555.7</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>120394266.18</t>
+          <t>120263879.18</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>46159996</t>
+          <t>39196276</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-3742417.326026477</t>
+          <t>-2157550.973595275</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>6943645.052739069</t>
+          <t>6559213.964776337</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>82950382</v>
+        <v>106177736</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>50.11</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>90.14</t>
+          <t>90.28</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>46.75</t>
+          <t>48.67</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>7594</t>
+          <t>7605</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>67.9</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1393.968</t>
+          <t>1168.47</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-12.34</t>
+          <t>-10.76</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>61.27</t>
+          <t>53.47</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>10.62</t>
+          <t>9.23</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12.58</t>
+          <t>10.54</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,77 +3630,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>427</t>
+          <t>436</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>6.43</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>69.38</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>66.06</t>
+          <t>66.24</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>66.34</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>62.79</t>
+          <t>63.02</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>768.32</t>
+          <t>262.06</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-95.88</t>
+          <t>-88.05</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>75226946.41032998</t>
+          <t>75179432.90759313</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>100281347.0</t>
+          <t>82950382.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>131264222.4</t>
+          <t>132496129.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>81393410.0</t>
+          <t>86336133.4</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>119695734.58</t>
+          <t>120394266.18</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>49870812</t>
+          <t>46159996</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-5685337.758529304</t>
+          <t>-3742417.326026477</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>9733490.069373712</t>
+          <t>6943645.052739069</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>100281347</v>
+        <v>82950382</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>52.01</t>
+          <t>50.11</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>90.14</t>
+          <t>90.28</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>46.75</t>
+          <t>48.67</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>7594</t>
+          <t>7605</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2657.246</t>
+          <t>1393.968</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-13.28</t>
+          <t>-12.17</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>59.46</t>
+          <t>61.27</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4030,12 +4030,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>11.54</t>
+          <t>10.62</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>23.97</t>
+          <t>12.58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,77 +4066,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>427</t>
+          <t>436</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>6.65</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>5.60</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>67.98</t>
+          <t>69.38</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>65.84</t>
+          <t>66.06</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>66.06</t>
+          <t>66.34</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>62.56</t>
+          <t>62.79</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>686.39</t>
+          <t>768.32</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-103.80</t>
+          <t>-95.88</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>75226946.41032998</t>
+          <t>75179432.90759313</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>190606270.0</t>
+          <t>100281347.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>118462794.8</t>
+          <t>131264222.4</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>74290109.7</t>
+          <t>81393410.0</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>120126016.38</t>
+          <t>119695734.58</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>44172685</t>
+          <t>49870812</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-8488760.999966215</t>
+          <t>-5685337.758529304</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>11514469.19780271</t>
+          <t>9733490.069373712</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>190606270</v>
+        <v>100281347</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>53.28</t>
+          <t>52.01</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4259,17 +4259,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>90.14</t>
+          <t>90.28</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>46.75</t>
+          <t>48.67</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>7594</t>
+          <t>7605</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
+          <t>71.2</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
           <t>70.6</t>
         </is>
       </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>72.8</t>
-        </is>
-      </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>69.7</t>
-        </is>
-      </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2598.844</t>
+          <t>2657.246</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,74 +4386,74 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>72.5</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-13.1</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>-1.01</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>59.46</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2025-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2025-09-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>70.0</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>-9.38</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>-1.85</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>46.05</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2025-11-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2025-09-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>70.0</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
       <c r="T10" t="inlineStr">
         <is>
           <t>67.8</t>
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>11.54</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>23.45</t>
+          <t>23.97</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,12 +4502,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>427</t>
+          <t>436</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4522,57 +4522,57 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>5.80</t>
+          <t>6.65</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>5.60</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>66.16</t>
+          <t>67.98</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>65.64</t>
+          <t>65.84</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>65.73</t>
+          <t>66.06</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>62.31</t>
+          <t>62.56</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>122.79</t>
+          <t>686.39</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-110.31</t>
+          <t>-103.80</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>75226946.41032998</t>
+          <t>75179432.90759313</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>182793426.0</t>
+          <t>190606270.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>85235906.2</t>
+          <t>118462794.8</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>58360010.8</t>
+          <t>74290109.7</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>117218867.38</t>
+          <t>120126016.38</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>26875895</t>
+          <t>44172685</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-12125711.94501511</t>
+          <t>-8488760.999966215</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>3969823.731351182</t>
+          <t>11514469.19780271</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>182793426</v>
+        <v>190606270</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>47.99</t>
+          <t>53.28</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4705,7 +4705,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>90.14</t>
+          <t>90.28</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>46.75</t>
+          <t>48.67</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>7594</t>
+          <t>7605</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>70.6</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1558.105</t>
+          <t>2598.844</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>67.1</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,22 +4832,22 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-9.2</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>24.49</t>
+          <t>46.05</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -4887,7 +4887,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14.06</t>
+          <t>23.45</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,12 +4938,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>427</t>
+          <t>436</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4953,62 +4953,62 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>94.25</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>5.80</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>5.49</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>64.66</t>
+          <t>66.16</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>65.52</t>
+          <t>65.64</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>65.47</t>
+          <t>65.73</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>62.1</t>
+          <t>62.31</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>122.79</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-113.47</t>
+          <t>-110.31</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,50 +5028,50 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>75226946.41032998</t>
+          <t>75179432.90759313</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>105849223.0</t>
+          <t>182793426.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>54169279.2</t>
+          <t>85235906.2</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>43512116.9</t>
+          <t>58360010.8</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>113935358.54</t>
+          <t>117218867.38</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>10657162</t>
+          <t>26875895</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-15052172.97708171</t>
+          <t>-12125711.94501511</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-6112930.21112781</t>
+          <t>3969823.731351182</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>105849223</v>
+        <v>182793426</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>41.86</t>
+          <t>47.99</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>90.14</t>
+          <t>90.28</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>46.75</t>
+          <t>48.67</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>7594</t>
+          <t>7605</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>67.1</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1161.669</t>
+          <t>1558.105</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>65.4</t>
+          <t>67.1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>11.47</t>
+          <t>24.49</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10.48</t>
+          <t>14.06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.60</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,12 +5374,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>427</t>
+          <t>436</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5389,57 +5389,57 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>70.01</t>
+          <t>94.25</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>5.35</t>
+          <t>5.42</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>63.86000000000001</t>
+          <t>64.66</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>65.67</t>
+          <t>65.52</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>65.26</t>
+          <t>65.47</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>61.95</t>
+          <t>62.1</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-65.80</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>75226946.41032998</t>
+          <t>75179432.90759313</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>76790846.0</t>
+          <t>105849223.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>40176137.2</t>
+          <t>54169279.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>36041288.8</t>
+          <t>43512116.9</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>112225732.82</t>
+          <t>113935358.54</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>4134848</t>
+          <t>10657162</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-16677489.84361878</t>
+          <t>-15052172.97708171</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-12054523.72855752</t>
+          <t>-6112930.21112781</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>76790846</v>
+        <v>105849223</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>38.27</t>
+          <t>41.86</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>90.14</t>
+          <t>90.28</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>46.75</t>
+          <t>48.67</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>7594</t>
+          <t>7605</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>65.1</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>67.4</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>65.1</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>65.4</t>
+          <t>67.1</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2408.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>56.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5704,17 +5704,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>-2.03</t>
-        </is>
-      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-34.72</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5724,37 +5724,37 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2025-11-14 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2025-11-17 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2025-09-17 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2025-10-03 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -5764,12 +5764,12 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>59.6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>61.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -5779,167 +5779,167 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>-4.07</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3484</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>16.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-2.71</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>57.36</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>58.46</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>60.09</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>57.91</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-36.35</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-110.50</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>815920.4784172662</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>136228.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>212208.6</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>325088.9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>556448.64</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-112880</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-35122.32563935201</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-37227.52474402849</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>136228</v>
+        <v>0</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -5948,17 +5948,17 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>2025/08/29</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-3.57</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6013,7 +6013,7 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>42.08</t>
+          <t>42.67</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6063,27 +6063,27 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>其他電子業右上上櫃</t>
+          <t>其他電子業右下上櫃</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>56.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6098,4367 +6098,7 @@
       </c>
       <c r="CJ13" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>1785</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>-4.5</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>4791.0</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>56.2</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>1.06</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>-2.03</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>-31.67</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>2025-10-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>58.1</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>59.6</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>61.5</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>-3.27</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>-4.07</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>8.27</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>-4.09</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
           <t>False</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr"/>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>2408</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AG14" t="inlineStr">
-        <is>
-          <t>15.46</t>
-        </is>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>-2.46</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>-1.76</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>-2.42</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>3.95</t>
-        </is>
-      </c>
-      <c r="AL14" t="inlineStr">
-        <is>
-          <t>57.62</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>58.66</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>60.11</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>57.83</t>
-        </is>
-      </c>
-      <c r="AP14" t="inlineStr">
-        <is>
-          <t>-36.02</t>
-        </is>
-      </c>
-      <c r="AQ14" t="inlineStr">
-        <is>
-          <t>-0.69</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>-0.51</t>
-        </is>
-      </c>
-      <c r="AS14" t="inlineStr">
-        <is>
-          <t>5.31</t>
-        </is>
-      </c>
-      <c r="AT14" t="inlineStr">
-        <is>
-          <t>-109.54</t>
-        </is>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV14" t="inlineStr">
-        <is>
-          <t>815920.4784172662</t>
-        </is>
-      </c>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>273475.0</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>241628.6</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>353601.2</t>
-        </is>
-      </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>558552.82</t>
-        </is>
-      </c>
-      <c r="BA14" t="inlineStr">
-        <is>
-          <t>-111972</t>
-        </is>
-      </c>
-      <c r="BB14" t="inlineStr">
-        <is>
-          <t>-34739.56216577447</t>
-        </is>
-      </c>
-      <c r="BC14" t="inlineStr">
-        <is>
-          <t>-29935.8845248259</t>
-        </is>
-      </c>
-      <c r="BD14" t="n">
-        <v>273475</v>
-      </c>
-      <c r="BE14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF14" t="inlineStr">
-        <is>
-          <t>58.9</t>
-        </is>
-      </c>
-      <c r="BG14" t="inlineStr">
-        <is>
-          <t>2025/08/29</t>
-        </is>
-      </c>
-      <c r="BH14" t="inlineStr">
-        <is>
-          <t>-4.58</t>
-        </is>
-      </c>
-      <c r="BI14" t="inlineStr">
-        <is>
-          <t>光洋科</t>
-        </is>
-      </c>
-      <c r="BJ14" t="inlineStr">
-        <is>
-          <t>光洋科</t>
-        </is>
-      </c>
-      <c r="BK14" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL14" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM14" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="BN14" t="inlineStr">
-        <is>
-          <t>-1.228328584465341</t>
-        </is>
-      </c>
-      <c r="BO14" t="inlineStr">
-        <is>
-          <t>47.44460114587924</t>
-        </is>
-      </c>
-      <c r="BP14" t="inlineStr">
-        <is>
-          <t>32.54445648609581</t>
-        </is>
-      </c>
-      <c r="BQ14" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR14" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS14" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
-      </c>
-      <c r="BT14" t="inlineStr">
-        <is>
-          <t>3.52</t>
-        </is>
-      </c>
-      <c r="BU14" t="inlineStr">
-        <is>
-          <t>17.51</t>
-        </is>
-      </c>
-      <c r="BV14" t="inlineStr">
-        <is>
-          <t>24.17</t>
-        </is>
-      </c>
-      <c r="BW14" t="inlineStr">
-        <is>
-          <t>14.09%</t>
-        </is>
-      </c>
-      <c r="BX14" t="inlineStr">
-        <is>
-          <t>9.19%</t>
-        </is>
-      </c>
-      <c r="BY14" t="inlineStr">
-        <is>
-          <t>42.08</t>
-        </is>
-      </c>
-      <c r="BZ14" t="inlineStr">
-        <is>
-          <t>33854</t>
-        </is>
-      </c>
-      <c r="CA14" t="inlineStr">
-        <is>
-          <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB14" t="inlineStr">
-        <is>
-          <t>光洋科-其他電子業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC14" t="inlineStr">
-        <is>
-          <t>其他電子業右上上櫃</t>
-        </is>
-      </c>
-      <c r="CD14" t="inlineStr">
-        <is>
-          <t>57.8</t>
-        </is>
-      </c>
-      <c r="CE14" t="inlineStr">
-        <is>
-          <t>58.7</t>
-        </is>
-      </c>
-      <c r="CF14" t="inlineStr">
-        <is>
-          <t>56.0</t>
-        </is>
-      </c>
-      <c r="CG14" t="inlineStr">
-        <is>
-          <t>56.2</t>
-        </is>
-      </c>
-      <c r="CH14" t="inlineStr">
-        <is>
-          <t>22.98</t>
-        </is>
-      </c>
-      <c r="CI14" t="inlineStr">
-        <is>
-          <t>** 半導體 - 化學品** 電腦及週邊設備 - 硬碟機** 平面顯示器 - 化學品(如光阻劑、靶材等)** 觸控面板 - ITO靶材** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 印刷電路板 - 生產製程及檢測設備** 其他 - 環保潔能服務產業** 汽車 - 其他** 太陽能產業 - 材料</t>
-        </is>
-      </c>
-      <c r="CJ14" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1785</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>2.04</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>4747.0</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>58.8</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>-3.52</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>-2.03</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>-31.52</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>2025-10-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>58.1</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>59.6</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>61.5</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>1.20</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>-4.07</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2025-11-20</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>8.19</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>0.87</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr"/>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>2408</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>33.33</t>
-        </is>
-      </c>
-      <c r="AG15" t="inlineStr">
-        <is>
-          <t>19.01</t>
-        </is>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>1.07</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>-1.21</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>-2.1</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>4.12</t>
-        </is>
-      </c>
-      <c r="AL15" t="inlineStr">
-        <is>
-          <t>58.17999999999999</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>58.9</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>60.16</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>57.77</t>
-        </is>
-      </c>
-      <c r="AP15" t="inlineStr">
-        <is>
-          <t>-14.48</t>
-        </is>
-      </c>
-      <c r="AQ15" t="inlineStr">
-        <is>
-          <t>-0.53</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>-0.46</t>
-        </is>
-      </c>
-      <c r="AS15" t="inlineStr">
-        <is>
-          <t>5.31</t>
-        </is>
-      </c>
-      <c r="AT15" t="inlineStr">
-        <is>
-          <t>-108.68</t>
-        </is>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV15" t="inlineStr">
-        <is>
-          <t>815920.4784172662</t>
-        </is>
-      </c>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>278164.0</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>235377.2</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>343709.9</t>
-        </is>
-      </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>560862.08</t>
-        </is>
-      </c>
-      <c r="BA15" t="inlineStr">
-        <is>
-          <t>-108332</t>
-        </is>
-      </c>
-      <c r="BB15" t="inlineStr">
-        <is>
-          <t>-35612.95810049239</t>
-        </is>
-      </c>
-      <c r="BC15" t="inlineStr">
-        <is>
-          <t>-33155.15262150689</t>
-        </is>
-      </c>
-      <c r="BD15" t="n">
-        <v>278164</v>
-      </c>
-      <c r="BE15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF15" t="inlineStr">
-        <is>
-          <t>58.9</t>
-        </is>
-      </c>
-      <c r="BG15" t="inlineStr">
-        <is>
-          <t>2025/08/29</t>
-        </is>
-      </c>
-      <c r="BH15" t="inlineStr">
-        <is>
-          <t>-0.17</t>
-        </is>
-      </c>
-      <c r="BI15" t="inlineStr">
-        <is>
-          <t>光洋科</t>
-        </is>
-      </c>
-      <c r="BJ15" t="inlineStr">
-        <is>
-          <t>光洋科</t>
-        </is>
-      </c>
-      <c r="BK15" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL15" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM15" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="BN15" t="inlineStr">
-        <is>
-          <t>-1.228328584465341</t>
-        </is>
-      </c>
-      <c r="BO15" t="inlineStr">
-        <is>
-          <t>47.44460114587924</t>
-        </is>
-      </c>
-      <c r="BP15" t="inlineStr">
-        <is>
-          <t>32.54445648609581</t>
-        </is>
-      </c>
-      <c r="BQ15" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR15" t="inlineStr">
-        <is>
-          <t>價漲量-</t>
-        </is>
-      </c>
-      <c r="BS15" t="inlineStr">
-        <is>
-          <t>2.56</t>
-        </is>
-      </c>
-      <c r="BT15" t="inlineStr">
-        <is>
-          <t>3.52</t>
-        </is>
-      </c>
-      <c r="BU15" t="inlineStr">
-        <is>
-          <t>17.51</t>
-        </is>
-      </c>
-      <c r="BV15" t="inlineStr">
-        <is>
-          <t>24.17</t>
-        </is>
-      </c>
-      <c r="BW15" t="inlineStr">
-        <is>
-          <t>14.09%</t>
-        </is>
-      </c>
-      <c r="BX15" t="inlineStr">
-        <is>
-          <t>9.19%</t>
-        </is>
-      </c>
-      <c r="BY15" t="inlineStr">
-        <is>
-          <t>42.08</t>
-        </is>
-      </c>
-      <c r="BZ15" t="inlineStr">
-        <is>
-          <t>33854</t>
-        </is>
-      </c>
-      <c r="CA15" t="inlineStr">
-        <is>
-          <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB15" t="inlineStr">
-        <is>
-          <t>光洋科-其他電子業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC15" t="inlineStr">
-        <is>
-          <t>其他電子業右上上櫃</t>
-        </is>
-      </c>
-      <c r="CD15" t="inlineStr">
-        <is>
-          <t>58.8</t>
-        </is>
-      </c>
-      <c r="CE15" t="inlineStr">
-        <is>
-          <t>59.2</t>
-        </is>
-      </c>
-      <c r="CF15" t="inlineStr">
-        <is>
-          <t>57.9</t>
-        </is>
-      </c>
-      <c r="CG15" t="inlineStr">
-        <is>
-          <t>58.8</t>
-        </is>
-      </c>
-      <c r="CH15" t="inlineStr">
-        <is>
-          <t>22.98</t>
-        </is>
-      </c>
-      <c r="CI15" t="inlineStr">
-        <is>
-          <t>** 半導體 - 化學品** 電腦及週邊設備 - 硬碟機** 平面顯示器 - 化學品(如光阻劑、靶材等)** 觸控面板 - ITO靶材** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 印刷電路板 - 生產製程及檢測設備** 其他 - 環保潔能服務產業** 汽車 - 其他** 太陽能產業 - 材料</t>
-        </is>
-      </c>
-      <c r="CJ15" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1785</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>0.34</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>3082.0</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>57.6</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>-1.41</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>-2.03</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>-33.50</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>2025-10-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>58.1</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>59.6</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>61.5</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>-0.86</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>-4.07</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>5.32</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>-1.04</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr"/>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>2408</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>13.04</t>
-        </is>
-      </c>
-      <c r="AG16" t="inlineStr">
-        <is>
-          <t>21.45</t>
-        </is>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>-1.34</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>-1.07</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>-1.87</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>4.23</t>
-        </is>
-      </c>
-      <c r="AL16" t="inlineStr">
-        <is>
-          <t>58.38000000000001</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>59.01</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>60.14</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>57.69</t>
-        </is>
-      </c>
-      <c r="AP16" t="inlineStr">
-        <is>
-          <t>-30.25</t>
-        </is>
-      </c>
-      <c r="AQ16" t="inlineStr">
-        <is>
-          <t>-0.58</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>-0.44</t>
-        </is>
-      </c>
-      <c r="AS16" t="inlineStr">
-        <is>
-          <t>5.31</t>
-        </is>
-      </c>
-      <c r="AT16" t="inlineStr">
-        <is>
-          <t>-108.37</t>
-        </is>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV16" t="inlineStr">
-        <is>
-          <t>815920.4784172662</t>
-        </is>
-      </c>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>178445.0</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>221675.6</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>333361.3</t>
-        </is>
-      </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>566147.36</t>
-        </is>
-      </c>
-      <c r="BA16" t="inlineStr">
-        <is>
-          <t>-111685</t>
-        </is>
-      </c>
-      <c r="BB16" t="inlineStr">
-        <is>
-          <t>-36059.8318239443</t>
-        </is>
-      </c>
-      <c r="BC16" t="inlineStr">
-        <is>
-          <t>-37072.38730885455</t>
-        </is>
-      </c>
-      <c r="BD16" t="n">
-        <v>178445</v>
-      </c>
-      <c r="BE16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF16" t="inlineStr">
-        <is>
-          <t>58.9</t>
-        </is>
-      </c>
-      <c r="BG16" t="inlineStr">
-        <is>
-          <t>2025/08/29</t>
-        </is>
-      </c>
-      <c r="BH16" t="inlineStr">
-        <is>
-          <t>-2.21</t>
-        </is>
-      </c>
-      <c r="BI16" t="inlineStr">
-        <is>
-          <t>光洋科</t>
-        </is>
-      </c>
-      <c r="BJ16" t="inlineStr">
-        <is>
-          <t>光洋科</t>
-        </is>
-      </c>
-      <c r="BK16" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL16" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM16" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="BN16" t="inlineStr">
-        <is>
-          <t>-1.228328584465341</t>
-        </is>
-      </c>
-      <c r="BO16" t="inlineStr">
-        <is>
-          <t>47.44460114587924</t>
-        </is>
-      </c>
-      <c r="BP16" t="inlineStr">
-        <is>
-          <t>32.54445648609581</t>
-        </is>
-      </c>
-      <c r="BQ16" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR16" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS16" t="inlineStr">
-        <is>
-          <t>2.51</t>
-        </is>
-      </c>
-      <c r="BT16" t="inlineStr">
-        <is>
-          <t>3.52</t>
-        </is>
-      </c>
-      <c r="BU16" t="inlineStr">
-        <is>
-          <t>17.51</t>
-        </is>
-      </c>
-      <c r="BV16" t="inlineStr">
-        <is>
-          <t>24.17</t>
-        </is>
-      </c>
-      <c r="BW16" t="inlineStr">
-        <is>
-          <t>14.09%</t>
-        </is>
-      </c>
-      <c r="BX16" t="inlineStr">
-        <is>
-          <t>9.19%</t>
-        </is>
-      </c>
-      <c r="BY16" t="inlineStr">
-        <is>
-          <t>42.08</t>
-        </is>
-      </c>
-      <c r="BZ16" t="inlineStr">
-        <is>
-          <t>33854</t>
-        </is>
-      </c>
-      <c r="CA16" t="inlineStr">
-        <is>
-          <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB16" t="inlineStr">
-        <is>
-          <t>光洋科-其他電子業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC16" t="inlineStr">
-        <is>
-          <t>其他電子業右上上櫃</t>
-        </is>
-      </c>
-      <c r="CD16" t="inlineStr">
-        <is>
-          <t>58.1</t>
-        </is>
-      </c>
-      <c r="CE16" t="inlineStr">
-        <is>
-          <t>58.5</t>
-        </is>
-      </c>
-      <c r="CF16" t="inlineStr">
-        <is>
-          <t>57.3</t>
-        </is>
-      </c>
-      <c r="CG16" t="inlineStr">
-        <is>
-          <t>57.6</t>
-        </is>
-      </c>
-      <c r="CH16" t="inlineStr">
-        <is>
-          <t>22.98</t>
-        </is>
-      </c>
-      <c r="CI16" t="inlineStr">
-        <is>
-          <t>** 半導體 - 化學品** 電腦及週邊設備 - 硬碟機** 平面顯示器 - 化學品(如光阻劑、靶材等)** 觸控面板 - ITO靶材** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 印刷電路板 - 生產製程及檢測設備** 其他 - 環保潔能服務產業** 汽車 - 其他** 太陽能產業 - 材料</t>
-        </is>
-      </c>
-      <c r="CJ16" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1785</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>-1.21</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>3352.0</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>57.4</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>-1.06</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>-2.03</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>-15.27</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>2025-10-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>58.1</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>59.6</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>61.5</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>-1.20</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>-4.07</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>5.78</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>-3.14</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr"/>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>2408</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>10.64</t>
-        </is>
-      </c>
-      <c r="AG17" t="inlineStr">
-        <is>
-          <t>35.75</t>
-        </is>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>-2.55</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>-0.57</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>-1.45</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>4.32</t>
-        </is>
-      </c>
-      <c r="AL17" t="inlineStr">
-        <is>
-          <t>58.9</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>59.24</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>60.11</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>57.62</t>
-        </is>
-      </c>
-      <c r="AP17" t="inlineStr">
-        <is>
-          <t>-24.96</t>
-        </is>
-      </c>
-      <c r="AQ17" t="inlineStr">
-        <is>
-          <t>-0.51</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>-0.41</t>
-        </is>
-      </c>
-      <c r="AS17" t="inlineStr">
-        <is>
-          <t>5.31</t>
-        </is>
-      </c>
-      <c r="AT17" t="inlineStr">
-        <is>
-          <t>-107.74</t>
-        </is>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV17" t="inlineStr">
-        <is>
-          <t>815920.4784172662</t>
-        </is>
-      </c>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>194731.0</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>289419.6</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>341561.2</t>
-        </is>
-      </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>568481.84</t>
-        </is>
-      </c>
-      <c r="BA17" t="inlineStr">
-        <is>
-          <t>-52141</t>
-        </is>
-      </c>
-      <c r="BB17" t="inlineStr">
-        <is>
-          <t>-35875.73082668789</t>
-        </is>
-      </c>
-      <c r="BC17" t="inlineStr">
-        <is>
-          <t>-30660.24445832073</t>
-        </is>
-      </c>
-      <c r="BD17" t="n">
-        <v>194731</v>
-      </c>
-      <c r="BE17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF17" t="inlineStr">
-        <is>
-          <t>58.9</t>
-        </is>
-      </c>
-      <c r="BG17" t="inlineStr">
-        <is>
-          <t>2025/08/29</t>
-        </is>
-      </c>
-      <c r="BH17" t="inlineStr">
-        <is>
-          <t>-2.55</t>
-        </is>
-      </c>
-      <c r="BI17" t="inlineStr">
-        <is>
-          <t>光洋科</t>
-        </is>
-      </c>
-      <c r="BJ17" t="inlineStr">
-        <is>
-          <t>光洋科</t>
-        </is>
-      </c>
-      <c r="BK17" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL17" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM17" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="BN17" t="inlineStr">
-        <is>
-          <t>-1.228328584465341</t>
-        </is>
-      </c>
-      <c r="BO17" t="inlineStr">
-        <is>
-          <t>47.44460114587924</t>
-        </is>
-      </c>
-      <c r="BP17" t="inlineStr">
-        <is>
-          <t>32.54445648609581</t>
-        </is>
-      </c>
-      <c r="BQ17" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
-      <c r="BR17" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS17" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-      <c r="BT17" t="inlineStr">
-        <is>
-          <t>3.52</t>
-        </is>
-      </c>
-      <c r="BU17" t="inlineStr">
-        <is>
-          <t>17.51</t>
-        </is>
-      </c>
-      <c r="BV17" t="inlineStr">
-        <is>
-          <t>24.17</t>
-        </is>
-      </c>
-      <c r="BW17" t="inlineStr">
-        <is>
-          <t>14.09%</t>
-        </is>
-      </c>
-      <c r="BX17" t="inlineStr">
-        <is>
-          <t>9.19%</t>
-        </is>
-      </c>
-      <c r="BY17" t="inlineStr">
-        <is>
-          <t>42.08</t>
-        </is>
-      </c>
-      <c r="BZ17" t="inlineStr">
-        <is>
-          <t>33854</t>
-        </is>
-      </c>
-      <c r="CA17" t="inlineStr">
-        <is>
-          <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB17" t="inlineStr">
-        <is>
-          <t>光洋科-其他電子業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC17" t="inlineStr">
-        <is>
-          <t>其他電子業右上上櫃</t>
-        </is>
-      </c>
-      <c r="CD17" t="inlineStr">
-        <is>
-          <t>58.0</t>
-        </is>
-      </c>
-      <c r="CE17" t="inlineStr">
-        <is>
-          <t>59.2</t>
-        </is>
-      </c>
-      <c r="CF17" t="inlineStr">
-        <is>
-          <t>57.4</t>
-        </is>
-      </c>
-      <c r="CG17" t="inlineStr">
-        <is>
-          <t>57.4</t>
-        </is>
-      </c>
-      <c r="CH17" t="inlineStr">
-        <is>
-          <t>22.98</t>
-        </is>
-      </c>
-      <c r="CI17" t="inlineStr">
-        <is>
-          <t>** 半導體 - 化學品** 電腦及週邊設備 - 硬碟機** 平面顯示器 - 化學品(如光阻劑、靶材等)** 觸控面板 - ITO靶材** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 印刷電路板 - 生產製程及檢測設備** 其他 - 環保潔能服務產業** 汽車 - 其他** 太陽能產業 - 材料</t>
-        </is>
-      </c>
-      <c r="CJ17" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1785</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>-1.51</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>4870.0</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>58.1</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>-2.29</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>-2.03</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>22.85</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>2025-10-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>58.1</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>59.6</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>61.5</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>-1.53</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>-4.07</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>8.40</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>-1.35</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr"/>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>2408</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>40.68</t>
-        </is>
-      </c>
-      <c r="AG18" t="inlineStr">
-        <is>
-          <t>55.37</t>
-        </is>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>-2.75</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>0.39</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>4.44</t>
-        </is>
-      </c>
-      <c r="AL18" t="inlineStr">
-        <is>
-          <t>59.73999999999999</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>59.51</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>60.1</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>57.55</t>
-        </is>
-      </c>
-      <c r="AP18" t="inlineStr">
-        <is>
-          <t>-4.35</t>
-        </is>
-      </c>
-      <c r="AQ18" t="inlineStr">
-        <is>
-          <t>-0.40</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>-0.39</t>
-        </is>
-      </c>
-      <c r="AS18" t="inlineStr">
-        <is>
-          <t>5.31</t>
-        </is>
-      </c>
-      <c r="AT18" t="inlineStr">
-        <is>
-          <t>-107.25</t>
-        </is>
-      </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV18" t="inlineStr">
-        <is>
-          <t>815920.4784172662</t>
-        </is>
-      </c>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>283328.0</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>437969.2</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>356514.8</t>
-        </is>
-      </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>570563.3</t>
-        </is>
-      </c>
-      <c r="BA18" t="inlineStr">
-        <is>
-          <t>81454</t>
-        </is>
-      </c>
-      <c r="BB18" t="inlineStr">
-        <is>
-          <t>-36824.00107548192</t>
-        </is>
-      </c>
-      <c r="BC18" t="inlineStr">
-        <is>
-          <t>-22149.96022690379</t>
-        </is>
-      </c>
-      <c r="BD18" t="n">
-        <v>283328</v>
-      </c>
-      <c r="BE18" t="inlineStr">
-        <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="BF18" t="inlineStr">
-        <is>
-          <t>58.9</t>
-        </is>
-      </c>
-      <c r="BG18" t="inlineStr">
-        <is>
-          <t>2025/08/29</t>
-        </is>
-      </c>
-      <c r="BH18" t="inlineStr">
-        <is>
-          <t>-1.36</t>
-        </is>
-      </c>
-      <c r="BI18" t="inlineStr">
-        <is>
-          <t>光洋科</t>
-        </is>
-      </c>
-      <c r="BJ18" t="inlineStr">
-        <is>
-          <t>光洋科</t>
-        </is>
-      </c>
-      <c r="BK18" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL18" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM18" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="BN18" t="inlineStr">
-        <is>
-          <t>-1.228328584465341</t>
-        </is>
-      </c>
-      <c r="BO18" t="inlineStr">
-        <is>
-          <t>47.44460114587924</t>
-        </is>
-      </c>
-      <c r="BP18" t="inlineStr">
-        <is>
-          <t>32.54445648609581</t>
-        </is>
-      </c>
-      <c r="BQ18" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
-      <c r="BR18" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS18" t="inlineStr">
-        <is>
-          <t>2.53</t>
-        </is>
-      </c>
-      <c r="BT18" t="inlineStr">
-        <is>
-          <t>3.52</t>
-        </is>
-      </c>
-      <c r="BU18" t="inlineStr">
-        <is>
-          <t>17.51</t>
-        </is>
-      </c>
-      <c r="BV18" t="inlineStr">
-        <is>
-          <t>24.17</t>
-        </is>
-      </c>
-      <c r="BW18" t="inlineStr">
-        <is>
-          <t>14.09%</t>
-        </is>
-      </c>
-      <c r="BX18" t="inlineStr">
-        <is>
-          <t>9.19%</t>
-        </is>
-      </c>
-      <c r="BY18" t="inlineStr">
-        <is>
-          <t>42.08</t>
-        </is>
-      </c>
-      <c r="BZ18" t="inlineStr">
-        <is>
-          <t>33854</t>
-        </is>
-      </c>
-      <c r="CA18" t="inlineStr">
-        <is>
-          <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB18" t="inlineStr">
-        <is>
-          <t>光洋科-其他電子業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC18" t="inlineStr">
-        <is>
-          <t>其他電子業右上上櫃</t>
-        </is>
-      </c>
-      <c r="CD18" t="inlineStr">
-        <is>
-          <t>59.8</t>
-        </is>
-      </c>
-      <c r="CE18" t="inlineStr">
-        <is>
-          <t>59.8</t>
-        </is>
-      </c>
-      <c r="CF18" t="inlineStr">
-        <is>
-          <t>57.2</t>
-        </is>
-      </c>
-      <c r="CG18" t="inlineStr">
-        <is>
-          <t>58.1</t>
-        </is>
-      </c>
-      <c r="CH18" t="inlineStr">
-        <is>
-          <t>22.98</t>
-        </is>
-      </c>
-      <c r="CI18" t="inlineStr">
-        <is>
-          <t>** 半導體 - 化學品** 電腦及週邊設備 - 硬碟機** 平面顯示器 - 化學品(如光阻劑、靶材等)** 觸控面板 - ITO靶材** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 印刷電路板 - 生產製程及檢測設備** 其他 - 環保潔能服務產業** 汽車 - 其他** 太陽能產業 - 材料</t>
-        </is>
-      </c>
-      <c r="CJ18" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1785</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>-1.35</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>4060.0</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>-3.87</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>-2.03</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>36.21</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>2025-10-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>58.1</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>59.6</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>61.5</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>-4.07</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>7.01</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>-1.86</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr"/>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>2408</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>55.93</t>
-        </is>
-      </c>
-      <c r="AG19" t="inlineStr">
-        <is>
-          <t>67.23</t>
-        </is>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>-1.86</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>0.64</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>-0.58</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>4.58</t>
-        </is>
-      </c>
-      <c r="AL19" t="inlineStr">
-        <is>
-          <t>60.12</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>59.74</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>60.09</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>57.46</t>
-        </is>
-      </c>
-      <c r="AP19" t="inlineStr">
-        <is>
-          <t>14.66</t>
-        </is>
-      </c>
-      <c r="AQ19" t="inlineStr">
-        <is>
-          <t>-0.33</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>-0.38</t>
-        </is>
-      </c>
-      <c r="AS19" t="inlineStr">
-        <is>
-          <t>5.31</t>
-        </is>
-      </c>
-      <c r="AT19" t="inlineStr">
-        <is>
-          <t>-107.17</t>
-        </is>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV19" t="inlineStr">
-        <is>
-          <t>815920.4784172662</t>
-        </is>
-      </c>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>242218.0</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>465573.8</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>341803.5</t>
-        </is>
-      </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>579417.88</t>
-        </is>
-      </c>
-      <c r="BA19" t="inlineStr">
-        <is>
-          <t>123770</t>
-        </is>
-      </c>
-      <c r="BB19" t="inlineStr">
-        <is>
-          <t>-39492.00850249613</t>
-        </is>
-      </c>
-      <c r="BC19" t="inlineStr">
-        <is>
-          <t>-18693.87703106157</t>
-        </is>
-      </c>
-      <c r="BD19" t="n">
-        <v>242218</v>
-      </c>
-      <c r="BE19" t="inlineStr">
-        <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="BF19" t="inlineStr">
-        <is>
-          <t>58.9</t>
-        </is>
-      </c>
-      <c r="BG19" t="inlineStr">
-        <is>
-          <t>2025/08/29</t>
-        </is>
-      </c>
-      <c r="BH19" t="inlineStr">
-        <is>
-          <t>0.17</t>
-        </is>
-      </c>
-      <c r="BI19" t="inlineStr">
-        <is>
-          <t>光洋科</t>
-        </is>
-      </c>
-      <c r="BJ19" t="inlineStr">
-        <is>
-          <t>光洋科</t>
-        </is>
-      </c>
-      <c r="BK19" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL19" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM19" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="BN19" t="inlineStr">
-        <is>
-          <t>-1.228328584465341</t>
-        </is>
-      </c>
-      <c r="BO19" t="inlineStr">
-        <is>
-          <t>47.44460114587924</t>
-        </is>
-      </c>
-      <c r="BP19" t="inlineStr">
-        <is>
-          <t>32.54445648609581</t>
-        </is>
-      </c>
-      <c r="BQ19" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
-      <c r="BR19" t="inlineStr">
-        <is>
-          <t>價跌量縮</t>
-        </is>
-      </c>
-      <c r="BS19" t="inlineStr">
-        <is>
-          <t>2.57</t>
-        </is>
-      </c>
-      <c r="BT19" t="inlineStr">
-        <is>
-          <t>3.52</t>
-        </is>
-      </c>
-      <c r="BU19" t="inlineStr">
-        <is>
-          <t>17.51</t>
-        </is>
-      </c>
-      <c r="BV19" t="inlineStr">
-        <is>
-          <t>24.17</t>
-        </is>
-      </c>
-      <c r="BW19" t="inlineStr">
-        <is>
-          <t>14.09%</t>
-        </is>
-      </c>
-      <c r="BX19" t="inlineStr">
-        <is>
-          <t>9.19%</t>
-        </is>
-      </c>
-      <c r="BY19" t="inlineStr">
-        <is>
-          <t>42.08</t>
-        </is>
-      </c>
-      <c r="BZ19" t="inlineStr">
-        <is>
-          <t>33854</t>
-        </is>
-      </c>
-      <c r="CA19" t="inlineStr">
-        <is>
-          <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB19" t="inlineStr">
-        <is>
-          <t>光洋科-其他電子業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC19" t="inlineStr">
-        <is>
-          <t>其他電子業右上上櫃</t>
-        </is>
-      </c>
-      <c r="CD19" t="inlineStr">
-        <is>
-          <t>59.3</t>
-        </is>
-      </c>
-      <c r="CE19" t="inlineStr">
-        <is>
-          <t>60.6</t>
-        </is>
-      </c>
-      <c r="CF19" t="inlineStr">
-        <is>
-          <t>58.5</t>
-        </is>
-      </c>
-      <c r="CG19" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="CH19" t="inlineStr">
-        <is>
-          <t>22.98</t>
-        </is>
-      </c>
-      <c r="CI19" t="inlineStr">
-        <is>
-          <t>** 半導體 - 化學品** 電腦及週邊設備 - 硬碟機** 平面顯示器 - 化學品(如光阻劑、靶材等)** 觸控面板 - ITO靶材** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 印刷電路板 - 生產製程及檢測設備** 其他 - 環保潔能服務產業** 汽車 - 其他** 太陽能產業 - 材料</t>
-        </is>
-      </c>
-      <c r="CJ19" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1785</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>-0.67</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>3505.0</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>59.8</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>-5.28</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>-2.03</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>36.04</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>2025-10-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>58.1</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>59.6</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>61.5</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>2.93</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>-4.07</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>6.05</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr"/>
-      <c r="AD20" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>2408</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>69.49</t>
-        </is>
-      </c>
-      <c r="AG20" t="inlineStr">
-        <is>
-          <t>81.92</t>
-        </is>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>0.13</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>-0.44</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>-0.18</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>4.74</t>
-        </is>
-      </c>
-      <c r="AL20" t="inlineStr">
-        <is>
-          <t>59.72000000000001</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>59.98</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>60.1</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>57.38</t>
-        </is>
-      </c>
-      <c r="AP20" t="inlineStr">
-        <is>
-          <t>20.51</t>
-        </is>
-      </c>
-      <c r="AQ20" t="inlineStr">
-        <is>
-          <t>-0.31</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>-0.40</t>
-        </is>
-      </c>
-      <c r="AS20" t="inlineStr">
-        <is>
-          <t>5.31</t>
-        </is>
-      </c>
-      <c r="AT20" t="inlineStr">
-        <is>
-          <t>-107.44</t>
-        </is>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV20" t="inlineStr">
-        <is>
-          <t>815920.4784172662</t>
-        </is>
-      </c>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>209656.0</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>452042.6</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>332281.8</t>
-        </is>
-      </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>596784.86</t>
-        </is>
-      </c>
-      <c r="BA20" t="inlineStr">
-        <is>
-          <t>119760</t>
-        </is>
-      </c>
-      <c r="BB20" t="inlineStr">
-        <is>
-          <t>-43273.48695184787</t>
-        </is>
-      </c>
-      <c r="BC20" t="inlineStr">
-        <is>
-          <t>-8684.334000177623</t>
-        </is>
-      </c>
-      <c r="BD20" t="n">
-        <v>209656</v>
-      </c>
-      <c r="BE20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF20" t="inlineStr">
-        <is>
-          <t>58.9</t>
-        </is>
-      </c>
-      <c r="BG20" t="inlineStr">
-        <is>
-          <t>2025/08/29</t>
-        </is>
-      </c>
-      <c r="BH20" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="BI20" t="inlineStr">
-        <is>
-          <t>光洋科</t>
-        </is>
-      </c>
-      <c r="BJ20" t="inlineStr">
-        <is>
-          <t>光洋科</t>
-        </is>
-      </c>
-      <c r="BK20" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL20" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM20" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="BN20" t="inlineStr">
-        <is>
-          <t>-1.228328584465341</t>
-        </is>
-      </c>
-      <c r="BO20" t="inlineStr">
-        <is>
-          <t>47.44460114587924</t>
-        </is>
-      </c>
-      <c r="BP20" t="inlineStr">
-        <is>
-          <t>32.54445648609581</t>
-        </is>
-      </c>
-      <c r="BQ20" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR20" t="inlineStr">
-        <is>
-          <t>價跌量-</t>
-        </is>
-      </c>
-      <c r="BS20" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
-      </c>
-      <c r="BT20" t="inlineStr">
-        <is>
-          <t>3.52</t>
-        </is>
-      </c>
-      <c r="BU20" t="inlineStr">
-        <is>
-          <t>17.51</t>
-        </is>
-      </c>
-      <c r="BV20" t="inlineStr">
-        <is>
-          <t>24.17</t>
-        </is>
-      </c>
-      <c r="BW20" t="inlineStr">
-        <is>
-          <t>14.09%</t>
-        </is>
-      </c>
-      <c r="BX20" t="inlineStr">
-        <is>
-          <t>9.19%</t>
-        </is>
-      </c>
-      <c r="BY20" t="inlineStr">
-        <is>
-          <t>42.08</t>
-        </is>
-      </c>
-      <c r="BZ20" t="inlineStr">
-        <is>
-          <t>33854</t>
-        </is>
-      </c>
-      <c r="CA20" t="inlineStr">
-        <is>
-          <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB20" t="inlineStr">
-        <is>
-          <t>光洋科-其他電子業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC20" t="inlineStr">
-        <is>
-          <t>其他電子業右上上櫃</t>
-        </is>
-      </c>
-      <c r="CD20" t="inlineStr">
-        <is>
-          <t>60.1</t>
-        </is>
-      </c>
-      <c r="CE20" t="inlineStr">
-        <is>
-          <t>60.4</t>
-        </is>
-      </c>
-      <c r="CF20" t="inlineStr">
-        <is>
-          <t>59.2</t>
-        </is>
-      </c>
-      <c r="CG20" t="inlineStr">
-        <is>
-          <t>59.8</t>
-        </is>
-      </c>
-      <c r="CH20" t="inlineStr">
-        <is>
-          <t>22.98</t>
-        </is>
-      </c>
-      <c r="CI20" t="inlineStr">
-        <is>
-          <t>** 半導體 - 化學品** 電腦及週邊設備 - 硬碟機** 平面顯示器 - 化學品(如光阻劑、靶材等)** 觸控面板 - ITO靶材** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 印刷電路板 - 生產製程及檢測設備** 其他 - 環保潔能服務產業** 汽車 - 其他** 太陽能產業 - 材料</t>
-        </is>
-      </c>
-      <c r="CJ20" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1785</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>-2.27</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>8540.0</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>60.2</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>-5.99</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>-2.03</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>30.92</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>2025-10-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>58.1</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>59.6</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>61.5</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>3.61</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>-4.07</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>14.74</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>-1.65</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr"/>
-      <c r="AD21" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>2408</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>76.27</t>
-        </is>
-      </c>
-      <c r="AG21" t="inlineStr">
-        <is>
-          <t>91.33</t>
-        </is>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>1.79</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>-1.58</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>4.83</t>
-        </is>
-      </c>
-      <c r="AL21" t="inlineStr">
-        <is>
-          <t>59.14</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>60.09</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>60.08</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>57.31</t>
-        </is>
-      </c>
-      <c r="AP21" t="inlineStr">
-        <is>
-          <t>9.30</t>
-        </is>
-      </c>
-      <c r="AQ21" t="inlineStr">
-        <is>
-          <t>-0.38</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>-0.42</t>
-        </is>
-      </c>
-      <c r="AS21" t="inlineStr">
-        <is>
-          <t>5.31</t>
-        </is>
-      </c>
-      <c r="AT21" t="inlineStr">
-        <is>
-          <t>-107.82</t>
-        </is>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV21" t="inlineStr">
-        <is>
-          <t>815920.4784172662</t>
-        </is>
-      </c>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>517165.0</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>445047.0</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>339942.5</t>
-        </is>
-      </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>643736.64</t>
-        </is>
-      </c>
-      <c r="BA21" t="inlineStr">
-        <is>
-          <t>105104</t>
-        </is>
-      </c>
-      <c r="BB21" t="inlineStr">
-        <is>
-          <t>-49562.42385215155</t>
-        </is>
-      </c>
-      <c r="BC21" t="inlineStr">
-        <is>
-          <t>9413.953686805733</t>
-        </is>
-      </c>
-      <c r="BD21" t="n">
-        <v>517165</v>
-      </c>
-      <c r="BE21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF21" t="inlineStr">
-        <is>
-          <t>58.9</t>
-        </is>
-      </c>
-      <c r="BG21" t="inlineStr">
-        <is>
-          <t>2025/08/29</t>
-        </is>
-      </c>
-      <c r="BH21" t="inlineStr">
-        <is>
-          <t>2.21</t>
-        </is>
-      </c>
-      <c r="BI21" t="inlineStr">
-        <is>
-          <t>光洋科</t>
-        </is>
-      </c>
-      <c r="BJ21" t="inlineStr">
-        <is>
-          <t>光洋科</t>
-        </is>
-      </c>
-      <c r="BK21" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL21" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM21" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="BN21" t="inlineStr">
-        <is>
-          <t>-1.228328584465341</t>
-        </is>
-      </c>
-      <c r="BO21" t="inlineStr">
-        <is>
-          <t>47.44460114587924</t>
-        </is>
-      </c>
-      <c r="BP21" t="inlineStr">
-        <is>
-          <t>32.54445648609581</t>
-        </is>
-      </c>
-      <c r="BQ21" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR21" t="inlineStr">
-        <is>
-          <t>價漲量增</t>
-        </is>
-      </c>
-      <c r="BS21" t="inlineStr">
-        <is>
-          <t>2.62</t>
-        </is>
-      </c>
-      <c r="BT21" t="inlineStr">
-        <is>
-          <t>3.52</t>
-        </is>
-      </c>
-      <c r="BU21" t="inlineStr">
-        <is>
-          <t>17.51</t>
-        </is>
-      </c>
-      <c r="BV21" t="inlineStr">
-        <is>
-          <t>24.17</t>
-        </is>
-      </c>
-      <c r="BW21" t="inlineStr">
-        <is>
-          <t>14.09%</t>
-        </is>
-      </c>
-      <c r="BX21" t="inlineStr">
-        <is>
-          <t>9.19%</t>
-        </is>
-      </c>
-      <c r="BY21" t="inlineStr">
-        <is>
-          <t>42.08</t>
-        </is>
-      </c>
-      <c r="BZ21" t="inlineStr">
-        <is>
-          <t>33854</t>
-        </is>
-      </c>
-      <c r="CA21" t="inlineStr">
-        <is>
-          <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB21" t="inlineStr">
-        <is>
-          <t>光洋科-其他電子業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC21" t="inlineStr">
-        <is>
-          <t>其他電子業右上上櫃</t>
-        </is>
-      </c>
-      <c r="CD21" t="inlineStr">
-        <is>
-          <t>61.7</t>
-        </is>
-      </c>
-      <c r="CE21" t="inlineStr">
-        <is>
-          <t>61.8</t>
-        </is>
-      </c>
-      <c r="CF21" t="inlineStr">
-        <is>
-          <t>59.6</t>
-        </is>
-      </c>
-      <c r="CG21" t="inlineStr">
-        <is>
-          <t>60.2</t>
-        </is>
-      </c>
-      <c r="CH21" t="inlineStr">
-        <is>
-          <t>22.98</t>
-        </is>
-      </c>
-      <c r="CI21" t="inlineStr">
-        <is>
-          <t>** 半導體 - 化學品** 電腦及週邊設備 - 硬碟機** 平面顯示器 - 化學品(如光阻劑、靶材等)** 觸控面板 - ITO靶材** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 印刷電路板 - 生產製程及檢測設備** 其他 - 環保潔能服務產業** 汽車 - 其他** 太陽能產業 - 材料</t>
-        </is>
-      </c>
-      <c r="CJ21" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>1785</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>2.64</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>15157.0</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>61.6</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>-8.45</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>-2.03</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>29.74</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>2025-10-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>58.1</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>59.6</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>61.5</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>6.02</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>-4.07</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>26.15</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>0.07</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr"/>
-      <c r="AD22" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>2408</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="AG22" t="inlineStr">
-        <is>
-          <t>75.54</t>
-        </is>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>5.77</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>-3.09</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>4.96</t>
-        </is>
-      </c>
-      <c r="AL22" t="inlineStr">
-        <is>
-          <t>58.24000000000001</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>60.09</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>60.08</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>57.24</t>
-        </is>
-      </c>
-      <c r="AP22" t="inlineStr">
-        <is>
-          <t>-15.74</t>
-        </is>
-      </c>
-      <c r="AQ22" t="inlineStr">
-        <is>
-          <t>-0.49</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>-0.43</t>
-        </is>
-      </c>
-      <c r="AS22" t="inlineStr">
-        <is>
-          <t>5.31</t>
-        </is>
-      </c>
-      <c r="AT22" t="inlineStr">
-        <is>
-          <t>-108.00</t>
-        </is>
-      </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV22" t="inlineStr">
-        <is>
-          <t>815920.4784172662</t>
-        </is>
-      </c>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>937479.0</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>393702.8</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>303455.3</t>
-        </is>
-      </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>659423.84</t>
-        </is>
-      </c>
-      <c r="BA22" t="inlineStr">
-        <is>
-          <t>90247</t>
-        </is>
-      </c>
-      <c r="BB22" t="inlineStr">
-        <is>
-          <t>-60285.40158650742</t>
-        </is>
-      </c>
-      <c r="BC22" t="inlineStr">
-        <is>
-          <t>1985.044893681828</t>
-        </is>
-      </c>
-      <c r="BD22" t="n">
-        <v>937479</v>
-      </c>
-      <c r="BE22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF22" t="inlineStr">
-        <is>
-          <t>58.9</t>
-        </is>
-      </c>
-      <c r="BG22" t="inlineStr">
-        <is>
-          <t>2025/08/29</t>
-        </is>
-      </c>
-      <c r="BH22" t="inlineStr">
-        <is>
-          <t>4.58</t>
-        </is>
-      </c>
-      <c r="BI22" t="inlineStr">
-        <is>
-          <t>光洋科</t>
-        </is>
-      </c>
-      <c r="BJ22" t="inlineStr">
-        <is>
-          <t>光洋科</t>
-        </is>
-      </c>
-      <c r="BK22" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL22" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM22" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="BN22" t="inlineStr">
-        <is>
-          <t>-1.228328584465341</t>
-        </is>
-      </c>
-      <c r="BO22" t="inlineStr">
-        <is>
-          <t>47.44460114587924</t>
-        </is>
-      </c>
-      <c r="BP22" t="inlineStr">
-        <is>
-          <t>32.54445648609581</t>
-        </is>
-      </c>
-      <c r="BQ22" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
-        </is>
-      </c>
-      <c r="BR22" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS22" t="inlineStr">
-        <is>
-          <t>2.68</t>
-        </is>
-      </c>
-      <c r="BT22" t="inlineStr">
-        <is>
-          <t>3.52</t>
-        </is>
-      </c>
-      <c r="BU22" t="inlineStr">
-        <is>
-          <t>17.51</t>
-        </is>
-      </c>
-      <c r="BV22" t="inlineStr">
-        <is>
-          <t>24.17</t>
-        </is>
-      </c>
-      <c r="BW22" t="inlineStr">
-        <is>
-          <t>14.09%</t>
-        </is>
-      </c>
-      <c r="BX22" t="inlineStr">
-        <is>
-          <t>9.19%</t>
-        </is>
-      </c>
-      <c r="BY22" t="inlineStr">
-        <is>
-          <t>42.08</t>
-        </is>
-      </c>
-      <c r="BZ22" t="inlineStr">
-        <is>
-          <t>33854</t>
-        </is>
-      </c>
-      <c r="CA22" t="inlineStr">
-        <is>
-          <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB22" t="inlineStr">
-        <is>
-          <t>光洋科-其他電子業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC22" t="inlineStr">
-        <is>
-          <t>其他電子業右上上櫃</t>
-        </is>
-      </c>
-      <c r="CD22" t="inlineStr">
-        <is>
-          <t>60.5</t>
-        </is>
-      </c>
-      <c r="CE22" t="inlineStr">
-        <is>
-          <t>63.2</t>
-        </is>
-      </c>
-      <c r="CF22" t="inlineStr">
-        <is>
-          <t>60.0</t>
-        </is>
-      </c>
-      <c r="CG22" t="inlineStr">
-        <is>
-          <t>61.6</t>
-        </is>
-      </c>
-      <c r="CH22" t="inlineStr">
-        <is>
-          <t>22.98</t>
-        </is>
-      </c>
-      <c r="CI22" t="inlineStr">
-        <is>
-          <t>** 半導體 - 化學品** 電腦及週邊設備 - 硬碟機** 平面顯示器 - 化學品(如光阻劑、靶材等)** 觸控面板 - ITO靶材** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 印刷電路板 - 生產製程及檢測設備** 其他 - 環保潔能服務產業** 汽車 - 其他** 太陽能產業 - 材料</t>
-        </is>
-      </c>
-      <c r="CJ22" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>1785</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>5.2</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>7091.0</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>60.0</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>-5.63</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>-2.03</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>17.44</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>2025-10-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>58.1</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>59.6</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>61.5</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>3.27</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>-4.07</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>12.24</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>3.65</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr"/>
-      <c r="AD23" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>2408</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>97.73</t>
-        </is>
-      </c>
-      <c r="AG23" t="inlineStr">
-        <is>
-          <t>50.21</t>
-        </is>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>4.79</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>-4.77</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>0.31</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>4.90</t>
-        </is>
-      </c>
-      <c r="AL23" t="inlineStr">
-        <is>
-          <t>57.26000000000001</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>60.13</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>59.94</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>57.14</t>
-        </is>
-      </c>
-      <c r="AP23" t="inlineStr">
-        <is>
-          <t>-89.66</t>
-        </is>
-      </c>
-      <c r="AQ23" t="inlineStr">
-        <is>
-          <t>-0.77</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>-0.41</t>
-        </is>
-      </c>
-      <c r="AS23" t="inlineStr">
-        <is>
-          <t>5.31</t>
-        </is>
-      </c>
-      <c r="AT23" t="inlineStr">
-        <is>
-          <t>-107.68</t>
-        </is>
-      </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV23" t="inlineStr">
-        <is>
-          <t>815920.4784172662</t>
-        </is>
-      </c>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>421351.0</t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>275060.4</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>234213.9</t>
-        </is>
-      </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>643815.04</t>
-        </is>
-      </c>
-      <c r="BA23" t="inlineStr">
-        <is>
-          <t>40846</t>
-        </is>
-      </c>
-      <c r="BB23" t="inlineStr">
-        <is>
-          <t>-71607.30094654183</t>
-        </is>
-      </c>
-      <c r="BC23" t="inlineStr">
-        <is>
-          <t>-53732.21927126963</t>
-        </is>
-      </c>
-      <c r="BD23" t="n">
-        <v>421351</v>
-      </c>
-      <c r="BE23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF23" t="inlineStr">
-        <is>
-          <t>58.9</t>
-        </is>
-      </c>
-      <c r="BG23" t="inlineStr">
-        <is>
-          <t>2025/08/29</t>
-        </is>
-      </c>
-      <c r="BH23" t="inlineStr">
-        <is>
-          <t>1.87</t>
-        </is>
-      </c>
-      <c r="BI23" t="inlineStr">
-        <is>
-          <t>光洋科</t>
-        </is>
-      </c>
-      <c r="BJ23" t="inlineStr">
-        <is>
-          <t>光洋科</t>
-        </is>
-      </c>
-      <c r="BK23" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL23" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM23" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="BN23" t="inlineStr">
-        <is>
-          <t>-1.228328584465341</t>
-        </is>
-      </c>
-      <c r="BO23" t="inlineStr">
-        <is>
-          <t>47.44460114587924</t>
-        </is>
-      </c>
-      <c r="BP23" t="inlineStr">
-        <is>
-          <t>32.54445648609581</t>
-        </is>
-      </c>
-      <c r="BQ23" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
-        </is>
-      </c>
-      <c r="BR23" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS23" t="inlineStr">
-        <is>
-          <t>2.61</t>
-        </is>
-      </c>
-      <c r="BT23" t="inlineStr">
-        <is>
-          <t>3.52</t>
-        </is>
-      </c>
-      <c r="BU23" t="inlineStr">
-        <is>
-          <t>17.51</t>
-        </is>
-      </c>
-      <c r="BV23" t="inlineStr">
-        <is>
-          <t>24.17</t>
-        </is>
-      </c>
-      <c r="BW23" t="inlineStr">
-        <is>
-          <t>14.09%</t>
-        </is>
-      </c>
-      <c r="BX23" t="inlineStr">
-        <is>
-          <t>9.19%</t>
-        </is>
-      </c>
-      <c r="BY23" t="inlineStr">
-        <is>
-          <t>42.08</t>
-        </is>
-      </c>
-      <c r="BZ23" t="inlineStr">
-        <is>
-          <t>33854</t>
-        </is>
-      </c>
-      <c r="CA23" t="inlineStr">
-        <is>
-          <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB23" t="inlineStr">
-        <is>
-          <t>光洋科-其他電子業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC23" t="inlineStr">
-        <is>
-          <t>其他電子業右上上櫃</t>
-        </is>
-      </c>
-      <c r="CD23" t="inlineStr">
-        <is>
-          <t>57.7</t>
-        </is>
-      </c>
-      <c r="CE23" t="inlineStr">
-        <is>
-          <t>60.2</t>
-        </is>
-      </c>
-      <c r="CF23" t="inlineStr">
-        <is>
-          <t>57.7</t>
-        </is>
-      </c>
-      <c r="CG23" t="inlineStr">
-        <is>
-          <t>60.0</t>
-        </is>
-      </c>
-      <c r="CH23" t="inlineStr">
-        <is>
-          <t>22.98</t>
-        </is>
-      </c>
-      <c r="CI23" t="inlineStr">
-        <is>
-          <t>** 半導體 - 化學品** 電腦及週邊設備 - 硬碟機** 平面顯示器 - 化學品(如光阻劑、靶材等)** 觸控面板 - ITO靶材** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 印刷電路板 - 生產製程及檢測設備** 其他 - 環保潔能服務產業** 汽車 - 其他** 太陽能產業 - 材料</t>
-        </is>
-      </c>
-      <c r="CJ23" t="inlineStr">
-        <is>
-          <t>True</t>
         </is>
       </c>
     </row>

--- a/Result/checksun_type/濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料).xlsx
+++ b/Result/checksun_type/濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料).xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CJ13"/>
+  <dimension ref="A1:CJ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>436.423</t>
+          <t>308.105</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>64.1</t>
+          <t>65.4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-57.89</t>
+          <t>-56.32</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,47 +1014,47 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>308</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>17.72</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>65.24000000000001</t>
+          <t>65.12</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
@@ -1064,27 +1064,27 @@
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>66.84</t>
+          <t>66.83</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>63.67</t>
+          <t>63.8</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-128.59</t>
+          <t>-169.68</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-87.16</t>
+          <t>-90.99</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>75179432.90759313</t>
+          <t>75115086.28111587</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>28041681.0</t>
+          <t>20134094.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>35349677.8</t>
+          <t>29566216.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>83955755.0</t>
+          <t>67689821.8</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>105161801.84</t>
+          <t>102474885.18</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-48606077</t>
+          <t>-38123605</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-4140084.045800703</t>
+          <t>-5188194.843829334</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-9472320.967936054</t>
+          <t>-10952804.2329868</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>28041681</v>
+        <v>20134094</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>35.52</t>
+          <t>38.27</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,22 +1207,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>90.28</t>
+          <t>92.11</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>48.67</t>
+          <t>47.59</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>7605</t>
+          <t>7760</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>64.7</t>
+          <t>64.3</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>65.8</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>63.5</t>
+          <t>64.3</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>64.1</t>
+          <t>65.4</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>427.384</t>
+          <t>436.423</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>64.1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-44.43</t>
+          <t>-57.89</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>308</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>65.24000000000001</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>66.14</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>66.9</t>
+          <t>66.84</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>63.56</t>
+          <t>63.67</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-72.20</t>
+          <t>-128.59</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-83.03</t>
+          <t>-87.16</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>75179432.90759313</t>
+          <t>75115086.28111587</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>27698337.0</t>
+          <t>28041681.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>50976888.8</t>
+          <t>35349677.8</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>91736509.2</t>
+          <t>83955755.0</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>107077260.2</t>
+          <t>105161801.84</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-40759620</t>
+          <t>-48606077</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-3170586.423594275</t>
+          <t>-4140084.045800703</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-7866289.16186586</t>
+          <t>-9472320.967936054</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>27698337</v>
+        <v>28041681</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>35.31</t>
+          <t>35.52</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>90.28</t>
+          <t>92.11</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>48.67</t>
+          <t>47.59</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>7605</t>
+          <t>7760</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>64.7</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>63.5</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>64.1</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-3.15</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>677.83</t>
+          <t>427.384</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,72 +1770,72 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>64.0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>-0.13</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-44.43</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-09-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
           <t>65.0</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>-1.4</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>-1.01</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>-35.82</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-11-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-09-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>-7.14</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,12 +1886,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>308</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1901,62 +1901,62 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>12.81</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>5.55</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>67.4</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>66.28</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>66.98</t>
+          <t>66.9</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>63.46</t>
+          <t>63.56</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-21.43</t>
+          <t>-72.20</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-79.97</t>
+          <t>-83.03</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,50 +1976,50 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>75179432.90759313</t>
+          <t>75115086.28111587</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>44220240.0</t>
+          <t>27698337.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>62027297.8</t>
+          <t>50976888.8</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>96645760.1</t>
+          <t>91736509.2</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>113463276.16</t>
+          <t>107077260.2</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-34618462</t>
+          <t>-40759620</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-2316822.289363078</t>
+          <t>-3170586.423594275</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-5254232.254556075</t>
+          <t>-7866289.16186586</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>44220240</v>
+        <v>27698337</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>37.42</t>
+          <t>35.31</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2089,12 +2089,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>90.28</t>
+          <t>92.11</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>48.67</t>
+          <t>47.59</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>7605</t>
+          <t>7760</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>64.3</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>-3.15</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>412.165</t>
+          <t>677.83</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>67.1</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-23.59</t>
+          <t>-35.82</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-7.14</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,52 +2322,52 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>308</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>23.94</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>29.29</t>
+          <t>12.81</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>5.55</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>68.78000000000002</t>
+          <t>67.4</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>66.31</t>
+          <t>66.28</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2377,22 +2377,22 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>63.36</t>
+          <t>63.46</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>21.92</t>
+          <t>-21.43</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-78.90</t>
+          <t>-79.97</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>75179432.90759313</t>
+          <t>75115086.28111587</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>27736728.0</t>
+          <t>44220240.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>73239519.2</t>
+          <t>62027297.8</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>95851157.0</t>
+          <t>96645760.1</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>115231412.04</t>
+          <t>113463276.16</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-22611637</t>
+          <t>-34618462</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-1782747.750237079</t>
+          <t>-2316822.289363078</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-3105275.127879396</t>
+          <t>-5254232.254556075</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>27736728</v>
+        <v>44220240</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>41.86</t>
+          <t>37.42</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,22 +2515,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>90.28</t>
+          <t>92.11</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>48.67</t>
+          <t>47.59</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>7605</t>
+          <t>7760</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>67.9</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>67.9</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>66.5</t>
+          <t>64.3</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>67.1</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>735.417</t>
+          <t>412.165</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>10.77</t>
+          <t>-23.59</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>-5.71</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,77 +2758,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>308</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>14.47</t>
+          <t>23.94</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>49.64</t>
+          <t>29.29</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-5.53</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>5.80</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>69.86000000000001</t>
+          <t>68.78000000000002</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>66.24</t>
+          <t>66.31</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>66.9</t>
+          <t>66.98</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>63.24</t>
+          <t>63.36</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>50.55</t>
+          <t>21.92</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-80.05</t>
+          <t>-78.90</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>75179432.90759313</t>
+          <t>75115086.28111587</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>49051403.0</t>
+          <t>27736728.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>105813427.6</t>
+          <t>73239519.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>95524666.9</t>
+          <t>95851157.0</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>120066640.9</t>
+          <t>115231412.04</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>10288760</t>
+          <t>-22611637</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-1542288.227029385</t>
+          <t>-1782747.750237079</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>1841656.879083008</t>
+          <t>-3105275.127879396</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>49051403</v>
+        <v>27736728</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>39.53</t>
+          <t>41.86</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2951,22 +2951,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>90.28</t>
+          <t>92.11</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>48.67</t>
+          <t>47.59</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>7605</t>
+          <t>7760</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>68.6</t>
+          <t>67.9</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>68.6</t>
+          <t>67.9</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>66.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.1</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1542.065</t>
+          <t>735.417</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>67.9</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-5.93</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.98</t>
+          <t>10.77</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>-3.00</t>
+          <t>-5.71</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13.91</t>
+          <t>6.63</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,77 +3194,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>308</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>49.45</t>
+          <t>14.47</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>76.15</t>
+          <t>49.64</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-5.53</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>5.70</t>
+          <t>5.80</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>70.66</t>
+          <t>69.86000000000001</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>66.3</t>
+          <t>66.24</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>66.75</t>
+          <t>66.9</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>63.15</t>
+          <t>63.24</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>125.60</t>
+          <t>50.55</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-82.57</t>
+          <t>-80.05</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>75179432.90759313</t>
+          <t>75115086.28111587</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>106177736.0</t>
+          <t>49051403.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>132561832.2</t>
+          <t>105813427.6</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>93365555.7</t>
+          <t>95524666.9</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>120263879.18</t>
+          <t>120066640.9</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>39196276</t>
+          <t>10288760</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-2157550.973595275</t>
+          <t>-1542288.227029385</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>6559213.964776337</t>
+          <t>1841656.879083008</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>106177736</v>
+        <v>49051403</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>39.53</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,22 +3387,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>90.28</t>
+          <t>92.11</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>48.67</t>
+          <t>47.59</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>7605</t>
+          <t>7760</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>67.9</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1168.47</t>
+          <t>1542.065</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>67.9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-10.76</t>
+          <t>-3.82</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>53.47</t>
+          <t>41.98</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>-3.00</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>9.23</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10.54</t>
+          <t>13.91</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,77 +3630,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>308</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>49.45</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>76.15</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>6.43</t>
+          <t>6.58</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>5.70</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>70.66</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>66.24</t>
+          <t>66.3</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>66.75</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>63.02</t>
+          <t>63.15</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>262.06</t>
+          <t>125.60</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-88.05</t>
+          <t>-82.57</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>75179432.90759313</t>
+          <t>75115086.28111587</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>82950382.0</t>
+          <t>106177736.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>132496129.6</t>
+          <t>132561832.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>86336133.4</t>
+          <t>93365555.7</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>120394266.18</t>
+          <t>120263879.18</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>46159996</t>
+          <t>39196276</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-3742417.326026477</t>
+          <t>-2157550.973595275</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>6943645.052739069</t>
+          <t>6559213.964776337</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>82950382</v>
+        <v>106177736</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>50.11</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3828,17 +3828,17 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>90.28</t>
+          <t>92.11</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>48.67</t>
+          <t>47.59</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>7605</t>
+          <t>7760</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>67.9</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1393.968</t>
+          <t>1168.47</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-12.17</t>
+          <t>-8.56</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>61.27</t>
+          <t>53.47</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4030,12 +4030,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>10.62</t>
+          <t>9.23</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12.58</t>
+          <t>10.54</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,77 +4066,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>308</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>6.43</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>69.38</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>66.06</t>
+          <t>66.24</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>66.34</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>62.79</t>
+          <t>63.02</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>768.32</t>
+          <t>262.06</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-95.88</t>
+          <t>-88.05</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>75179432.90759313</t>
+          <t>75115086.28111587</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>100281347.0</t>
+          <t>82950382.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>131264222.4</t>
+          <t>132496129.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>81393410.0</t>
+          <t>86336133.4</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>119695734.58</t>
+          <t>120394266.18</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>49870812</t>
+          <t>46159996</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-5685337.758529304</t>
+          <t>-3742417.326026477</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>9733490.069373712</t>
+          <t>6943645.052739069</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>100281347</v>
+        <v>82950382</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>52.01</t>
+          <t>50.11</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4264,17 +4264,17 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>90.28</t>
+          <t>92.11</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>48.67</t>
+          <t>47.59</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>7605</t>
+          <t>7760</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2657.246</t>
+          <t>1393.968</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-13.1</t>
+          <t>-9.94</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>59.46</t>
+          <t>61.27</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>11.54</t>
+          <t>10.62</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>23.97</t>
+          <t>12.58</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,77 +4502,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>308</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>6.65</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>5.60</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>67.98</t>
+          <t>69.38</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>65.84</t>
+          <t>66.06</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>66.06</t>
+          <t>66.34</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>62.56</t>
+          <t>62.79</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>686.39</t>
+          <t>768.32</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-103.80</t>
+          <t>-95.88</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>75179432.90759313</t>
+          <t>75115086.28111587</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>190606270.0</t>
+          <t>100281347.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>118462794.8</t>
+          <t>131264222.4</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>74290109.7</t>
+          <t>81393410.0</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>120126016.38</t>
+          <t>119695734.58</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>44172685</t>
+          <t>49870812</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-8488760.999966215</t>
+          <t>-5685337.758529304</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>11514469.19780271</t>
+          <t>9733490.069373712</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>190606270</v>
+        <v>100281347</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>53.28</t>
+          <t>52.01</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4705,12 +4705,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>90.28</t>
+          <t>92.11</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>48.67</t>
+          <t>47.59</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>7605</t>
+          <t>7760</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
+          <t>71.2</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
           <t>70.6</t>
         </is>
       </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>72.8</t>
-        </is>
-      </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>69.7</t>
-        </is>
-      </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2598.844</t>
+          <t>2657.246</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,74 +4822,74 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>72.5</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-10.86</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>-0.13</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>59.46</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-09-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>70.0</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>-9.2</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>-1.01</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>46.05</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2025-11-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-09-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
         <is>
           <t>70.0</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
       <c r="T11" t="inlineStr">
         <is>
           <t>67.8</t>
@@ -4902,12 +4902,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>11.54</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>23.45</t>
+          <t>23.97</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,12 +4938,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>308</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4958,57 +4958,57 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>5.80</t>
+          <t>6.65</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>5.60</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>66.16</t>
+          <t>67.98</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>65.64</t>
+          <t>65.84</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>65.73</t>
+          <t>66.06</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>62.31</t>
+          <t>62.56</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>122.79</t>
+          <t>686.39</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-110.31</t>
+          <t>-103.80</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>75179432.90759313</t>
+          <t>75115086.28111587</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>182793426.0</t>
+          <t>190606270.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>85235906.2</t>
+          <t>118462794.8</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>58360010.8</t>
+          <t>74290109.7</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>117218867.38</t>
+          <t>120126016.38</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>26875895</t>
+          <t>44172685</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-12125711.94501511</t>
+          <t>-8488760.999966215</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>3969823.731351182</t>
+          <t>11514469.19780271</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>182793426</v>
+        <v>190606270</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>47.99</t>
+          <t>53.28</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>90.28</t>
+          <t>92.11</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>48.67</t>
+          <t>47.59</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>7605</t>
+          <t>7760</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>70.6</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1558.105</t>
+          <t>2598.844</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>67.1</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,22 +5268,22 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-7.03</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>24.49</t>
+          <t>46.05</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -5323,7 +5323,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -5338,12 +5338,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14.06</t>
+          <t>23.45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,12 +5374,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>308</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5389,62 +5389,62 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>94.25</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>5.80</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>5.49</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>64.66</t>
+          <t>66.16</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>65.52</t>
+          <t>65.64</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>65.47</t>
+          <t>65.73</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>62.1</t>
+          <t>62.31</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>122.79</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-113.47</t>
+          <t>-110.31</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,50 +5464,50 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>75179432.90759313</t>
+          <t>75115086.28111587</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>105849223.0</t>
+          <t>182793426.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>54169279.2</t>
+          <t>85235906.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>43512116.9</t>
+          <t>58360010.8</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>113935358.54</t>
+          <t>117218867.38</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>10657162</t>
+          <t>26875895</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-15052172.97708171</t>
+          <t>-12125711.94501511</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-6112930.21112781</t>
+          <t>3969823.731351182</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>105849223</v>
+        <v>182793426</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>41.86</t>
+          <t>47.99</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>90.28</t>
+          <t>92.11</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>48.67</t>
+          <t>47.59</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>7605</t>
+          <t>7760</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>67.1</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5679,42 +5679,42 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2826.0</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>57.2</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5724,37 +5724,37 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-14 00:00:00</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-17 00:00:00</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-09-17 00:00:00</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-10-03 00:00:00</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -5764,12 +5764,12 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>59.6</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>61.5</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -5779,324 +5779,4684 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-4.07</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>3484</t>
+          <t>2826</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
+          <t>35.71</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>22.46</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>0.07</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>-1.69</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>-3.21</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>3.43</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>57.16</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>58.14</t>
+        </is>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>60.07</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>58.08</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>-24.14</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>-0.80</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>-0.65</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>5.31</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>-112.17</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>814356.8199426112</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>162030.0</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>209836.2</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>215755.9</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>550120.9</t>
+        </is>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>-5919</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>-35791.36830932057</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>-38160.02218378661</t>
+        </is>
+      </c>
+      <c r="BD13" t="n">
+        <v>162030</v>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>58.9</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>2025/08/29</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>-2.89</t>
+        </is>
+      </c>
+      <c r="BI13" t="inlineStr">
+        <is>
+          <t>光洋科</t>
+        </is>
+      </c>
+      <c r="BJ13" t="inlineStr">
+        <is>
+          <t>光洋科</t>
+        </is>
+      </c>
+      <c r="BK13" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL13" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM13" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="BN13" t="inlineStr">
+        <is>
+          <t>-1.228328584465341</t>
+        </is>
+      </c>
+      <c r="BO13" t="inlineStr">
+        <is>
+          <t>47.44460114587924</t>
+        </is>
+      </c>
+      <c r="BP13" t="inlineStr">
+        <is>
+          <t>32.54445648609581</t>
+        </is>
+      </c>
+      <c r="BQ13" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR13" t="inlineStr">
+        <is>
+          <t>價漲量-</t>
+        </is>
+      </c>
+      <c r="BS13" t="inlineStr">
+        <is>
+          <t>2.49</t>
+        </is>
+      </c>
+      <c r="BT13" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="BU13" t="inlineStr">
+        <is>
+          <t>17.51</t>
+        </is>
+      </c>
+      <c r="BV13" t="inlineStr">
+        <is>
+          <t>24.34</t>
+        </is>
+      </c>
+      <c r="BW13" t="inlineStr">
+        <is>
+          <t>14.09%</t>
+        </is>
+      </c>
+      <c r="BX13" t="inlineStr">
+        <is>
+          <t>9.19%</t>
+        </is>
+      </c>
+      <c r="BY13" t="inlineStr">
+        <is>
+          <t>43.25</t>
+        </is>
+      </c>
+      <c r="BZ13" t="inlineStr">
+        <is>
+          <t>34092</t>
+        </is>
+      </c>
+      <c r="CA13" t="inlineStr">
+        <is>
+          <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB13" t="inlineStr">
+        <is>
+          <t>光洋科-其他電子業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC13" t="inlineStr">
+        <is>
+          <t>其他電子業右上上櫃</t>
+        </is>
+      </c>
+      <c r="CD13" t="inlineStr">
+        <is>
+          <t>57.5</t>
+        </is>
+      </c>
+      <c r="CE13" t="inlineStr">
+        <is>
+          <t>57.8</t>
+        </is>
+      </c>
+      <c r="CF13" t="inlineStr">
+        <is>
+          <t>56.9</t>
+        </is>
+      </c>
+      <c r="CG13" t="inlineStr">
+        <is>
+          <t>57.2</t>
+        </is>
+      </c>
+      <c r="CH13" t="inlineStr">
+        <is>
+          <t>22.98</t>
+        </is>
+      </c>
+      <c r="CI13" t="inlineStr">
+        <is>
+          <t>** 半導體 - 化學品** 電腦及週邊設備 - 硬碟機** 平面顯示器 - 化學品(如光阻劑、靶材等)** 觸控面板 - ITO靶材** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 印刷電路板 - 生產製程及檢測設備** 其他 - 環保潔能服務產業** 汽車 - 其他** 太陽能產業 - 材料</t>
+        </is>
+      </c>
+      <c r="CJ13" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1785</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AG13" t="inlineStr">
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>3484.0</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>56.8</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>-2.14</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>-15.18</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2025-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>-2.24</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>-4.07</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>6.01</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>-2.29</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>2826</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>16.67</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>10.56</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>-0.77</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>-1.80</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>-2.94</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>3.56</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>57.23999999999999</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>58.29</t>
+        </is>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>60.05</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>57.99</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>-32.85</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>-0.81</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>-0.61</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>5.31</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>-111.43</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>814356.8199426112</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>199284.0</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>213119.2</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>251269.4</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>555483.94</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>-38150</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>-35360.70396850856</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>-36671.78477886959</t>
+        </is>
+      </c>
+      <c r="BD14" t="n">
+        <v>199284</v>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>58.9</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>2025/08/29</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>-3.57</t>
+        </is>
+      </c>
+      <c r="BI14" t="inlineStr">
+        <is>
+          <t>光洋科</t>
+        </is>
+      </c>
+      <c r="BJ14" t="inlineStr">
+        <is>
+          <t>光洋科</t>
+        </is>
+      </c>
+      <c r="BK14" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL14" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM14" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="BN14" t="inlineStr">
+        <is>
+          <t>-1.228328584465341</t>
+        </is>
+      </c>
+      <c r="BO14" t="inlineStr">
+        <is>
+          <t>47.44460114587924</t>
+        </is>
+      </c>
+      <c r="BP14" t="inlineStr">
+        <is>
+          <t>32.54445648609581</t>
+        </is>
+      </c>
+      <c r="BQ14" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR14" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS14" t="inlineStr">
+        <is>
+          <t>2.47</t>
+        </is>
+      </c>
+      <c r="BT14" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="BU14" t="inlineStr">
+        <is>
+          <t>17.51</t>
+        </is>
+      </c>
+      <c r="BV14" t="inlineStr">
+        <is>
+          <t>24.34</t>
+        </is>
+      </c>
+      <c r="BW14" t="inlineStr">
+        <is>
+          <t>14.09%</t>
+        </is>
+      </c>
+      <c r="BX14" t="inlineStr">
+        <is>
+          <t>9.19%</t>
+        </is>
+      </c>
+      <c r="BY14" t="inlineStr">
+        <is>
+          <t>43.25</t>
+        </is>
+      </c>
+      <c r="BZ14" t="inlineStr">
+        <is>
+          <t>34092</t>
+        </is>
+      </c>
+      <c r="CA14" t="inlineStr">
+        <is>
+          <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB14" t="inlineStr">
+        <is>
+          <t>光洋科-其他電子業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC14" t="inlineStr">
+        <is>
+          <t>其他電子業右上上櫃</t>
+        </is>
+      </c>
+      <c r="CD14" t="inlineStr">
+        <is>
+          <t>57.4</t>
+        </is>
+      </c>
+      <c r="CE14" t="inlineStr">
+        <is>
+          <t>58.3</t>
+        </is>
+      </c>
+      <c r="CF14" t="inlineStr">
+        <is>
+          <t>56.6</t>
+        </is>
+      </c>
+      <c r="CG14" t="inlineStr">
+        <is>
+          <t>56.8</t>
+        </is>
+      </c>
+      <c r="CH14" t="inlineStr">
+        <is>
+          <t>22.98</t>
+        </is>
+      </c>
+      <c r="CI14" t="inlineStr">
+        <is>
+          <t>** 半導體 - 化學品** 電腦及週邊設備 - 硬碟機** 平面顯示器 - 化學品(如光阻劑、靶材等)** 觸控面板 - ITO靶材** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 印刷電路板 - 生產製程及檢測設備** 其他 - 環保潔能服務產業** 汽車 - 其他** 太陽能產業 - 材料</t>
+        </is>
+      </c>
+      <c r="CJ14" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1785</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2408.0</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>56.8</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>-2.14</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>-34.72</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2025-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>-2.24</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>-4.07</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>4.15</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>0.19</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>2826</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>16.11</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>-0.98</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>-1.88</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>-2.71</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>3.76</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>57.36</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>58.46</t>
+        </is>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>60.09</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>57.91</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>-36.35</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>-0.76</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>-0.56</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>5.31</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>-110.50</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>814356.8199426112</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>136228.0</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>212208.6</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>325088.9</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>556448.64</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>-112880</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>-35122.32563935201</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>-37227.52474402849</t>
+        </is>
+      </c>
+      <c r="BD15" t="n">
+        <v>136228</v>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>58.9</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>2025/08/29</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>-3.57</t>
+        </is>
+      </c>
+      <c r="BI15" t="inlineStr">
+        <is>
+          <t>光洋科</t>
+        </is>
+      </c>
+      <c r="BJ15" t="inlineStr">
+        <is>
+          <t>光洋科</t>
+        </is>
+      </c>
+      <c r="BK15" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL15" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM15" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="BN15" t="inlineStr">
+        <is>
+          <t>-1.228328584465341</t>
+        </is>
+      </c>
+      <c r="BO15" t="inlineStr">
+        <is>
+          <t>47.44460114587924</t>
+        </is>
+      </c>
+      <c r="BP15" t="inlineStr">
+        <is>
+          <t>32.54445648609581</t>
+        </is>
+      </c>
+      <c r="BQ15" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR15" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS15" t="inlineStr">
+        <is>
+          <t>2.47</t>
+        </is>
+      </c>
+      <c r="BT15" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="BU15" t="inlineStr">
+        <is>
+          <t>17.51</t>
+        </is>
+      </c>
+      <c r="BV15" t="inlineStr">
+        <is>
+          <t>24.34</t>
+        </is>
+      </c>
+      <c r="BW15" t="inlineStr">
+        <is>
+          <t>14.09%</t>
+        </is>
+      </c>
+      <c r="BX15" t="inlineStr">
+        <is>
+          <t>9.19%</t>
+        </is>
+      </c>
+      <c r="BY15" t="inlineStr">
+        <is>
+          <t>43.25</t>
+        </is>
+      </c>
+      <c r="BZ15" t="inlineStr">
+        <is>
+          <t>34092</t>
+        </is>
+      </c>
+      <c r="CA15" t="inlineStr">
+        <is>
+          <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB15" t="inlineStr">
+        <is>
+          <t>光洋科-其他電子業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC15" t="inlineStr">
+        <is>
+          <t>其他電子業右上上櫃</t>
+        </is>
+      </c>
+      <c r="CD15" t="inlineStr">
+        <is>
+          <t>57.3</t>
+        </is>
+      </c>
+      <c r="CE15" t="inlineStr">
+        <is>
+          <t>57.4</t>
+        </is>
+      </c>
+      <c r="CF15" t="inlineStr">
+        <is>
+          <t>56.1</t>
+        </is>
+      </c>
+      <c r="CG15" t="inlineStr">
+        <is>
+          <t>56.8</t>
+        </is>
+      </c>
+      <c r="CH15" t="inlineStr">
+        <is>
+          <t>22.98</t>
+        </is>
+      </c>
+      <c r="CI15" t="inlineStr">
+        <is>
+          <t>** 半導體 - 化學品** 電腦及週邊設備 - 硬碟機** 平面顯示器 - 化學品(如光阻劑、靶材等)** 觸控面板 - ITO靶材** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 印刷電路板 - 生產製程及檢測設備** 其他 - 環保潔能服務產業** 汽車 - 其他** 太陽能產業 - 材料</t>
+        </is>
+      </c>
+      <c r="CJ15" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1785</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>-4.5</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>4791.0</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>56.2</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>-2.14</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>-31.67</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2025-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>-3.27</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>-4.07</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>8.27</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>-4.09</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>2826</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AP13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AS13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AV13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BA13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BB13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BC13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BG13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BH13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BI13" t="inlineStr">
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>15.46</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>-2.46</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>-1.76</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>-2.42</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>3.95</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>57.62</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>58.66</t>
+        </is>
+      </c>
+      <c r="AN16" t="inlineStr">
+        <is>
+          <t>60.11</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>57.83</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>-36.02</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>-0.69</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>-0.51</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>5.31</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr">
+        <is>
+          <t>-109.54</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>814356.8199426112</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>273475.0</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>241628.6</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>353601.2</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>558552.82</t>
+        </is>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>-111972</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>-34739.56216577447</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>-29935.8845248259</t>
+        </is>
+      </c>
+      <c r="BD16" t="n">
+        <v>273475</v>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
+          <t>58.9</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>2025/08/29</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>-4.58</t>
+        </is>
+      </c>
+      <c r="BI16" t="inlineStr">
         <is>
           <t>光洋科</t>
         </is>
       </c>
-      <c r="BJ13" t="inlineStr">
+      <c r="BJ16" t="inlineStr">
         <is>
           <t>光洋科</t>
         </is>
       </c>
-      <c r="BK13" t="inlineStr">
+      <c r="BK16" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BL13" t="inlineStr">
+      <c r="BL16" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BM13" t="inlineStr">
+      <c r="BM16" t="inlineStr">
         <is>
           <t>1.09</t>
         </is>
       </c>
-      <c r="BN13" t="inlineStr">
+      <c r="BN16" t="inlineStr">
         <is>
           <t>-1.228328584465341</t>
         </is>
       </c>
-      <c r="BO13" t="inlineStr">
+      <c r="BO16" t="inlineStr">
         <is>
           <t>47.44460114587924</t>
         </is>
       </c>
-      <c r="BP13" t="inlineStr">
+      <c r="BP16" t="inlineStr">
         <is>
           <t>32.54445648609581</t>
         </is>
       </c>
-      <c r="BQ13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BR13" t="inlineStr">
+      <c r="BQ16" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR16" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BS13" t="inlineStr">
+      <c r="BS16" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="BT16" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="BU16" t="inlineStr">
+        <is>
+          <t>17.51</t>
+        </is>
+      </c>
+      <c r="BV16" t="inlineStr">
+        <is>
+          <t>24.34</t>
+        </is>
+      </c>
+      <c r="BW16" t="inlineStr">
+        <is>
+          <t>14.09%</t>
+        </is>
+      </c>
+      <c r="BX16" t="inlineStr">
+        <is>
+          <t>9.19%</t>
+        </is>
+      </c>
+      <c r="BY16" t="inlineStr">
+        <is>
+          <t>43.25</t>
+        </is>
+      </c>
+      <c r="BZ16" t="inlineStr">
+        <is>
+          <t>34092</t>
+        </is>
+      </c>
+      <c r="CA16" t="inlineStr">
+        <is>
+          <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB16" t="inlineStr">
+        <is>
+          <t>光洋科-其他電子業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC16" t="inlineStr">
+        <is>
+          <t>其他電子業右上上櫃</t>
+        </is>
+      </c>
+      <c r="CD16" t="inlineStr">
+        <is>
+          <t>57.8</t>
+        </is>
+      </c>
+      <c r="CE16" t="inlineStr">
+        <is>
+          <t>58.7</t>
+        </is>
+      </c>
+      <c r="CF16" t="inlineStr">
+        <is>
+          <t>56.0</t>
+        </is>
+      </c>
+      <c r="CG16" t="inlineStr">
+        <is>
+          <t>56.2</t>
+        </is>
+      </c>
+      <c r="CH16" t="inlineStr">
+        <is>
+          <t>22.98</t>
+        </is>
+      </c>
+      <c r="CI16" t="inlineStr">
+        <is>
+          <t>** 半導體 - 化學品** 電腦及週邊設備 - 硬碟機** 平面顯示器 - 化學品(如光阻劑、靶材等)** 觸控面板 - ITO靶材** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 印刷電路板 - 生產製程及檢測設備** 其他 - 環保潔能服務產業** 汽車 - 其他** 太陽能產業 - 材料</t>
+        </is>
+      </c>
+      <c r="CJ16" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1785</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>4747.0</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>58.8</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-2.8</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>-2.14</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>-31.52</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2025-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>1.20</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>-4.07</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>8.19</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>0.87</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>2826</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>33.33</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>19.01</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>1.07</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>-1.21</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>-2.1</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>4.12</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>58.17999999999999</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>58.9</t>
+        </is>
+      </c>
+      <c r="AN17" t="inlineStr">
+        <is>
+          <t>60.16</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>57.77</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>-14.48</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>-0.53</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>-0.46</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>5.31</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr">
+        <is>
+          <t>-108.68</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>814356.8199426112</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>278164.0</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>235377.2</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>343709.9</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>560862.08</t>
+        </is>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>-108332</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>-35612.95810049239</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>-33155.15262150689</t>
+        </is>
+      </c>
+      <c r="BD17" t="n">
+        <v>278164</v>
+      </c>
+      <c r="BE17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF17" t="inlineStr">
+        <is>
+          <t>58.9</t>
+        </is>
+      </c>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>2025/08/29</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>-0.17</t>
+        </is>
+      </c>
+      <c r="BI17" t="inlineStr">
+        <is>
+          <t>光洋科</t>
+        </is>
+      </c>
+      <c r="BJ17" t="inlineStr">
+        <is>
+          <t>光洋科</t>
+        </is>
+      </c>
+      <c r="BK17" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL17" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM17" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="BN17" t="inlineStr">
+        <is>
+          <t>-1.228328584465341</t>
+        </is>
+      </c>
+      <c r="BO17" t="inlineStr">
+        <is>
+          <t>47.44460114587924</t>
+        </is>
+      </c>
+      <c r="BP17" t="inlineStr">
+        <is>
+          <t>32.54445648609581</t>
+        </is>
+      </c>
+      <c r="BQ17" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR17" t="inlineStr">
+        <is>
+          <t>價漲量-</t>
+        </is>
+      </c>
+      <c r="BS17" t="inlineStr">
+        <is>
+          <t>2.56</t>
+        </is>
+      </c>
+      <c r="BT17" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="BU17" t="inlineStr">
+        <is>
+          <t>17.51</t>
+        </is>
+      </c>
+      <c r="BV17" t="inlineStr">
+        <is>
+          <t>24.34</t>
+        </is>
+      </c>
+      <c r="BW17" t="inlineStr">
+        <is>
+          <t>14.09%</t>
+        </is>
+      </c>
+      <c r="BX17" t="inlineStr">
+        <is>
+          <t>9.19%</t>
+        </is>
+      </c>
+      <c r="BY17" t="inlineStr">
+        <is>
+          <t>43.25</t>
+        </is>
+      </c>
+      <c r="BZ17" t="inlineStr">
+        <is>
+          <t>34092</t>
+        </is>
+      </c>
+      <c r="CA17" t="inlineStr">
+        <is>
+          <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB17" t="inlineStr">
+        <is>
+          <t>光洋科-其他電子業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC17" t="inlineStr">
+        <is>
+          <t>其他電子業右上上櫃</t>
+        </is>
+      </c>
+      <c r="CD17" t="inlineStr">
+        <is>
+          <t>58.8</t>
+        </is>
+      </c>
+      <c r="CE17" t="inlineStr">
+        <is>
+          <t>59.2</t>
+        </is>
+      </c>
+      <c r="CF17" t="inlineStr">
+        <is>
+          <t>57.9</t>
+        </is>
+      </c>
+      <c r="CG17" t="inlineStr">
+        <is>
+          <t>58.8</t>
+        </is>
+      </c>
+      <c r="CH17" t="inlineStr">
+        <is>
+          <t>22.98</t>
+        </is>
+      </c>
+      <c r="CI17" t="inlineStr">
+        <is>
+          <t>** 半導體 - 化學品** 電腦及週邊設備 - 硬碟機** 平面顯示器 - 化學品(如光阻劑、靶材等)** 觸控面板 - ITO靶材** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 印刷電路板 - 生產製程及檢測設備** 其他 - 環保潔能服務產業** 汽車 - 其他** 太陽能產業 - 材料</t>
+        </is>
+      </c>
+      <c r="CJ17" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1785</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0.34</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>3082.0</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>57.6</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-0.7</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-2.14</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>-33.50</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2025-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>-0.86</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>-4.07</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>5.32</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>-1.04</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>2826</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>13.04</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>21.45</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>-1.34</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>-1.07</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>-1.87</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>4.23</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>58.38000000000001</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>59.01</t>
+        </is>
+      </c>
+      <c r="AN18" t="inlineStr">
+        <is>
+          <t>60.14</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>57.69</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>-30.25</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>-0.58</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>-0.44</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>5.31</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr">
+        <is>
+          <t>-108.37</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV18" t="inlineStr">
+        <is>
+          <t>814356.8199426112</t>
+        </is>
+      </c>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>178445.0</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>221675.6</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>333361.3</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>566147.36</t>
+        </is>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>-111685</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>-36059.8318239443</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>-37072.38730885455</t>
+        </is>
+      </c>
+      <c r="BD18" t="n">
+        <v>178445</v>
+      </c>
+      <c r="BE18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF18" t="inlineStr">
+        <is>
+          <t>58.9</t>
+        </is>
+      </c>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>2025/08/29</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>-2.21</t>
+        </is>
+      </c>
+      <c r="BI18" t="inlineStr">
+        <is>
+          <t>光洋科</t>
+        </is>
+      </c>
+      <c r="BJ18" t="inlineStr">
+        <is>
+          <t>光洋科</t>
+        </is>
+      </c>
+      <c r="BK18" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL18" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM18" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="BN18" t="inlineStr">
+        <is>
+          <t>-1.228328584465341</t>
+        </is>
+      </c>
+      <c r="BO18" t="inlineStr">
+        <is>
+          <t>47.44460114587924</t>
+        </is>
+      </c>
+      <c r="BP18" t="inlineStr">
+        <is>
+          <t>32.54445648609581</t>
+        </is>
+      </c>
+      <c r="BQ18" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR18" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS18" t="inlineStr">
+        <is>
+          <t>2.51</t>
+        </is>
+      </c>
+      <c r="BT18" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="BU18" t="inlineStr">
+        <is>
+          <t>17.51</t>
+        </is>
+      </c>
+      <c r="BV18" t="inlineStr">
+        <is>
+          <t>24.34</t>
+        </is>
+      </c>
+      <c r="BW18" t="inlineStr">
+        <is>
+          <t>14.09%</t>
+        </is>
+      </c>
+      <c r="BX18" t="inlineStr">
+        <is>
+          <t>9.19%</t>
+        </is>
+      </c>
+      <c r="BY18" t="inlineStr">
+        <is>
+          <t>43.25</t>
+        </is>
+      </c>
+      <c r="BZ18" t="inlineStr">
+        <is>
+          <t>34092</t>
+        </is>
+      </c>
+      <c r="CA18" t="inlineStr">
+        <is>
+          <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB18" t="inlineStr">
+        <is>
+          <t>光洋科-其他電子業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC18" t="inlineStr">
+        <is>
+          <t>其他電子業右上上櫃</t>
+        </is>
+      </c>
+      <c r="CD18" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="CE18" t="inlineStr">
+        <is>
+          <t>58.5</t>
+        </is>
+      </c>
+      <c r="CF18" t="inlineStr">
+        <is>
+          <t>57.3</t>
+        </is>
+      </c>
+      <c r="CG18" t="inlineStr">
+        <is>
+          <t>57.6</t>
+        </is>
+      </c>
+      <c r="CH18" t="inlineStr">
+        <is>
+          <t>22.98</t>
+        </is>
+      </c>
+      <c r="CI18" t="inlineStr">
+        <is>
+          <t>** 半導體 - 化學品** 電腦及週邊設備 - 硬碟機** 平面顯示器 - 化學品(如光阻劑、靶材等)** 觸控面板 - ITO靶材** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 印刷電路板 - 生產製程及檢測設備** 其他 - 環保潔能服務產業** 汽車 - 其他** 太陽能產業 - 材料</t>
+        </is>
+      </c>
+      <c r="CJ18" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1785</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>-1.21</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>3352.0</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>57.4</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-0.35</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>-2.14</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>-15.27</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2025-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>-1.20</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>-4.07</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>5.78</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>-3.14</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>2826</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>10.64</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>35.75</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>-2.55</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>-0.57</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>-1.45</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>4.32</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>58.9</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>59.24</t>
+        </is>
+      </c>
+      <c r="AN19" t="inlineStr">
+        <is>
+          <t>60.11</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>57.62</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>-24.96</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>-0.51</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>-0.41</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>5.31</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr">
+        <is>
+          <t>-107.74</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>814356.8199426112</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>194731.0</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>289419.6</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>341561.2</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>568481.84</t>
+        </is>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>-52141</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>-35875.73082668789</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>-30660.24445832073</t>
+        </is>
+      </c>
+      <c r="BD19" t="n">
+        <v>194731</v>
+      </c>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
+          <t>58.9</t>
+        </is>
+      </c>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>2025/08/29</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>-2.55</t>
+        </is>
+      </c>
+      <c r="BI19" t="inlineStr">
+        <is>
+          <t>光洋科</t>
+        </is>
+      </c>
+      <c r="BJ19" t="inlineStr">
+        <is>
+          <t>光洋科</t>
+        </is>
+      </c>
+      <c r="BK19" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL19" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM19" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="BN19" t="inlineStr">
+        <is>
+          <t>-1.228328584465341</t>
+        </is>
+      </c>
+      <c r="BO19" t="inlineStr">
+        <is>
+          <t>47.44460114587924</t>
+        </is>
+      </c>
+      <c r="BP19" t="inlineStr">
+        <is>
+          <t>32.54445648609581</t>
+        </is>
+      </c>
+      <c r="BQ19" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BR19" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS19" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="BT19" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="BU19" t="inlineStr">
+        <is>
+          <t>17.51</t>
+        </is>
+      </c>
+      <c r="BV19" t="inlineStr">
+        <is>
+          <t>24.34</t>
+        </is>
+      </c>
+      <c r="BW19" t="inlineStr">
+        <is>
+          <t>14.09%</t>
+        </is>
+      </c>
+      <c r="BX19" t="inlineStr">
+        <is>
+          <t>9.19%</t>
+        </is>
+      </c>
+      <c r="BY19" t="inlineStr">
+        <is>
+          <t>43.25</t>
+        </is>
+      </c>
+      <c r="BZ19" t="inlineStr">
+        <is>
+          <t>34092</t>
+        </is>
+      </c>
+      <c r="CA19" t="inlineStr">
+        <is>
+          <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB19" t="inlineStr">
+        <is>
+          <t>光洋科-其他電子業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC19" t="inlineStr">
+        <is>
+          <t>其他電子業右上上櫃</t>
+        </is>
+      </c>
+      <c r="CD19" t="inlineStr">
+        <is>
+          <t>58.0</t>
+        </is>
+      </c>
+      <c r="CE19" t="inlineStr">
+        <is>
+          <t>59.2</t>
+        </is>
+      </c>
+      <c r="CF19" t="inlineStr">
+        <is>
+          <t>57.4</t>
+        </is>
+      </c>
+      <c r="CG19" t="inlineStr">
+        <is>
+          <t>57.4</t>
+        </is>
+      </c>
+      <c r="CH19" t="inlineStr">
+        <is>
+          <t>22.98</t>
+        </is>
+      </c>
+      <c r="CI19" t="inlineStr">
+        <is>
+          <t>** 半導體 - 化學品** 電腦及週邊設備 - 硬碟機** 平面顯示器 - 化學品(如光阻劑、靶材等)** 觸控面板 - ITO靶材** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 印刷電路板 - 生產製程及檢測設備** 其他 - 環保潔能服務產業** 汽車 - 其他** 太陽能產業 - 材料</t>
+        </is>
+      </c>
+      <c r="CJ19" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1785</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>-1.51</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>4870.0</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-1.57</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>-2.14</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>22.85</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2025-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>-1.53</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="BT13" t="inlineStr">
-        <is>
-          <t>3.52</t>
-        </is>
-      </c>
-      <c r="BU13" t="inlineStr">
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>-4.07</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>8.40</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>-1.35</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>2826</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>40.68</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>55.37</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>-2.75</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>0.39</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>4.44</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>59.73999999999999</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>59.51</t>
+        </is>
+      </c>
+      <c r="AN20" t="inlineStr">
+        <is>
+          <t>60.1</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>57.55</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>-4.35</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>-0.40</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>-0.39</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>5.31</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr">
+        <is>
+          <t>-107.25</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>814356.8199426112</t>
+        </is>
+      </c>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>283328.0</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>437969.2</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>356514.8</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>570563.3</t>
+        </is>
+      </c>
+      <c r="BA20" t="inlineStr">
+        <is>
+          <t>81454</t>
+        </is>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>-36824.00107548192</t>
+        </is>
+      </c>
+      <c r="BC20" t="inlineStr">
+        <is>
+          <t>-22149.96022690379</t>
+        </is>
+      </c>
+      <c r="BD20" t="n">
+        <v>283328</v>
+      </c>
+      <c r="BE20" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="BF20" t="inlineStr">
+        <is>
+          <t>58.9</t>
+        </is>
+      </c>
+      <c r="BG20" t="inlineStr">
+        <is>
+          <t>2025/08/29</t>
+        </is>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>-1.36</t>
+        </is>
+      </c>
+      <c r="BI20" t="inlineStr">
+        <is>
+          <t>光洋科</t>
+        </is>
+      </c>
+      <c r="BJ20" t="inlineStr">
+        <is>
+          <t>光洋科</t>
+        </is>
+      </c>
+      <c r="BK20" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL20" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM20" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="BN20" t="inlineStr">
+        <is>
+          <t>-1.228328584465341</t>
+        </is>
+      </c>
+      <c r="BO20" t="inlineStr">
+        <is>
+          <t>47.44460114587924</t>
+        </is>
+      </c>
+      <c r="BP20" t="inlineStr">
+        <is>
+          <t>32.54445648609581</t>
+        </is>
+      </c>
+      <c r="BQ20" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BR20" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS20" t="inlineStr">
+        <is>
+          <t>2.53</t>
+        </is>
+      </c>
+      <c r="BT20" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="BU20" t="inlineStr">
         <is>
           <t>17.51</t>
         </is>
       </c>
-      <c r="BV13" t="inlineStr">
-        <is>
-          <t>24.17</t>
-        </is>
-      </c>
-      <c r="BW13" t="inlineStr">
+      <c r="BV20" t="inlineStr">
+        <is>
+          <t>24.34</t>
+        </is>
+      </c>
+      <c r="BW20" t="inlineStr">
         <is>
           <t>14.09%</t>
         </is>
       </c>
-      <c r="BX13" t="inlineStr">
+      <c r="BX20" t="inlineStr">
         <is>
           <t>9.19%</t>
         </is>
       </c>
-      <c r="BY13" t="inlineStr">
-        <is>
-          <t>42.67</t>
-        </is>
-      </c>
-      <c r="BZ13" t="inlineStr">
-        <is>
-          <t>33854</t>
-        </is>
-      </c>
-      <c r="CA13" t="inlineStr">
+      <c r="BY20" t="inlineStr">
+        <is>
+          <t>43.25</t>
+        </is>
+      </c>
+      <c r="BZ20" t="inlineStr">
+        <is>
+          <t>34092</t>
+        </is>
+      </c>
+      <c r="CA20" t="inlineStr">
         <is>
           <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
         </is>
       </c>
-      <c r="CB13" t="inlineStr">
+      <c r="CB20" t="inlineStr">
         <is>
           <t>光洋科-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CC13" t="inlineStr">
-        <is>
-          <t>其他電子業右下上櫃</t>
-        </is>
-      </c>
-      <c r="CD13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CE13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="CF13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="CG13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="CH13" t="inlineStr">
+      <c r="CC20" t="inlineStr">
+        <is>
+          <t>其他電子業右上上櫃</t>
+        </is>
+      </c>
+      <c r="CD20" t="inlineStr">
+        <is>
+          <t>59.8</t>
+        </is>
+      </c>
+      <c r="CE20" t="inlineStr">
+        <is>
+          <t>59.8</t>
+        </is>
+      </c>
+      <c r="CF20" t="inlineStr">
+        <is>
+          <t>57.2</t>
+        </is>
+      </c>
+      <c r="CG20" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="CH20" t="inlineStr">
         <is>
           <t>22.98</t>
         </is>
       </c>
-      <c r="CI13" t="inlineStr">
+      <c r="CI20" t="inlineStr">
         <is>
           <t>** 半導體 - 化學品** 電腦及週邊設備 - 硬碟機** 平面顯示器 - 化學品(如光阻劑、靶材等)** 觸控面板 - ITO靶材** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 印刷電路板 - 生產製程及檢測設備** 其他 - 環保潔能服務產業** 汽車 - 其他** 太陽能產業 - 材料</t>
         </is>
       </c>
-      <c r="CJ13" t="inlineStr">
+      <c r="CJ20" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1785</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>-1.35</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>4060.0</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-3.15</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>-2.14</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>36.21</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2025-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>-4.07</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>7.01</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>-1.86</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>2826</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>55.93</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>67.23</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>-1.86</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>0.64</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>-0.58</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>4.58</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>60.12</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>59.74</t>
+        </is>
+      </c>
+      <c r="AN21" t="inlineStr">
+        <is>
+          <t>60.09</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>57.46</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>14.66</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>-0.33</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>-0.38</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>5.31</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr">
+        <is>
+          <t>-107.17</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV21" t="inlineStr">
+        <is>
+          <t>814356.8199426112</t>
+        </is>
+      </c>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>242218.0</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>465573.8</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>341803.5</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>579417.88</t>
+        </is>
+      </c>
+      <c r="BA21" t="inlineStr">
+        <is>
+          <t>123770</t>
+        </is>
+      </c>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>-39492.00850249613</t>
+        </is>
+      </c>
+      <c r="BC21" t="inlineStr">
+        <is>
+          <t>-18693.87703106157</t>
+        </is>
+      </c>
+      <c r="BD21" t="n">
+        <v>242218</v>
+      </c>
+      <c r="BE21" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="BF21" t="inlineStr">
+        <is>
+          <t>58.9</t>
+        </is>
+      </c>
+      <c r="BG21" t="inlineStr">
+        <is>
+          <t>2025/08/29</t>
+        </is>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>0.17</t>
+        </is>
+      </c>
+      <c r="BI21" t="inlineStr">
+        <is>
+          <t>光洋科</t>
+        </is>
+      </c>
+      <c r="BJ21" t="inlineStr">
+        <is>
+          <t>光洋科</t>
+        </is>
+      </c>
+      <c r="BK21" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL21" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM21" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="BN21" t="inlineStr">
+        <is>
+          <t>-1.228328584465341</t>
+        </is>
+      </c>
+      <c r="BO21" t="inlineStr">
+        <is>
+          <t>47.44460114587924</t>
+        </is>
+      </c>
+      <c r="BP21" t="inlineStr">
+        <is>
+          <t>32.54445648609581</t>
+        </is>
+      </c>
+      <c r="BQ21" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BR21" t="inlineStr">
+        <is>
+          <t>價跌量增</t>
+        </is>
+      </c>
+      <c r="BS21" t="inlineStr">
+        <is>
+          <t>2.57</t>
+        </is>
+      </c>
+      <c r="BT21" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="BU21" t="inlineStr">
+        <is>
+          <t>17.51</t>
+        </is>
+      </c>
+      <c r="BV21" t="inlineStr">
+        <is>
+          <t>24.34</t>
+        </is>
+      </c>
+      <c r="BW21" t="inlineStr">
+        <is>
+          <t>14.09%</t>
+        </is>
+      </c>
+      <c r="BX21" t="inlineStr">
+        <is>
+          <t>9.19%</t>
+        </is>
+      </c>
+      <c r="BY21" t="inlineStr">
+        <is>
+          <t>43.25</t>
+        </is>
+      </c>
+      <c r="BZ21" t="inlineStr">
+        <is>
+          <t>34092</t>
+        </is>
+      </c>
+      <c r="CA21" t="inlineStr">
+        <is>
+          <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB21" t="inlineStr">
+        <is>
+          <t>光洋科-其他電子業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC21" t="inlineStr">
+        <is>
+          <t>其他電子業右上上櫃</t>
+        </is>
+      </c>
+      <c r="CD21" t="inlineStr">
+        <is>
+          <t>59.3</t>
+        </is>
+      </c>
+      <c r="CE21" t="inlineStr">
+        <is>
+          <t>60.6</t>
+        </is>
+      </c>
+      <c r="CF21" t="inlineStr">
+        <is>
+          <t>58.5</t>
+        </is>
+      </c>
+      <c r="CG21" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="CH21" t="inlineStr">
+        <is>
+          <t>22.98</t>
+        </is>
+      </c>
+      <c r="CI21" t="inlineStr">
+        <is>
+          <t>** 半導體 - 化學品** 電腦及週邊設備 - 硬碟機** 平面顯示器 - 化學品(如光阻劑、靶材等)** 觸控面板 - ITO靶材** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 印刷電路板 - 生產製程及檢測設備** 其他 - 環保潔能服務產業** 汽車 - 其他** 太陽能產業 - 材料</t>
+        </is>
+      </c>
+      <c r="CJ21" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>1785</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>-0.67</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>3505.0</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>59.8</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-4.55</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>-2.14</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>36.04</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2025-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>2.93</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>-4.07</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>6.05</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>2826</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>69.49</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>81.92</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>0.13</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>-0.44</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>-0.18</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>4.74</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>59.72000000000001</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>59.98</t>
+        </is>
+      </c>
+      <c r="AN22" t="inlineStr">
+        <is>
+          <t>60.1</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>57.38</t>
+        </is>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t>20.51</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>-0.31</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>-0.40</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>5.31</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr">
+        <is>
+          <t>-107.44</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV22" t="inlineStr">
+        <is>
+          <t>814356.8199426112</t>
+        </is>
+      </c>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>209656.0</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>452042.6</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>332281.8</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>596784.86</t>
+        </is>
+      </c>
+      <c r="BA22" t="inlineStr">
+        <is>
+          <t>119760</t>
+        </is>
+      </c>
+      <c r="BB22" t="inlineStr">
+        <is>
+          <t>-43273.48695184787</t>
+        </is>
+      </c>
+      <c r="BC22" t="inlineStr">
+        <is>
+          <t>-8684.334000177623</t>
+        </is>
+      </c>
+      <c r="BD22" t="n">
+        <v>209656</v>
+      </c>
+      <c r="BE22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF22" t="inlineStr">
+        <is>
+          <t>58.9</t>
+        </is>
+      </c>
+      <c r="BG22" t="inlineStr">
+        <is>
+          <t>2025/08/29</t>
+        </is>
+      </c>
+      <c r="BH22" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="BI22" t="inlineStr">
+        <is>
+          <t>光洋科</t>
+        </is>
+      </c>
+      <c r="BJ22" t="inlineStr">
+        <is>
+          <t>光洋科</t>
+        </is>
+      </c>
+      <c r="BK22" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL22" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM22" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="BN22" t="inlineStr">
+        <is>
+          <t>-1.228328584465341</t>
+        </is>
+      </c>
+      <c r="BO22" t="inlineStr">
+        <is>
+          <t>47.44460114587924</t>
+        </is>
+      </c>
+      <c r="BP22" t="inlineStr">
+        <is>
+          <t>32.54445648609581</t>
+        </is>
+      </c>
+      <c r="BQ22" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR22" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS22" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="BT22" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="BU22" t="inlineStr">
+        <is>
+          <t>17.51</t>
+        </is>
+      </c>
+      <c r="BV22" t="inlineStr">
+        <is>
+          <t>24.34</t>
+        </is>
+      </c>
+      <c r="BW22" t="inlineStr">
+        <is>
+          <t>14.09%</t>
+        </is>
+      </c>
+      <c r="BX22" t="inlineStr">
+        <is>
+          <t>9.19%</t>
+        </is>
+      </c>
+      <c r="BY22" t="inlineStr">
+        <is>
+          <t>43.25</t>
+        </is>
+      </c>
+      <c r="BZ22" t="inlineStr">
+        <is>
+          <t>34092</t>
+        </is>
+      </c>
+      <c r="CA22" t="inlineStr">
+        <is>
+          <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB22" t="inlineStr">
+        <is>
+          <t>光洋科-其他電子業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC22" t="inlineStr">
+        <is>
+          <t>其他電子業右上上櫃</t>
+        </is>
+      </c>
+      <c r="CD22" t="inlineStr">
+        <is>
+          <t>60.1</t>
+        </is>
+      </c>
+      <c r="CE22" t="inlineStr">
+        <is>
+          <t>60.4</t>
+        </is>
+      </c>
+      <c r="CF22" t="inlineStr">
+        <is>
+          <t>59.2</t>
+        </is>
+      </c>
+      <c r="CG22" t="inlineStr">
+        <is>
+          <t>59.8</t>
+        </is>
+      </c>
+      <c r="CH22" t="inlineStr">
+        <is>
+          <t>22.98</t>
+        </is>
+      </c>
+      <c r="CI22" t="inlineStr">
+        <is>
+          <t>** 半導體 - 化學品** 電腦及週邊設備 - 硬碟機** 平面顯示器 - 化學品(如光阻劑、靶材等)** 觸控面板 - ITO靶材** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 印刷電路板 - 生產製程及檢測設備** 其他 - 環保潔能服務產業** 汽車 - 其他** 太陽能產業 - 材料</t>
+        </is>
+      </c>
+      <c r="CJ22" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1785</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>-2.27</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>8540.0</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>60.2</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-5.24</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>-2.14</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>30.92</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2025-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>3.61</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>-4.07</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14.74</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>-1.65</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>2826</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>76.27</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>91.33</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>-1.58</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>4.83</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>59.14</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>60.09</t>
+        </is>
+      </c>
+      <c r="AN23" t="inlineStr">
+        <is>
+          <t>60.08</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>57.31</t>
+        </is>
+      </c>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>9.30</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>-0.38</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>-0.42</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>5.31</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr">
+        <is>
+          <t>-107.82</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV23" t="inlineStr">
+        <is>
+          <t>814356.8199426112</t>
+        </is>
+      </c>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>517165.0</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>445047.0</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>339942.5</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>643736.64</t>
+        </is>
+      </c>
+      <c r="BA23" t="inlineStr">
+        <is>
+          <t>105104</t>
+        </is>
+      </c>
+      <c r="BB23" t="inlineStr">
+        <is>
+          <t>-49562.42385215155</t>
+        </is>
+      </c>
+      <c r="BC23" t="inlineStr">
+        <is>
+          <t>9413.953686805733</t>
+        </is>
+      </c>
+      <c r="BD23" t="n">
+        <v>517165</v>
+      </c>
+      <c r="BE23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF23" t="inlineStr">
+        <is>
+          <t>58.9</t>
+        </is>
+      </c>
+      <c r="BG23" t="inlineStr">
+        <is>
+          <t>2025/08/29</t>
+        </is>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="BI23" t="inlineStr">
+        <is>
+          <t>光洋科</t>
+        </is>
+      </c>
+      <c r="BJ23" t="inlineStr">
+        <is>
+          <t>光洋科</t>
+        </is>
+      </c>
+      <c r="BK23" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL23" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM23" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="BN23" t="inlineStr">
+        <is>
+          <t>-1.228328584465341</t>
+        </is>
+      </c>
+      <c r="BO23" t="inlineStr">
+        <is>
+          <t>47.44460114587924</t>
+        </is>
+      </c>
+      <c r="BP23" t="inlineStr">
+        <is>
+          <t>32.54445648609581</t>
+        </is>
+      </c>
+      <c r="BQ23" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR23" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS23" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="BT23" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="BU23" t="inlineStr">
+        <is>
+          <t>17.51</t>
+        </is>
+      </c>
+      <c r="BV23" t="inlineStr">
+        <is>
+          <t>24.34</t>
+        </is>
+      </c>
+      <c r="BW23" t="inlineStr">
+        <is>
+          <t>14.09%</t>
+        </is>
+      </c>
+      <c r="BX23" t="inlineStr">
+        <is>
+          <t>9.19%</t>
+        </is>
+      </c>
+      <c r="BY23" t="inlineStr">
+        <is>
+          <t>43.25</t>
+        </is>
+      </c>
+      <c r="BZ23" t="inlineStr">
+        <is>
+          <t>34092</t>
+        </is>
+      </c>
+      <c r="CA23" t="inlineStr">
+        <is>
+          <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB23" t="inlineStr">
+        <is>
+          <t>光洋科-其他電子業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC23" t="inlineStr">
+        <is>
+          <t>其他電子業右上上櫃</t>
+        </is>
+      </c>
+      <c r="CD23" t="inlineStr">
+        <is>
+          <t>61.7</t>
+        </is>
+      </c>
+      <c r="CE23" t="inlineStr">
+        <is>
+          <t>61.8</t>
+        </is>
+      </c>
+      <c r="CF23" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="CG23" t="inlineStr">
+        <is>
+          <t>60.2</t>
+        </is>
+      </c>
+      <c r="CH23" t="inlineStr">
+        <is>
+          <t>22.98</t>
+        </is>
+      </c>
+      <c r="CI23" t="inlineStr">
+        <is>
+          <t>** 半導體 - 化學品** 電腦及週邊設備 - 硬碟機** 平面顯示器 - 化學品(如光阻劑、靶材等)** 觸控面板 - ITO靶材** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 印刷電路板 - 生產製程及檢測設備** 其他 - 環保潔能服務產業** 汽車 - 其他** 太陽能產業 - 材料</t>
+        </is>
+      </c>
+      <c r="CJ23" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料).xlsx
+++ b/Result/checksun_type/濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料).xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>65.12</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>66.14</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>66.83</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>66.14</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>66.83</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>20134094.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>29566216.0</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>29566216</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>67689821.8</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>102474885.18</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>102474885.18</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-10952804.2329868</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>20134094</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>20134094.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>65.24000000000001</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>66.14</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>66.84</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>66.14</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>66.84</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>28041681.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>35349677.8</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>35349677.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>83955755.0</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>105161801.84</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>105161801.84</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-9472320.967936054</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>28041681</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>28041681.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>66.0</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>66.2</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>66.9</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>66.90000000000001</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>27698337.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>50976888.8</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>50976888.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>91736509.2</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>107077260.2</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>107077260.2</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-7866289.16186586</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>27698337</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>27698337.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>67.4</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>66.28</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>66.98</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>66.28</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>66.98</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>44220240.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>62027297.8</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>62027297.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>96645760.1</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>113463276.16</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>113463276.16</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-5254232.254556075</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>44220240</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>44220240.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>68.78000000000002</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>66.31</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>66.98</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>66.31</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>66.98</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>27736728.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>73239519.2</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>73239519.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>95851157.0</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>115231412.04</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>115231412.04</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-3105275.127879396</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>27736728</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>27736728.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>69.86000000000001</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>66.24</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>66.9</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>66.23999999999999</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>66.90000000000001</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>49051403.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>105813427.6</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>105813427.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>95524666.9</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>120066640.9</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>120066640.9</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>1841656.879083008</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>49051403</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>49051403.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>70.66</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>66.3</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>66.75</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>66.75</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>106177736.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>132561832.2</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>132561832.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>93365555.7</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>120263879.18</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>120263879.18</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>6559213.964776337</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>106177736</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>106177736.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>70.5</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>66.24</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>66.23999999999999</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>66.59999999999999</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>82950382.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>132496129.6</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>132496129.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>86336133.4</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>120394266.18</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>120394266.18</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>6943645.052739069</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>82950382</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>82950382.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>69.38</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>66.06</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>66.34</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>66.06</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>66.34</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>100281347.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>131264222.4</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>131264222.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>81393410.0</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>119695734.58</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>119695734.58</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>9733490.069373712</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>100281347</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>100281347.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>67.98</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>65.84</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>66.06</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>65.84</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>66.06</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>190606270.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>118462794.8</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>118462794.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>74290109.7</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>120126016.38</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>120126016.38</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>11514469.19780271</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>190606270</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>190606270.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>66.16</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>65.64</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>65.73</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>65.64</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>65.73</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>182793426.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>85235906.2</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>85235906.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>58360010.8</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>117218867.38</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>117218867.38</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>3969823.731351182</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>182793426</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>182793426.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>57.16</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>58.14</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>60.07</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>58.14</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>60.07</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>162030.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>209836.2</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>209836.2</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>215755.9</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>550120.9</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>550120.9</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-38160.02218378661</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>162030</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>162030.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>57.23999999999999</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>58.29</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>60.05</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>58.29</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>60.05</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>199284.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>213119.2</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>213119.2</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>251269.4</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>555483.94</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>555483.9399999999</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-36671.78477886959</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>199284</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>199284.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>57.36</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>58.46</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>60.09</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>58.46</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>60.09</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>136228.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>212208.6</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>212208.6</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>325088.9</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>556448.64</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>556448.64</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-37227.52474402849</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>136228</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>136228.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>57.62</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>58.66</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>60.11</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>58.66</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>60.11</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>273475.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>241628.6</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>241628.6</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>353601.2</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>558552.82</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>558552.8199999999</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-29935.8845248259</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>273475</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>273475.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>58.17999999999999</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>58.9</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>60.16</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>58.9</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>60.16</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>278164.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>235377.2</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>235377.2</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>343709.9</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>560862.08</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>560862.08</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-33155.15262150689</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>278164</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>278164.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>58.38000000000001</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>59.01</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>60.14</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>59.01</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>60.14</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>178445.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>221675.6</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>221675.6</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>333361.3</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>566147.36</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>566147.36</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-37072.38730885455</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>178445</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>178445.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>58.9</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>59.24</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>60.11</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>59.24</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>60.11</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>194731.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>289419.6</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>289419.6</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>341561.2</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>568481.84</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>568481.84</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-30660.24445832073</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>194731</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>194731.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>59.73999999999999</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>59.51</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>60.1</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>59.51</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>60.1</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>283328.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>437969.2</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>437969.2</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>356514.8</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>570563.3</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>570563.3</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-22149.96022690379</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>283328</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>283328.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>60.12</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>59.74</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>60.09</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>59.74</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>60.09</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>242218.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>465573.8</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>465573.8</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>341803.5</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>579417.88</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>579417.88</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-18693.87703106157</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>242218</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>242218.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>59.72000000000001</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>59.98</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>60.1</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>59.98</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>60.1</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>209656.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>452042.6</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>452042.6</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>332281.8</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>596784.86</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>596784.86</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-8684.334000177623</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>209656</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>209656.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>59.14</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>60.09</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>60.08</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>60.09</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>60.08</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>517165.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>445047.0</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>445047</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>339942.5</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>643736.64</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>643736.64</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>9413.953686805733</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>517165</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>517165.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>

--- a/Result/checksun_type/濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料).xlsx
+++ b/Result/checksun_type/濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料).xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>308.105</t>
+          <t>692.026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>65.4</t>
+          <t>68.3</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-56.32</t>
+          <t>-37.39</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>6.24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>692</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>17.72</t>
+          <t>61.43</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>26.78</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>65.12</t>
+          <t>65.36</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>66.14</v>
+        <v>66.36</v>
       </c>
       <c r="AN2" t="n">
-        <v>66.83</v>
+        <v>66.92</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>63.8</t>
+          <t>63.96</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-169.68</t>
+          <t>-93.40</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-90.99</t>
+          <t>-92.69</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>75115086.28111587</t>
+          <t>75108071.75142857</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>20134094.0</t>
+          <t>46803277.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>29566216</v>
+        <v>33379525.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>67689821.8</t>
+          <t>53309522.5</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>102474885.18</v>
+        <v>101686881.5</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-38123605</t>
+          <t>-19929996</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-5188194.843829334</t>
+          <t>-5884646.973655229</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-10952804.2329868</t>
+          <t>-9715133.687697649</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>20134094.0</t>
+          <t>46803277.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>38.27</t>
+          <t>44.40</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>92.11</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>47.59</t>
+          <t>48.32</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>7760</t>
+          <t>8104</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>64.3</t>
+          <t>65.4</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>65.8</t>
+          <t>68.3</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>64.3</t>
+          <t>65.4</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>65.4</t>
+          <t>68.3</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>436.423</t>
+          <t>308.105</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>64.1</t>
+          <t>65.4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-57.89</t>
+          <t>-56.32</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>692</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>17.72</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>65.24000000000001</t>
+          <t>65.12</t>
         </is>
       </c>
       <c r="AM3" t="n">
         <v>66.14</v>
       </c>
       <c r="AN3" t="n">
-        <v>66.84</v>
+        <v>66.83</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>63.67</t>
+          <t>63.8</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-128.59</t>
+          <t>-169.68</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-87.16</t>
+          <t>-90.99</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>75115086.28111587</t>
+          <t>75108071.75142857</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>28041681.0</t>
+          <t>20134094.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>35349677.8</v>
+        <v>29566216</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>83955755.0</t>
+          <t>67689821.8</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>105161801.84</v>
+        <v>102474885.18</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-48606077</t>
+          <t>-38123605</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-4140084.045800703</t>
+          <t>-5188194.843829334</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-9472320.967936054</t>
+          <t>-10952804.2329868</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>28041681.0</t>
+          <t>20134094.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>35.52</t>
+          <t>38.27</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>92.11</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>47.59</t>
+          <t>48.32</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>7760</t>
+          <t>8104</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>64.7</t>
+          <t>64.3</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>65.8</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>63.5</t>
+          <t>64.3</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>64.1</t>
+          <t>65.4</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>427.384</t>
+          <t>436.423</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>64.1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-44.43</t>
+          <t>-57.89</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>692</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>65.24000000000001</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>66.2</v>
+        <v>66.14</v>
       </c>
       <c r="AN4" t="n">
-        <v>66.90000000000001</v>
+        <v>66.84</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>63.56</t>
+          <t>63.67</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-72.20</t>
+          <t>-128.59</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-83.03</t>
+          <t>-87.16</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>75115086.28111587</t>
+          <t>75108071.75142857</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>27698337.0</t>
+          <t>28041681.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>50976888.8</v>
+        <v>35349677.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>91736509.2</t>
+          <t>83955755.0</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>107077260.2</v>
+        <v>105161801.84</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-40759620</t>
+          <t>-48606077</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-3170586.423594275</t>
+          <t>-4140084.045800703</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-7866289.16186586</t>
+          <t>-9472320.967936054</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>27698337.0</t>
+          <t>28041681.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>35.31</t>
+          <t>35.52</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>92.11</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>47.59</t>
+          <t>48.32</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>7760</t>
+          <t>8104</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>64.7</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>63.5</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>64.1</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-3.15</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>677.83</t>
+          <t>427.384</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,74 +2188,74 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>64.0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>-0.16</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-44.43</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-09-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
           <t>65.0</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0.61</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>-0.13</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>-35.82</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2025-11-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-09-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
       <c r="T5" t="inlineStr">
         <is>
           <t>67.8</t>
@@ -2268,12 +2268,12 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>-7.14</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,12 +2304,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>692</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2319,58 +2319,58 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>12.81</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>5.55</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>67.4</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>66.28</v>
+        <v>66.2</v>
       </c>
       <c r="AN5" t="n">
-        <v>66.98</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>63.46</t>
+          <t>63.56</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-21.43</t>
+          <t>-72.20</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-79.97</t>
+          <t>-83.03</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,48 +2390,48 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>75115086.28111587</t>
+          <t>75108071.75142857</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>44220240.0</t>
+          <t>27698337.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>62027297.8</v>
+        <v>50976888.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>96645760.1</t>
+          <t>91736509.2</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>113463276.16</v>
+        <v>107077260.2</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-34618462</t>
+          <t>-40759620</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-2316822.289363078</t>
+          <t>-3170586.423594275</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-5254232.254556075</t>
+          <t>-7866289.16186586</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>44220240.0</t>
+          <t>27698337.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>37.42</t>
+          <t>35.31</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>92.11</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>47.59</t>
+          <t>48.32</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>7760</t>
+          <t>8104</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>64.3</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2593,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>-3.15</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>412.165</t>
+          <t>677.83</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>67.1</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-23.59</t>
+          <t>-35.82</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-7.14</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>692</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>23.94</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>29.29</t>
+          <t>12.81</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>5.55</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>68.78000000000002</t>
+          <t>67.4</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>66.31</v>
+        <v>66.28</v>
       </c>
       <c r="AN6" t="n">
         <v>66.98</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>63.36</t>
+          <t>63.46</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>21.92</t>
+          <t>-21.43</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-78.90</t>
+          <t>-79.97</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>75115086.28111587</t>
+          <t>75108071.75142857</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>27736728.0</t>
+          <t>44220240.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>73239519.2</v>
+        <v>62027297.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>95851157.0</t>
+          <t>96645760.1</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>115231412.04</v>
+        <v>113463276.16</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-22611637</t>
+          <t>-34618462</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-1782747.750237079</t>
+          <t>-2316822.289363078</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-3105275.127879396</t>
+          <t>-5254232.254556075</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>27736728.0</t>
+          <t>44220240.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>41.86</t>
+          <t>37.42</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>92.11</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>47.59</t>
+          <t>48.32</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>7760</t>
+          <t>8104</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>67.9</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>67.9</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>66.5</t>
+          <t>64.3</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>67.1</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>735.417</t>
+          <t>412.165</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>10.77</t>
+          <t>-23.59</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3128,12 +3128,12 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>-5.71</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>692</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>14.47</t>
+          <t>23.94</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>49.64</t>
+          <t>29.29</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-5.53</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>5.80</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>69.86000000000001</t>
+          <t>68.78000000000002</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>66.23999999999999</v>
+        <v>66.31</v>
       </c>
       <c r="AN7" t="n">
-        <v>66.90000000000001</v>
+        <v>66.98</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>63.24</t>
+          <t>63.36</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>50.55</t>
+          <t>21.92</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-80.05</t>
+          <t>-78.90</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>75115086.28111587</t>
+          <t>75108071.75142857</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>49051403.0</t>
+          <t>27736728.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>105813427.6</v>
+        <v>73239519.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>95524666.9</t>
+          <t>95851157.0</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>120066640.9</v>
+        <v>115231412.04</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>10288760</t>
+          <t>-22611637</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-1542288.227029385</t>
+          <t>-1782747.750237079</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>1841656.879083008</t>
+          <t>-3105275.127879396</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>49051403.0</t>
+          <t>27736728.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>39.53</t>
+          <t>41.86</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>92.11</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>47.59</t>
+          <t>48.32</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>7760</t>
+          <t>8104</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>68.6</t>
+          <t>67.9</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>68.6</t>
+          <t>67.9</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>66.5</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.1</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1542.065</t>
+          <t>735.417</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>67.9</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-3.82</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>41.98</t>
+          <t>10.77</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3558,12 +3558,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>-3.00</t>
+          <t>-5.71</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13.91</t>
+          <t>6.63</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>692</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>49.45</t>
+          <t>14.47</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>76.15</t>
+          <t>49.64</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-5.53</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>5.70</t>
+          <t>5.80</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>70.66</t>
+          <t>69.86000000000001</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>66.3</v>
+        <v>66.23999999999999</v>
       </c>
       <c r="AN8" t="n">
-        <v>66.75</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>63.15</t>
+          <t>63.24</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>125.60</t>
+          <t>50.55</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-82.57</t>
+          <t>-80.05</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>75115086.28111587</t>
+          <t>75108071.75142857</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>106177736.0</t>
+          <t>49051403.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>132561832.2</v>
+        <v>105813427.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>93365555.7</t>
+          <t>95524666.9</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>120263879.18</v>
+        <v>120066640.9</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>39196276</t>
+          <t>10288760</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-2157550.973595275</t>
+          <t>-1542288.227029385</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>6559213.964776337</t>
+          <t>1841656.879083008</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>106177736.0</t>
+          <t>49051403.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>39.53</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>92.11</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>47.59</t>
+          <t>48.32</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>7760</t>
+          <t>8104</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>67.9</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1168.47</t>
+          <t>1542.065</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>67.9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-8.56</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>53.47</t>
+          <t>41.98</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>-3.00</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>9.23</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10.54</t>
+          <t>13.91</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>692</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>49.45</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>76.15</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>6.43</t>
+          <t>6.58</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>5.70</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>70.66</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>66.23999999999999</v>
+        <v>66.3</v>
       </c>
       <c r="AN9" t="n">
-        <v>66.59999999999999</v>
+        <v>66.75</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>63.02</t>
+          <t>63.15</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>262.06</t>
+          <t>125.60</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-88.05</t>
+          <t>-82.57</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>75115086.28111587</t>
+          <t>75108071.75142857</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>82950382.0</t>
+          <t>106177736.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>132496129.6</v>
+        <v>132561832.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>86336133.4</t>
+          <t>93365555.7</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>120394266.18</v>
+        <v>120263879.18</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>46159996</t>
+          <t>39196276</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-3742417.326026477</t>
+          <t>-2157550.973595275</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>6943645.052739069</t>
+          <t>6559213.964776337</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>82950382.0</t>
+          <t>106177736.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>50.11</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4216,17 +4216,17 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>92.11</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>47.59</t>
+          <t>48.32</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>7760</t>
+          <t>8104</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>67.9</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1393.968</t>
+          <t>1168.47</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-9.94</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>61.27</t>
+          <t>53.47</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>10.62</t>
+          <t>9.23</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12.58</t>
+          <t>10.54</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>692</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>6.43</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>69.38</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>66.06</v>
+        <v>66.23999999999999</v>
       </c>
       <c r="AN10" t="n">
-        <v>66.34</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>62.79</t>
+          <t>63.02</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>768.32</t>
+          <t>262.06</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-95.88</t>
+          <t>-88.05</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>75115086.28111587</t>
+          <t>75108071.75142857</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>100281347.0</t>
+          <t>82950382.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>131264222.4</v>
+        <v>132496129.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>81393410.0</t>
+          <t>86336133.4</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>119695734.58</v>
+        <v>120394266.18</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>49870812</t>
+          <t>46159996</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-5685337.758529304</t>
+          <t>-3742417.326026477</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>9733490.069373712</t>
+          <t>6943645.052739069</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>100281347.0</t>
+          <t>82950382.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>52.01</t>
+          <t>50.11</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4646,17 +4646,17 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>92.11</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>47.59</t>
+          <t>48.32</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>7760</t>
+          <t>8104</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2657.246</t>
+          <t>1393.968</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-10.86</t>
+          <t>-5.27</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>59.46</t>
+          <t>61.27</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4848,12 +4848,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>11.54</t>
+          <t>10.62</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>23.97</t>
+          <t>12.58</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>692</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>6.65</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>5.60</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>67.98</t>
+          <t>69.38</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>65.84</v>
+        <v>66.06</v>
       </c>
       <c r="AN11" t="n">
-        <v>66.06</v>
+        <v>66.34</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>62.56</t>
+          <t>62.79</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>686.39</t>
+          <t>768.32</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-103.80</t>
+          <t>-95.88</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>75115086.28111587</t>
+          <t>75108071.75142857</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>190606270.0</t>
+          <t>100281347.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>118462794.8</v>
+        <v>131264222.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>74290109.7</t>
+          <t>81393410.0</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>120126016.38</v>
+        <v>119695734.58</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>44172685</t>
+          <t>49870812</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-8488760.999966215</t>
+          <t>-5685337.758529304</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>11514469.19780271</t>
+          <t>9733490.069373712</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>190606270.0</t>
+          <t>100281347.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>53.28</t>
+          <t>52.01</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>92.11</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>47.59</t>
+          <t>48.32</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>7760</t>
+          <t>8104</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
+          <t>71.2</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
           <t>70.6</t>
         </is>
       </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>72.8</t>
-        </is>
-      </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>69.7</t>
-        </is>
-      </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2598.844</t>
+          <t>2657.246</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,74 +5198,74 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>72.5</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-6.15</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-0.16</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>59.46</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-09-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>70.0</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>-7.03</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>-0.13</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>46.05</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2025-11-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-09-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
         <is>
           <t>70.0</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
       <c r="T12" t="inlineStr">
         <is>
           <t>67.8</t>
@@ -5278,12 +5278,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>11.54</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>23.45</t>
+          <t>23.97</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>692</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5334,53 +5334,53 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>5.80</t>
+          <t>6.65</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>5.60</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>66.16</t>
+          <t>67.98</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>65.64</v>
+        <v>65.84</v>
       </c>
       <c r="AN12" t="n">
-        <v>65.73</v>
+        <v>66.06</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>62.31</t>
+          <t>62.56</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>122.79</t>
+          <t>686.39</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-110.31</t>
+          <t>-103.80</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>75115086.28111587</t>
+          <t>75108071.75142857</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>182793426.0</t>
+          <t>190606270.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>85235906.2</v>
+        <v>118462794.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>58360010.8</t>
+          <t>74290109.7</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>117218867.38</v>
+        <v>120126016.38</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>26875895</t>
+          <t>44172685</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-12125711.94501511</t>
+          <t>-8488760.999966215</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>3969823.731351182</t>
+          <t>11514469.19780271</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>182793426.0</t>
+          <t>190606270.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>47.99</t>
+          <t>53.28</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>92.11</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>47.59</t>
+          <t>48.32</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>7760</t>
+          <t>8104</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>70.6</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2826.0</t>
+          <t>2961.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>57.2</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>-11.08</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,73 +5744,73 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>2826</t>
+          <t>2961</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>35.71</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>22.46</t>
+          <t>34.13</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>57.16</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>58.14</v>
+        <v>58.08</v>
       </c>
       <c r="AN13" t="n">
-        <v>60.07</v>
+        <v>60.1</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>58.08</t>
+          <t>58.16</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-24.14</t>
+          <t>-14.26</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-112.17</t>
+          <t>-112.62</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>814356.8199426112</t>
+          <t>813557.9312320916</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>162030.0</t>
+          <t>171155.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>209836.2</v>
+        <v>188434.4</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>215755.9</t>
+          <t>211905.8</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>550120.9</v>
+        <v>549840.7</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-5919</t>
+          <t>-23471</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-35791.36830932057</t>
+          <t>-36063.99054059955</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-38160.02218378661</t>
+          <t>-37563.41281263391</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>162030.0</t>
+          <t>171155.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,22 +5931,22 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>24.34</t>
+          <t>24.47</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>34092</t>
+          <t>34271</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
+          <t>57.7</t>
+        </is>
+      </c>
+      <c r="CE13" t="inlineStr">
+        <is>
+          <t>58.5</t>
+        </is>
+      </c>
+      <c r="CF13" t="inlineStr">
+        <is>
+          <t>57.3</t>
+        </is>
+      </c>
+      <c r="CG13" t="inlineStr">
+        <is>
           <t>57.5</t>
-        </is>
-      </c>
-      <c r="CE13" t="inlineStr">
-        <is>
-          <t>57.8</t>
-        </is>
-      </c>
-      <c r="CF13" t="inlineStr">
-        <is>
-          <t>56.9</t>
-        </is>
-      </c>
-      <c r="CG13" t="inlineStr">
-        <is>
-          <t>57.2</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>3484.0</t>
+          <t>2826.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>56.8</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-15.18</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,73 +6174,73 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>2826</t>
+          <t>2961</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>35.71</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>10.56</t>
+          <t>22.46</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>57.23999999999999</t>
+          <t>57.16</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>58.29</v>
+        <v>58.14</v>
       </c>
       <c r="AN14" t="n">
-        <v>60.05</v>
+        <v>60.07</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>57.99</t>
+          <t>58.08</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-32.85</t>
+          <t>-24.14</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-111.43</t>
+          <t>-112.17</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>814356.8199426112</t>
+          <t>813557.9312320916</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>199284.0</t>
+          <t>162030.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>213119.2</v>
+        <v>209836.2</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>251269.4</t>
+          <t>215755.9</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>555483.9399999999</v>
+        <v>550120.9</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-38150</t>
+          <t>-5919</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-35360.70396850856</t>
+          <t>-35791.36830932057</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-36671.78477886959</t>
+          <t>-38160.02218378661</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>199284.0</t>
+          <t>162030.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-3.57</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,22 +6361,22 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>24.34</t>
+          <t>24.47</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>34092</t>
+          <t>34271</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>58.3</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>56.8</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2408.0</t>
+          <t>3484.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-34.72</t>
+          <t>-15.18</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6518,7 +6518,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,73 +6604,73 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>2826</t>
+          <t>2961</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>16.11</t>
+          <t>10.56</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-2.71</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>57.36</t>
+          <t>57.23999999999999</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>58.46</v>
+        <v>58.29</v>
       </c>
       <c r="AN15" t="n">
-        <v>60.09</v>
+        <v>60.05</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>57.91</t>
+          <t>57.99</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-36.35</t>
+          <t>-32.85</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-110.50</t>
+          <t>-111.43</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>814356.8199426112</t>
+          <t>813557.9312320916</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>136228.0</t>
+          <t>199284.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>212208.6</v>
+        <v>213119.2</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>325088.9</t>
+          <t>251269.4</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>556448.64</v>
+        <v>555483.9399999999</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-112880</t>
+          <t>-38150</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-35122.32563935201</t>
+          <t>-35360.70396850856</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-37227.52474402849</t>
+          <t>-36671.78477886959</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>136228.0</t>
+          <t>199284.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6806,7 +6806,7 @@
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>24.34</t>
+          <t>24.47</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>34092</t>
+          <t>34271</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,17 +6856,17 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>58.3</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-4.5</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>4791.0</t>
+          <t>2408.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-31.67</t>
+          <t>-34.72</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6948,7 +6948,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>8.27</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,73 +7034,73 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>2826</t>
+          <t>2961</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>15.46</t>
+          <t>16.11</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-2.71</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>57.62</t>
+          <t>57.36</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>58.66</v>
+        <v>58.46</v>
       </c>
       <c r="AN16" t="n">
-        <v>60.11</v>
+        <v>60.09</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>57.83</t>
+          <t>57.91</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-36.02</t>
+          <t>-36.35</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-109.54</t>
+          <t>-110.50</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>814356.8199426112</t>
+          <t>813557.9312320916</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>273475.0</t>
+          <t>136228.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>241628.6</v>
+        <v>212208.6</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>353601.2</t>
+          <t>325088.9</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>558552.8199999999</v>
+        <v>556448.64</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-111972</t>
+          <t>-112880</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-34739.56216577447</t>
+          <t>-35122.32563935201</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-29935.8845248259</t>
+          <t>-37227.52474402849</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>273475.0</t>
+          <t>136228.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-3.57</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>24.34</t>
+          <t>24.47</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>34092</t>
+          <t>34271</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>58.7</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>-4.5</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>4747.0</t>
+          <t>4791.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-2.8</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-31.52</t>
+          <t>-31.67</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7378,7 +7378,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>8.19</t>
+          <t>8.27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,73 +7464,73 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>2826</t>
+          <t>2961</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>19.01</t>
+          <t>15.46</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-2.1</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>58.17999999999999</t>
+          <t>57.62</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>58.9</v>
+        <v>58.66</v>
       </c>
       <c r="AN17" t="n">
-        <v>60.16</v>
+        <v>60.11</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>57.77</t>
+          <t>57.83</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-14.48</t>
+          <t>-36.02</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-108.68</t>
+          <t>-109.54</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>814356.8199426112</t>
+          <t>813557.9312320916</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>278164.0</t>
+          <t>273475.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>235377.2</v>
+        <v>241628.6</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>343709.9</t>
+          <t>353601.2</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>560862.08</v>
+        <v>558552.8199999999</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-108332</t>
+          <t>-111972</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-35612.95810049239</t>
+          <t>-34739.56216577447</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-33155.15262150689</t>
+          <t>-29935.8845248259</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>278164.0</t>
+          <t>273475.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,22 +7651,22 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>24.34</t>
+          <t>24.47</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>34092</t>
+          <t>34271</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>58.7</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>57.9</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3082.0</t>
+          <t>4747.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-33.50</t>
+          <t>-31.52</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>8.19</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,73 +7894,73 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>2826</t>
+          <t>2961</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>13.04</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>19.01</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-2.1</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>58.38000000000001</t>
+          <t>58.17999999999999</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>59.01</v>
+        <v>58.9</v>
       </c>
       <c r="AN18" t="n">
-        <v>60.14</v>
+        <v>60.16</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>57.69</t>
+          <t>57.77</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-30.25</t>
+          <t>-14.48</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-108.37</t>
+          <t>-108.68</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>814356.8199426112</t>
+          <t>813557.9312320916</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>178445.0</t>
+          <t>278164.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>221675.6</v>
+        <v>235377.2</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>333361.3</t>
+          <t>343709.9</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>566147.36</v>
+        <v>560862.08</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-111685</t>
+          <t>-108332</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-36059.8318239443</t>
+          <t>-35612.95810049239</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-37072.38730885455</t>
+          <t>-33155.15262150689</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>178445.0</t>
+          <t>278164.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,22 +8081,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>24.34</t>
+          <t>24.47</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>34092</t>
+          <t>34271</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.9</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>3352.0</t>
+          <t>3082.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-15.27</t>
+          <t>-33.50</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8238,7 +8238,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,141 +8324,141 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>2826</t>
+          <t>2961</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>10.64</t>
+          <t>13.04</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
+          <t>58.38000000000001</t>
+        </is>
+      </c>
+      <c r="AM19" t="n">
+        <v>59.01</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>60.14</v>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>57.69</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>-30.25</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>-0.58</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>-0.44</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>5.31</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr">
+        <is>
+          <t>-108.37</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>813557.9312320916</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>178445.0</t>
+        </is>
+      </c>
+      <c r="AX19" t="n">
+        <v>221675.6</v>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>333361.3</t>
+        </is>
+      </c>
+      <c r="AZ19" t="n">
+        <v>566147.36</v>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>-111685</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>-36059.8318239443</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>-37072.38730885455</t>
+        </is>
+      </c>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>178445.0</t>
+        </is>
+      </c>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
           <t>58.9</t>
         </is>
       </c>
-      <c r="AM19" t="n">
-        <v>59.24</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>60.11</v>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>57.62</t>
-        </is>
-      </c>
-      <c r="AP19" t="inlineStr">
-        <is>
-          <t>-24.96</t>
-        </is>
-      </c>
-      <c r="AQ19" t="inlineStr">
-        <is>
-          <t>-0.51</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>-0.41</t>
-        </is>
-      </c>
-      <c r="AS19" t="inlineStr">
-        <is>
-          <t>5.31</t>
-        </is>
-      </c>
-      <c r="AT19" t="inlineStr">
-        <is>
-          <t>-107.74</t>
-        </is>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV19" t="inlineStr">
-        <is>
-          <t>814356.8199426112</t>
-        </is>
-      </c>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>194731.0</t>
-        </is>
-      </c>
-      <c r="AX19" t="n">
-        <v>289419.6</v>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>341561.2</t>
-        </is>
-      </c>
-      <c r="AZ19" t="n">
-        <v>568481.84</v>
-      </c>
-      <c r="BA19" t="inlineStr">
-        <is>
-          <t>-52141</t>
-        </is>
-      </c>
-      <c r="BB19" t="inlineStr">
-        <is>
-          <t>-35875.73082668789</t>
-        </is>
-      </c>
-      <c r="BC19" t="inlineStr">
-        <is>
-          <t>-30660.24445832073</t>
-        </is>
-      </c>
-      <c r="BD19" t="inlineStr">
-        <is>
-          <t>194731.0</t>
-        </is>
-      </c>
-      <c r="BE19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF19" t="inlineStr">
-        <is>
-          <t>58.9</t>
-        </is>
-      </c>
       <c r="BG19" t="inlineStr">
         <is>
           <t>2025/08/29</t>
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8521,12 +8521,12 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>24.34</t>
+          <t>24.47</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>34092</t>
+          <t>34271</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>4870.0</t>
+          <t>3352.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,74 +8638,74 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
+          <t>57.4</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>0.17</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>-0.82</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>-15.27</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2025-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
           <t>58.1</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>-1.57</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>-2.14</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>22.85</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>2025-10-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>58.1</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
       <c r="T20" t="inlineStr">
         <is>
           <t>59.6</t>
@@ -8718,12 +8718,12 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>8.40</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,73 +8754,73 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>2826</t>
+          <t>2961</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>40.68</t>
+          <t>10.64</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>55.37</t>
+          <t>35.75</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>59.73999999999999</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>59.51</v>
+        <v>59.24</v>
       </c>
       <c r="AN20" t="n">
-        <v>60.1</v>
+        <v>60.11</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>57.55</t>
+          <t>57.62</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-24.96</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-107.25</t>
+          <t>-107.74</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,48 +8840,48 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>814356.8199426112</t>
+          <t>813557.9312320916</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>283328.0</t>
+          <t>194731.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>437969.2</v>
+        <v>289419.6</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>356514.8</t>
+          <t>341561.2</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>570563.3</v>
+        <v>568481.84</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>81454</t>
+          <t>-52141</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-36824.00107548192</t>
+          <t>-35875.73082668789</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-22149.96022690379</t>
+          <t>-30660.24445832073</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>283328.0</t>
+          <t>194731.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -8951,12 +8951,12 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>24.34</t>
+          <t>24.47</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>34092</t>
+          <t>34271</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>57.2</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9043,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9053,127 +9053,127 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>-1.51</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>4870.0</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-1.04</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>-0.82</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>22.85</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2025-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>-1.53</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>-4.07</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>8.40</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
           <t>-1.35</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>4060.0</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>-3.15</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>-2.14</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>36.21</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>2025-10-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>58.1</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>59.6</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>61.5</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>-4.07</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>7.01</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>-1.86</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,73 +9184,73 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>2826</t>
+          <t>2961</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>55.93</t>
+          <t>40.68</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>67.23</t>
+          <t>55.37</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>60.12</t>
+          <t>59.73999999999999</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>59.74</v>
+        <v>59.51</v>
       </c>
       <c r="AN21" t="n">
-        <v>60.09</v>
+        <v>60.1</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>57.46</t>
+          <t>57.55</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>14.66</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-107.17</t>
+          <t>-107.25</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>814356.8199426112</t>
+          <t>813557.9312320916</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>242218.0</t>
+          <t>283328.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>465573.8</v>
+        <v>437969.2</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>341803.5</t>
+          <t>356514.8</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>579417.88</v>
+        <v>570563.3</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>123770</t>
+          <t>81454</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-39492.00850249613</t>
+          <t>-36824.00107548192</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-18693.87703106157</t>
+          <t>-22149.96022690379</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>242218.0</t>
+          <t>283328.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,22 +9371,22 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>24.34</t>
+          <t>24.47</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>34092</t>
+          <t>34271</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>59.3</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>60.6</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3505.0</t>
+          <t>4060.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,27 +9508,27 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-4.55</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>36.21</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -9563,7 +9563,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,73 +9614,73 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>2826</t>
+          <t>2961</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>69.49</t>
+          <t>55.93</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>81.92</t>
+          <t>67.23</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>59.72000000000001</t>
+          <t>60.12</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>59.98</v>
+        <v>59.74</v>
       </c>
       <c r="AN22" t="n">
-        <v>60.1</v>
+        <v>60.09</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>57.38</t>
+          <t>57.46</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>20.51</t>
+          <t>14.66</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-107.44</t>
+          <t>-107.17</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,48 +9700,48 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>814356.8199426112</t>
+          <t>813557.9312320916</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>209656.0</t>
+          <t>242218.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>452042.6</v>
+        <v>465573.8</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>332281.8</t>
+          <t>341803.5</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>596784.86</v>
+        <v>579417.88</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>119760</t>
+          <t>123770</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-43273.48695184787</t>
+          <t>-39492.00850249613</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-8684.334000177623</t>
+          <t>-18693.87703106157</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>209656.0</t>
+          <t>242218.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="BF22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>24.34</t>
+          <t>24.47</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>34092</t>
+          <t>34271</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>60.1</t>
+          <t>59.3</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9903,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8540.0</t>
+          <t>3505.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>60.2</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>30.92</t>
+          <t>36.04</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -9958,7 +9958,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14.74</t>
+          <t>6.05</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,73 +10044,73 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>2826</t>
+          <t>2961</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>76.27</t>
+          <t>69.49</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>91.33</t>
+          <t>81.92</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>59.14</t>
+          <t>59.72000000000001</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>60.09</v>
+        <v>59.98</v>
       </c>
       <c r="AN23" t="n">
-        <v>60.08</v>
+        <v>60.1</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>57.31</t>
+          <t>57.38</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>9.30</t>
+          <t>20.51</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-107.82</t>
+          <t>-107.44</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>814356.8199426112</t>
+          <t>813557.9312320916</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>517165.0</t>
+          <t>209656.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>445047</v>
+        <v>452042.6</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>339942.5</t>
+          <t>332281.8</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>643736.64</v>
+        <v>596784.86</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>105104</t>
+          <t>119760</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-49562.42385215155</t>
+          <t>-43273.48695184787</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>9413.953686805733</t>
+          <t>-8684.334000177623</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>517165.0</t>
+          <t>209656.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>24.34</t>
+          <t>24.47</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>34092</t>
+          <t>34271</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>61.7</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>61.8</t>
+          <t>60.4</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>59.6</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>60.2</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料).xlsx
+++ b/Result/checksun_type/濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料).xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>692.026</t>
+          <t>470.74</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>68.3</t>
+          <t>68.4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-37.39</t>
+          <t>-33.44</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>5.23</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>6.24</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,68 +1014,68 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>471</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>61.43</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>26.78</t>
+          <t>59.72</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>65.36</t>
+          <t>66.04</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>66.36</v>
+        <v>66.58</v>
       </c>
       <c r="AN2" t="n">
-        <v>66.92</v>
+        <v>66.97</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>63.96</t>
+          <t>64.12</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-93.40</t>
+          <t>-13.94</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-92.69</t>
+          <t>-92.94</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>75108071.75142857</t>
+          <t>75069439.97931527</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>46803277.0</t>
+          <t>32018133.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>33379525.8</v>
+        <v>30939104.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>53309522.5</t>
+          <t>46483201.1</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>101686881.5</v>
+        <v>100844624.6</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-19929996</t>
+          <t>-15544096</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-5884646.973655229</t>
+          <t>-6473896.94137024</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-9715133.687697649</t>
+          <t>-9714771.763802804</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>46803277.0</t>
+          <t>32018133.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>44.40</t>
+          <t>44.61</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>96.34</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>48.32</t>
+          <t>48.84</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>8104</t>
+          <t>8116</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>65.4</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>68.3</t>
+          <t>69.2</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>65.4</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>68.3</t>
+          <t>68.4</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>308.105</t>
+          <t>692.026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>65.4</t>
+          <t>68.3</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-56.32</t>
+          <t>-37.39</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>6.24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>471</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>17.72</t>
+          <t>61.43</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>26.78</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>65.12</t>
+          <t>65.36</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>66.14</v>
+        <v>66.36</v>
       </c>
       <c r="AN3" t="n">
-        <v>66.83</v>
+        <v>66.92</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>63.8</t>
+          <t>63.96</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-169.68</t>
+          <t>-93.40</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-90.99</t>
+          <t>-92.69</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>75108071.75142857</t>
+          <t>75069439.97931527</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>20134094.0</t>
+          <t>46803277.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>29566216</v>
+        <v>33379525.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>67689821.8</t>
+          <t>53309522.5</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>102474885.18</v>
+        <v>101686881.5</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-38123605</t>
+          <t>-19929996</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-5188194.843829334</t>
+          <t>-5884646.973655229</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-10952804.2329868</t>
+          <t>-9715133.687697649</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>20134094.0</t>
+          <t>46803277.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>38.27</t>
+          <t>44.40</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>96.34</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>48.32</t>
+          <t>48.84</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>8104</t>
+          <t>8116</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>64.3</t>
+          <t>65.4</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>65.8</t>
+          <t>68.3</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>64.3</t>
+          <t>65.4</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>65.4</t>
+          <t>68.3</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>436.423</t>
+          <t>308.105</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>64.1</t>
+          <t>65.4</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-57.89</t>
+          <t>-56.32</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>471</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>17.72</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>65.24000000000001</t>
+          <t>65.12</t>
         </is>
       </c>
       <c r="AM4" t="n">
         <v>66.14</v>
       </c>
       <c r="AN4" t="n">
-        <v>66.84</v>
+        <v>66.83</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>63.67</t>
+          <t>63.8</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-128.59</t>
+          <t>-169.68</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-87.16</t>
+          <t>-90.99</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>75108071.75142857</t>
+          <t>75069439.97931527</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>28041681.0</t>
+          <t>20134094.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>35349677.8</v>
+        <v>29566216</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>83955755.0</t>
+          <t>67689821.8</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>105161801.84</v>
+        <v>102474885.18</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-48606077</t>
+          <t>-38123605</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-4140084.045800703</t>
+          <t>-5188194.843829334</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-9472320.967936054</t>
+          <t>-10952804.2329868</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>28041681.0</t>
+          <t>20134094.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>35.52</t>
+          <t>38.27</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>96.34</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>48.32</t>
+          <t>48.84</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>8104</t>
+          <t>8116</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>64.7</t>
+          <t>64.3</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>65.8</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>63.5</t>
+          <t>64.3</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>64.1</t>
+          <t>65.4</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>427.384</t>
+          <t>436.423</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>64.1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>6.29</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-44.43</t>
+          <t>-57.89</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>471</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>65.24000000000001</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>66.2</v>
+        <v>66.14</v>
       </c>
       <c r="AN5" t="n">
-        <v>66.90000000000001</v>
+        <v>66.84</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>63.56</t>
+          <t>63.67</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-72.20</t>
+          <t>-128.59</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-83.03</t>
+          <t>-87.16</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>75108071.75142857</t>
+          <t>75069439.97931527</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>27698337.0</t>
+          <t>28041681.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>50976888.8</v>
+        <v>35349677.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>91736509.2</t>
+          <t>83955755.0</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>107077260.2</v>
+        <v>105161801.84</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-40759620</t>
+          <t>-48606077</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-3170586.423594275</t>
+          <t>-4140084.045800703</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-7866289.16186586</t>
+          <t>-9472320.967936054</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>27698337.0</t>
+          <t>28041681.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>35.31</t>
+          <t>35.52</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>96.34</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>48.32</t>
+          <t>48.84</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>8104</t>
+          <t>8116</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>64.7</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>63.5</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>64.1</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-3.15</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>677.83</t>
+          <t>427.384</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,74 +2618,74 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>64.0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>6.43</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>-1.84</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>-44.43</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2025-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2025-09-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
           <t>65.0</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>4.83</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>-0.16</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>-35.82</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2025-11-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-09-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
       <c r="T6" t="inlineStr">
         <is>
           <t>67.8</t>
@@ -2698,12 +2698,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>-7.14</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,12 +2734,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>471</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2749,58 +2749,58 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>12.81</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>5.55</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>67.4</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>66.28</v>
+        <v>66.2</v>
       </c>
       <c r="AN6" t="n">
-        <v>66.98</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>63.46</t>
+          <t>63.56</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-21.43</t>
+          <t>-72.20</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-79.97</t>
+          <t>-83.03</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,48 +2820,48 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>75108071.75142857</t>
+          <t>75069439.97931527</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>44220240.0</t>
+          <t>27698337.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>62027297.8</v>
+        <v>50976888.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>96645760.1</t>
+          <t>91736509.2</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>113463276.16</v>
+        <v>107077260.2</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-34618462</t>
+          <t>-40759620</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-2316822.289363078</t>
+          <t>-3170586.423594275</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-5254232.254556075</t>
+          <t>-7866289.16186586</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>44220240.0</t>
+          <t>27698337.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>37.42</t>
+          <t>35.31</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>96.34</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>48.32</t>
+          <t>48.84</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>8104</t>
+          <t>8116</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>64.3</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3016,14 +3016,14 @@
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>-3.15</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>412.165</t>
+          <t>677.83</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>67.1</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-23.59</t>
+          <t>-35.82</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3128,12 +3128,12 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-7.14</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>471</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>23.94</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>29.29</t>
+          <t>12.81</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>5.55</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>68.78000000000002</t>
+          <t>67.4</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>66.31</v>
+        <v>66.28</v>
       </c>
       <c r="AN7" t="n">
         <v>66.98</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>63.36</t>
+          <t>63.46</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>21.92</t>
+          <t>-21.43</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-78.90</t>
+          <t>-79.97</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>75108071.75142857</t>
+          <t>75069439.97931527</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>27736728.0</t>
+          <t>44220240.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>73239519.2</v>
+        <v>62027297.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>95851157.0</t>
+          <t>96645760.1</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>115231412.04</v>
+        <v>113463276.16</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-22611637</t>
+          <t>-34618462</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-1782747.750237079</t>
+          <t>-2316822.289363078</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-3105275.127879396</t>
+          <t>-5254232.254556075</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>27736728.0</t>
+          <t>44220240.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>41.86</t>
+          <t>37.42</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,17 +3351,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>96.34</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>48.32</t>
+          <t>48.84</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>8104</t>
+          <t>8116</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>67.9</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>67.9</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>66.5</t>
+          <t>64.3</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>67.1</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="CJ7" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>735.417</t>
+          <t>412.165</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>10.77</t>
+          <t>-23.59</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3558,12 +3558,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>-5.71</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>471</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>14.47</t>
+          <t>23.94</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>49.64</t>
+          <t>29.29</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-5.53</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>5.80</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>69.86000000000001</t>
+          <t>68.78000000000002</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>66.23999999999999</v>
+        <v>66.31</v>
       </c>
       <c r="AN8" t="n">
-        <v>66.90000000000001</v>
+        <v>66.98</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>63.24</t>
+          <t>63.36</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>50.55</t>
+          <t>21.92</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-80.05</t>
+          <t>-78.90</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>75108071.75142857</t>
+          <t>75069439.97931527</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>49051403.0</t>
+          <t>27736728.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>105813427.6</v>
+        <v>73239519.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>95524666.9</t>
+          <t>95851157.0</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>120066640.9</v>
+        <v>115231412.04</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>10288760</t>
+          <t>-22611637</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-1542288.227029385</t>
+          <t>-1782747.750237079</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>1841656.879083008</t>
+          <t>-3105275.127879396</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>49051403.0</t>
+          <t>27736728.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>39.53</t>
+          <t>41.86</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,17 +3781,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>96.34</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>48.32</t>
+          <t>48.84</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>8104</t>
+          <t>8116</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>68.6</t>
+          <t>67.9</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>68.6</t>
+          <t>67.9</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>66.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.1</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="CJ8" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1542.065</t>
+          <t>735.417</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>67.9</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>41.98</t>
+          <t>10.77</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>-3.00</t>
+          <t>-5.71</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13.91</t>
+          <t>6.63</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>471</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>49.45</t>
+          <t>14.47</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>76.15</t>
+          <t>49.64</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-5.53</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>5.70</t>
+          <t>5.80</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>70.66</t>
+          <t>69.86000000000001</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>66.3</v>
+        <v>66.23999999999999</v>
       </c>
       <c r="AN9" t="n">
-        <v>66.75</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>63.15</t>
+          <t>63.24</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>125.60</t>
+          <t>50.55</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-82.57</t>
+          <t>-80.05</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>75108071.75142857</t>
+          <t>75069439.97931527</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>106177736.0</t>
+          <t>49051403.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>132561832.2</v>
+        <v>105813427.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>93365555.7</t>
+          <t>95524666.9</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>120263879.18</v>
+        <v>120066640.9</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>39196276</t>
+          <t>10288760</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-2157550.973595275</t>
+          <t>-1542288.227029385</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>6559213.964776337</t>
+          <t>1841656.879083008</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>106177736.0</t>
+          <t>49051403.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>39.53</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,17 +4211,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>96.34</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>48.32</t>
+          <t>48.84</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>8104</t>
+          <t>8116</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>67.9</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="CJ9" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1168.47</t>
+          <t>1542.065</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>67.9</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>53.47</t>
+          <t>41.98</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>-3.00</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>9.23</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10.54</t>
+          <t>13.91</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>471</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>49.45</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>76.15</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>6.43</t>
+          <t>6.58</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>5.70</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>70.66</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>66.23999999999999</v>
+        <v>66.3</v>
       </c>
       <c r="AN10" t="n">
-        <v>66.59999999999999</v>
+        <v>66.75</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>63.02</t>
+          <t>63.15</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>262.06</t>
+          <t>125.60</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-88.05</t>
+          <t>-82.57</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>75108071.75142857</t>
+          <t>75069439.97931527</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>82950382.0</t>
+          <t>106177736.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>132496129.6</v>
+        <v>132561832.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>86336133.4</t>
+          <t>93365555.7</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>120394266.18</v>
+        <v>120263879.18</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>46159996</t>
+          <t>39196276</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-3742417.326026477</t>
+          <t>-2157550.973595275</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>6943645.052739069</t>
+          <t>6559213.964776337</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>82950382.0</t>
+          <t>106177736.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>50.11</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4646,12 +4646,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>96.34</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>48.32</t>
+          <t>48.84</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>8104</t>
+          <t>8116</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>67.9</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="CJ10" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1393.968</t>
+          <t>1168.47</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-5.27</t>
+          <t>-3.8</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>61.27</t>
+          <t>53.47</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4848,12 +4848,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>10.62</t>
+          <t>9.23</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12.58</t>
+          <t>10.54</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>471</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>6.43</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>69.38</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>66.06</v>
+        <v>66.23999999999999</v>
       </c>
       <c r="AN11" t="n">
-        <v>66.34</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>62.79</t>
+          <t>63.02</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>768.32</t>
+          <t>262.06</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-95.88</t>
+          <t>-88.05</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>75108071.75142857</t>
+          <t>75069439.97931527</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>100281347.0</t>
+          <t>82950382.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>131264222.4</v>
+        <v>132496129.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>81393410.0</t>
+          <t>86336133.4</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>119695734.58</v>
+        <v>120394266.18</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>49870812</t>
+          <t>46159996</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-5685337.758529304</t>
+          <t>-3742417.326026477</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>9733490.069373712</t>
+          <t>6943645.052739069</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>100281347.0</t>
+          <t>82950382.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>52.01</t>
+          <t>50.11</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>96.34</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>48.32</t>
+          <t>48.84</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>8104</t>
+          <t>8116</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="CJ11" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2657.246</t>
+          <t>1393.968</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-6.15</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>59.46</t>
+          <t>61.27</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5278,12 +5278,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>11.54</t>
+          <t>10.62</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>23.97</t>
+          <t>12.58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>471</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>6.65</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>5.60</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>67.98</t>
+          <t>69.38</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>65.84</v>
+        <v>66.06</v>
       </c>
       <c r="AN12" t="n">
-        <v>66.06</v>
+        <v>66.34</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>62.56</t>
+          <t>62.79</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>686.39</t>
+          <t>768.32</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-103.80</t>
+          <t>-95.88</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>75108071.75142857</t>
+          <t>75069439.97931527</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>190606270.0</t>
+          <t>100281347.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>118462794.8</v>
+        <v>131264222.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>74290109.7</t>
+          <t>81393410.0</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>120126016.38</v>
+        <v>119695734.58</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>44172685</t>
+          <t>49870812</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-8488760.999966215</t>
+          <t>-5685337.758529304</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>11514469.19780271</t>
+          <t>9733490.069373712</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>190606270.0</t>
+          <t>100281347.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>53.28</t>
+          <t>52.01</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>96.34</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>48.32</t>
+          <t>48.84</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>8104</t>
+          <t>8116</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
+          <t>71.2</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
           <t>70.6</t>
         </is>
       </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>72.8</t>
-        </is>
-      </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>69.7</t>
-        </is>
-      </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="CJ12" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -5618,7 +5618,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2961.0</t>
+          <t>3965.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-11.08</t>
+          <t>-14.74</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>6.84</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,73 +5744,73 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>2961</t>
+          <t>3965</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>61.54</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>34.13</t>
+          <t>49.08</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-3.55</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>56.9</t>
+          <t>57.22000000000001</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>58.08</v>
+        <v>58</v>
       </c>
       <c r="AN13" t="n">
-        <v>60.1</v>
+        <v>60.13</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>58.16</t>
+          <t>58.25</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-14.26</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-112.62</t>
+          <t>-112.75</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>813557.9312320916</t>
+          <t>812885.6566523606</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>171155.0</t>
+          <t>229092.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>188434.4</v>
+        <v>179557.8</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>211905.8</t>
+          <t>210593.2</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>549840.7</v>
+        <v>551119.74</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-23471</t>
+          <t>-31035</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-36063.99054059955</t>
+          <t>-35417.44213935517</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-37563.41281263391</t>
+          <t>-31861.42593251113</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>171155.0</t>
+          <t>229092.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>24.47</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>34271</t>
+          <t>34450</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,12 +5996,12 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>58.3</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
@@ -6011,7 +6011,7 @@
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2826.0</t>
+          <t>2961.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>57.2</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>-11.08</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,73 +6174,73 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>2961</t>
+          <t>3965</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>35.71</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>22.46</t>
+          <t>34.13</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>57.16</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>58.14</v>
+        <v>58.08</v>
       </c>
       <c r="AN14" t="n">
-        <v>60.07</v>
+        <v>60.1</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>58.08</t>
+          <t>58.16</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-24.14</t>
+          <t>-14.26</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-112.17</t>
+          <t>-112.62</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>813557.9312320916</t>
+          <t>812885.6566523606</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>162030.0</t>
+          <t>171155.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>209836.2</v>
+        <v>188434.4</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>215755.9</t>
+          <t>211905.8</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>550120.9</v>
+        <v>549840.7</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-5919</t>
+          <t>-23471</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-35791.36830932057</t>
+          <t>-36063.99054059955</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-38160.02218378661</t>
+          <t>-37563.41281263391</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>162030.0</t>
+          <t>171155.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,22 +6361,22 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>24.47</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>34271</t>
+          <t>34450</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
+          <t>57.7</t>
+        </is>
+      </c>
+      <c r="CE14" t="inlineStr">
+        <is>
+          <t>58.5</t>
+        </is>
+      </c>
+      <c r="CF14" t="inlineStr">
+        <is>
+          <t>57.3</t>
+        </is>
+      </c>
+      <c r="CG14" t="inlineStr">
+        <is>
           <t>57.5</t>
-        </is>
-      </c>
-      <c r="CE14" t="inlineStr">
-        <is>
-          <t>57.8</t>
-        </is>
-      </c>
-      <c r="CF14" t="inlineStr">
-        <is>
-          <t>56.9</t>
-        </is>
-      </c>
-      <c r="CG14" t="inlineStr">
-        <is>
-          <t>57.2</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3484.0</t>
+          <t>2826.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>56.8</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-15.18</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,73 +6604,73 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>2961</t>
+          <t>3965</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>35.71</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>10.56</t>
+          <t>22.46</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>57.23999999999999</t>
+          <t>57.16</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>58.29</v>
+        <v>58.14</v>
       </c>
       <c r="AN15" t="n">
-        <v>60.05</v>
+        <v>60.07</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>57.99</t>
+          <t>58.08</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-32.85</t>
+          <t>-24.14</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-111.43</t>
+          <t>-112.17</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>813557.9312320916</t>
+          <t>812885.6566523606</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>199284.0</t>
+          <t>162030.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>213119.2</v>
+        <v>209836.2</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>251269.4</t>
+          <t>215755.9</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>555483.9399999999</v>
+        <v>550120.9</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-38150</t>
+          <t>-5919</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-35360.70396850856</t>
+          <t>-35791.36830932057</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-36671.78477886959</t>
+          <t>-38160.02218378661</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>199284.0</t>
+          <t>162030.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-3.57</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,22 +6791,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>24.47</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>34271</t>
+          <t>34450</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>58.3</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>56.8</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2408.0</t>
+          <t>3484.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-34.72</t>
+          <t>-15.18</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,73 +7034,73 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>2961</t>
+          <t>3965</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>16.11</t>
+          <t>10.56</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-2.71</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>57.36</t>
+          <t>57.23999999999999</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>58.46</v>
+        <v>58.29</v>
       </c>
       <c r="AN16" t="n">
-        <v>60.09</v>
+        <v>60.05</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>57.91</t>
+          <t>57.99</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-36.35</t>
+          <t>-32.85</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-110.50</t>
+          <t>-111.43</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>813557.9312320916</t>
+          <t>812885.6566523606</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>136228.0</t>
+          <t>199284.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>212208.6</v>
+        <v>213119.2</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>325088.9</t>
+          <t>251269.4</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>556448.64</v>
+        <v>555483.9399999999</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-112880</t>
+          <t>-38150</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-35122.32563935201</t>
+          <t>-35360.70396850856</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-37227.52474402849</t>
+          <t>-36671.78477886959</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>136228.0</t>
+          <t>199284.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7236,7 +7236,7 @@
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>24.47</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>34271</t>
+          <t>34450</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,17 +7286,17 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>58.3</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-4.5</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>4791.0</t>
+          <t>2408.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-31.67</t>
+          <t>-34.72</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>8.27</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,73 +7464,73 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>2961</t>
+          <t>3965</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>15.46</t>
+          <t>16.11</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-2.71</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>57.62</t>
+          <t>57.36</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>58.66</v>
+        <v>58.46</v>
       </c>
       <c r="AN17" t="n">
-        <v>60.11</v>
+        <v>60.09</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>57.83</t>
+          <t>57.91</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-36.02</t>
+          <t>-36.35</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-109.54</t>
+          <t>-110.50</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>813557.9312320916</t>
+          <t>812885.6566523606</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>273475.0</t>
+          <t>136228.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>241628.6</v>
+        <v>212208.6</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>353601.2</t>
+          <t>325088.9</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>558552.8199999999</v>
+        <v>556448.64</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-111972</t>
+          <t>-112880</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-34739.56216577447</t>
+          <t>-35122.32563935201</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-29935.8845248259</t>
+          <t>-37227.52474402849</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>273475.0</t>
+          <t>136228.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-3.57</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7661,12 +7661,12 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>24.47</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>34271</t>
+          <t>34450</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>58.7</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>-4.5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>4747.0</t>
+          <t>4791.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-31.52</t>
+          <t>-31.67</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>8.19</t>
+          <t>8.27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,73 +7894,73 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>2961</t>
+          <t>3965</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>19.01</t>
+          <t>15.46</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-2.1</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>58.17999999999999</t>
+          <t>57.62</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>58.9</v>
+        <v>58.66</v>
       </c>
       <c r="AN18" t="n">
-        <v>60.16</v>
+        <v>60.11</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>57.77</t>
+          <t>57.83</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-14.48</t>
+          <t>-36.02</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-108.68</t>
+          <t>-109.54</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>813557.9312320916</t>
+          <t>812885.6566523606</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>278164.0</t>
+          <t>273475.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>235377.2</v>
+        <v>241628.6</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>343709.9</t>
+          <t>353601.2</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>560862.08</v>
+        <v>558552.8199999999</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-108332</t>
+          <t>-111972</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-35612.95810049239</t>
+          <t>-34739.56216577447</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-33155.15262150689</t>
+          <t>-29935.8845248259</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>278164.0</t>
+          <t>273475.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,22 +8081,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>24.47</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>34271</t>
+          <t>34450</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>58.7</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>57.9</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>3082.0</t>
+          <t>4747.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-33.50</t>
+          <t>-31.52</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>8.19</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,73 +8324,73 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>2961</t>
+          <t>3965</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>13.04</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>19.01</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-2.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>58.38000000000001</t>
+          <t>58.17999999999999</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>59.01</v>
+        <v>58.9</v>
       </c>
       <c r="AN19" t="n">
-        <v>60.14</v>
+        <v>60.16</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>57.69</t>
+          <t>57.77</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-30.25</t>
+          <t>-14.48</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-108.37</t>
+          <t>-108.68</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>813557.9312320916</t>
+          <t>812885.6566523606</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>178445.0</t>
+          <t>278164.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>221675.6</v>
+        <v>235377.2</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>333361.3</t>
+          <t>343709.9</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>566147.36</v>
+        <v>560862.08</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-111685</t>
+          <t>-108332</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-36059.8318239443</t>
+          <t>-35612.95810049239</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-37072.38730885455</t>
+          <t>-33155.15262150689</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>178445.0</t>
+          <t>278164.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,22 +8511,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>24.47</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>34271</t>
+          <t>34450</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.9</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3352.0</t>
+          <t>3082.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-15.27</t>
+          <t>-33.50</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,141 +8754,141 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>2961</t>
+          <t>3965</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>10.64</t>
+          <t>13.04</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
+          <t>58.38000000000001</t>
+        </is>
+      </c>
+      <c r="AM20" t="n">
+        <v>59.01</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>60.14</v>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>57.69</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>-30.25</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>-0.58</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>-0.44</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>5.31</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr">
+        <is>
+          <t>-108.37</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>812885.6566523606</t>
+        </is>
+      </c>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>178445.0</t>
+        </is>
+      </c>
+      <c r="AX20" t="n">
+        <v>221675.6</v>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>333361.3</t>
+        </is>
+      </c>
+      <c r="AZ20" t="n">
+        <v>566147.36</v>
+      </c>
+      <c r="BA20" t="inlineStr">
+        <is>
+          <t>-111685</t>
+        </is>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>-36059.8318239443</t>
+        </is>
+      </c>
+      <c r="BC20" t="inlineStr">
+        <is>
+          <t>-37072.38730885455</t>
+        </is>
+      </c>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>178445.0</t>
+        </is>
+      </c>
+      <c r="BE20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF20" t="inlineStr">
+        <is>
           <t>58.9</t>
         </is>
       </c>
-      <c r="AM20" t="n">
-        <v>59.24</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>60.11</v>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>57.62</t>
-        </is>
-      </c>
-      <c r="AP20" t="inlineStr">
-        <is>
-          <t>-24.96</t>
-        </is>
-      </c>
-      <c r="AQ20" t="inlineStr">
-        <is>
-          <t>-0.51</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>-0.41</t>
-        </is>
-      </c>
-      <c r="AS20" t="inlineStr">
-        <is>
-          <t>5.31</t>
-        </is>
-      </c>
-      <c r="AT20" t="inlineStr">
-        <is>
-          <t>-107.74</t>
-        </is>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV20" t="inlineStr">
-        <is>
-          <t>813557.9312320916</t>
-        </is>
-      </c>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>194731.0</t>
-        </is>
-      </c>
-      <c r="AX20" t="n">
-        <v>289419.6</v>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>341561.2</t>
-        </is>
-      </c>
-      <c r="AZ20" t="n">
-        <v>568481.84</v>
-      </c>
-      <c r="BA20" t="inlineStr">
-        <is>
-          <t>-52141</t>
-        </is>
-      </c>
-      <c r="BB20" t="inlineStr">
-        <is>
-          <t>-35875.73082668789</t>
-        </is>
-      </c>
-      <c r="BC20" t="inlineStr">
-        <is>
-          <t>-30660.24445832073</t>
-        </is>
-      </c>
-      <c r="BD20" t="inlineStr">
-        <is>
-          <t>194731.0</t>
-        </is>
-      </c>
-      <c r="BE20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF20" t="inlineStr">
-        <is>
-          <t>58.9</t>
-        </is>
-      </c>
       <c r="BG20" t="inlineStr">
         <is>
           <t>2025/08/29</t>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -8951,12 +8951,12 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>24.47</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>34271</t>
+          <t>34450</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>4870.0</t>
+          <t>3352.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,74 +9068,74 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>57.4</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>0.69</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>-1.14</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>-15.27</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2025-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
           <t>58.1</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>-1.04</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>-0.82</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>22.85</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>2025-10-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>58.1</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
       <c r="T21" t="inlineStr">
         <is>
           <t>59.6</t>
@@ -9148,12 +9148,12 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>8.40</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,73 +9184,73 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>2961</t>
+          <t>3965</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>40.68</t>
+          <t>10.64</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>55.37</t>
+          <t>35.75</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>59.73999999999999</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>59.51</v>
+        <v>59.24</v>
       </c>
       <c r="AN21" t="n">
-        <v>60.1</v>
+        <v>60.11</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>57.55</t>
+          <t>57.62</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-24.96</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-107.25</t>
+          <t>-107.74</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,48 +9270,48 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>813557.9312320916</t>
+          <t>812885.6566523606</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>283328.0</t>
+          <t>194731.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>437969.2</v>
+        <v>289419.6</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>356514.8</t>
+          <t>341561.2</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>570563.3</v>
+        <v>568481.84</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>81454</t>
+          <t>-52141</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-36824.00107548192</t>
+          <t>-35875.73082668789</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-22149.96022690379</t>
+          <t>-30660.24445832073</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>283328.0</t>
+          <t>194731.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,22 +9371,22 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>24.47</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>34271</t>
+          <t>34450</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>57.2</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9473,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9483,127 +9483,127 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
+          <t>-1.51</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>4870.0</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-0.52</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>-1.14</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>22.85</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2025-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>-1.53</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>-4.07</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>8.40</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
           <t>-1.35</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>4060.0</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>-2.61</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>-0.82</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>36.21</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>2025-10-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>58.1</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>59.6</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>61.5</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>-4.07</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>7.01</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>-1.86</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,73 +9614,73 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>2961</t>
+          <t>3965</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>55.93</t>
+          <t>40.68</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>67.23</t>
+          <t>55.37</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>60.12</t>
+          <t>59.73999999999999</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>59.74</v>
+        <v>59.51</v>
       </c>
       <c r="AN22" t="n">
-        <v>60.09</v>
+        <v>60.1</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>57.46</t>
+          <t>57.55</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>14.66</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-107.17</t>
+          <t>-107.25</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>813557.9312320916</t>
+          <t>812885.6566523606</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>242218.0</t>
+          <t>283328.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>465573.8</v>
+        <v>437969.2</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>341803.5</t>
+          <t>356514.8</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>579417.88</v>
+        <v>570563.3</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>123770</t>
+          <t>81454</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-39492.00850249613</t>
+          <t>-36824.00107548192</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-18693.87703106157</t>
+          <t>-22149.96022690379</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>242218.0</t>
+          <t>283328.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>24.47</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>34271</t>
+          <t>34450</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>59.3</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>60.6</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3505.0</t>
+          <t>4060.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,22 +9938,22 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>36.21</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -9993,7 +9993,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
@@ -10008,12 +10008,12 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,73 +10044,73 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>2961</t>
+          <t>3965</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>69.49</t>
+          <t>55.93</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>81.92</t>
+          <t>67.23</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>59.72000000000001</t>
+          <t>60.12</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>59.98</v>
+        <v>59.74</v>
       </c>
       <c r="AN23" t="n">
-        <v>60.1</v>
+        <v>60.09</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>57.38</t>
+          <t>57.46</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>20.51</t>
+          <t>14.66</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-107.44</t>
+          <t>-107.17</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,48 +10130,48 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>813557.9312320916</t>
+          <t>812885.6566523606</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>209656.0</t>
+          <t>242218.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>452042.6</v>
+        <v>465573.8</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>332281.8</t>
+          <t>341803.5</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>596784.86</v>
+        <v>579417.88</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>119760</t>
+          <t>123770</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-43273.48695184787</t>
+          <t>-39492.00850249613</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-8684.334000177623</t>
+          <t>-18693.87703106157</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>209656.0</t>
+          <t>242218.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="BF23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>24.47</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>34271</t>
+          <t>34450</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>60.1</t>
+          <t>59.3</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料).xlsx
+++ b/Result/checksun_type/濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料).xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>470.74</t>
+          <t>883.83</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>68.4</t>
+          <t>69.1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,17 +913,17 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-33.44</t>
+          <t>-14.94</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -933,77 +933,77 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
           <t>2025-11-12 00:00:00</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>2025-11-21 00:00:00</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-09-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
       <c r="Q2" t="inlineStr">
         <is>
+          <t>69.1</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>69.1</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
           <t>70.0</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>65.0</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>67.8</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>70.1</t>
-        </is>
-      </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>5.23</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>7.97</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>471</t>
+          <t>884</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,58 +1029,58 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>59.72</t>
+          <t>87.14</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>66.04</t>
+          <t>67.06</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>66.58</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="AN2" t="n">
-        <v>66.97</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>64.12</t>
+          <t>64.27</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-13.94</t>
+          <t>53.39</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,58 +1090,58 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-92.94</t>
+          <t>-91.85</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>75069439.97931527</t>
+          <t>75094211.38675213</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>32018133.0</t>
+          <t>61639312.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>30939104.4</v>
+        <v>37727299.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>46483201.1</t>
+          <t>44352094.1</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>100844624.6</v>
+        <v>100893408.28</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-15544096</t>
+          <t>-6624794</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-6473896.94137024</t>
+          <t>-6593306.750079641</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-9714771.763802804</t>
+          <t>-7250060.697981343</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>32018133.0</t>
+          <t>61639312.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>44.61</t>
+          <t>46.09</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>96.34</t>
+          <t>97.32</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>48.84</t>
+          <t>47.57</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>8116</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1271,17 +1271,17 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>69.2</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.1</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>68.4</t>
+          <t>69.1</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>692.026</t>
+          <t>470.74</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>68.3</t>
+          <t>68.4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-37.39</t>
+          <t>-33.44</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1363,49 +1363,49 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
           <t>2025-11-12 00:00:00</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>2025-11-21 00:00:00</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-09-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
       <c r="Q3" t="inlineStr">
         <is>
+          <t>69.1</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
           <t>70.0</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>65.0</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>67.8</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>70.1</t>
-        </is>
-      </c>
       <c r="V3" t="inlineStr">
         <is>
           <t>0</t>
@@ -1413,27 +1413,27 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>6.24</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,68 +1444,68 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>471</t>
+          <t>884</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>61.43</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>26.78</t>
+          <t>59.72</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>65.36</t>
+          <t>66.04</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>66.36</v>
+        <v>66.58</v>
       </c>
       <c r="AN3" t="n">
-        <v>66.92</v>
+        <v>66.97</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>63.96</t>
+          <t>64.12</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-93.40</t>
+          <t>-13.94</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -1520,53 +1520,53 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-92.69</t>
+          <t>-92.94</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>75069439.97931527</t>
+          <t>75094211.38675213</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>46803277.0</t>
+          <t>32018133.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>33379525.8</v>
+        <v>30939104.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>53309522.5</t>
+          <t>46483201.1</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>101686881.5</v>
+        <v>100844624.6</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-19929996</t>
+          <t>-15544096</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-5884646.973655229</t>
+          <t>-6473896.94137024</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-9715133.687697649</t>
+          <t>-9714771.763802804</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>46803277.0</t>
+          <t>32018133.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>44.40</t>
+          <t>44.61</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,12 +1631,12 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>96.34</t>
+          <t>97.32</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>48.84</t>
+          <t>47.57</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>8116</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>65.4</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>68.3</t>
+          <t>69.2</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>65.4</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>68.3</t>
+          <t>68.4</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>308.105</t>
+          <t>692.026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>65.4</t>
+          <t>68.3</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-56.32</t>
+          <t>-37.39</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1793,49 +1793,49 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
           <t>2025-11-12 00:00:00</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>2025-11-21 00:00:00</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-09-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
       <c r="Q4" t="inlineStr">
         <is>
+          <t>69.1</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
           <t>70.0</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>65.0</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>67.8</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>70.1</t>
-        </is>
-      </c>
       <c r="V4" t="inlineStr">
         <is>
           <t>0</t>
@@ -1843,27 +1843,27 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>6.24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>471</t>
+          <t>884</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>17.72</t>
+          <t>61.43</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>26.78</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>65.12</t>
+          <t>65.36</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>66.14</v>
+        <v>66.36</v>
       </c>
       <c r="AN4" t="n">
-        <v>66.83</v>
+        <v>66.92</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>63.8</t>
+          <t>63.96</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-169.68</t>
+          <t>-93.40</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,53 +1950,53 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-90.99</t>
+          <t>-92.69</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>75069439.97931527</t>
+          <t>75094211.38675213</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>20134094.0</t>
+          <t>46803277.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>29566216</v>
+        <v>33379525.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>67689821.8</t>
+          <t>53309522.5</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>102474885.18</v>
+        <v>101686881.5</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-38123605</t>
+          <t>-19929996</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-5188194.843829334</t>
+          <t>-5884646.973655229</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-10952804.2329868</t>
+          <t>-9715133.687697649</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>20134094.0</t>
+          <t>46803277.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>38.27</t>
+          <t>44.40</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>96.34</t>
+          <t>97.32</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>48.84</t>
+          <t>47.57</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>8116</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>64.3</t>
+          <t>65.4</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>65.8</t>
+          <t>68.3</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>64.3</t>
+          <t>65.4</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>65.4</t>
+          <t>68.3</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>436.423</t>
+          <t>308.105</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>64.1</t>
+          <t>65.4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6.29</t>
+          <t>5.35</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-57.89</t>
+          <t>-56.32</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2223,49 +2223,49 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
           <t>2025-11-12 00:00:00</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>2025-11-21 00:00:00</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-09-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
       <c r="Q5" t="inlineStr">
         <is>
+          <t>69.1</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
           <t>70.0</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>65.0</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>67.8</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>70.1</t>
-        </is>
-      </c>
       <c r="V5" t="inlineStr">
         <is>
           <t>0</t>
@@ -2273,27 +2273,27 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>471</t>
+          <t>884</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>17.72</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>65.24000000000001</t>
+          <t>65.12</t>
         </is>
       </c>
       <c r="AM5" t="n">
         <v>66.14</v>
       </c>
       <c r="AN5" t="n">
-        <v>66.84</v>
+        <v>66.83</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>63.67</t>
+          <t>63.8</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-128.59</t>
+          <t>-169.68</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,53 +2380,53 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-87.16</t>
+          <t>-90.99</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>75069439.97931527</t>
+          <t>75094211.38675213</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>28041681.0</t>
+          <t>20134094.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>35349677.8</v>
+        <v>29566216</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>83955755.0</t>
+          <t>67689821.8</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>105161801.84</v>
+        <v>102474885.18</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-48606077</t>
+          <t>-38123605</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-4140084.045800703</t>
+          <t>-5188194.843829334</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-9472320.967936054</t>
+          <t>-10952804.2329868</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>28041681.0</t>
+          <t>20134094.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>35.52</t>
+          <t>38.27</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>96.34</t>
+          <t>97.32</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>48.84</t>
+          <t>47.57</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>8116</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>64.7</t>
+          <t>64.3</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>65.8</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>63.5</t>
+          <t>64.3</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>64.1</t>
+          <t>65.4</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>427.384</t>
+          <t>436.423</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>64.1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6.43</t>
+          <t>7.24</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-44.43</t>
+          <t>-57.89</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2653,49 +2653,49 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
           <t>2025-11-12 00:00:00</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>2025-11-21 00:00:00</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-09-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
       <c r="Q6" t="inlineStr">
         <is>
+          <t>69.1</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
           <t>70.0</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>65.0</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>67.8</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>70.1</t>
-        </is>
-      </c>
       <c r="V6" t="inlineStr">
         <is>
           <t>0</t>
@@ -2703,27 +2703,27 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>471</t>
+          <t>884</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>65.24000000000001</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>66.2</v>
+        <v>66.14</v>
       </c>
       <c r="AN6" t="n">
-        <v>66.90000000000001</v>
+        <v>66.84</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>63.56</t>
+          <t>63.67</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-72.20</t>
+          <t>-128.59</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,53 +2810,53 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-83.03</t>
+          <t>-87.16</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>75069439.97931527</t>
+          <t>75094211.38675213</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>27698337.0</t>
+          <t>28041681.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>50976888.8</v>
+        <v>35349677.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>91736509.2</t>
+          <t>83955755.0</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>107077260.2</v>
+        <v>105161801.84</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-40759620</t>
+          <t>-48606077</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-3170586.423594275</t>
+          <t>-4140084.045800703</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-7866289.16186586</t>
+          <t>-9472320.967936054</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>27698337.0</t>
+          <t>28041681.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>35.31</t>
+          <t>35.52</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>96.34</t>
+          <t>97.32</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>48.84</t>
+          <t>47.57</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>8116</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>64.7</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>63.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>64.1</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-3.15</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>677.83</t>
+          <t>427.384</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,112 +3048,112 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>64.0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>-2.61</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>-44.43</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2025-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>69.1</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
           <t>65.0</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>4.97</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>-1.84</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>-35.82</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2025-11-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2025-09-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>67.8</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>70.1</t>
-        </is>
-      </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>-7.14</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3164,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>471</t>
+          <t>884</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3179,58 +3179,58 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>12.81</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>5.55</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>67.4</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>66.28</v>
+        <v>66.2</v>
       </c>
       <c r="AN7" t="n">
-        <v>66.98</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>63.46</t>
+          <t>63.56</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-21.43</t>
+          <t>-72.20</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,58 +3240,58 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-79.97</t>
+          <t>-83.03</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>75069439.97931527</t>
+          <t>75094211.38675213</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>44220240.0</t>
+          <t>27698337.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>62027297.8</v>
+        <v>50976888.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>96645760.1</t>
+          <t>91736509.2</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>113463276.16</v>
+        <v>107077260.2</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-34618462</t>
+          <t>-40759620</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-2316822.289363078</t>
+          <t>-3170586.423594275</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-5254232.254556075</t>
+          <t>-7866289.16186586</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>44220240.0</t>
+          <t>27698337.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>37.42</t>
+          <t>35.31</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>96.34</t>
+          <t>97.32</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>48.84</t>
+          <t>47.57</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>8116</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>64.3</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3453,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>-3.15</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>412.165</t>
+          <t>677.83</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>67.1</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-23.59</t>
+          <t>-35.82</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3513,77 +3513,77 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
           <t>2025-11-12 00:00:00</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>2025-11-21 00:00:00</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2025-09-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
       <c r="Q8" t="inlineStr">
         <is>
+          <t>69.1</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
           <t>70.0</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
         <is>
           <t>65.0</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>67.8</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>70.1</t>
-        </is>
-      </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-7.14</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>471</t>
+          <t>884</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>23.94</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>29.29</t>
+          <t>12.81</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>5.55</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>68.78000000000002</t>
+          <t>67.4</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>66.31</v>
+        <v>66.28</v>
       </c>
       <c r="AN8" t="n">
         <v>66.98</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>63.36</t>
+          <t>63.46</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>21.92</t>
+          <t>-21.43</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,53 +3670,53 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-78.90</t>
+          <t>-79.97</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>75069439.97931527</t>
+          <t>75094211.38675213</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>27736728.0</t>
+          <t>44220240.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>73239519.2</v>
+        <v>62027297.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>95851157.0</t>
+          <t>96645760.1</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>115231412.04</v>
+        <v>113463276.16</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-22611637</t>
+          <t>-34618462</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-1782747.750237079</t>
+          <t>-2316822.289363078</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-3105275.127879396</t>
+          <t>-5254232.254556075</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>27736728.0</t>
+          <t>44220240.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>41.86</t>
+          <t>37.42</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>96.34</t>
+          <t>97.32</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>48.84</t>
+          <t>47.57</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>8116</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>67.9</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>67.9</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>66.5</t>
+          <t>64.3</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>67.1</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>735.417</t>
+          <t>412.165</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>10.77</t>
+          <t>-23.59</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3943,77 +3943,77 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
           <t>2025-11-12 00:00:00</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>2025-11-21 00:00:00</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2025-09-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
       <c r="Q9" t="inlineStr">
         <is>
+          <t>69.1</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
           <t>70.0</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
         <is>
           <t>65.0</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>67.8</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>70.1</t>
-        </is>
-      </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>-5.71</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>471</t>
+          <t>884</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>14.47</t>
+          <t>23.94</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>49.64</t>
+          <t>29.29</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-5.53</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>5.80</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>69.86000000000001</t>
+          <t>68.78000000000002</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>66.23999999999999</v>
+        <v>66.31</v>
       </c>
       <c r="AN9" t="n">
-        <v>66.90000000000001</v>
+        <v>66.98</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>63.24</t>
+          <t>63.36</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>50.55</t>
+          <t>21.92</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,53 +4100,53 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-80.05</t>
+          <t>-78.90</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>75069439.97931527</t>
+          <t>75094211.38675213</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>49051403.0</t>
+          <t>27736728.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>105813427.6</v>
+        <v>73239519.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>95524666.9</t>
+          <t>95851157.0</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>120066640.9</v>
+        <v>115231412.04</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>10288760</t>
+          <t>-22611637</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-1542288.227029385</t>
+          <t>-1782747.750237079</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>1841656.879083008</t>
+          <t>-3105275.127879396</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>49051403.0</t>
+          <t>27736728.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>39.53</t>
+          <t>41.86</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>96.34</t>
+          <t>97.32</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>48.84</t>
+          <t>47.57</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>8116</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>68.6</t>
+          <t>67.9</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>68.6</t>
+          <t>67.9</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>66.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.1</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1542.065</t>
+          <t>735.417</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>67.9</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>4.49</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>41.98</t>
+          <t>10.77</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4373,77 +4373,77 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
           <t>2025-11-12 00:00:00</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>2025-11-21 00:00:00</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2025-09-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
       <c r="Q10" t="inlineStr">
         <is>
+          <t>69.1</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
           <t>70.0</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
         <is>
           <t>65.0</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>67.8</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>70.1</t>
-        </is>
-      </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>-3.00</t>
+          <t>-5.71</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13.91</t>
+          <t>6.63</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>471</t>
+          <t>884</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>49.45</t>
+          <t>14.47</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>76.15</t>
+          <t>49.64</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-5.53</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>5.70</t>
+          <t>5.80</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>70.66</t>
+          <t>69.86000000000001</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>66.3</v>
+        <v>66.23999999999999</v>
       </c>
       <c r="AN10" t="n">
-        <v>66.75</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>63.15</t>
+          <t>63.24</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>125.60</t>
+          <t>50.55</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,53 +4530,53 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-82.57</t>
+          <t>-80.05</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>75069439.97931527</t>
+          <t>75094211.38675213</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>106177736.0</t>
+          <t>49051403.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>132561832.2</v>
+        <v>105813427.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>93365555.7</t>
+          <t>95524666.9</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>120263879.18</v>
+        <v>120066640.9</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>39196276</t>
+          <t>10288760</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-2157550.973595275</t>
+          <t>-1542288.227029385</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>6559213.964776337</t>
+          <t>1841656.879083008</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>106177736.0</t>
+          <t>49051403.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>39.53</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>96.34</t>
+          <t>97.32</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>48.84</t>
+          <t>47.57</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>8116</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>67.9</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1168.47</t>
+          <t>1542.065</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>67.9</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-3.8</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>53.47</t>
+          <t>41.98</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4803,77 +4803,77 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
           <t>2025-11-12 00:00:00</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>2025-11-21 00:00:00</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-09-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
       <c r="Q11" t="inlineStr">
         <is>
+          <t>69.1</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
           <t>70.0</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
         <is>
           <t>65.0</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>67.8</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>70.1</t>
-        </is>
-      </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>-3.00</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>9.23</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10.54</t>
+          <t>13.91</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>471</t>
+          <t>884</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>49.45</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>76.15</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>6.43</t>
+          <t>6.58</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>5.70</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>70.66</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>66.23999999999999</v>
+        <v>66.3</v>
       </c>
       <c r="AN11" t="n">
-        <v>66.59999999999999</v>
+        <v>66.75</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>63.02</t>
+          <t>63.15</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>262.06</t>
+          <t>125.60</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,53 +4960,53 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-88.05</t>
+          <t>-82.57</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>75069439.97931527</t>
+          <t>75094211.38675213</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>82950382.0</t>
+          <t>106177736.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>132496129.6</v>
+        <v>132561832.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>86336133.4</t>
+          <t>93365555.7</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>120394266.18</v>
+        <v>120263879.18</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>46159996</t>
+          <t>39196276</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-3742417.326026477</t>
+          <t>-2157550.973595275</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>6943645.052739069</t>
+          <t>6559213.964776337</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>82950382.0</t>
+          <t>106177736.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>50.11</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>96.34</t>
+          <t>97.32</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>48.84</t>
+          <t>47.57</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>8116</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>67.9</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1393.968</t>
+          <t>1168.47</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>61.27</t>
+          <t>53.47</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5233,77 +5233,77 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
           <t>2025-11-12 00:00:00</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>2025-11-21 00:00:00</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-09-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
       <c r="Q12" t="inlineStr">
         <is>
+          <t>69.1</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
           <t>70.0</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
         <is>
           <t>65.0</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>67.8</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>70.1</t>
-        </is>
-      </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>10.62</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12.58</t>
+          <t>10.54</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>471</t>
+          <t>884</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>6.43</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>69.38</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>66.06</v>
+        <v>66.23999999999999</v>
       </c>
       <c r="AN12" t="n">
-        <v>66.34</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>62.79</t>
+          <t>63.02</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>768.32</t>
+          <t>262.06</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,53 +5390,53 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-95.88</t>
+          <t>-88.05</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>75069439.97931527</t>
+          <t>75094211.38675213</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>100281347.0</t>
+          <t>82950382.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>131264222.4</v>
+        <v>132496129.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>81393410.0</t>
+          <t>86336133.4</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>119695734.58</v>
+        <v>120394266.18</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>49870812</t>
+          <t>46159996</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-5685337.758529304</t>
+          <t>-3742417.326026477</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>9733490.069373712</t>
+          <t>6943645.052739069</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>100281347.0</t>
+          <t>82950382.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>52.01</t>
+          <t>50.11</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>96.34</t>
+          <t>97.32</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>48.84</t>
+          <t>47.57</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>8116</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3965.0</t>
+          <t>3642.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-14.74</t>
+          <t>-4.40</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>6.84</t>
+          <t>6.28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,63 +5744,63 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>3965</t>
+          <t>3642</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>61.54</t>
+          <t>38.46</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>49.08</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-3.55</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>57.22000000000001</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>58</v>
+        <v>57.92</v>
       </c>
       <c r="AN13" t="n">
-        <v>60.13</v>
+        <v>60.12</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>58.25</t>
+          <t>58.33</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-112.75</t>
+          <t>-112.82</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>812885.6566523606</t>
+          <t>812174.5907142857</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>229092.0</t>
+          <t>210093.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>179557.8</v>
+        <v>194330.8</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>210593.2</t>
+          <t>203269.7</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>551119.74</v>
+        <v>548208.92</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-31035</t>
+          <t>-8938</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-35417.44213935517</t>
+          <t>-34352.97788224091</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-31861.42593251113</t>
+          <t>-28498.42446811244</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>229092.0</t>
+          <t>210093.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.34</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>34450</t>
+          <t>34092</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>58.3</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>58.3</t>
+          <t>58.7</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6048,7 +6048,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2961.0</t>
+          <t>3965.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-11.08</t>
+          <t>-14.74</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>6.84</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,73 +6174,73 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>3965</t>
+          <t>3642</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>61.54</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>34.13</t>
+          <t>49.08</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-3.55</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>56.9</t>
+          <t>57.22000000000001</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>58.08</v>
+        <v>58</v>
       </c>
       <c r="AN14" t="n">
-        <v>60.1</v>
+        <v>60.13</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>58.16</t>
+          <t>58.25</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-14.26</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-112.62</t>
+          <t>-112.75</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>812885.6566523606</t>
+          <t>812174.5907142857</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>171155.0</t>
+          <t>229092.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>188434.4</v>
+        <v>179557.8</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>211905.8</t>
+          <t>210593.2</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>549840.7</v>
+        <v>551119.74</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-23471</t>
+          <t>-31035</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-36063.99054059955</t>
+          <t>-35417.44213935517</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-37563.41281263391</t>
+          <t>-31861.42593251113</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>171155.0</t>
+          <t>229092.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.34</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>34450</t>
+          <t>34092</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>58.3</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2826.0</t>
+          <t>2961.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>57.2</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>-11.08</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6518,7 +6518,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,73 +6604,73 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>3965</t>
+          <t>3642</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>35.71</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>22.46</t>
+          <t>34.13</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>57.16</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>58.14</v>
+        <v>58.08</v>
       </c>
       <c r="AN15" t="n">
-        <v>60.07</v>
+        <v>60.1</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>58.08</t>
+          <t>58.16</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-24.14</t>
+          <t>-14.26</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-112.17</t>
+          <t>-112.62</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>812885.6566523606</t>
+          <t>812174.5907142857</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>162030.0</t>
+          <t>171155.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>209836.2</v>
+        <v>188434.4</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>215755.9</t>
+          <t>211905.8</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>550120.9</v>
+        <v>549840.7</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-5919</t>
+          <t>-23471</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-35791.36830932057</t>
+          <t>-36063.99054059955</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-38160.02218378661</t>
+          <t>-37563.41281263391</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>162030.0</t>
+          <t>171155.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,22 +6791,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.34</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>34450</t>
+          <t>34092</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
+          <t>57.7</t>
+        </is>
+      </c>
+      <c r="CE15" t="inlineStr">
+        <is>
+          <t>58.5</t>
+        </is>
+      </c>
+      <c r="CF15" t="inlineStr">
+        <is>
+          <t>57.3</t>
+        </is>
+      </c>
+      <c r="CG15" t="inlineStr">
+        <is>
           <t>57.5</t>
-        </is>
-      </c>
-      <c r="CE15" t="inlineStr">
-        <is>
-          <t>57.8</t>
-        </is>
-      </c>
-      <c r="CF15" t="inlineStr">
-        <is>
-          <t>56.9</t>
-        </is>
-      </c>
-      <c r="CG15" t="inlineStr">
-        <is>
-          <t>57.2</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,42 +6903,42 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2826.0</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>57.2</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>3484.0</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>56.8</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-15.18</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6948,7 +6948,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,73 +7034,73 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>3965</t>
+          <t>3642</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>35.71</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>10.56</t>
+          <t>22.46</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>57.23999999999999</t>
+          <t>57.16</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>58.29</v>
+        <v>58.14</v>
       </c>
       <c r="AN16" t="n">
-        <v>60.05</v>
+        <v>60.07</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>57.99</t>
+          <t>58.08</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-32.85</t>
+          <t>-24.14</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-111.43</t>
+          <t>-112.17</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>812885.6566523606</t>
+          <t>812174.5907142857</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>199284.0</t>
+          <t>162030.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>213119.2</v>
+        <v>209836.2</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>251269.4</t>
+          <t>215755.9</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>555483.9399999999</v>
+        <v>550120.9</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-38150</t>
+          <t>-5919</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-35360.70396850856</t>
+          <t>-35791.36830932057</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-36671.78477886959</t>
+          <t>-38160.02218378661</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>199284.0</t>
+          <t>162030.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-3.57</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,22 +7221,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.34</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>34450</t>
+          <t>34092</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>58.3</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>56.8</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2408.0</t>
+          <t>3484.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-34.72</t>
+          <t>-15.18</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7378,7 +7378,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,73 +7464,73 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>3965</t>
+          <t>3642</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>16.11</t>
+          <t>10.56</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-2.71</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>57.36</t>
+          <t>57.23999999999999</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>58.46</v>
+        <v>58.29</v>
       </c>
       <c r="AN17" t="n">
-        <v>60.09</v>
+        <v>60.05</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>57.91</t>
+          <t>57.99</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-36.35</t>
+          <t>-32.85</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-110.50</t>
+          <t>-111.43</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>812885.6566523606</t>
+          <t>812174.5907142857</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>136228.0</t>
+          <t>199284.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>212208.6</v>
+        <v>213119.2</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>325088.9</t>
+          <t>251269.4</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>556448.64</v>
+        <v>555483.9399999999</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-112880</t>
+          <t>-38150</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-35122.32563935201</t>
+          <t>-35360.70396850856</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-37227.52474402849</t>
+          <t>-36671.78477886959</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>136228.0</t>
+          <t>199284.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.34</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>34450</t>
+          <t>34092</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,17 +7716,17 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>58.3</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-4.5</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>4791.0</t>
+          <t>2408.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-31.67</t>
+          <t>-34.72</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>8.27</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,73 +7894,73 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>3965</t>
+          <t>3642</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>15.46</t>
+          <t>16.11</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-2.71</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>57.62</t>
+          <t>57.36</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>58.66</v>
+        <v>58.46</v>
       </c>
       <c r="AN18" t="n">
-        <v>60.11</v>
+        <v>60.09</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>57.83</t>
+          <t>57.91</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-36.02</t>
+          <t>-36.35</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-109.54</t>
+          <t>-110.50</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>812885.6566523606</t>
+          <t>812174.5907142857</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>273475.0</t>
+          <t>136228.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>241628.6</v>
+        <v>212208.6</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>353601.2</t>
+          <t>325088.9</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>558552.8199999999</v>
+        <v>556448.64</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-111972</t>
+          <t>-112880</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-34739.56216577447</t>
+          <t>-35122.32563935201</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-29935.8845248259</t>
+          <t>-37227.52474402849</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>273475.0</t>
+          <t>136228.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-3.57</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.34</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>34450</t>
+          <t>34092</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>58.7</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>-4.5</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>4747.0</t>
+          <t>4791.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-31.52</t>
+          <t>-31.67</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8238,7 +8238,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>8.19</t>
+          <t>8.27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,73 +8324,73 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>3965</t>
+          <t>3642</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>19.01</t>
+          <t>15.46</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-2.1</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>58.17999999999999</t>
+          <t>57.62</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>58.9</v>
+        <v>58.66</v>
       </c>
       <c r="AN19" t="n">
-        <v>60.16</v>
+        <v>60.11</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>57.77</t>
+          <t>57.83</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-14.48</t>
+          <t>-36.02</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-108.68</t>
+          <t>-109.54</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>812885.6566523606</t>
+          <t>812174.5907142857</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>278164.0</t>
+          <t>273475.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>235377.2</v>
+        <v>241628.6</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>343709.9</t>
+          <t>353601.2</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>560862.08</v>
+        <v>558552.8199999999</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-108332</t>
+          <t>-111972</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-35612.95810049239</t>
+          <t>-34739.56216577447</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-33155.15262150689</t>
+          <t>-29935.8845248259</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>278164.0</t>
+          <t>273475.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,22 +8511,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.34</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>34450</t>
+          <t>34092</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>58.7</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>57.9</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3082.0</t>
+          <t>4747.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-2.8</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-33.50</t>
+          <t>-31.52</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8668,7 +8668,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>8.19</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,73 +8754,73 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>3965</t>
+          <t>3642</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>13.04</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>19.01</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-2.1</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>58.38000000000001</t>
+          <t>58.17999999999999</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>59.01</v>
+        <v>58.9</v>
       </c>
       <c r="AN20" t="n">
-        <v>60.14</v>
+        <v>60.16</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>57.69</t>
+          <t>57.77</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-30.25</t>
+          <t>-14.48</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-108.37</t>
+          <t>-108.68</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>812885.6566523606</t>
+          <t>812174.5907142857</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>178445.0</t>
+          <t>278164.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>221675.6</v>
+        <v>235377.2</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>333361.3</t>
+          <t>343709.9</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>566147.36</v>
+        <v>560862.08</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-111685</t>
+          <t>-108332</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-36059.8318239443</t>
+          <t>-35612.95810049239</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-37072.38730885455</t>
+          <t>-33155.15262150689</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>178445.0</t>
+          <t>278164.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,22 +8941,22 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.34</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>34450</t>
+          <t>34092</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.9</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3352.0</t>
+          <t>3082.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-15.27</t>
+          <t>-33.50</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9098,7 +9098,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,141 +9184,141 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>3965</t>
+          <t>3642</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>10.64</t>
+          <t>13.04</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
+          <t>58.38000000000001</t>
+        </is>
+      </c>
+      <c r="AM21" t="n">
+        <v>59.01</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>60.14</v>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>57.69</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>-30.25</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>-0.58</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>-0.44</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>5.31</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr">
+        <is>
+          <t>-108.37</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV21" t="inlineStr">
+        <is>
+          <t>812174.5907142857</t>
+        </is>
+      </c>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>178445.0</t>
+        </is>
+      </c>
+      <c r="AX21" t="n">
+        <v>221675.6</v>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>333361.3</t>
+        </is>
+      </c>
+      <c r="AZ21" t="n">
+        <v>566147.36</v>
+      </c>
+      <c r="BA21" t="inlineStr">
+        <is>
+          <t>-111685</t>
+        </is>
+      </c>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>-36059.8318239443</t>
+        </is>
+      </c>
+      <c r="BC21" t="inlineStr">
+        <is>
+          <t>-37072.38730885455</t>
+        </is>
+      </c>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>178445.0</t>
+        </is>
+      </c>
+      <c r="BE21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF21" t="inlineStr">
+        <is>
           <t>58.9</t>
         </is>
       </c>
-      <c r="AM21" t="n">
-        <v>59.24</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>60.11</v>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>57.62</t>
-        </is>
-      </c>
-      <c r="AP21" t="inlineStr">
-        <is>
-          <t>-24.96</t>
-        </is>
-      </c>
-      <c r="AQ21" t="inlineStr">
-        <is>
-          <t>-0.51</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>-0.41</t>
-        </is>
-      </c>
-      <c r="AS21" t="inlineStr">
-        <is>
-          <t>5.31</t>
-        </is>
-      </c>
-      <c r="AT21" t="inlineStr">
-        <is>
-          <t>-107.74</t>
-        </is>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV21" t="inlineStr">
-        <is>
-          <t>812885.6566523606</t>
-        </is>
-      </c>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>194731.0</t>
-        </is>
-      </c>
-      <c r="AX21" t="n">
-        <v>289419.6</v>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>341561.2</t>
-        </is>
-      </c>
-      <c r="AZ21" t="n">
-        <v>568481.84</v>
-      </c>
-      <c r="BA21" t="inlineStr">
-        <is>
-          <t>-52141</t>
-        </is>
-      </c>
-      <c r="BB21" t="inlineStr">
-        <is>
-          <t>-35875.73082668789</t>
-        </is>
-      </c>
-      <c r="BC21" t="inlineStr">
-        <is>
-          <t>-30660.24445832073</t>
-        </is>
-      </c>
-      <c r="BD21" t="inlineStr">
-        <is>
-          <t>194731.0</t>
-        </is>
-      </c>
-      <c r="BE21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF21" t="inlineStr">
-        <is>
-          <t>58.9</t>
-        </is>
-      </c>
       <c r="BG21" t="inlineStr">
         <is>
           <t>2025/08/29</t>
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,22 +9371,22 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.34</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>34450</t>
+          <t>34092</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>4870.0</t>
+          <t>3352.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,72 +9498,72 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
+          <t>57.4</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-0.35</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>-0.98</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>-15.27</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2025-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
           <t>58.1</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>-0.52</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>-1.14</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>22.85</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>2025-10-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>58.1</t>
-        </is>
-      </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>8.40</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,73 +9614,73 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>3965</t>
+          <t>3642</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>40.68</t>
+          <t>10.64</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>55.37</t>
+          <t>35.75</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>59.73999999999999</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>59.51</v>
+        <v>59.24</v>
       </c>
       <c r="AN22" t="n">
-        <v>60.1</v>
+        <v>60.11</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>57.55</t>
+          <t>57.62</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-24.96</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-107.25</t>
+          <t>-107.74</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,48 +9700,48 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>812885.6566523606</t>
+          <t>812174.5907142857</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>283328.0</t>
+          <t>194731.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>437969.2</v>
+        <v>289419.6</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>356514.8</t>
+          <t>341561.2</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>570563.3</v>
+        <v>568481.84</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>81454</t>
+          <t>-52141</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-36824.00107548192</t>
+          <t>-35875.73082668789</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-22149.96022690379</t>
+          <t>-30660.24445832073</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>283328.0</t>
+          <t>194731.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.34</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>34450</t>
+          <t>34092</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>57.2</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9903,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -9913,127 +9913,127 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
+          <t>-1.51</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>4870.0</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-1.57</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>-0.98</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>22.85</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2025-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>-1.53</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>-4.07</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>8.40</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
           <t>-1.35</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>4060.0</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>-2.08</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>-1.14</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>36.21</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>2025-10-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>58.1</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>59.6</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>61.5</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>-4.07</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>7.01</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>-1.86</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,73 +10044,73 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>3965</t>
+          <t>3642</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>55.93</t>
+          <t>40.68</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>67.23</t>
+          <t>55.37</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>60.12</t>
+          <t>59.73999999999999</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>59.74</v>
+        <v>59.51</v>
       </c>
       <c r="AN23" t="n">
-        <v>60.09</v>
+        <v>60.1</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>57.46</t>
+          <t>57.55</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>14.66</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-107.17</t>
+          <t>-107.25</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>812885.6566523606</t>
+          <t>812174.5907142857</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>242218.0</t>
+          <t>283328.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>465573.8</v>
+        <v>437969.2</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>341803.5</t>
+          <t>356514.8</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>579417.88</v>
+        <v>570563.3</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>123770</t>
+          <t>81454</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-39492.00850249613</t>
+          <t>-36824.00107548192</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-18693.87703106157</t>
+          <t>-22149.96022690379</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>242218.0</t>
+          <t>283328.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.34</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>34450</t>
+          <t>34092</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>59.3</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>60.6</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料).xlsx
+++ b/Result/checksun_type/濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料).xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>883.83</t>
+          <t>919.445</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,74 +898,74 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>70.3</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>-2.84</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>12.09</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-12-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2025-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>69.1</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>-2.61</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>-14.94</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2025-12-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2025-12-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-11-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>69.1</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>69.1</t>
-        </is>
-      </c>
       <c r="T2" t="inlineStr">
         <is>
           <t>70.0</t>
@@ -978,7 +978,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -993,33 +993,33 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>7.97</t>
+          <t>8.30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>919</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,58 +1029,58 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>87.14</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>4.31</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>67.06</t>
+          <t>68.30000000000001</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>66.84999999999999</v>
+        <v>67.22</v>
       </c>
       <c r="AN2" t="n">
-        <v>67.06999999999999</v>
+        <v>67.2</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>64.27</t>
+          <t>64.43</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>53.39</t>
+          <t>95.94</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-91.85</t>
+          <t>-89.28</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,63 +1100,63 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>75094211.38675213</t>
+          <t>75125562.09601706</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>61639312.0</t>
+          <t>64755840.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>37727299.4</v>
+        <v>45070131.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>44352094.1</t>
+          <t>40209904.5</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>100893408.28</v>
+        <v>101350514.72</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-6624794</t>
+          <t>4860226</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-6593306.750079641</t>
+          <t>-6365070.609214586</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-7250060.697981343</t>
+          <t>-5109771.834456787</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>61639312.0</t>
+          <t>64755840.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>70.3</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>2025/06/02</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>46.09</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>97.32</t>
+          <t>99.01</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>47.57</t>
+          <t>47.81</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>8199</t>
+          <t>8341</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>68.1</t>
+          <t>69.1</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>69.1</t>
+          <t>70.3</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1303,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>470.74</t>
+          <t>883.83</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>68.4</t>
+          <t>69.1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,27 +1338,27 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-33.44</t>
+          <t>-14.94</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1393,7 +1393,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>69.1</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>7.97</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,12 +1444,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>919</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1459,58 +1459,58 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>59.72</t>
+          <t>87.14</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>66.04</t>
+          <t>67.06</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>66.58</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="AN3" t="n">
-        <v>66.97</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>64.12</t>
+          <t>64.27</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-13.94</t>
+          <t>53.39</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-92.94</t>
+          <t>-91.85</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,63 +1530,63 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>75094211.38675213</t>
+          <t>75125562.09601706</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>32018133.0</t>
+          <t>61639312.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>30939104.4</v>
+        <v>37727299.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>46483201.1</t>
+          <t>44352094.1</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>100844624.6</v>
+        <v>100893408.28</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-15544096</t>
+          <t>-6624794</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-6473896.94137024</t>
+          <t>-6593306.750079641</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-9714771.763802804</t>
+          <t>-7250060.697981343</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>32018133.0</t>
+          <t>61639312.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>70.3</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>2025/06/02</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>44.61</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>97.32</t>
+          <t>99.01</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>47.57</t>
+          <t>47.81</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>8199</t>
+          <t>8341</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1701,17 +1701,17 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>69.2</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.1</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>68.4</t>
+          <t>69.1</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>692.026</t>
+          <t>470.74</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>68.3</t>
+          <t>68.4</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-37.39</t>
+          <t>-33.44</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>6.24</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,68 +1874,68 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>919</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>61.43</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>26.78</t>
+          <t>59.72</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>65.36</t>
+          <t>66.04</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>66.36</v>
+        <v>66.58</v>
       </c>
       <c r="AN4" t="n">
-        <v>66.92</v>
+        <v>66.97</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>63.96</t>
+          <t>64.12</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-93.40</t>
+          <t>-13.94</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-92.69</t>
+          <t>-92.94</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>75094211.38675213</t>
+          <t>75125562.09601706</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>46803277.0</t>
+          <t>32018133.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>33379525.8</v>
+        <v>30939104.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>53309522.5</t>
+          <t>46483201.1</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>101686881.5</v>
+        <v>100844624.6</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-19929996</t>
+          <t>-15544096</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-5884646.973655229</t>
+          <t>-6473896.94137024</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-9715133.687697649</t>
+          <t>-9714771.763802804</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>46803277.0</t>
+          <t>32018133.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2006,17 +2006,17 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>70.3</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>2025/06/02</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>44.40</t>
+          <t>-2.70</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>97.32</t>
+          <t>99.01</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>47.57</t>
+          <t>47.81</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>8199</t>
+          <t>8341</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>65.4</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>68.3</t>
+          <t>69.2</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>65.4</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>68.3</t>
+          <t>68.4</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>308.105</t>
+          <t>692.026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>65.4</t>
+          <t>68.3</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>5.35</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-56.32</t>
+          <t>-37.39</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>6.24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>919</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>17.72</t>
+          <t>61.43</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>26.78</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>65.12</t>
+          <t>65.36</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>66.14</v>
+        <v>66.36</v>
       </c>
       <c r="AN5" t="n">
-        <v>66.83</v>
+        <v>66.92</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>63.8</t>
+          <t>63.96</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-169.68</t>
+          <t>-93.40</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-90.99</t>
+          <t>-92.69</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>75094211.38675213</t>
+          <t>75125562.09601706</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>20134094.0</t>
+          <t>46803277.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>29566216</v>
+        <v>33379525.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>67689821.8</t>
+          <t>53309522.5</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>102474885.18</v>
+        <v>101686881.5</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-38123605</t>
+          <t>-19929996</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-5188194.843829334</t>
+          <t>-5884646.973655229</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-10952804.2329868</t>
+          <t>-9715133.687697649</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>20134094.0</t>
+          <t>46803277.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2436,17 +2436,17 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>70.3</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>2025/06/02</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>38.27</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>97.32</t>
+          <t>99.01</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>47.57</t>
+          <t>47.81</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>8199</t>
+          <t>8341</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>64.3</t>
+          <t>65.4</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>65.8</t>
+          <t>68.3</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>64.3</t>
+          <t>65.4</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>65.4</t>
+          <t>68.3</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>436.423</t>
+          <t>308.105</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>64.1</t>
+          <t>65.4</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>7.24</t>
+          <t>6.97</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-57.89</t>
+          <t>-56.32</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2658,7 +2658,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>919</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>17.72</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>65.24000000000001</t>
+          <t>65.12</t>
         </is>
       </c>
       <c r="AM6" t="n">
         <v>66.14</v>
       </c>
       <c r="AN6" t="n">
-        <v>66.84</v>
+        <v>66.83</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>63.67</t>
+          <t>63.8</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-128.59</t>
+          <t>-169.68</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-87.16</t>
+          <t>-90.99</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>75094211.38675213</t>
+          <t>75125562.09601706</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>28041681.0</t>
+          <t>20134094.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>35349677.8</v>
+        <v>29566216</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>83955755.0</t>
+          <t>67689821.8</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>105161801.84</v>
+        <v>102474885.18</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-48606077</t>
+          <t>-38123605</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-4140084.045800703</t>
+          <t>-5188194.843829334</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-9472320.967936054</t>
+          <t>-10952804.2329868</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>28041681.0</t>
+          <t>20134094.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2866,17 +2866,17 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>70.3</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>2025/06/02</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>35.52</t>
+          <t>-6.97</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>97.32</t>
+          <t>99.01</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>47.57</t>
+          <t>47.81</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>8199</t>
+          <t>8341</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>64.7</t>
+          <t>64.3</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>65.8</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>63.5</t>
+          <t>64.3</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>64.1</t>
+          <t>65.4</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>427.384</t>
+          <t>436.423</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>64.1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>8.82</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-44.43</t>
+          <t>-57.89</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>919</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>65.24000000000001</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>66.2</v>
+        <v>66.14</v>
       </c>
       <c r="AN7" t="n">
-        <v>66.90000000000001</v>
+        <v>66.84</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>63.56</t>
+          <t>63.67</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-72.20</t>
+          <t>-128.59</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-83.03</t>
+          <t>-87.16</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>75094211.38675213</t>
+          <t>75125562.09601706</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>27698337.0</t>
+          <t>28041681.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>50976888.8</v>
+        <v>35349677.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>91736509.2</t>
+          <t>83955755.0</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>107077260.2</v>
+        <v>105161801.84</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-40759620</t>
+          <t>-48606077</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-3170586.423594275</t>
+          <t>-4140084.045800703</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-7866289.16186586</t>
+          <t>-9472320.967936054</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>27698337.0</t>
+          <t>28041681.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3296,17 +3296,17 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>70.3</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>2025/06/02</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>35.31</t>
+          <t>-8.82</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>97.32</t>
+          <t>99.01</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>47.57</t>
+          <t>47.81</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>8199</t>
+          <t>8341</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>64.7</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>63.5</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>64.1</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-3.15</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>677.83</t>
+          <t>427.384</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,87 +3478,87 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>64.0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>8.96</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>-2.84</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>-44.43</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-12-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2025-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>69.1</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
           <t>65.0</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>5.93</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>-2.61</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>-35.82</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2025-12-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2025-12-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2025-11-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>69.1</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>-7.14</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,12 +3594,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>919</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3609,58 +3609,58 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>12.81</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>5.55</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>67.4</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>66.28</v>
+        <v>66.2</v>
       </c>
       <c r="AN8" t="n">
-        <v>66.98</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>63.46</t>
+          <t>63.56</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-21.43</t>
+          <t>-72.20</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-79.97</t>
+          <t>-83.03</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,63 +3680,63 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>75094211.38675213</t>
+          <t>75125562.09601706</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>44220240.0</t>
+          <t>27698337.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>62027297.8</v>
+        <v>50976888.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>96645760.1</t>
+          <t>91736509.2</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>113463276.16</v>
+        <v>107077260.2</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-34618462</t>
+          <t>-40759620</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-2316822.289363078</t>
+          <t>-3170586.423594275</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-5254232.254556075</t>
+          <t>-7866289.16186586</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>44220240.0</t>
+          <t>27698337.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>70.3</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>2025/06/02</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>37.42</t>
+          <t>-8.96</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>97.32</t>
+          <t>99.01</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>47.57</t>
+          <t>47.81</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>8199</t>
+          <t>8341</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>64.3</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3883,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>-3.15</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>412.165</t>
+          <t>677.83</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>67.1</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>7.54</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-23.59</t>
+          <t>-35.82</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-7.14</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>919</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>23.94</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>29.29</t>
+          <t>12.81</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>5.55</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>68.78000000000002</t>
+          <t>67.4</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>66.31</v>
+        <v>66.28</v>
       </c>
       <c r="AN9" t="n">
         <v>66.98</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>63.36</t>
+          <t>63.46</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>21.92</t>
+          <t>-21.43</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-78.90</t>
+          <t>-79.97</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>75094211.38675213</t>
+          <t>75125562.09601706</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>27736728.0</t>
+          <t>44220240.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>73239519.2</v>
+        <v>62027297.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>95851157.0</t>
+          <t>96645760.1</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>115231412.04</v>
+        <v>113463276.16</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-22611637</t>
+          <t>-34618462</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-1782747.750237079</t>
+          <t>-2316822.289363078</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-3105275.127879396</t>
+          <t>-5254232.254556075</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>27736728.0</t>
+          <t>44220240.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4156,17 +4156,17 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>70.3</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>2025/06/02</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>41.86</t>
+          <t>-7.54</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>97.32</t>
+          <t>99.01</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>47.57</t>
+          <t>47.81</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>8199</t>
+          <t>8341</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>67.9</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>67.9</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>66.5</t>
+          <t>64.3</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>67.1</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>735.417</t>
+          <t>412.165</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4.49</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>10.77</t>
+          <t>-23.59</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>-5.71</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>919</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>14.47</t>
+          <t>23.94</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>49.64</t>
+          <t>29.29</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-5.53</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>5.80</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>69.86000000000001</t>
+          <t>68.78000000000002</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>66.23999999999999</v>
+        <v>66.31</v>
       </c>
       <c r="AN10" t="n">
-        <v>66.90000000000001</v>
+        <v>66.98</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>63.24</t>
+          <t>63.36</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>50.55</t>
+          <t>21.92</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-80.05</t>
+          <t>-78.90</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>75094211.38675213</t>
+          <t>75125562.09601706</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>49051403.0</t>
+          <t>27736728.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>105813427.6</v>
+        <v>73239519.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>95524666.9</t>
+          <t>95851157.0</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>120066640.9</v>
+        <v>115231412.04</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>10288760</t>
+          <t>-22611637</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-1542288.227029385</t>
+          <t>-1782747.750237079</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>1841656.879083008</t>
+          <t>-3105275.127879396</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>49051403.0</t>
+          <t>27736728.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4586,17 +4586,17 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>70.3</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>2025/06/02</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>39.53</t>
+          <t>-4.55</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>97.32</t>
+          <t>99.01</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>47.57</t>
+          <t>47.81</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>8199</t>
+          <t>8341</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>68.6</t>
+          <t>67.9</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>68.6</t>
+          <t>67.9</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>66.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.1</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1542.065</t>
+          <t>735.417</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>67.9</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>41.98</t>
+          <t>10.77</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4848,7 +4848,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>-3.00</t>
+          <t>-5.71</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13.91</t>
+          <t>6.63</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>919</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>49.45</t>
+          <t>14.47</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>76.15</t>
+          <t>49.64</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-5.53</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>5.70</t>
+          <t>5.80</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>70.66</t>
+          <t>69.86000000000001</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>66.3</v>
+        <v>66.23999999999999</v>
       </c>
       <c r="AN11" t="n">
-        <v>66.75</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>63.15</t>
+          <t>63.24</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>125.60</t>
+          <t>50.55</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-82.57</t>
+          <t>-80.05</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>75094211.38675213</t>
+          <t>75125562.09601706</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>106177736.0</t>
+          <t>49051403.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>132561832.2</v>
+        <v>105813427.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>93365555.7</t>
+          <t>95524666.9</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>120263879.18</v>
+        <v>120066640.9</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>39196276</t>
+          <t>10288760</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-2157550.973595275</t>
+          <t>-1542288.227029385</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>6559213.964776337</t>
+          <t>1841656.879083008</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>106177736.0</t>
+          <t>49051403.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5016,17 +5016,17 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>70.3</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>2025/06/02</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>-6.12</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>97.32</t>
+          <t>99.01</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>47.57</t>
+          <t>47.81</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>8199</t>
+          <t>8341</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>67.9</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1168.47</t>
+          <t>1542.065</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>67.9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>53.47</t>
+          <t>41.98</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>-3.00</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10.54</t>
+          <t>13.91</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>919</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>49.45</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>76.15</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>6.43</t>
+          <t>6.58</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>5.70</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>70.66</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>66.23999999999999</v>
+        <v>66.3</v>
       </c>
       <c r="AN12" t="n">
-        <v>66.59999999999999</v>
+        <v>66.75</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>63.02</t>
+          <t>63.15</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>262.06</t>
+          <t>125.60</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-88.05</t>
+          <t>-82.57</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>75094211.38675213</t>
+          <t>75125562.09601706</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>82950382.0</t>
+          <t>106177736.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>132496129.6</v>
+        <v>132561832.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>86336133.4</t>
+          <t>93365555.7</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>120394266.18</v>
+        <v>120263879.18</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>46159996</t>
+          <t>39196276</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-3742417.326026477</t>
+          <t>-2157550.973595275</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>6943645.052739069</t>
+          <t>6559213.964776337</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>82950382.0</t>
+          <t>106177736.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5446,17 +5446,17 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>70.3</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>2025/06/02</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>50.11</t>
+          <t>-3.41</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>97.32</t>
+          <t>99.01</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>47.57</t>
+          <t>47.81</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>8199</t>
+          <t>8341</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>67.9</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5603,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3642.0</t>
+          <t>2707.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>57.2</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-4.40</t>
+          <t>-6.84</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>6.28</t>
+          <t>4.67</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,73 +5744,73 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>3642</t>
+          <t>2707</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>38.46</t>
+          <t>61.54</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>53.85</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>57.92</v>
+        <v>57.97</v>
       </c>
       <c r="AN13" t="n">
-        <v>60.12</v>
+        <v>60.08</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>58.33</t>
+          <t>58.41</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,53 +5820,53 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-112.82</t>
+          <t>-112.64</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>812174.5907142857</t>
+          <t>811351.4336661913</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>210093.0</t>
+          <t>156761.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>194330.8</v>
+        <v>185826.2</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>203269.7</t>
+          <t>199472.7</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>548208.92</v>
+        <v>509521.28</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-8938</t>
+          <t>-13646</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-34352.97788224091</t>
+          <t>-33595.86787440854</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-28498.42446811244</t>
+          <t>-29431.76283133053</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>210093.0</t>
+          <t>156761.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>24.34</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>34092</t>
+          <t>34450</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
+          <t>57.8</t>
+        </is>
+      </c>
+      <c r="CE13" t="inlineStr">
+        <is>
           <t>58.3</t>
         </is>
       </c>
-      <c r="CE13" t="inlineStr">
-        <is>
-          <t>58.7</t>
-        </is>
-      </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>57.2</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>3965.0</t>
+          <t>3642.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-14.74</t>
+          <t>-4.40</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>6.84</t>
+          <t>6.28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,63 +6174,63 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>3642</t>
+          <t>2707</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>61.54</t>
+          <t>38.46</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>49.08</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-3.55</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>57.22000000000001</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>58</v>
+        <v>57.92</v>
       </c>
       <c r="AN14" t="n">
-        <v>60.13</v>
+        <v>60.12</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>58.25</t>
+          <t>58.33</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
@@ -6250,53 +6250,53 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-112.75</t>
+          <t>-112.82</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>812174.5907142857</t>
+          <t>811351.4336661913</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>229092.0</t>
+          <t>210093.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>179557.8</v>
+        <v>194330.8</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>210593.2</t>
+          <t>203269.7</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>551119.74</v>
+        <v>548208.92</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-31035</t>
+          <t>-8938</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-35417.44213935517</t>
+          <t>-34352.97788224091</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-31861.42593251113</t>
+          <t>-28498.42446811244</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>229092.0</t>
+          <t>210093.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>24.34</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>34092</t>
+          <t>34450</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>58.3</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>58.3</t>
+          <t>58.7</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2961.0</t>
+          <t>3965.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,84 +6498,84 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>-0.96</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>-14.74</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2025-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
           <t>-0.52</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>-0.98</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>-11.08</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>2025-10-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>58.1</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>59.6</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>61.5</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>-1.03</t>
-        </is>
-      </c>
       <c r="X15" t="inlineStr">
         <is>
           <t>-4.07</t>
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>6.84</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,73 +6604,73 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>3642</t>
+          <t>2707</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>61.54</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>34.13</t>
+          <t>49.08</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-3.55</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>56.9</t>
+          <t>57.22000000000001</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>58.08</v>
+        <v>58</v>
       </c>
       <c r="AN15" t="n">
-        <v>60.1</v>
+        <v>60.13</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>58.16</t>
+          <t>58.25</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-14.26</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,53 +6680,53 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-112.62</t>
+          <t>-112.75</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>812174.5907142857</t>
+          <t>811351.4336661913</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>171155.0</t>
+          <t>229092.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>188434.4</v>
+        <v>179557.8</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>211905.8</t>
+          <t>210593.2</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>549840.7</v>
+        <v>551119.74</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-23471</t>
+          <t>-31035</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-36063.99054059955</t>
+          <t>-35417.44213935517</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-37563.41281263391</t>
+          <t>-31861.42593251113</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>171155.0</t>
+          <t>229092.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6801,12 +6801,12 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>24.34</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>34092</t>
+          <t>34450</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,12 +6856,12 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>58.3</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
@@ -6871,7 +6871,7 @@
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2826.0</t>
+          <t>2961.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>57.2</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>-11.08</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6948,7 +6948,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,73 +7034,73 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>3642</t>
+          <t>2707</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>35.71</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>22.46</t>
+          <t>34.13</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>57.16</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>58.14</v>
+        <v>58.08</v>
       </c>
       <c r="AN16" t="n">
-        <v>60.07</v>
+        <v>60.1</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>58.08</t>
+          <t>58.16</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-24.14</t>
+          <t>-14.26</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,53 +7110,53 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-112.17</t>
+          <t>-112.62</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>812174.5907142857</t>
+          <t>811351.4336661913</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>162030.0</t>
+          <t>171155.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>209836.2</v>
+        <v>188434.4</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>215755.9</t>
+          <t>211905.8</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>550120.9</v>
+        <v>549840.7</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-5919</t>
+          <t>-23471</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-35791.36830932057</t>
+          <t>-36063.99054059955</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-38160.02218378661</t>
+          <t>-37563.41281263391</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>162030.0</t>
+          <t>171155.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,22 +7221,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>24.34</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>34092</t>
+          <t>34450</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
+          <t>57.7</t>
+        </is>
+      </c>
+      <c r="CE16" t="inlineStr">
+        <is>
+          <t>58.5</t>
+        </is>
+      </c>
+      <c r="CF16" t="inlineStr">
+        <is>
+          <t>57.3</t>
+        </is>
+      </c>
+      <c r="CG16" t="inlineStr">
+        <is>
           <t>57.5</t>
-        </is>
-      </c>
-      <c r="CE16" t="inlineStr">
-        <is>
-          <t>57.8</t>
-        </is>
-      </c>
-      <c r="CF16" t="inlineStr">
-        <is>
-          <t>56.9</t>
-        </is>
-      </c>
-      <c r="CG16" t="inlineStr">
-        <is>
-          <t>57.2</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>3484.0</t>
+          <t>2826.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>56.8</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-15.18</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7378,7 +7378,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,73 +7464,73 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>3642</t>
+          <t>2707</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>35.71</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>10.56</t>
+          <t>22.46</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>57.23999999999999</t>
+          <t>57.16</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>58.29</v>
+        <v>58.14</v>
       </c>
       <c r="AN17" t="n">
-        <v>60.05</v>
+        <v>60.07</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>57.99</t>
+          <t>58.08</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-32.85</t>
+          <t>-24.14</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,53 +7540,53 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-111.43</t>
+          <t>-112.17</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>812174.5907142857</t>
+          <t>811351.4336661913</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>199284.0</t>
+          <t>162030.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>213119.2</v>
+        <v>209836.2</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>251269.4</t>
+          <t>215755.9</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>555483.9399999999</v>
+        <v>550120.9</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-38150</t>
+          <t>-5919</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-35360.70396850856</t>
+          <t>-35791.36830932057</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-36671.78477886959</t>
+          <t>-38160.02218378661</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>199284.0</t>
+          <t>162030.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-3.57</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,22 +7651,22 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>24.34</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>34092</t>
+          <t>34450</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>58.3</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>56.8</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2408.0</t>
+          <t>3484.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-34.72</t>
+          <t>-15.18</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,73 +7894,73 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>3642</t>
+          <t>2707</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>16.11</t>
+          <t>10.56</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-2.71</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>57.36</t>
+          <t>57.23999999999999</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>58.46</v>
+        <v>58.29</v>
       </c>
       <c r="AN18" t="n">
-        <v>60.09</v>
+        <v>60.05</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>57.91</t>
+          <t>57.99</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-36.35</t>
+          <t>-32.85</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,53 +7970,53 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-110.50</t>
+          <t>-111.43</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>812174.5907142857</t>
+          <t>811351.4336661913</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>136228.0</t>
+          <t>199284.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>212208.6</v>
+        <v>213119.2</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>325088.9</t>
+          <t>251269.4</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>556448.64</v>
+        <v>555483.9399999999</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-112880</t>
+          <t>-38150</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-35122.32563935201</t>
+          <t>-35360.70396850856</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-37227.52474402849</t>
+          <t>-36671.78477886959</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>136228.0</t>
+          <t>199284.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>24.34</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>34092</t>
+          <t>34450</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,17 +8146,17 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>58.3</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-4.5</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>4791.0</t>
+          <t>2408.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-31.67</t>
+          <t>-34.72</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8238,7 +8238,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>8.27</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,73 +8324,73 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>3642</t>
+          <t>2707</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>15.46</t>
+          <t>16.11</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-2.71</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>57.62</t>
+          <t>57.36</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>58.66</v>
+        <v>58.46</v>
       </c>
       <c r="AN19" t="n">
-        <v>60.11</v>
+        <v>60.09</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>57.83</t>
+          <t>57.91</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-36.02</t>
+          <t>-36.35</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,53 +8400,53 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-109.54</t>
+          <t>-110.50</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>812174.5907142857</t>
+          <t>811351.4336661913</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>273475.0</t>
+          <t>136228.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>241628.6</v>
+        <v>212208.6</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>353601.2</t>
+          <t>325088.9</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>558552.8199999999</v>
+        <v>556448.64</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-111972</t>
+          <t>-112880</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-34739.56216577447</t>
+          <t>-35122.32563935201</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-29935.8845248259</t>
+          <t>-37227.52474402849</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>273475.0</t>
+          <t>136228.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-3.57</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8521,12 +8521,12 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>24.34</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>34092</t>
+          <t>34450</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>58.7</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>-4.5</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>4747.0</t>
+          <t>4791.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-2.8</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-31.52</t>
+          <t>-31.67</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8668,7 +8668,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>8.19</t>
+          <t>8.27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,73 +8754,73 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>3642</t>
+          <t>2707</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>19.01</t>
+          <t>15.46</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-2.1</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>58.17999999999999</t>
+          <t>57.62</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>58.9</v>
+        <v>58.66</v>
       </c>
       <c r="AN20" t="n">
-        <v>60.16</v>
+        <v>60.11</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>57.77</t>
+          <t>57.83</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-14.48</t>
+          <t>-36.02</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,53 +8830,53 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-108.68</t>
+          <t>-109.54</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>812174.5907142857</t>
+          <t>811351.4336661913</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>278164.0</t>
+          <t>273475.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>235377.2</v>
+        <v>241628.6</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>343709.9</t>
+          <t>353601.2</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>560862.08</v>
+        <v>558552.8199999999</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-108332</t>
+          <t>-111972</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-35612.95810049239</t>
+          <t>-34739.56216577447</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-33155.15262150689</t>
+          <t>-29935.8845248259</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>278164.0</t>
+          <t>273475.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,22 +8941,22 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>24.34</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>34092</t>
+          <t>34450</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>58.7</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>57.9</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3082.0</t>
+          <t>4747.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-33.50</t>
+          <t>-31.52</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9098,7 +9098,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>8.19</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,73 +9184,73 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>3642</t>
+          <t>2707</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>13.04</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>19.01</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-2.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>58.38000000000001</t>
+          <t>58.17999999999999</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>59.01</v>
+        <v>58.9</v>
       </c>
       <c r="AN21" t="n">
-        <v>60.14</v>
+        <v>60.16</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>57.69</t>
+          <t>57.77</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-30.25</t>
+          <t>-14.48</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,53 +9260,53 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-108.37</t>
+          <t>-108.68</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>812174.5907142857</t>
+          <t>811351.4336661913</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>178445.0</t>
+          <t>278164.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>221675.6</v>
+        <v>235377.2</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>333361.3</t>
+          <t>343709.9</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>566147.36</v>
+        <v>560862.08</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-111685</t>
+          <t>-108332</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-36059.8318239443</t>
+          <t>-35612.95810049239</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-37072.38730885455</t>
+          <t>-33155.15262150689</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>178445.0</t>
+          <t>278164.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,12 +9381,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>24.34</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>34092</t>
+          <t>34450</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.9</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3352.0</t>
+          <t>3082.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-15.27</t>
+          <t>-33.50</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9528,7 +9528,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,141 +9614,141 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>3642</t>
+          <t>2707</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>10.64</t>
+          <t>13.04</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
+          <t>58.38000000000001</t>
+        </is>
+      </c>
+      <c r="AM22" t="n">
+        <v>59.01</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>60.14</v>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>57.69</t>
+        </is>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t>-30.25</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>-0.58</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>-0.44</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>5.31</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr">
+        <is>
+          <t>-108.37</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>2025/12/02</t>
+        </is>
+      </c>
+      <c r="AV22" t="inlineStr">
+        <is>
+          <t>811351.4336661913</t>
+        </is>
+      </c>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>178445.0</t>
+        </is>
+      </c>
+      <c r="AX22" t="n">
+        <v>221675.6</v>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>333361.3</t>
+        </is>
+      </c>
+      <c r="AZ22" t="n">
+        <v>566147.36</v>
+      </c>
+      <c r="BA22" t="inlineStr">
+        <is>
+          <t>-111685</t>
+        </is>
+      </c>
+      <c r="BB22" t="inlineStr">
+        <is>
+          <t>-36059.8318239443</t>
+        </is>
+      </c>
+      <c r="BC22" t="inlineStr">
+        <is>
+          <t>-37072.38730885455</t>
+        </is>
+      </c>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>178445.0</t>
+        </is>
+      </c>
+      <c r="BE22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF22" t="inlineStr">
+        <is>
           <t>58.9</t>
         </is>
       </c>
-      <c r="AM22" t="n">
-        <v>59.24</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>60.11</v>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>57.62</t>
-        </is>
-      </c>
-      <c r="AP22" t="inlineStr">
-        <is>
-          <t>-24.96</t>
-        </is>
-      </c>
-      <c r="AQ22" t="inlineStr">
-        <is>
-          <t>-0.51</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>-0.41</t>
-        </is>
-      </c>
-      <c r="AS22" t="inlineStr">
-        <is>
-          <t>5.31</t>
-        </is>
-      </c>
-      <c r="AT22" t="inlineStr">
-        <is>
-          <t>-107.74</t>
-        </is>
-      </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV22" t="inlineStr">
-        <is>
-          <t>812174.5907142857</t>
-        </is>
-      </c>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>194731.0</t>
-        </is>
-      </c>
-      <c r="AX22" t="n">
-        <v>289419.6</v>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>341561.2</t>
-        </is>
-      </c>
-      <c r="AZ22" t="n">
-        <v>568481.84</v>
-      </c>
-      <c r="BA22" t="inlineStr">
-        <is>
-          <t>-52141</t>
-        </is>
-      </c>
-      <c r="BB22" t="inlineStr">
-        <is>
-          <t>-35875.73082668789</t>
-        </is>
-      </c>
-      <c r="BC22" t="inlineStr">
-        <is>
-          <t>-30660.24445832073</t>
-        </is>
-      </c>
-      <c r="BD22" t="inlineStr">
-        <is>
-          <t>194731.0</t>
-        </is>
-      </c>
-      <c r="BE22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF22" t="inlineStr">
-        <is>
-          <t>58.9</t>
-        </is>
-      </c>
       <c r="BG22" t="inlineStr">
         <is>
           <t>2025/08/29</t>
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>24.34</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>34092</t>
+          <t>34450</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>4870.0</t>
+          <t>3352.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,72 +9928,72 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
+          <t>57.4</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>0.69</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>-0.96</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>-15.27</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2025-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
           <t>58.1</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>-1.57</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>-0.98</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>22.85</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>2025-10-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>58.1</t>
-        </is>
-      </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
@@ -10008,12 +10008,12 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>8.40</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,73 +10044,73 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>3642</t>
+          <t>2707</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>40.68</t>
+          <t>10.64</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>55.37</t>
+          <t>35.75</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>59.73999999999999</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>59.51</v>
+        <v>59.24</v>
       </c>
       <c r="AN23" t="n">
-        <v>60.1</v>
+        <v>60.11</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>57.55</t>
+          <t>57.62</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-24.96</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,58 +10120,58 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-107.25</t>
+          <t>-107.74</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>812174.5907142857</t>
+          <t>811351.4336661913</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>283328.0</t>
+          <t>194731.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>437969.2</v>
+        <v>289419.6</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>356514.8</t>
+          <t>341561.2</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>570563.3</v>
+        <v>568481.84</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>81454</t>
+          <t>-52141</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-36824.00107548192</t>
+          <t>-35875.73082668789</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-22149.96022690379</t>
+          <t>-30660.24445832073</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>283328.0</t>
+          <t>194731.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>24.34</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>34092</t>
+          <t>34450</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>57.2</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料).xlsx
+++ b/Result/checksun_type/濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料).xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>919.445</t>
+          <t>693.079</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>70.3</t>
+          <t>69.4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>12.09</t>
+          <t>26.37</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-12-03 00:00:00</t>
+          <t>2025-12-04 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>8.30</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>919</t>
+          <t>693</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>85.71</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>95.24</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>68.30000000000001</t>
+          <t>69.1</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>67.22</v>
+        <v>67.56</v>
       </c>
       <c r="AN2" t="n">
-        <v>67.2</v>
+        <v>67.31</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>64.43</t>
+          <t>64.58</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>95.94</t>
+          <t>82.83</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-89.28</t>
+          <t>-86.48</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,48 +1100,48 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>75125562.09601706</t>
+          <t>75122213.4971591</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>64755840.0</t>
+          <t>48512099.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>45070131.2</v>
+        <v>50745732.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>40209904.5</t>
+          <t>40155974.1</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>101350514.72</v>
+        <v>101578248.06</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>4860226</t>
+          <t>10589758</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-6365070.609214586</t>
+          <t>-6109229.886124369</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-5109771.834456787</t>
+          <t>-4702105.909128174</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>64755840.0</t>
+          <t>48512099.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>99.01</t>
+          <t>97.75</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>47.81</t>
+          <t>47.85</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>8341</t>
+          <t>8234</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>70.6</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>69.1</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>70.3</t>
+          <t>69.4</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1303,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>883.83</t>
+          <t>919.445</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,74 +1328,74 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>70.3</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-1.3</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-1.28</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>12.09</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-12-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>69.1</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>1.71</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>-2.84</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>-14.94</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-12-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-12-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-11-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>69.1</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>69.1</t>
-        </is>
-      </c>
       <c r="T3" t="inlineStr">
         <is>
           <t>70.0</t>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1423,33 +1423,33 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>7.97</t>
+          <t>8.30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>919</t>
+          <t>693</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1459,58 +1459,58 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>87.14</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>4.31</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>67.06</t>
+          <t>68.30000000000001</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>66.84999999999999</v>
+        <v>67.22</v>
       </c>
       <c r="AN3" t="n">
-        <v>67.06999999999999</v>
+        <v>67.2</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>64.27</t>
+          <t>64.43</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>53.39</t>
+          <t>95.94</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-91.85</t>
+          <t>-89.28</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,48 +1530,48 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>75125562.09601706</t>
+          <t>75122213.4971591</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>61639312.0</t>
+          <t>64755840.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>37727299.4</v>
+        <v>45070131.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>44352094.1</t>
+          <t>40209904.5</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>100893408.28</v>
+        <v>101350514.72</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-6624794</t>
+          <t>4860226</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-6593306.750079641</t>
+          <t>-6365070.609214586</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-7250060.697981343</t>
+          <t>-5109771.834456787</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>61639312.0</t>
+          <t>64755840.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>99.01</t>
+          <t>97.75</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>47.81</t>
+          <t>47.85</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>8341</t>
+          <t>8234</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>68.1</t>
+          <t>69.1</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>69.1</t>
+          <t>70.3</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>470.74</t>
+          <t>883.83</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>68.4</t>
+          <t>69.1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,22 +1768,22 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-33.44</t>
+          <t>-14.94</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-12-03 00:00:00</t>
+          <t>2025-12-04 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>69.1</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>7.97</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,12 +1874,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>919</t>
+          <t>693</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1889,58 +1889,58 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>59.72</t>
+          <t>87.14</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>66.04</t>
+          <t>67.06</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>66.58</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="AN4" t="n">
-        <v>66.97</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>64.12</t>
+          <t>64.27</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-13.94</t>
+          <t>53.39</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inl